--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -15,32 +15,65 @@
     <sheet name="Cas 2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_A" localSheetId="0">'Cas 2'!$B$20</definedName>
-    <definedName name="_Av" localSheetId="0">'Cas 2'!$B$21</definedName>
+    <definedName name="_A" localSheetId="0">'Cas 2'!$B$29</definedName>
+    <definedName name="_A0" localSheetId="0">'Cas 2'!$B$72</definedName>
+    <definedName name="_Ace" localSheetId="0">'Cas 2'!$E$4</definedName>
+    <definedName name="_Acr" localSheetId="0">'Cas 2'!$B$68</definedName>
+    <definedName name="_As_inf" localSheetId="0">'Cas 2'!$E$10</definedName>
+    <definedName name="_Av" localSheetId="0">'Cas 2'!$B$30</definedName>
     <definedName name="_b" localSheetId="0">'Cas 2'!$B$4</definedName>
+    <definedName name="_B0" localSheetId="0">'Cas 2'!$B$73</definedName>
+    <definedName name="_bb" localSheetId="0">'Cas 2'!$E$20</definedName>
+    <definedName name="_bc" localSheetId="0">'Cas 2'!$E$3</definedName>
+    <definedName name="_bm" localSheetId="0">'Cas 2'!$E$21</definedName>
+    <definedName name="_bp" localSheetId="0">'Cas 2'!$B$67</definedName>
+    <definedName name="_bt" localSheetId="0">'Cas 2'!$E$19</definedName>
     <definedName name="_cf" localSheetId="0">'Cas 2'!$B$10</definedName>
     <definedName name="_cw" localSheetId="0">'Cas 2'!$B$11</definedName>
+    <definedName name="_d" localSheetId="0">'Cas 2'!$H$12</definedName>
+    <definedName name="_Ecm_dalle" localSheetId="0">'Cas 2'!$H$8</definedName>
+    <definedName name="_ep" localSheetId="0">'Cas 2'!$E$18</definedName>
     <definedName name="_epsilon" localSheetId="0">'Cas 2'!$B$14</definedName>
+    <definedName name="_fck_dalle" localSheetId="0">'Cas 2'!$H$5</definedName>
+    <definedName name="_fck_enrobage" localSheetId="0">'Cas 2'!$E$6</definedName>
+    <definedName name="_fcm_dalle" localSheetId="0">'Cas 2'!$H$6</definedName>
+    <definedName name="_fcm_enrobage" localSheetId="0">'Cas 2'!$E$7</definedName>
+    <definedName name="_fctm_dalle" localSheetId="0">'Cas 2'!$H$7</definedName>
+    <definedName name="_fctm_enrobage" localSheetId="0">'Cas 2'!$E$8</definedName>
+    <definedName name="_fusc" localSheetId="0">'Cas 2'!$H$13</definedName>
     <definedName name="_fy" localSheetId="0">'Cas 2'!$B$13</definedName>
+    <definedName name="_fyp" localSheetId="0">'Cas 2'!$E$23</definedName>
     <definedName name="_h" localSheetId="0">'Cas 2'!$B$3</definedName>
+    <definedName name="_hp" localSheetId="0">'Cas 2'!$E$16</definedName>
+    <definedName name="_hpg" localSheetId="0">'Cas 2'!$E$17</definedName>
+    <definedName name="_hsc" localSheetId="0">'Cas 2'!$H$11</definedName>
     <definedName name="_hw" localSheetId="0">'Cas 2'!$B$8</definedName>
-    <definedName name="_Iy" localSheetId="0">'Cas 2'!$B$22</definedName>
-    <definedName name="_Iz" localSheetId="0">'Cas 2'!$B$23</definedName>
+    <definedName name="_Iy" localSheetId="0">'Cas 2'!$B$31</definedName>
+    <definedName name="_Iz" localSheetId="0">'Cas 2'!$B$32</definedName>
+    <definedName name="_kr">'Cas 2'!$B$69</definedName>
     <definedName name="_L" localSheetId="0">'Cas 2'!$B$2</definedName>
-    <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$41</definedName>
-    <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$42</definedName>
-    <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$43</definedName>
-    <definedName name="_Mpl_z_Rd" localSheetId="0">'Cas 2'!$B$44</definedName>
-    <definedName name="_NtRd" localSheetId="0">'Cas 2'!$B$39</definedName>
+    <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$50</definedName>
+    <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$51</definedName>
+    <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$52</definedName>
+    <definedName name="_Mpl_z_Rd" localSheetId="0">'Cas 2'!$B$53</definedName>
+    <definedName name="_n" localSheetId="0">'Cas 2'!$B$66</definedName>
+    <definedName name="_NtRd" localSheetId="0">'Cas 2'!$B$48</definedName>
     <definedName name="_r" localSheetId="0">'Cas 2'!$B$7</definedName>
     <definedName name="_rho" localSheetId="0">'Cas 2'!$B$16</definedName>
+    <definedName name="_tc" localSheetId="0">'Cas 2'!$H$4</definedName>
+    <definedName name="_td" localSheetId="0">'Cas 2'!$H$3</definedName>
     <definedName name="_tf" localSheetId="0">'Cas 2'!$B$5</definedName>
+    <definedName name="_tp" localSheetId="0">'Cas 2'!$E$22</definedName>
     <definedName name="_tw" localSheetId="0">'Cas 2'!$B$6</definedName>
-    <definedName name="_VplRd" localSheetId="0">'Cas 2'!$B$40</definedName>
-    <definedName name="_Wel_y" localSheetId="0">'Cas 2'!$B$24</definedName>
-    <definedName name="_Wel_z" localSheetId="0">'Cas 2'!$B$25</definedName>
-    <definedName name="_Wpl_y" localSheetId="0">'Cas 2'!$B$26</definedName>
-    <definedName name="_Wpl_z" localSheetId="0">'Cas 2'!$B$27</definedName>
+    <definedName name="_VplRd" localSheetId="0">'Cas 2'!$B$49</definedName>
+    <definedName name="_Wel_y" localSheetId="0">'Cas 2'!$B$33</definedName>
+    <definedName name="_Wel_z" localSheetId="0">'Cas 2'!$B$34</definedName>
+    <definedName name="_Wpl_y" localSheetId="0">'Cas 2'!$B$35</definedName>
+    <definedName name="_Wpl_z" localSheetId="0">'Cas 2'!$B$36</definedName>
+    <definedName name="_za" localSheetId="0">'Cas 2'!$B$71</definedName>
+    <definedName name="_zcr" localSheetId="0">'Cas 2'!$B$70</definedName>
+    <definedName name="_zel" localSheetId="0">'Cas 2'!$B$74</definedName>
+    <definedName name="_zs_inf" localSheetId="0">'Cas 2'!$E$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -52,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="95">
   <si>
     <t>h (mm)</t>
   </si>
@@ -75,9 +108,6 @@
     <t>Av (cm2)</t>
   </si>
   <si>
-    <t>Données</t>
-  </si>
-  <si>
     <t>PropSection</t>
   </si>
   <si>
@@ -214,19 +244,146 @@
   </si>
   <si>
     <t>hw/tw</t>
+  </si>
+  <si>
+    <t>Val ref</t>
+  </si>
+  <si>
+    <t>Ecart (%)</t>
+  </si>
+  <si>
+    <t>Données acier seul</t>
+  </si>
+  <si>
+    <t>Données enrobage</t>
+  </si>
+  <si>
+    <t>bc/bf</t>
+  </si>
+  <si>
+    <t>bc (mm)</t>
+  </si>
+  <si>
+    <t>Ace (cm2)</t>
+  </si>
+  <si>
+    <t>h0 (mm)</t>
+  </si>
+  <si>
+    <t>fcm (MPa)</t>
+  </si>
+  <si>
+    <t>fck (MPa)</t>
+  </si>
+  <si>
+    <t>fctm (MPa)</t>
+  </si>
+  <si>
+    <t>Ecm (MPa)</t>
+  </si>
+  <si>
+    <t>Données dalle</t>
+  </si>
+  <si>
+    <t>Données bac</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Perpendiculaire</t>
+  </si>
+  <si>
+    <t>hp (mm)</t>
+  </si>
+  <si>
+    <t>hpg (mm)</t>
+  </si>
+  <si>
+    <t>ep (mm)</t>
+  </si>
+  <si>
+    <t>bt (mm)</t>
+  </si>
+  <si>
+    <t>bb (mm)</t>
+  </si>
+  <si>
+    <t>tp (mm)</t>
+  </si>
+  <si>
+    <t>fyp (MPa)</t>
+  </si>
+  <si>
+    <t>tc (mm)</t>
+  </si>
+  <si>
+    <t>td (mm)</t>
+  </si>
+  <si>
+    <t>bm (mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propriétés élastiques </t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>As,inf (cm2)</t>
+  </si>
+  <si>
+    <t>zs,inf (mm)</t>
+  </si>
+  <si>
+    <t>Acr (mm2)</t>
+  </si>
+  <si>
+    <t>kr</t>
+  </si>
+  <si>
+    <t>bp (mm)</t>
+  </si>
+  <si>
+    <t>zcr (mm)</t>
+  </si>
+  <si>
+    <t>za (mm)</t>
+  </si>
+  <si>
+    <t>A0 (mm2)</t>
+  </si>
+  <si>
+    <t>B0 (mm3)</t>
+  </si>
+  <si>
+    <t>zel (mm)</t>
+  </si>
+  <si>
+    <t>zel,min (mm)</t>
+  </si>
+  <si>
+    <t>zel,max (mm)</t>
+  </si>
+  <si>
+    <t>Condition respectée ?</t>
+  </si>
+  <si>
+    <t>Ih,y (cm4)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +402,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -369,16 +533,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -393,9 +551,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -403,15 +561,25 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -693,486 +861,1103 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="28"/>
+    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="4"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="12">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1"/>
+      <c r="D1" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="25"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="25"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="10">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C2"/>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="23">
+        <f>2*_tc*(1+_hp*_bm/(_ep*_tc))</f>
+        <v>209.67149758454107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1">
-        <v>500</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="1">
+        <f>E2*_b</f>
+        <v>200</v>
+      </c>
+      <c r="G3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="1">
         <v>200</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C4"/>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4">
+        <f>_b*_h/100-_A-(_b-_bc)*_hw/100</f>
+        <v>892.5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4">
+        <f>_td-_hp</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>14.5</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="23">
+        <f>_Ace*100/_hw</f>
+        <v>190.7051282051282</v>
+      </c>
+      <c r="G5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="1">
-        <v>10.199999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8.4</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="1">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6">
+        <f>_fck_enrobage+8</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="1">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C7"/>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7">
+        <f>_fck_enrobage+8</f>
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="30">
+        <f>0.3*_fck_enrobage^(2/3)</f>
+        <v>2.5649639200150443</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="8">
-        <f>_h-2*_tf-2*_r</f>
+        <v>32</v>
+      </c>
+      <c r="B8" s="6">
+        <f>_h-2*_tf</f>
+        <v>468</v>
+      </c>
+      <c r="C8"/>
+      <c r="D8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="30">
+        <f>0.3*_fck_enrobage^(2/3)</f>
+        <v>2.5649639200150443</v>
+      </c>
+      <c r="G8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="30">
+        <f>22*(_fcm_enrobage/10)^0.3*1000</f>
+        <v>31475.806210019346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="6"/>
+      <c r="C9"/>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="30">
+        <f>22*(_fcm_enrobage/10)^0.3*1000</f>
+        <v>31475.806210019346</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6">
+        <f>(_b-2*_r-_tw)/2</f>
+        <v>74.8</v>
+      </c>
+      <c r="C10"/>
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="31">
+        <f>PI()*(12^2+8^2)/4*2/100</f>
+        <v>3.267256359733385</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6">
+        <f>_hw-2*_r</f>
         <v>426</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="8"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="8">
-        <f>(_b-2*_r-_tw)/2</f>
-        <v>73.900000000000006</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="8">
-        <f>_hw</f>
-        <v>426</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C11"/>
+      <c r="D11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="1">
+        <v>422.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1">
         <v>355</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C13"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="16">
+        <v>33</v>
+      </c>
+      <c r="B14" s="14">
         <f>SQRT(235/_fy)</f>
         <v>0.81361651346682706</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="8"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C14"/>
+      <c r="D14" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="25"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="6"/>
+      <c r="C15"/>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1">
         <v>7850</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+      <c r="C16"/>
+      <c r="D16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="6"/>
+      <c r="C17"/>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="6"/>
+      <c r="C18"/>
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="1">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="6"/>
+      <c r="C19"/>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B20" s="6"/>
+      <c r="C20"/>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="6"/>
+      <c r="C21"/>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21">
+        <f>(E19+E20)/2</f>
+        <v>81.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="6"/>
+      <c r="C22"/>
+      <c r="D22" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="6"/>
+      <c r="C23"/>
+      <c r="D23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="6"/>
+      <c r="C24"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25"/>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C26"/>
+    </row>
+    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="25"/>
+      <c r="C27" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" s="8">
+        <f>(2*(_h-2*_r)+2*_b+2*(_b-2*_r-_tw)+2*PI()*_r)/10</f>
+        <v>174.11468914507714</v>
+      </c>
+      <c r="D28" t="str">
+        <f>IF(C28&lt;&gt;"",(B28/C28-1)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="4">
+        <v>101.5</v>
+      </c>
+      <c r="C29" s="28">
+        <v>101.1</v>
+      </c>
+      <c r="D29" s="30">
+        <f t="shared" ref="D29:D64" si="0">IF(C29&lt;&gt;"",(B29/C29-1)*100,"")</f>
+        <v>0.39564787339267937</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="5">
+        <f>B29-2*_b*_tf/100+2*(_tw+2*_r)*_tf/2/100</f>
+        <v>50.808</v>
+      </c>
+      <c r="C30" s="28">
+        <v>50.4</v>
+      </c>
+      <c r="D30" s="30">
+        <f t="shared" si="0"/>
+        <v>0.80952380952381553</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="4">
+        <v>43014.311000000002</v>
+      </c>
+      <c r="C31" s="28">
+        <v>42933</v>
+      </c>
+      <c r="D31" s="30">
+        <f t="shared" si="0"/>
+        <v>0.18939044557799711</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B32" s="4">
+        <v>1939.511</v>
+      </c>
+      <c r="C32" s="28">
+        <v>1936</v>
+      </c>
+      <c r="D32" s="30">
+        <f t="shared" si="0"/>
+        <v>0.18135330578512576</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="5">
+        <f>B31/(_h/2/10)</f>
+        <v>1730.9581891348089</v>
+      </c>
+      <c r="C33" s="28">
+        <v>1728</v>
+      </c>
+      <c r="D33" s="30">
+        <f t="shared" si="0"/>
+        <v>0.17119150085700419</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="5">
+        <f>B32/(_b/2/10)</f>
+        <v>193.9511</v>
+      </c>
+      <c r="C34" s="28">
+        <v>193.6</v>
+      </c>
+      <c r="D34" s="30">
+        <f t="shared" si="0"/>
+        <v>0.18135330578512576</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="4">
+        <v>1949.546</v>
+      </c>
+      <c r="C35" s="28">
+        <v>1946</v>
+      </c>
+      <c r="D35" s="30">
+        <f t="shared" si="0"/>
+        <v>0.18221993833504868</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="4">
+        <v>301.74400000000003</v>
+      </c>
+      <c r="C36" s="28">
+        <v>298.3</v>
+      </c>
+      <c r="D36" s="30">
+        <f t="shared" si="0"/>
+        <v>1.1545424069728583</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="9"/>
+      <c r="D37" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" s="9">
+        <f>_rho*_A/10000</f>
+        <v>79.677499999999995</v>
+      </c>
+      <c r="C38" s="28">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="D38" s="30">
+        <f t="shared" si="0"/>
+        <v>6.3785046728971784</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B39" s="9">
+        <f>B38*_L</f>
+        <v>995.96874999999989</v>
+      </c>
+      <c r="C39" s="28">
+        <v>992</v>
+      </c>
+      <c r="D39" s="30">
+        <f t="shared" si="0"/>
+        <v>0.40007560483870108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="9"/>
+      <c r="D40" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>30</v>
+      </c>
+      <c r="B41" s="11">
+        <f>B28*_L*100</f>
+        <v>217643.36143134642</v>
+      </c>
+      <c r="C41" s="28">
+        <v>217643</v>
+      </c>
+      <c r="D41" s="30">
+        <f t="shared" si="0"/>
+        <v>1.6606614796632613E-4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" s="11">
+        <f>(B28-_b/10)*_L*100</f>
+        <v>192643.36143134642</v>
+      </c>
+      <c r="C42" s="28">
+        <v>192643</v>
+      </c>
+      <c r="D42" s="30">
+        <f t="shared" si="0"/>
+        <v>1.8761717084370133E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="9"/>
+      <c r="D43" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="10">
-        <f>(2*(_h-2*_r)+2*_b+2*(_b-2*_r-_tw)+2*PI()*_r)/10</f>
-        <v>174.35468914507712</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="6">
-        <v>115.7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="7">
-        <f>B20-2*_b*_tf/100+2*(_tw+2*_r)*_tf/2/100</f>
-        <v>60.052000000000007</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="6">
-        <v>48279.445</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="6">
-        <v>2142.011</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="7">
-        <f>B22/(_h/2/10)</f>
-        <v>1931.1777999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="7">
-        <f>B23/(_b/2/10)</f>
-        <v>214.2011</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="6">
-        <v>2197.652</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B44" s="9">
+        <f>B28/_A*100</f>
+        <v>171.54156566017451</v>
+      </c>
+      <c r="C44" s="28">
+        <v>172.2</v>
+      </c>
+      <c r="D44" s="30">
+        <f t="shared" si="0"/>
+        <v>-0.38236605100201437</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>26</v>
+      </c>
+      <c r="B45" s="9">
+        <f>(B28-_b/10)/_A*100</f>
+        <v>151.83713216263757</v>
+      </c>
+      <c r="C45" s="28">
+        <v>152.4</v>
+      </c>
+      <c r="D45" s="30">
+        <f t="shared" si="0"/>
+        <v>-0.36933585128768875</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D46" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="6">
-        <v>335.89800000000002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B28" s="11"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="11">
-        <f>_rho*_A/10000</f>
-        <v>90.8245</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="11">
-        <f>B29*_L</f>
-        <v>1135.3062500000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="11"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="13">
-        <f>B19*_L*100</f>
-        <v>217943.36143134636</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="13">
-        <f>(B19-_b/10)*_L*100</f>
-        <v>192943.36143134639</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B34" s="11"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="11">
-        <f>B19/_A*100</f>
-        <v>150.69549623602171</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36" s="11">
-        <f>(B19-_b/10)/_A*100</f>
-        <v>133.40941153420667</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="3" t="s">
+      <c r="B47" s="25"/>
+      <c r="D47" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>17</v>
       </c>
-      <c r="B38" s="4"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B48" s="13">
+        <f>_A*100*_fy/1000</f>
+        <v>3603.25</v>
+      </c>
+      <c r="C48" s="28">
+        <v>3589</v>
+      </c>
+      <c r="D48" s="30">
+        <f t="shared" si="0"/>
+        <v>0.39704653106715782</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="13">
+        <f>_Av*100*_fy/(1000*SQRT(3))</f>
+        <v>1041.357442933021</v>
+      </c>
+      <c r="C49" s="28">
+        <v>1033</v>
+      </c>
+      <c r="D49" s="30">
+        <f t="shared" si="0"/>
+        <v>0.8090457824802666</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="F49" s="27"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="15">
-        <f>_A*100*_fy/1000</f>
-        <v>4107.3500000000004</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" s="15">
-        <f>_Av*100*_fy/(1000*SQRT(3))</f>
-        <v>1230.8218619708273</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>19</v>
-      </c>
-      <c r="B41" s="15">
+      <c r="B50" s="13">
         <f>_Wel_y*1000*_fy*10^(-6)</f>
-        <v>685.56811900000002</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>20</v>
-      </c>
-      <c r="B42" s="15">
-        <f>_Wel_z*1000*_fy*10^(-6)</f>
-        <v>76.041390499999991</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" s="15">
-        <f>_Wpl_y*1000*_fy*10^(-6)</f>
-        <v>780.16645999999992</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" s="15">
-        <f>_Wpl_z*1000*_fy*10^(-6)</f>
-        <v>119.24378999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B45" s="15"/>
-      <c r="D45" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="24"/>
-      <c r="G45" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="H45" s="26"/>
-      <c r="J45" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="K45" s="26"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="14">
-        <f>_cf/_tf</f>
-        <v>4.6187500000000004</v>
-      </c>
-      <c r="D46" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="E46" s="19">
+        <v>614.49015714285713</v>
+      </c>
+      <c r="C50" s="28">
+        <v>613</v>
+      </c>
+      <c r="D50" s="30">
+        <f t="shared" si="0"/>
+        <v>0.2430925192262956</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F50" s="17">
         <f>9*_epsilon</f>
         <v>7.3225486212014435</v>
       </c>
-      <c r="G46" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="H46" s="21">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B51" s="13">
+        <f>_Wel_z*1000*_fy*10^(-6)</f>
+        <v>68.852640499999993</v>
+      </c>
+      <c r="D51" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="17">
+        <f>10*_epsilon</f>
+        <v>8.1361651346682713</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" s="13">
+        <f>_Wpl_y*1000*_fy*10^(-6)</f>
+        <v>692.08882999999992</v>
+      </c>
+      <c r="C52" s="28">
+        <v>691</v>
+      </c>
+      <c r="D52" s="30">
+        <f t="shared" si="0"/>
+        <v>0.15757308248913748</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F52" s="18">
+        <f>14*_epsilon</f>
+        <v>11.390631188535579</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="13">
+        <f>_Wpl_z*1000*_fy*10^(-6)</f>
+        <v>107.11912</v>
+      </c>
+      <c r="D53" s="30" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B54" s="13"/>
+      <c r="D54" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F54" s="22"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="12">
+        <f>_cf/_tf</f>
+        <v>5.1586206896551721</v>
+      </c>
+      <c r="D55" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F55" s="19">
         <f>33*_epsilon</f>
         <v>26.849344944405292</v>
       </c>
-      <c r="J46" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="K46" s="21">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="12">
+        <f>_cw/_tw</f>
+        <v>50.714285714285715</v>
+      </c>
+      <c r="D56" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F56" s="19">
+        <f>38*_epsilon</f>
+        <v>30.917427511739429</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D57" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F57" s="20">
+        <f>42*_epsilon</f>
+        <v>34.171893565606737</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>34</v>
+      </c>
+      <c r="B58">
+        <f>IF(B55&lt;=F50,1,IF(B55&lt;=F51,2,IF(B55&lt;=F52,3,4)))</f>
+        <v>1</v>
+      </c>
+      <c r="D58" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59">
+        <f>IF(B56&lt;=F55,1,IF(B56&lt;=F56,2,IF(B56&lt;=F57,3,4)))</f>
+        <v>4</v>
+      </c>
+      <c r="D59" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F59" s="22"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60">
+        <f>IF(B56&lt;=F60,1,IF(B56&lt;=F61,2,IF(B56&lt;=F62,3,4)))</f>
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F60" s="19">
         <f>72*_epsilon</f>
         <v>58.580388969611548</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="14">
-        <f>_cw/_tw</f>
-        <v>41.764705882352942</v>
-      </c>
-      <c r="D47" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="E47" s="19">
-        <f>10*_epsilon</f>
-        <v>8.1361651346682713</v>
-      </c>
-      <c r="G47" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="H47" s="21">
-        <f>38*_epsilon</f>
-        <v>30.917427511739429</v>
-      </c>
-      <c r="J47" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="K47" s="21">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D61" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F61" s="19">
         <f>83*_epsilon</f>
         <v>67.530170617746649</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D48" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="E48" s="20">
-        <f>14*_epsilon</f>
-        <v>11.390631188535579</v>
-      </c>
-      <c r="G48" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="H48" s="22">
-        <f>42*_epsilon</f>
-        <v>34.171893565606737</v>
-      </c>
-      <c r="J48" s="18" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>52</v>
       </c>
-      <c r="K48" s="22">
+      <c r="B62" s="3">
+        <f>_hw/_tw</f>
+        <v>55.714285714285715</v>
+      </c>
+      <c r="D62" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F62" s="20">
         <f>124*_epsilon</f>
         <v>100.88844766988656</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49">
-        <f>IF(B46&lt;=E46,1,IF(B46&lt;=E47,2,IF(B46&lt;=E48,3,4)))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50">
-        <f>IF(B47&lt;=H46,1,IF(B47&lt;=H47,2,IF(B47&lt;=H48,3,4)))</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51">
-        <f>IF(B47&lt;=K46,1,IF(B47&lt;=K47,2,IF(B47&lt;=K48,3,4)))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53" s="5">
-        <f>_hw/_tw</f>
-        <v>41.764705882352942</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>52</v>
-      </c>
-      <c r="B54" s="27">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>51</v>
+      </c>
+      <c r="B63" s="23">
         <f>124*_epsilon</f>
         <v>100.88844766988656</v>
       </c>
+      <c r="D63" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D64" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B65" s="25"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66">
+        <v>6.67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>85</v>
+      </c>
+      <c r="B67">
+        <f>_bc-_tw</f>
+        <v>191.6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>83</v>
+      </c>
+      <c r="B68" s="30">
+        <f>(4-PI())*_r^2/(2*_n)</f>
+        <v>28.377634165434873</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" s="29">
+        <f>(10-3*PI())/(12-3*PI())</f>
+        <v>0.22336793894575216</v>
+      </c>
+      <c r="E69">
+        <f>(53002/52921-1)*100</f>
+        <v>0.15305833223107079</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>86</v>
+      </c>
+      <c r="B70">
+        <f>_tf+_kr*_r</f>
+        <v>19.190726717860795</v>
+      </c>
+      <c r="E70">
+        <f>(47200/47128-1)*100</f>
+        <v>0.15277542013241163</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>87</v>
+      </c>
+      <c r="B71">
+        <f>_h/2</f>
+        <v>248.5</v>
+      </c>
+      <c r="E71">
+        <f>(47083/47005-1)*100</f>
+        <v>0.16593979363896949</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>88</v>
+      </c>
+      <c r="B72" s="23">
+        <f>_A*100+_As_inf*100-_Acr-_bp*_tf/_n</f>
+        <v>10031.826262677469</v>
+      </c>
+      <c r="C72" s="28">
+        <v>9998</v>
+      </c>
+      <c r="D72">
+        <f>(B72/C72-1)*100</f>
+        <v>0.33833029283325544</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>89</v>
+      </c>
+      <c r="B73" s="23">
+        <f>_A*100*_za+_As_inf*100*_zs_inf-_Acr*_zcr-_bp*_tf^2/(2*_n)</f>
+        <v>2656752.2111678715</v>
+      </c>
+      <c r="C73" s="28">
+        <v>2646805</v>
+      </c>
+      <c r="D73">
+        <f>(B73/C73-1)*100</f>
+        <v>0.37581956992946974</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>90</v>
+      </c>
+      <c r="B74" s="3">
+        <f>_n*_A0/_bp*(-1+SQRT(1+2*_bp*_B0/(_n*_A0^2)))</f>
+        <v>204.78830751093571</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>91</v>
+      </c>
+      <c r="B75">
+        <f>_tf+_r</f>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>92</v>
+      </c>
+      <c r="B76">
+        <f>_zs_inf</f>
+        <v>422.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>93</v>
+      </c>
+      <c r="B77" t="b">
+        <f>IF(B75&lt;=_zel,IF(_zel&lt;=B76,TRUE,FALSE),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>94</v>
+      </c>
+      <c r="B78">
+        <f>(_Iy*10^4+_A*100*(_za-_zel)^2+_As_inf*100*(_zs_inf-_zel)^2+_bp*(_zel-_tf)^3/(3*_n)-_Acr*(_zcr-_zel)^2)*10^(-4)</f>
+        <v>53002.140380188146</v>
+      </c>
+      <c r="C78" s="28">
+        <f>52814</f>
+        <v>52814</v>
+      </c>
+      <c r="D78">
+        <f>(B78/C78-1)*100</f>
+        <v>0.35623202216863437</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="A65:B65"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="D1:E1"/>
   </mergeCells>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E15">
+      <formula1>"Aucun,Perpendiculaire,Longitudinal"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -15,64 +15,71 @@
     <sheet name="Cas 2" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_A" localSheetId="0">'Cas 2'!$B$29</definedName>
-    <definedName name="_A0" localSheetId="0">'Cas 2'!$B$72</definedName>
+    <definedName name="_A" localSheetId="0">'Cas 2'!$B$32</definedName>
+    <definedName name="_A0" localSheetId="0">'Cas 2'!$B$75</definedName>
     <definedName name="_Ace" localSheetId="0">'Cas 2'!$E$4</definedName>
-    <definedName name="_Acr" localSheetId="0">'Cas 2'!$B$68</definedName>
+    <definedName name="_Acr" localSheetId="0">'Cas 2'!$B$71</definedName>
     <definedName name="_As_inf" localSheetId="0">'Cas 2'!$E$10</definedName>
-    <definedName name="_Av" localSheetId="0">'Cas 2'!$B$30</definedName>
+    <definedName name="_Av" localSheetId="0">'Cas 2'!$B$33</definedName>
     <definedName name="_b" localSheetId="0">'Cas 2'!$B$4</definedName>
-    <definedName name="_B0" localSheetId="0">'Cas 2'!$B$73</definedName>
-    <definedName name="_bb" localSheetId="0">'Cas 2'!$E$20</definedName>
+    <definedName name="_B0" localSheetId="0">'Cas 2'!$B$76</definedName>
+    <definedName name="_bb" localSheetId="0">'Cas 2'!$E$21</definedName>
     <definedName name="_bc" localSheetId="0">'Cas 2'!$E$3</definedName>
-    <definedName name="_bm" localSheetId="0">'Cas 2'!$E$21</definedName>
-    <definedName name="_bp" localSheetId="0">'Cas 2'!$B$67</definedName>
-    <definedName name="_bt" localSheetId="0">'Cas 2'!$E$19</definedName>
-    <definedName name="_cf" localSheetId="0">'Cas 2'!$B$10</definedName>
-    <definedName name="_cw" localSheetId="0">'Cas 2'!$B$11</definedName>
-    <definedName name="_d" localSheetId="0">'Cas 2'!$H$12</definedName>
+    <definedName name="_bm" localSheetId="0">'Cas 2'!$E$22</definedName>
+    <definedName name="_bp" localSheetId="0">'Cas 2'!$B$70</definedName>
+    <definedName name="_bt" localSheetId="0">'Cas 2'!$E$20</definedName>
+    <definedName name="_cf" localSheetId="0">'Cas 2'!$B$11</definedName>
+    <definedName name="_cw" localSheetId="0">'Cas 2'!$B$12</definedName>
+    <definedName name="_d" localSheetId="0">'Cas 2'!$H$13</definedName>
+    <definedName name="_dw" localSheetId="0">'Cas 2'!$B$9</definedName>
     <definedName name="_Ecm_dalle" localSheetId="0">'Cas 2'!$H$8</definedName>
-    <definedName name="_ep" localSheetId="0">'Cas 2'!$E$18</definedName>
-    <definedName name="_epsilon" localSheetId="0">'Cas 2'!$B$14</definedName>
+    <definedName name="_ep" localSheetId="0">'Cas 2'!$E$19</definedName>
+    <definedName name="_epsilon" localSheetId="0">'Cas 2'!$B$15</definedName>
     <definedName name="_fck_dalle" localSheetId="0">'Cas 2'!$H$5</definedName>
     <definedName name="_fck_enrobage" localSheetId="0">'Cas 2'!$E$6</definedName>
     <definedName name="_fcm_dalle" localSheetId="0">'Cas 2'!$H$6</definedName>
     <definedName name="_fcm_enrobage" localSheetId="0">'Cas 2'!$E$7</definedName>
     <definedName name="_fctm_dalle" localSheetId="0">'Cas 2'!$H$7</definedName>
     <definedName name="_fctm_enrobage" localSheetId="0">'Cas 2'!$E$8</definedName>
-    <definedName name="_fusc" localSheetId="0">'Cas 2'!$H$13</definedName>
-    <definedName name="_fy" localSheetId="0">'Cas 2'!$B$13</definedName>
-    <definedName name="_fyp" localSheetId="0">'Cas 2'!$E$23</definedName>
+    <definedName name="_fusc" localSheetId="0">'Cas 2'!$H$14</definedName>
+    <definedName name="_fy" localSheetId="0">'Cas 2'!$B$14</definedName>
+    <definedName name="_fyd">'Cas 2'!$E$12</definedName>
+    <definedName name="_fyp" localSheetId="0">'Cas 2'!$E$24</definedName>
     <definedName name="_h" localSheetId="0">'Cas 2'!$B$3</definedName>
-    <definedName name="_hp" localSheetId="0">'Cas 2'!$E$16</definedName>
-    <definedName name="_hpg" localSheetId="0">'Cas 2'!$E$17</definedName>
-    <definedName name="_hsc" localSheetId="0">'Cas 2'!$H$11</definedName>
+    <definedName name="_hp" localSheetId="0">'Cas 2'!$E$17</definedName>
+    <definedName name="_hpg" localSheetId="0">'Cas 2'!$E$18</definedName>
+    <definedName name="_hsc" localSheetId="0">'Cas 2'!$H$12</definedName>
     <definedName name="_hw" localSheetId="0">'Cas 2'!$B$8</definedName>
-    <definedName name="_Iy" localSheetId="0">'Cas 2'!$B$31</definedName>
-    <definedName name="_Iz" localSheetId="0">'Cas 2'!$B$32</definedName>
-    <definedName name="_kr">'Cas 2'!$B$69</definedName>
+    <definedName name="_Iy" localSheetId="0">'Cas 2'!$B$34</definedName>
+    <definedName name="_Iz" localSheetId="0">'Cas 2'!$B$35</definedName>
+    <definedName name="_kr">'Cas 2'!$B$72</definedName>
     <definedName name="_L" localSheetId="0">'Cas 2'!$B$2</definedName>
-    <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$50</definedName>
-    <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$51</definedName>
-    <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$52</definedName>
-    <definedName name="_Mpl_z_Rd" localSheetId="0">'Cas 2'!$B$53</definedName>
-    <definedName name="_n" localSheetId="0">'Cas 2'!$B$66</definedName>
-    <definedName name="_NtRd" localSheetId="0">'Cas 2'!$B$48</definedName>
+    <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$53</definedName>
+    <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$54</definedName>
+    <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$55</definedName>
+    <definedName name="_Mpl_z_Rd" localSheetId="0">'Cas 2'!$B$56</definedName>
+    <definedName name="_n" localSheetId="0">'Cas 2'!$B$69</definedName>
+    <definedName name="_NtRd" localSheetId="0">'Cas 2'!$B$51</definedName>
+    <definedName name="_qBac" localSheetId="0">'Cas 2'!$E$26</definedName>
+    <definedName name="_qDalle" localSheetId="0">'Cas 2'!$H$10</definedName>
+    <definedName name="_qEnrobage" localSheetId="0">'Cas 2'!$E$13</definedName>
+    <definedName name="_qProfile" localSheetId="0">'Cas 2'!$B$18</definedName>
     <definedName name="_r" localSheetId="0">'Cas 2'!$B$7</definedName>
-    <definedName name="_rho" localSheetId="0">'Cas 2'!$B$16</definedName>
+    <definedName name="_rho" localSheetId="0">'Cas 2'!$B$17</definedName>
     <definedName name="_tc" localSheetId="0">'Cas 2'!$H$4</definedName>
     <definedName name="_td" localSheetId="0">'Cas 2'!$H$3</definedName>
     <definedName name="_tf" localSheetId="0">'Cas 2'!$B$5</definedName>
-    <definedName name="_tp" localSheetId="0">'Cas 2'!$E$22</definedName>
+    <definedName name="_tp" localSheetId="0">'Cas 2'!$E$23</definedName>
     <definedName name="_tw" localSheetId="0">'Cas 2'!$B$6</definedName>
-    <definedName name="_VplRd" localSheetId="0">'Cas 2'!$B$49</definedName>
-    <definedName name="_Wel_y" localSheetId="0">'Cas 2'!$B$33</definedName>
-    <definedName name="_Wel_z" localSheetId="0">'Cas 2'!$B$34</definedName>
-    <definedName name="_Wpl_y" localSheetId="0">'Cas 2'!$B$35</definedName>
-    <definedName name="_Wpl_z" localSheetId="0">'Cas 2'!$B$36</definedName>
-    <definedName name="_za" localSheetId="0">'Cas 2'!$B$71</definedName>
-    <definedName name="_zcr" localSheetId="0">'Cas 2'!$B$70</definedName>
-    <definedName name="_zel" localSheetId="0">'Cas 2'!$B$74</definedName>
+    <definedName name="_VplRd" localSheetId="0">'Cas 2'!$B$52</definedName>
+    <definedName name="_Wel_y" localSheetId="0">'Cas 2'!$B$36</definedName>
+    <definedName name="_Wel_z" localSheetId="0">'Cas 2'!$B$37</definedName>
+    <definedName name="_Wpl_y" localSheetId="0">'Cas 2'!$B$38</definedName>
+    <definedName name="_Wpl_z" localSheetId="0">'Cas 2'!$B$39</definedName>
+    <definedName name="_za" localSheetId="0">'Cas 2'!$B$74</definedName>
+    <definedName name="_zcr" localSheetId="0">'Cas 2'!$B$73</definedName>
+    <definedName name="_zel" localSheetId="0">'Cas 2'!$B$77</definedName>
+    <definedName name="_zpl" localSheetId="0">'Cas 2'!$B$102</definedName>
     <definedName name="_zs_inf" localSheetId="0">'Cas 2'!$E$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -85,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="152">
   <si>
     <t>h (mm)</t>
   </si>
@@ -370,6 +377,177 @@
   </si>
   <si>
     <t>Ih,y (cm4)</t>
+  </si>
+  <si>
+    <t>n0</t>
+  </si>
+  <si>
+    <t>psiL</t>
+  </si>
+  <si>
+    <t>Multiplicateur de fluage</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>Retrait</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>phi RH</t>
+  </si>
+  <si>
+    <t>beta(fcm)</t>
+  </si>
+  <si>
+    <t>t0 (j)</t>
+  </si>
+  <si>
+    <t>t (j)</t>
+  </si>
+  <si>
+    <t>beta (t0)</t>
+  </si>
+  <si>
+    <t>phi0</t>
+  </si>
+  <si>
+    <t>beta H</t>
+  </si>
+  <si>
+    <t>beta c(t,t0)</t>
+  </si>
+  <si>
+    <t>phi(t,t0)</t>
+  </si>
+  <si>
+    <t>nL</t>
+  </si>
+  <si>
+    <t>Propriétés plastiques</t>
+  </si>
+  <si>
+    <t>Nw (kN)</t>
+  </si>
+  <si>
+    <t>dw (mm)</t>
+  </si>
+  <si>
+    <t>Ns (kN)</t>
+  </si>
+  <si>
+    <t>fyd (MPa)</t>
+  </si>
+  <si>
+    <t>Ncw (kN)</t>
+  </si>
+  <si>
+    <t>Ncr (kN)</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>zpl (mm)</t>
+  </si>
+  <si>
+    <t>zpl,min (mm)</t>
+  </si>
+  <si>
+    <t>zpl,max (mm)</t>
+  </si>
+  <si>
+    <t>hc (mm)</t>
+  </si>
+  <si>
+    <t>Mpl,Rd (kN.m)</t>
+  </si>
+  <si>
+    <t>qProfilé (kN/ml)</t>
+  </si>
+  <si>
+    <t>qEnrobage</t>
+  </si>
+  <si>
+    <t>b (m)</t>
+  </si>
+  <si>
+    <t>mu (kg/m2)</t>
+  </si>
+  <si>
+    <t>qBac (kN/ml)</t>
+  </si>
+  <si>
+    <t>qDalle (kN/m)</t>
+  </si>
+  <si>
+    <t>qPP (kN/ml)</t>
+  </si>
+  <si>
+    <t>M(G1) (kN.m)</t>
+  </si>
+  <si>
+    <t>V(G1) (kN)</t>
+  </si>
+  <si>
+    <t>Analyse</t>
+  </si>
+  <si>
+    <t>Vérification</t>
+  </si>
+  <si>
+    <t>V(Qc) (kN)</t>
+  </si>
+  <si>
+    <t>M (Qc) (kN.m)</t>
+  </si>
+  <si>
+    <t>V(ELS) (kN)</t>
+  </si>
+  <si>
+    <t>M(ELS) (kN.m)</t>
+  </si>
+  <si>
+    <t>V(ELU) (kN)</t>
+  </si>
+  <si>
+    <t>M (ELU) (kN.m)</t>
+  </si>
+  <si>
+    <t>Critere M</t>
+  </si>
+  <si>
+    <t>Critere V</t>
+  </si>
+  <si>
+    <t>f(G1) (mm)</t>
+  </si>
+  <si>
+    <t>f (Qc)</t>
+  </si>
+  <si>
+    <t>Calcul sur RDM7</t>
+  </si>
+  <si>
+    <t>f (ELS) (mm)</t>
+  </si>
+  <si>
+    <t>f (G+0,2Q) (mm)</t>
+  </si>
+  <si>
+    <t>f (Hz)</t>
+  </si>
+  <si>
+    <t>MbRd (kN.m)</t>
+  </si>
+  <si>
+    <t>Critere LT</t>
+  </si>
+  <si>
+    <t>Valeur issue de l'article RCM 2023 n°3</t>
   </si>
 </sst>
 </file>
@@ -381,7 +559,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -428,7 +606,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -528,12 +706,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -564,6 +764,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -576,10 +780,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -861,30 +1067,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="28"/>
+    <col min="3" max="3" width="11.42578125" style="24"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="25"/>
+      <c r="B1" s="29"/>
       <c r="C1"/>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="25"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="24" t="s">
+      <c r="E1" s="29"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="25"/>
+      <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -943,7 +1151,7 @@
       </c>
       <c r="E4">
         <f>_b*_h/100-_A-(_b-_bc)*_hw/100</f>
-        <v>892.5</v>
+        <v>892.7</v>
       </c>
       <c r="G4" t="s">
         <v>76</v>
@@ -966,7 +1174,7 @@
       </c>
       <c r="E5" s="23">
         <f>_Ace*100/_hw</f>
-        <v>190.7051282051282</v>
+        <v>190.74786324786325</v>
       </c>
       <c r="G5" t="s">
         <v>62</v>
@@ -1015,7 +1223,7 @@
       <c r="G7" t="s">
         <v>63</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="26">
         <f>0.3*_fck_enrobage^(2/3)</f>
         <v>2.5649639200150443</v>
       </c>
@@ -1032,53 +1240,66 @@
       <c r="D8" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="26">
         <f>0.3*_fck_enrobage^(2/3)</f>
         <v>2.5649639200150443</v>
       </c>
       <c r="G8" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="26">
         <f>22*(_fcm_enrobage/10)^0.3*1000</f>
         <v>31475.806210019346</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="6"/>
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="6">
+        <f>_hw-2*_r</f>
+        <v>426</v>
+      </c>
       <c r="C9"/>
       <c r="D9" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="26">
         <f>22*(_fcm_enrobage/10)^0.3*1000</f>
         <v>31475.806210019346</v>
       </c>
+      <c r="G9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="6">
-        <f>(_b-2*_r-_tw)/2</f>
-        <v>74.8</v>
-      </c>
+      <c r="B10" s="6"/>
       <c r="C10"/>
       <c r="D10" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="27">
         <f>PI()*(12^2+8^2)/4*2/100</f>
         <v>3.267256359733385</v>
       </c>
+      <c r="G10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H10" s="26">
+        <f>(_tc+_hp*_bm/_ep)/1000*H9*2500*9.81/1000</f>
+        <v>6.4277418478260868</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="6">
-        <f>_hw-2*_r</f>
-        <v>426</v>
+        <f>(_b-2*_r-_tw)/2</f>
+        <v>74.8</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
@@ -1089,871 +1310,1340 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="6">
+        <f>_hw-2*_r</f>
+        <v>426</v>
+      </c>
       <c r="C12"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1">
-        <v>355</v>
-      </c>
+      <c r="D12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="23">
+        <f>500/1.15</f>
+        <v>434.78260869565219</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C13"/>
+      <c r="D13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="26">
+        <f>_Ace*10^(-4)*2500*9.81/1000</f>
+        <v>2.1893467500000003</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1">
+        <v>355</v>
+      </c>
+      <c r="C14"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B15" s="14">
         <f>SQRT(235/_fy)</f>
         <v>0.81361651346682706</v>
       </c>
-      <c r="C14"/>
-      <c r="D14" s="24" t="s">
+      <c r="C15"/>
+      <c r="D15" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="E14" s="25"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
-      <c r="C15"/>
-      <c r="D15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="E15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1">
-        <v>7850</v>
-      </c>
+      <c r="B16" s="6"/>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="1">
-        <v>58</v>
+        <v>67</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="6"/>
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1">
+        <v>7850</v>
+      </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" s="1">
         <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
+      <c r="A18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="35">
+        <f>_rho*_A*10^(-4)*9.81/1000</f>
+        <v>0.78009610500000004</v>
+      </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E18" s="1">
-        <v>207</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B19" s="6"/>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E19" s="1">
-        <v>101</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B20" s="6"/>
       <c r="C20"/>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E20" s="1">
-        <v>62</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B21" s="6"/>
       <c r="C21"/>
       <c r="D21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21">
-        <f>(E19+E20)/2</f>
-        <v>81.5</v>
+        <v>73</v>
+      </c>
+      <c r="E21" s="1">
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B22" s="6"/>
       <c r="C22"/>
       <c r="D22" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1</v>
+        <v>78</v>
+      </c>
+      <c r="E22">
+        <f>(E20+E21)/2</f>
+        <v>81.5</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B23" s="6"/>
       <c r="C23"/>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" s="1">
-        <v>350</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B24" s="6"/>
       <c r="C24"/>
+      <c r="D24" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="1">
+        <v>350</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="6"/>
+      <c r="C25"/>
+      <c r="D25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="1">
+        <v>11.37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="6"/>
+      <c r="C26"/>
+      <c r="D26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="25">
+        <f>E25*H9*9.81/1000</f>
+        <v>0.27884924999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="6"/>
+      <c r="C27"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C25"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
+      <c r="C28"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C29"/>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="25"/>
-      <c r="C27" s="28" t="s">
+      <c r="B30" s="29"/>
+      <c r="C30" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D30" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B31" s="8">
         <f>(2*(_h-2*_r)+2*_b+2*(_b-2*_r-_tw)+2*PI()*_r)/10</f>
         <v>174.11468914507714</v>
       </c>
-      <c r="D28" t="str">
-        <f>IF(C28&lt;&gt;"",(B28/C28-1)*100,"")</f>
+      <c r="D31" t="str">
+        <f>IF(C31&lt;&gt;"",(B31/C31-1)*100,"")</f>
         <v/>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="4">
-        <v>101.5</v>
-      </c>
-      <c r="C29" s="28">
-        <v>101.1</v>
-      </c>
-      <c r="D29" s="30">
-        <f t="shared" ref="D29:D64" si="0">IF(C29&lt;&gt;"",(B29/C29-1)*100,"")</f>
-        <v>0.39564787339267937</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="5">
-        <f>B29-2*_b*_tf/100+2*(_tw+2*_r)*_tf/2/100</f>
-        <v>50.808</v>
-      </c>
-      <c r="C30" s="28">
-        <v>50.4</v>
-      </c>
-      <c r="D30" s="30">
-        <f t="shared" si="0"/>
-        <v>0.80952380952381553</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="4">
-        <v>43014.311000000002</v>
-      </c>
-      <c r="C31" s="28">
-        <v>42933</v>
-      </c>
-      <c r="D31" s="30">
-        <f t="shared" si="0"/>
-        <v>0.18939044557799711</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B32" s="4">
-        <v>1939.511</v>
-      </c>
-      <c r="C32" s="28">
-        <v>1936</v>
-      </c>
-      <c r="D32" s="30">
-        <f t="shared" si="0"/>
-        <v>0.18135330578512576</v>
+        <v>101.3</v>
+      </c>
+      <c r="C32" s="24">
+        <v>101.1</v>
+      </c>
+      <c r="D32" s="26">
+        <f t="shared" ref="D32:D67" si="0">IF(C32&lt;&gt;"",(B32/C32-1)*100,"")</f>
+        <v>0.19782393669633969</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B33" s="5">
-        <f>B31/(_h/2/10)</f>
-        <v>1730.9581891348089</v>
-      </c>
-      <c r="C33" s="28">
-        <v>1728</v>
-      </c>
-      <c r="D33" s="30">
-        <f t="shared" si="0"/>
-        <v>0.17119150085700419</v>
+        <f>B32-2*_b*_tf/100+2*(_tw+2*_r)*_tf/2/100</f>
+        <v>50.607999999999997</v>
+      </c>
+      <c r="C33" s="24">
+        <v>50.4</v>
+      </c>
+      <c r="D33" s="26">
+        <f t="shared" si="0"/>
+        <v>0.41269841269842011</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="5">
-        <f>B32/(_b/2/10)</f>
-        <v>193.9511</v>
-      </c>
-      <c r="C34" s="28">
-        <v>193.6</v>
-      </c>
-      <c r="D34" s="30">
-        <f t="shared" si="0"/>
-        <v>0.18135330578512576</v>
+        <v>9</v>
+      </c>
+      <c r="B34" s="4">
+        <v>43014.311000000002</v>
+      </c>
+      <c r="C34" s="24">
+        <v>42933</v>
+      </c>
+      <c r="D34" s="26">
+        <f t="shared" si="0"/>
+        <v>0.18939044557799711</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B35" s="4">
-        <v>1949.546</v>
-      </c>
-      <c r="C35" s="28">
-        <v>1946</v>
-      </c>
-      <c r="D35" s="30">
-        <f t="shared" si="0"/>
-        <v>0.18221993833504868</v>
+        <v>1939.511</v>
+      </c>
+      <c r="C35" s="24">
+        <v>1936</v>
+      </c>
+      <c r="D35" s="26">
+        <f t="shared" si="0"/>
+        <v>0.18135330578512576</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" s="4">
-        <v>301.74400000000003</v>
-      </c>
-      <c r="C36" s="28">
-        <v>298.3</v>
-      </c>
-      <c r="D36" s="30">
-        <f t="shared" si="0"/>
-        <v>1.1545424069728583</v>
+        <v>12</v>
+      </c>
+      <c r="B36" s="5">
+        <f>B34/(_h/2/10)</f>
+        <v>1730.9581891348089</v>
+      </c>
+      <c r="C36" s="24">
+        <v>1728</v>
+      </c>
+      <c r="D36" s="26">
+        <f t="shared" si="0"/>
+        <v>0.17119150085700419</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B37" s="9"/>
-      <c r="D37" s="30" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="A37" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" s="5">
+        <f>B35/(_b/2/10)</f>
+        <v>193.9511</v>
+      </c>
+      <c r="C37" s="24">
+        <v>193.6</v>
+      </c>
+      <c r="D37" s="26">
+        <f t="shared" si="0"/>
+        <v>0.18135330578512576</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="9">
-        <f>_rho*_A/10000</f>
-        <v>79.677499999999995</v>
-      </c>
-      <c r="C38" s="28">
-        <v>74.900000000000006</v>
-      </c>
-      <c r="D38" s="30">
-        <f t="shared" si="0"/>
-        <v>6.3785046728971784</v>
+        <v>14</v>
+      </c>
+      <c r="B38" s="4">
+        <v>1949.546</v>
+      </c>
+      <c r="C38" s="24">
+        <v>1946</v>
+      </c>
+      <c r="D38" s="26">
+        <f t="shared" si="0"/>
+        <v>0.18221993833504868</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B39" s="9">
-        <f>B38*_L</f>
-        <v>995.96874999999989</v>
-      </c>
-      <c r="C39" s="28">
-        <v>992</v>
-      </c>
-      <c r="D39" s="30">
-        <f t="shared" si="0"/>
-        <v>0.40007560483870108</v>
+        <v>15</v>
+      </c>
+      <c r="B39" s="4">
+        <v>301.74400000000003</v>
+      </c>
+      <c r="C39" s="24">
+        <v>298.3</v>
+      </c>
+      <c r="D39" s="26">
+        <f t="shared" si="0"/>
+        <v>1.1545424069728583</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B40" s="9"/>
-      <c r="D40" s="30" t="str">
+      <c r="D40" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
-      </c>
-      <c r="B41" s="11">
-        <f>B28*_L*100</f>
-        <v>217643.36143134642</v>
-      </c>
-      <c r="C41" s="28">
-        <v>217643</v>
-      </c>
-      <c r="D41" s="30">
-        <f t="shared" si="0"/>
-        <v>1.6606614796632613E-4</v>
+        <v>27</v>
+      </c>
+      <c r="B41" s="9">
+        <f>_rho*_A/10000</f>
+        <v>79.520499999999998</v>
+      </c>
+      <c r="C41" s="24">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="D41" s="26">
+        <f t="shared" si="0"/>
+        <v>6.1688918558077344</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>31</v>
-      </c>
-      <c r="B42" s="11">
-        <f>(B28-_b/10)*_L*100</f>
-        <v>192643.36143134642</v>
-      </c>
-      <c r="C42" s="28">
-        <v>192643</v>
-      </c>
-      <c r="D42" s="30">
-        <f t="shared" si="0"/>
-        <v>1.8761717084370133E-4</v>
+        <v>29</v>
+      </c>
+      <c r="B42" s="9">
+        <f>B41*_L</f>
+        <v>994.00625000000002</v>
+      </c>
+      <c r="C42" s="24">
+        <v>992</v>
+      </c>
+      <c r="D42" s="26">
+        <f t="shared" si="0"/>
+        <v>0.20224294354838079</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B43" s="9"/>
-      <c r="D43" s="30" t="str">
+      <c r="D43" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>25</v>
-      </c>
-      <c r="B44" s="9">
-        <f>B28/_A*100</f>
-        <v>171.54156566017451</v>
-      </c>
-      <c r="C44" s="28">
-        <v>172.2</v>
-      </c>
-      <c r="D44" s="30">
-        <f t="shared" si="0"/>
-        <v>-0.38236605100201437</v>
+        <v>30</v>
+      </c>
+      <c r="B44" s="11">
+        <f>B31*_L*100</f>
+        <v>217643.36143134642</v>
+      </c>
+      <c r="C44" s="24">
+        <v>217643</v>
+      </c>
+      <c r="D44" s="26">
+        <f t="shared" si="0"/>
+        <v>1.6606614796632613E-4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>26</v>
-      </c>
-      <c r="B45" s="9">
-        <f>(B28-_b/10)/_A*100</f>
-        <v>151.83713216263757</v>
-      </c>
-      <c r="C45" s="28">
-        <v>152.4</v>
-      </c>
-      <c r="D45" s="30">
-        <f t="shared" si="0"/>
-        <v>-0.36933585128768875</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D46" s="30" t="str">
+        <v>31</v>
+      </c>
+      <c r="B45" s="11">
+        <f>(B31-_b/10)*_L*100</f>
+        <v>192643.36143134642</v>
+      </c>
+      <c r="C45" s="24">
+        <v>192643</v>
+      </c>
+      <c r="D45" s="26">
+        <f t="shared" si="0"/>
+        <v>1.8761717084370133E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="9"/>
+      <c r="D46" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B47" s="25"/>
-      <c r="D47" s="30" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" s="9">
+        <f>B31/_A*100</f>
+        <v>171.88024594775629</v>
+      </c>
+      <c r="C47" s="24">
+        <v>172.2</v>
+      </c>
+      <c r="D47" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.18568760292897446</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" s="9">
+        <f>(B31-_b/10)/_A*100</f>
+        <v>152.13690932386689</v>
+      </c>
+      <c r="C48" s="24">
+        <v>152.4</v>
+      </c>
+      <c r="D48" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.17263167725269923</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D49" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" s="29"/>
+      <c r="D50" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>17</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B51" s="13">
         <f>_A*100*_fy/1000</f>
-        <v>3603.25</v>
-      </c>
-      <c r="C48" s="28">
+        <v>3596.15</v>
+      </c>
+      <c r="C51" s="24">
         <v>3589</v>
       </c>
-      <c r="D48" s="30">
-        <f t="shared" si="0"/>
-        <v>0.39704653106715782</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="D51" s="26">
+        <f t="shared" si="0"/>
+        <v>0.19921983839510382</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B52" s="13">
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
-        <v>1041.357442933021</v>
-      </c>
-      <c r="C49" s="28">
+        <v>1037.2582560217745</v>
+      </c>
+      <c r="C52" s="24">
         <v>1033</v>
       </c>
-      <c r="D49" s="30">
-        <f t="shared" si="0"/>
-        <v>0.8090457824802666</v>
-      </c>
-      <c r="E49" s="26" t="s">
+      <c r="D52" s="26">
+        <f t="shared" si="0"/>
+        <v>0.41222226735473377</v>
+      </c>
+      <c r="E52" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="F49" s="27"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="F52" s="31"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>18</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B53" s="13">
         <f>_Wel_y*1000*_fy*10^(-6)</f>
         <v>614.49015714285713</v>
       </c>
-      <c r="C50" s="28">
+      <c r="C53" s="24">
         <v>613</v>
       </c>
-      <c r="D50" s="30">
+      <c r="D53" s="26">
         <f t="shared" si="0"/>
         <v>0.2430925192262956</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E53" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F50" s="17">
+      <c r="F53" s="17">
         <f>9*_epsilon</f>
         <v>7.3225486212014435</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B54" s="13">
         <f>_Wel_z*1000*_fy*10^(-6)</f>
         <v>68.852640499999993</v>
       </c>
-      <c r="D51" s="30" t="str">
+      <c r="D54" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E54" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F51" s="17">
+      <c r="F54" s="17">
         <f>10*_epsilon</f>
         <v>8.1361651346682713</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>20</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B55" s="13">
         <f>_Wpl_y*1000*_fy*10^(-6)</f>
         <v>692.08882999999992</v>
       </c>
-      <c r="C52" s="28">
+      <c r="C55" s="24">
         <v>691</v>
       </c>
-      <c r="D52" s="30">
+      <c r="D55" s="26">
         <f t="shared" si="0"/>
         <v>0.15757308248913748</v>
       </c>
-      <c r="E52" s="16" t="s">
+      <c r="E55" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="F52" s="18">
+      <c r="F55" s="18">
         <f>14*_epsilon</f>
         <v>11.390631188535579</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B56" s="13">
         <f>_Wpl_z*1000*_fy*10^(-6)</f>
         <v>107.11912</v>
       </c>
-      <c r="D53" s="30" t="str">
+      <c r="D56" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B54" s="13"/>
-      <c r="D54" s="3" t="str">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B57" s="13"/>
+      <c r="D57" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E54" s="21" t="s">
+      <c r="E57" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="F54" s="22"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="F57" s="22"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>39</v>
       </c>
-      <c r="B55" s="12">
+      <c r="B58" s="12">
         <f>_cf/_tf</f>
         <v>5.1586206896551721</v>
       </c>
-      <c r="D55" s="3" t="str">
+      <c r="D58" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E58" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F55" s="19">
+      <c r="F58" s="19">
         <f>33*_epsilon</f>
         <v>26.849344944405292</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>40</v>
       </c>
-      <c r="B56" s="12">
+      <c r="B59" s="12">
         <f>_cw/_tw</f>
         <v>50.714285714285715</v>
       </c>
-      <c r="D56" s="3" t="str">
+      <c r="D59" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E59" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F56" s="19">
+      <c r="F59" s="19">
         <f>38*_epsilon</f>
         <v>30.917427511739429</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D57" s="3" t="str">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D60" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E57" s="16" t="s">
+      <c r="E60" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F57" s="20">
+      <c r="F60" s="20">
         <f>42*_epsilon</f>
         <v>34.171893565606737</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>34</v>
       </c>
-      <c r="B58">
-        <f>IF(B55&lt;=F50,1,IF(B55&lt;=F51,2,IF(B55&lt;=F52,3,4)))</f>
+      <c r="B61">
+        <f>IF(B58&lt;=F53,1,IF(B58&lt;=F54,2,IF(B58&lt;=F55,3,4)))</f>
         <v>1</v>
       </c>
-      <c r="D58" s="3" t="str">
+      <c r="D61" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>35</v>
       </c>
-      <c r="B59">
-        <f>IF(B56&lt;=F55,1,IF(B56&lt;=F56,2,IF(B56&lt;=F57,3,4)))</f>
+      <c r="B62">
+        <f>IF(B59&lt;=F58,1,IF(B59&lt;=F59,2,IF(B59&lt;=F60,3,4)))</f>
         <v>4</v>
       </c>
-      <c r="D59" s="3" t="str">
+      <c r="D62" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E59" s="21" t="s">
+      <c r="E62" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="F59" s="22"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="F62" s="22"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>36</v>
       </c>
-      <c r="B60">
-        <f>IF(B56&lt;=F60,1,IF(B56&lt;=F61,2,IF(B56&lt;=F62,3,4)))</f>
+      <c r="B63">
+        <f>IF(B59&lt;=F63,1,IF(B59&lt;=F64,2,IF(B59&lt;=F65,3,4)))</f>
         <v>1</v>
       </c>
-      <c r="D60" s="3" t="str">
+      <c r="D63" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E60" s="15" t="s">
+      <c r="E63" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F60" s="19">
+      <c r="F63" s="19">
         <f>72*_epsilon</f>
         <v>58.580388969611548</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D61" s="3" t="str">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D64" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E61" s="15" t="s">
+      <c r="E64" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="F61" s="19">
+      <c r="F64" s="19">
         <f>83*_epsilon</f>
         <v>67.530170617746649</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>52</v>
       </c>
-      <c r="B62" s="3">
+      <c r="B65" s="3">
         <f>_hw/_tw</f>
         <v>55.714285714285715</v>
       </c>
-      <c r="D62" s="3" t="str">
+      <c r="D65" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="E62" s="16" t="s">
+      <c r="E65" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F62" s="20">
+      <c r="F65" s="20">
         <f>124*_epsilon</f>
         <v>100.88844766988656</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>51</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B66" s="23">
         <f>124*_epsilon</f>
         <v>100.88844766988656</v>
       </c>
-      <c r="D63" s="3" t="str">
+      <c r="D66" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D64" s="3" t="str">
+    <row r="67" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D67" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="24" t="s">
+    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="B65" s="25"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="B68" s="29"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>80</v>
       </c>
-      <c r="B66">
+      <c r="B69">
         <v>6.67</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>85</v>
       </c>
-      <c r="B67">
+      <c r="B70">
         <f>_bc-_tw</f>
         <v>191.6</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>83</v>
       </c>
-      <c r="B68" s="30">
+      <c r="B71" s="26">
         <f>(4-PI())*_r^2/(2*_n)</f>
         <v>28.377634165434873</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>84</v>
       </c>
-      <c r="B69" s="29">
+      <c r="B72" s="25">
         <f>(10-3*PI())/(12-3*PI())</f>
         <v>0.22336793894575216</v>
       </c>
-      <c r="E69">
+      <c r="E72">
         <f>(53002/52921-1)*100</f>
         <v>0.15305833223107079</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>86</v>
       </c>
-      <c r="B70">
+      <c r="B73">
         <f>_tf+_kr*_r</f>
         <v>19.190726717860795</v>
       </c>
-      <c r="E70">
+      <c r="E73">
         <f>(47200/47128-1)*100</f>
         <v>0.15277542013241163</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>87</v>
       </c>
-      <c r="B71">
+      <c r="B74">
         <f>_h/2</f>
         <v>248.5</v>
       </c>
-      <c r="E71">
+      <c r="E74">
         <f>(47083/47005-1)*100</f>
         <v>0.16593979363896949</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>88</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B75" s="23">
         <f>_A*100+_As_inf*100-_Acr-_bp*_tf/_n</f>
-        <v>10031.826262677469</v>
-      </c>
-      <c r="C72" s="28">
+        <v>10011.826262677469</v>
+      </c>
+      <c r="C75" s="24">
         <v>9998</v>
       </c>
-      <c r="D72">
-        <f>(B72/C72-1)*100</f>
-        <v>0.33833029283325544</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="D75">
+        <f>(B75/C75-1)*100</f>
+        <v>0.13829028483165473</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>89</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B76" s="23">
         <f>_A*100*_za+_As_inf*100*_zs_inf-_Acr*_zcr-_bp*_tf^2/(2*_n)</f>
-        <v>2656752.2111678715</v>
-      </c>
-      <c r="C73" s="28">
+        <v>2651782.2111678715</v>
+      </c>
+      <c r="C76" s="24">
         <v>2646805</v>
       </c>
-      <c r="D73">
-        <f>(B73/C73-1)*100</f>
-        <v>0.37581956992946974</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="D76">
+        <f>(B76/C76-1)*100</f>
+        <v>0.18804600897577295</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>90</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B77" s="3">
         <f>_n*_A0/_bp*(-1+SQRT(1+2*_bp*_B0/(_n*_A0^2)))</f>
-        <v>204.78830751093571</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+        <v>204.73330249305826</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
         <v>91</v>
       </c>
-      <c r="B75">
+      <c r="B78">
         <f>_tf+_r</f>
         <v>35.5</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>92</v>
       </c>
-      <c r="B76">
+      <c r="B79">
         <f>_zs_inf</f>
         <v>422.5</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>93</v>
       </c>
-      <c r="B77" t="b">
-        <f>IF(B75&lt;=_zel,IF(_zel&lt;=B76,TRUE,FALSE),FALSE)</f>
+      <c r="B80" t="b">
+        <f>IF(B78&lt;=_zel,IF(_zel&lt;=B79,TRUE,FALSE),FALSE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>94</v>
       </c>
-      <c r="B78">
+      <c r="B81">
         <f>(_Iy*10^4+_A*100*(_za-_zel)^2+_As_inf*100*(_zs_inf-_zel)^2+_bp*(_zel-_tf)^3/(3*_n)-_Acr*(_zcr-_zel)^2)*10^(-4)</f>
-        <v>53002.140380188146</v>
-      </c>
-      <c r="C78" s="28">
+        <v>52998.314147422454</v>
+      </c>
+      <c r="C81" s="24">
         <f>52814</f>
         <v>52814</v>
       </c>
-      <c r="D78">
-        <f>(B78/C78-1)*100</f>
-        <v>0.35623202216863437</v>
+      <c r="D81">
+        <f>(B81/C81-1)*100</f>
+        <v>0.34898729015497842</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>95</v>
+      </c>
+      <c r="B82" s="26">
+        <f>210000/_Ecm_dalle</f>
+        <v>6.6717909812633494</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>96</v>
+      </c>
+      <c r="B83" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E83" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F83" s="22"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>100</v>
+      </c>
+      <c r="B84" s="1">
+        <f>50/100</f>
+        <v>0.5</v>
+      </c>
+      <c r="E84" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="F84" s="33">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>101</v>
+      </c>
+      <c r="B85" s="25">
+        <f>IF(E6&lt;=35,1+(1-B84)/(0.1*E5^(1/3)),FALSE)</f>
+        <v>1.8685939040970632</v>
+      </c>
+      <c r="E85" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F85" s="34">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>102</v>
+      </c>
+      <c r="B86" s="25">
+        <f>16.8/SQRT(_fcm_enrobage)</f>
+        <v>2.9245046200557239</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>103</v>
+      </c>
+      <c r="B87">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>104</v>
+      </c>
+      <c r="B88">
+        <v>18250</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>105</v>
+      </c>
+      <c r="B89" s="25">
+        <f>1/(0.1+B87^0.2)</f>
+        <v>0.42792578098028256</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>106</v>
+      </c>
+      <c r="B90" s="26">
+        <f>B85*B86*B89</f>
+        <v>2.3384909388400645</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>107</v>
+      </c>
+      <c r="B91" s="3">
+        <f>IF(_fck_enrobage&lt;=25,MIN(1.5*(1+(0.012*B84*100)^18+250),1500),FALSE)</f>
+        <v>376.50015233993503</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>108</v>
+      </c>
+      <c r="B92" s="26">
+        <f>((B88-B87)/(B91+B88-B87))^0.3</f>
+        <v>0.9938741085684526</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>109</v>
+      </c>
+      <c r="B93" s="25">
+        <f>B90*B92</f>
+        <v>2.3241655972350728</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>110</v>
+      </c>
+      <c r="B94" s="26">
+        <f>B82*(1+B83*B93)</f>
+        <v>23.728772758918403</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B96" s="29"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>112</v>
+      </c>
+      <c r="B97">
+        <f>_dw*_tw*_fy/1000</f>
+        <v>1270.3320000000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>114</v>
+      </c>
+      <c r="B98" s="23">
+        <f>_As_inf*100*_fyd/1000</f>
+        <v>142.05462433623416</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>116</v>
+      </c>
+      <c r="B99" s="23">
+        <f>0.85*_dw*_bp*_fck_enrobage/(1.5*1000)</f>
+        <v>1156.3059999999996</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>117</v>
+      </c>
+      <c r="B100" s="3">
+        <f>0.85*(_r*_bp-(4-PI())*_r^2/2)*_fck_enrobage/(1.5*1000)</f>
+        <v>54.31955005165112</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>118</v>
+      </c>
+      <c r="B101" s="26">
+        <f>(B97+B98-B100)/(2*B97+B99)</f>
+        <v>0.36734598178632322</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>119</v>
+      </c>
+      <c r="B102" s="23">
+        <f>_tf+_r+B101*_dw</f>
+        <v>191.98938824097368</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>120</v>
+      </c>
+      <c r="B103">
+        <f>_tf+_r</f>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>121</v>
+      </c>
+      <c r="B104">
+        <f>_zs_inf</f>
+        <v>422.5</v>
+      </c>
+      <c r="D104" s="3"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>93</v>
+      </c>
+      <c r="B105" t="b">
+        <f>IF(B103&lt;=_zpl,IF(_zpl&lt;=B104,TRUE,FALSE),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>122</v>
+      </c>
+      <c r="B106" s="23">
+        <f>_zpl-_tf-_r</f>
+        <v>156.48938824097368</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>123</v>
+      </c>
+      <c r="B107" s="3">
+        <f>((_Wpl_y*10^3-(_h/2-_zpl)^2*_tw)*_fy+B98*1000*(_zs_inf-_h/2)+0.85*B106*_bp*_fck_enrobage/1.5*(_h/2-_tf-_r-B106/2)+B100*1000*(_h/2-_tf-_r/2))*10^(-6)</f>
+        <v>776.66314007116341</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="B109" s="29"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>130</v>
+      </c>
+      <c r="B110" s="26">
+        <f>_qProfile+_qEnrobage+_qBac+_qDalle</f>
+        <v>9.6760339528260868</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>132</v>
+      </c>
+      <c r="B111" s="3">
+        <f>B110*_L/2</f>
+        <v>60.475212205163039</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>131</v>
+      </c>
+      <c r="B112" s="3">
+        <f>B110*_L^2/8</f>
+        <v>188.98503814113451</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>135</v>
+      </c>
+      <c r="B113" s="3">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>136</v>
+      </c>
+      <c r="B114" s="3">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>137</v>
+      </c>
+      <c r="B115" s="3">
+        <f>B111+B113</f>
+        <v>73.775212205163044</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>138</v>
+      </c>
+      <c r="B116" s="3">
+        <f t="shared" ref="B116" si="1">B112+B114</f>
+        <v>234.28503814113452</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>139</v>
+      </c>
+      <c r="B117" s="3">
+        <f>1.35*B111+1.5*B113</f>
+        <v>101.59153647697011</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>140</v>
+      </c>
+      <c r="B118" s="3">
+        <f>1.35*B112+1.5*B114</f>
+        <v>323.07980149053162</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="B120" s="29"/>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>141</v>
+      </c>
+      <c r="B121" s="26">
+        <f>B118/B107</f>
+        <v>0.41598446587915677</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>142</v>
+      </c>
+      <c r="B122" s="26">
+        <f>B117/_VplRd</f>
+        <v>9.794237441561271E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>149</v>
+      </c>
+      <c r="B123" s="36">
+        <v>492.5</v>
+      </c>
+      <c r="C123" s="24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>150</v>
+      </c>
+      <c r="B124" s="26">
+        <f>B118/B123</f>
+        <v>0.65599959693508958</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>143</v>
+      </c>
+      <c r="B125" s="3">
+        <f>5*B110*(_L*1000)^4/(384*210000*47199*10^(4))</f>
+        <v>31.033025872841279</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>144</v>
+      </c>
+      <c r="B126" s="37">
+        <v>6.476</v>
+      </c>
+      <c r="C126" s="24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>146</v>
+      </c>
+      <c r="B127" s="3">
+        <f>B125+B126</f>
+        <v>37.509025872841278</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>147</v>
+      </c>
+      <c r="B128">
+        <f>B125+0.2*B126</f>
+        <v>32.32822587284128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>148</v>
+      </c>
+      <c r="B129">
+        <f>PI()/2*SQRT(210*52998*10/(B110*1000/9.81*_L*_L^4))</f>
+        <v>0.95514662218841706</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="A120:B120"/>
     <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="E52:F52"/>
     <mergeCell ref="D1:E1"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E15">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16">
       <formula1>"Aucun,Perpendiculaire,Longitudinal"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15300" windowHeight="4260"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15300" windowHeight="4260" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Cas 2" sheetId="1" r:id="rId1"/>
+    <sheet name="Cas 3" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_A" localSheetId="0">'Cas 2'!$B$32</definedName>
@@ -2650,4 +2651,13 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -17,71 +17,139 @@
   </sheets>
   <definedNames>
     <definedName name="_A" localSheetId="0">'Cas 2'!$B$32</definedName>
+    <definedName name="_A" localSheetId="1">'Cas 3'!$B$33</definedName>
     <definedName name="_A0" localSheetId="0">'Cas 2'!$B$75</definedName>
+    <definedName name="_A0" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_Ace" localSheetId="0">'Cas 2'!$E$4</definedName>
+    <definedName name="_Ace" localSheetId="1">'Cas 3'!$E$4</definedName>
     <definedName name="_Acr" localSheetId="0">'Cas 2'!$B$71</definedName>
+    <definedName name="_Acr" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_As_inf" localSheetId="0">'Cas 2'!$E$10</definedName>
+    <definedName name="_As_inf" localSheetId="1">'Cas 3'!$E$10</definedName>
     <definedName name="_Av" localSheetId="0">'Cas 2'!$B$33</definedName>
+    <definedName name="_Av" localSheetId="1">'Cas 3'!$B$34</definedName>
     <definedName name="_b" localSheetId="0">'Cas 2'!$B$4</definedName>
+    <definedName name="_b" localSheetId="1">'Cas 3'!$B$15</definedName>
     <definedName name="_B0" localSheetId="0">'Cas 2'!$B$76</definedName>
+    <definedName name="_B0" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_bb" localSheetId="0">'Cas 2'!$E$21</definedName>
     <definedName name="_bc" localSheetId="0">'Cas 2'!$E$3</definedName>
+    <definedName name="_bc" localSheetId="1">'Cas 3'!$E$3</definedName>
+    <definedName name="_bdroite" localSheetId="1">'Cas 3'!$B$4</definedName>
+    <definedName name="_be1" localSheetId="1">'Cas 3'!$B$6</definedName>
+    <definedName name="_be2" localSheetId="1">'Cas 3'!$B$7</definedName>
+    <definedName name="_beff_appui" localSheetId="1">'Cas 3'!$B$11</definedName>
+    <definedName name="_beff_mi_travee" localSheetId="1">'Cas 3'!$B$10</definedName>
+    <definedName name="_beta1" localSheetId="1">'Cas 3'!$B$8</definedName>
+    <definedName name="_beta2" localSheetId="1">'Cas 3'!$B$9</definedName>
+    <definedName name="_bgauche" localSheetId="1">'Cas 3'!$B$3</definedName>
     <definedName name="_bm" localSheetId="0">'Cas 2'!$E$22</definedName>
+    <definedName name="_bm" localSheetId="1">'Cas 3'!$E$22</definedName>
     <definedName name="_bp" localSheetId="0">'Cas 2'!$B$70</definedName>
+    <definedName name="_bp" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_bt" localSheetId="0">'Cas 2'!$E$20</definedName>
     <definedName name="_cf" localSheetId="0">'Cas 2'!$B$11</definedName>
+    <definedName name="_cf" localSheetId="1">'Cas 3'!$B$22</definedName>
     <definedName name="_cw" localSheetId="0">'Cas 2'!$B$12</definedName>
+    <definedName name="_cw" localSheetId="1">'Cas 3'!$B$23</definedName>
     <definedName name="_d" localSheetId="0">'Cas 2'!$H$13</definedName>
+    <definedName name="_dsc" localSheetId="1">'Cas 3'!$H$14</definedName>
     <definedName name="_dw" localSheetId="0">'Cas 2'!$B$9</definedName>
+    <definedName name="_dw" localSheetId="1">'Cas 3'!$B$20</definedName>
     <definedName name="_Ecm_dalle" localSheetId="0">'Cas 2'!$H$8</definedName>
+    <definedName name="_Ecm_dalle" localSheetId="1">'Cas 3'!$H$8</definedName>
     <definedName name="_ep" localSheetId="0">'Cas 2'!$E$19</definedName>
+    <definedName name="_ep" localSheetId="1">'Cas 3'!$E$19</definedName>
     <definedName name="_epsilon" localSheetId="0">'Cas 2'!$B$15</definedName>
+    <definedName name="_epsilon" localSheetId="1">'Cas 3'!$B$26</definedName>
+    <definedName name="_eta" localSheetId="1">'Cas 3'!$H$28</definedName>
     <definedName name="_fck_dalle" localSheetId="0">'Cas 2'!$H$5</definedName>
+    <definedName name="_fck_dalle" localSheetId="1">'Cas 3'!$H$5</definedName>
     <definedName name="_fck_enrobage" localSheetId="0">'Cas 2'!$E$6</definedName>
+    <definedName name="_fck_enrobage" localSheetId="1">'Cas 3'!$E$6</definedName>
     <definedName name="_fcm_dalle" localSheetId="0">'Cas 2'!$H$6</definedName>
     <definedName name="_fcm_enrobage" localSheetId="0">'Cas 2'!$E$7</definedName>
+    <definedName name="_fcm_enrobage" localSheetId="1">'Cas 3'!$E$7</definedName>
     <definedName name="_fctm_dalle" localSheetId="0">'Cas 2'!$H$7</definedName>
     <definedName name="_fctm_enrobage" localSheetId="0">'Cas 2'!$E$8</definedName>
     <definedName name="_fusc" localSheetId="0">'Cas 2'!$H$14</definedName>
+    <definedName name="_fusc" localSheetId="1">'Cas 3'!$H$15</definedName>
     <definedName name="_fy" localSheetId="0">'Cas 2'!$B$14</definedName>
-    <definedName name="_fyd">'Cas 2'!$E$12</definedName>
+    <definedName name="_fy" localSheetId="1">'Cas 3'!$B$25</definedName>
+    <definedName name="_fyd" localSheetId="0">'Cas 2'!$E$12</definedName>
+    <definedName name="_fyd" localSheetId="1">'Cas 3'!$E$12</definedName>
     <definedName name="_fyp" localSheetId="0">'Cas 2'!$E$24</definedName>
     <definedName name="_h" localSheetId="0">'Cas 2'!$B$3</definedName>
+    <definedName name="_h" localSheetId="1">'Cas 3'!$B$14</definedName>
     <definedName name="_hp" localSheetId="0">'Cas 2'!$E$17</definedName>
+    <definedName name="_hp" localSheetId="1">'Cas 3'!$E$17</definedName>
     <definedName name="_hpg" localSheetId="0">'Cas 2'!$E$18</definedName>
     <definedName name="_hsc" localSheetId="0">'Cas 2'!$H$12</definedName>
+    <definedName name="_hsc" localSheetId="1">'Cas 3'!$H$13</definedName>
     <definedName name="_hw" localSheetId="0">'Cas 2'!$B$8</definedName>
+    <definedName name="_hw" localSheetId="1">'Cas 3'!$B$19</definedName>
     <definedName name="_Iy" localSheetId="0">'Cas 2'!$B$34</definedName>
+    <definedName name="_Iy" localSheetId="1">'Cas 3'!$B$35</definedName>
     <definedName name="_Iz" localSheetId="0">'Cas 2'!$B$35</definedName>
-    <definedName name="_kr">'Cas 2'!$B$72</definedName>
+    <definedName name="_kr" localSheetId="0">'Cas 2'!$B$72</definedName>
+    <definedName name="_kr" localSheetId="1">'Cas 3'!#REF!</definedName>
+    <definedName name="_kt" localSheetId="1">'Cas 3'!$H$21</definedName>
+    <definedName name="_kt_max" localSheetId="1">'Cas 3'!$H$20</definedName>
     <definedName name="_L" localSheetId="0">'Cas 2'!$B$2</definedName>
+    <definedName name="_L" localSheetId="1">'Cas 3'!$B$2</definedName>
     <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$53</definedName>
     <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$54</definedName>
     <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$55</definedName>
     <definedName name="_Mpl_z_Rd" localSheetId="0">'Cas 2'!$B$56</definedName>
     <definedName name="_n" localSheetId="0">'Cas 2'!$B$69</definedName>
+    <definedName name="_n_dalle" localSheetId="1">'Cas 3'!$B$70</definedName>
+    <definedName name="_n_enrobage" localSheetId="1">'Cas 3'!#REF!</definedName>
+    <definedName name="_Nf" localSheetId="1">'Cas 3'!$B$93</definedName>
+    <definedName name="_nr" localSheetId="1">'Cas 3'!$H$16</definedName>
     <definedName name="_NtRd" localSheetId="0">'Cas 2'!$B$51</definedName>
+    <definedName name="_Nw" localSheetId="1">'Cas 3'!$B$94</definedName>
     <definedName name="_qBac" localSheetId="0">'Cas 2'!$E$26</definedName>
+    <definedName name="_qBac" localSheetId="1">'Cas 3'!$E$26</definedName>
     <definedName name="_qDalle" localSheetId="0">'Cas 2'!$H$10</definedName>
+    <definedName name="_qDalle" localSheetId="1">'Cas 3'!$H$10</definedName>
     <definedName name="_qEnrobage" localSheetId="0">'Cas 2'!$E$13</definedName>
+    <definedName name="_qEnrobage" localSheetId="1">'Cas 3'!$E$13</definedName>
     <definedName name="_qProfile" localSheetId="0">'Cas 2'!$B$18</definedName>
+    <definedName name="_qProfile" localSheetId="1">'Cas 3'!$B$29</definedName>
     <definedName name="_r" localSheetId="0">'Cas 2'!$B$7</definedName>
+    <definedName name="_r" localSheetId="1">'Cas 3'!$B$18</definedName>
     <definedName name="_rho" localSheetId="0">'Cas 2'!$B$17</definedName>
+    <definedName name="_rho" localSheetId="1">'Cas 3'!$B$28</definedName>
     <definedName name="_tc" localSheetId="0">'Cas 2'!$H$4</definedName>
+    <definedName name="_tc" localSheetId="1">'Cas 3'!$H$4</definedName>
     <definedName name="_td" localSheetId="0">'Cas 2'!$H$3</definedName>
+    <definedName name="_td" localSheetId="1">'Cas 3'!$H$3</definedName>
     <definedName name="_tf" localSheetId="0">'Cas 2'!$B$5</definedName>
+    <definedName name="_tf" localSheetId="1">'Cas 3'!$B$16</definedName>
     <definedName name="_tp" localSheetId="0">'Cas 2'!$E$23</definedName>
     <definedName name="_tw" localSheetId="0">'Cas 2'!$B$6</definedName>
+    <definedName name="_tw" localSheetId="1">'Cas 3'!$B$17</definedName>
     <definedName name="_VplRd" localSheetId="0">'Cas 2'!$B$52</definedName>
+    <definedName name="_VplRd" localSheetId="1">'Cas 3'!$B$53</definedName>
     <definedName name="_Wel_y" localSheetId="0">'Cas 2'!$B$36</definedName>
+    <definedName name="_Wel_y" localSheetId="1">'Cas 3'!$B$37</definedName>
     <definedName name="_Wel_z" localSheetId="0">'Cas 2'!$B$37</definedName>
+    <definedName name="_Wel_z" localSheetId="1">'Cas 3'!$B$38</definedName>
     <definedName name="_Wpl_y" localSheetId="0">'Cas 2'!$B$38</definedName>
+    <definedName name="_Wpl_y" localSheetId="1">'Cas 3'!$B$39</definedName>
     <definedName name="_Wpl_z" localSheetId="0">'Cas 2'!$B$39</definedName>
+    <definedName name="_Wpl_z" localSheetId="1">'Cas 3'!$B$40</definedName>
     <definedName name="_za" localSheetId="0">'Cas 2'!$B$74</definedName>
+    <definedName name="_za" localSheetId="1">'Cas 3'!$B$71</definedName>
     <definedName name="_zcr" localSheetId="0">'Cas 2'!$B$73</definedName>
+    <definedName name="_zcr" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_zel" localSheetId="0">'Cas 2'!$B$77</definedName>
+    <definedName name="_zel" localSheetId="1">'Cas 3'!$B$73</definedName>
     <definedName name="_zpl" localSheetId="0">'Cas 2'!$B$102</definedName>
+    <definedName name="_zpl" localSheetId="1">'Cas 3'!$B$96</definedName>
+    <definedName name="_zs" localSheetId="1">'Cas 3'!$B$72</definedName>
     <definedName name="_zs_inf" localSheetId="0">'Cas 2'!$E$11</definedName>
+    <definedName name="_zs_inf" localSheetId="1">'Cas 3'!$E$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -93,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="187">
   <si>
     <t>h (mm)</t>
   </si>
@@ -549,6 +617,111 @@
   </si>
   <si>
     <t>Valeur issue de l'article RCM 2023 n°3</t>
+  </si>
+  <si>
+    <t>Données poutre</t>
+  </si>
+  <si>
+    <t>bgauche (m)</t>
+  </si>
+  <si>
+    <t>bdroite (m)</t>
+  </si>
+  <si>
+    <t>L/8 (m)</t>
+  </si>
+  <si>
+    <t>be1 (m)</t>
+  </si>
+  <si>
+    <t>be2 (m)</t>
+  </si>
+  <si>
+    <t>beta 1</t>
+  </si>
+  <si>
+    <t>beta 2</t>
+  </si>
+  <si>
+    <t>beff mi travée (m)</t>
+  </si>
+  <si>
+    <t>beff appui (m)</t>
+  </si>
+  <si>
+    <t>Données connecteurs</t>
+  </si>
+  <si>
+    <t>hsc (mm)</t>
+  </si>
+  <si>
+    <t>dsc (mm)</t>
+  </si>
+  <si>
+    <t>Prd,s (kN)</t>
+  </si>
+  <si>
+    <t>fu,sc (MPa)</t>
+  </si>
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>PRd,c (kN)</t>
+  </si>
+  <si>
+    <t>kt,max</t>
+  </si>
+  <si>
+    <t>kt</t>
+  </si>
+  <si>
+    <t>nr</t>
+  </si>
+  <si>
+    <t>PRd (kN)</t>
+  </si>
+  <si>
+    <t>Na (kN)</t>
+  </si>
+  <si>
+    <t>Nc (kN)</t>
+  </si>
+  <si>
+    <t>Résistance à la traction du profilé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résistance à la compression de la dalle béton </t>
+  </si>
+  <si>
+    <t>Ns,inf (kN)</t>
+  </si>
+  <si>
+    <t>Résistance à la traction des aciers d'enrobage (on ne prend pas en compte les armatures supérieures)</t>
+  </si>
+  <si>
+    <t>Nconnex (kN)</t>
+  </si>
+  <si>
+    <t>Nconnecteur (kN)</t>
+  </si>
+  <si>
+    <t>eta</t>
+  </si>
+  <si>
+    <t>eta min</t>
+  </si>
+  <si>
+    <t>n dalle</t>
+  </si>
+  <si>
+    <t>zs (mm)</t>
+  </si>
+  <si>
+    <t>Nf (kN)</t>
+  </si>
+  <si>
+    <t>Ncp (kN)</t>
   </si>
 </sst>
 </file>
@@ -734,7 +907,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -769,6 +942,12 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -781,12 +960,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -1080,20 +1256,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="29"/>
+      <c r="B1" s="35"/>
       <c r="C1"/>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="29"/>
+      <c r="E1" s="35"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="29"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -1355,10 +1531,10 @@
         <v>0.81361651346682706</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="28" t="s">
+      <c r="D15" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="29"/>
+      <c r="E15" s="35"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
@@ -1389,7 +1565,7 @@
       <c r="A18" t="s">
         <v>124</v>
       </c>
-      <c r="B18" s="35">
+      <c r="B18" s="31">
         <f>_rho*_A*10^(-4)*9.81/1000</f>
         <v>0.78009610500000004</v>
       </c>
@@ -1497,10 +1673,10 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="29"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="24" t="s">
         <v>53</v>
       </c>
@@ -1768,10 +1944,10 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="28" t="s">
+      <c r="A50" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="29"/>
+      <c r="B50" s="35"/>
       <c r="D50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1808,10 +1984,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E52" s="30" t="s">
+      <c r="E52" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="F52" s="31"/>
+      <c r="F52" s="37"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -2059,10 +2235,10 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="28" t="s">
+      <c r="A68" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="B68" s="29"/>
+      <c r="B68" s="35"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -2243,10 +2419,10 @@
         <f>50/100</f>
         <v>0.5</v>
       </c>
-      <c r="E84" s="32" t="s">
+      <c r="E84" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="F84" s="33">
+      <c r="F84" s="29">
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -2261,7 +2437,7 @@
       <c r="E85" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="F85" s="34">
+      <c r="F85" s="30">
         <v>0.55000000000000004</v>
       </c>
     </row>
@@ -2346,10 +2522,10 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="28" t="s">
+      <c r="A96" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="B96" s="29"/>
+      <c r="B96" s="35"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -2453,10 +2629,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="28" t="s">
+      <c r="A109" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="B109" s="29"/>
+      <c r="B109" s="35"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -2539,10 +2715,10 @@
     </row>
     <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="28" t="s">
+      <c r="A120" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="B120" s="29"/>
+      <c r="B120" s="35"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
@@ -2566,7 +2742,7 @@
       <c r="A123" t="s">
         <v>149</v>
       </c>
-      <c r="B123" s="36">
+      <c r="B123" s="32">
         <v>492.5</v>
       </c>
       <c r="C123" s="24" t="s">
@@ -2595,7 +2771,7 @@
       <c r="A126" t="s">
         <v>144</v>
       </c>
-      <c r="B126" s="37">
+      <c r="B126" s="33">
         <v>6.476</v>
       </c>
       <c r="C126" s="24" t="s">
@@ -2655,9 +2831,1686 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" style="24"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1"/>
+      <c r="D1" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="35"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="35"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="10">
+        <v>12.5</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="23">
+        <f>2*_tc*(1+_hp*_bm/(_ep*_tc))</f>
+        <v>209.67149758454107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="C3"/>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="1">
+        <f>E2*_b</f>
+        <v>200</v>
+      </c>
+      <c r="G3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="10">
+        <v>1.25</v>
+      </c>
+      <c r="C4"/>
+      <c r="D4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4">
+        <f>_b*_h/100-_A-(_b-_bc)*_hw/100</f>
+        <v>892.7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4">
+        <f>_td-_hp</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5">
+        <f>_L/8</f>
+        <v>1.5625</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="23">
+        <f>_Ace*100/_hw</f>
+        <v>190.74786324786325</v>
+      </c>
+      <c r="G5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6">
+        <f>MIN(_bgauche,B5)</f>
+        <v>1.25</v>
+      </c>
+      <c r="C6"/>
+      <c r="D6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="1">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6">
+        <f>_fck_enrobage+8</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7">
+        <f>MIN(_bdroite,B5)</f>
+        <v>1.25</v>
+      </c>
+      <c r="C7"/>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7">
+        <f>_fck_enrobage+8</f>
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="26">
+        <f>0.3*_fck_enrobage^(2/3)</f>
+        <v>2.5649639200150443</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8">
+        <f>MIN(1,0.55+0.025*_L/_be1)</f>
+        <v>0.8</v>
+      </c>
+      <c r="C8"/>
+      <c r="D8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="26">
+        <f>0.3*_fck_enrobage^(2/3)</f>
+        <v>2.5649639200150443</v>
+      </c>
+      <c r="G8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="26">
+        <f>22*(_fcm_enrobage/10)^0.3*1000</f>
+        <v>31475.806210019346</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9">
+        <f>MIN(1,0.55+0.025*_L/_be2)</f>
+        <v>0.8</v>
+      </c>
+      <c r="C9"/>
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="26">
+        <f>22*(_fcm_enrobage/10)^0.3*1000</f>
+        <v>31475.806210019346</v>
+      </c>
+      <c r="G9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H9">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="26">
+        <f>_be1+_be2</f>
+        <v>2.5</v>
+      </c>
+      <c r="C10"/>
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="27">
+        <f>PI()*(12^2+8^2)/4*2/100</f>
+        <v>3.267256359733385</v>
+      </c>
+      <c r="G10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H10" s="26">
+        <f>(_tc+_hp*_bm/_ep)/1000*H9*2500*9.81/1000</f>
+        <v>6.4277418478260868</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="26">
+        <f>_be1*_beta1+_be2*_beta2</f>
+        <v>2</v>
+      </c>
+      <c r="C11"/>
+      <c r="D11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="1">
+        <v>422.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C12"/>
+      <c r="D12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="23">
+        <f>500/1.15</f>
+        <v>434.78260869565219</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="H12" s="35"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="35"/>
+      <c r="C13"/>
+      <c r="D13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="26">
+        <f>_Ace*10^(-4)*2500*9.81/1000</f>
+        <v>2.1893467500000003</v>
+      </c>
+      <c r="G13" t="s">
+        <v>163</v>
+      </c>
+      <c r="H13" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1">
+        <v>497</v>
+      </c>
+      <c r="C14"/>
+      <c r="G14" t="s">
+        <v>164</v>
+      </c>
+      <c r="H14" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="1">
+        <v>200</v>
+      </c>
+      <c r="C15"/>
+      <c r="D15" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="E15" s="35"/>
+      <c r="G15" t="s">
+        <v>166</v>
+      </c>
+      <c r="H15" s="10">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="C16"/>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="C17"/>
+      <c r="D17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="1">
+        <v>58</v>
+      </c>
+      <c r="G17" t="s">
+        <v>165</v>
+      </c>
+      <c r="H17" s="3">
+        <f>0.8*_fusc*PI()*_dsc^2/4/(1000*1.25)</f>
+        <v>81.656276252105897</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="1">
+        <v>21</v>
+      </c>
+      <c r="C18"/>
+      <c r="D18" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="1">
+        <v>58</v>
+      </c>
+      <c r="G18" t="s">
+        <v>167</v>
+      </c>
+      <c r="H18" s="3">
+        <f>IF(_hsc/_dsc&gt;=4,1,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="6">
+        <f>_h-2*_tf</f>
+        <v>468</v>
+      </c>
+      <c r="C19"/>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="1">
+        <v>207</v>
+      </c>
+      <c r="G19" t="s">
+        <v>168</v>
+      </c>
+      <c r="H19" s="3">
+        <f>0.29*H18*_dsc^2*SQRT(H5*_Ecm_dalle)/(1000*1.25)</f>
+        <v>74.293979654469197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="6">
+        <f>_hw-2*_r</f>
+        <v>426</v>
+      </c>
+      <c r="C20"/>
+      <c r="D20" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="1">
+        <v>101</v>
+      </c>
+      <c r="G20" t="s">
+        <v>169</v>
+      </c>
+      <c r="H20">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="6"/>
+      <c r="C21"/>
+      <c r="D21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="1">
+        <v>62</v>
+      </c>
+      <c r="G21" t="s">
+        <v>170</v>
+      </c>
+      <c r="H21" s="25">
+        <f>0.7*_bm/(SQRT(_nr)*_hp)*(_hsc/_hp-1)</f>
+        <v>0.5036559329373026</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="6">
+        <f>(_b-2*_r-_tw)/2</f>
+        <v>74.8</v>
+      </c>
+      <c r="C22"/>
+      <c r="D22" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22">
+        <f>(E20+E21)/2</f>
+        <v>81.5</v>
+      </c>
+      <c r="G22" t="s">
+        <v>172</v>
+      </c>
+      <c r="H22" s="26">
+        <f>MIN(_kt,_kt_max)*MIN(H17,H19)</f>
+        <v>37.418603634496662</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="6">
+        <f>_hw-2*_r</f>
+        <v>426</v>
+      </c>
+      <c r="C23"/>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>173</v>
+      </c>
+      <c r="H23" s="23">
+        <f>_A*100*_fy/1000</f>
+        <v>3596.15</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C24"/>
+      <c r="D24" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="1">
+        <v>350</v>
+      </c>
+      <c r="G24" t="s">
+        <v>177</v>
+      </c>
+      <c r="H24" s="3">
+        <f>_As_inf*100*_fyd/1000</f>
+        <v>142.05462433623416</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1">
+        <v>355</v>
+      </c>
+      <c r="C25"/>
+      <c r="D25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="1">
+        <v>11.37</v>
+      </c>
+      <c r="G25" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="23">
+        <f>0.85*_beff_mi_travee*1000*_tc*H5/1.5/1000</f>
+        <v>2904.1666666666665</v>
+      </c>
+      <c r="I25" s="24" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="14">
+        <f>SQRT(235/_fy)</f>
+        <v>0.81361651346682706</v>
+      </c>
+      <c r="C26"/>
+      <c r="D26" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="25">
+        <f>E25*H9*9.81/1000</f>
+        <v>0.27884924999999999</v>
+      </c>
+      <c r="G26" t="s">
+        <v>179</v>
+      </c>
+      <c r="H26" s="23">
+        <f>MIN(H25,H23+H24)</f>
+        <v>2904.1666666666665</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="6"/>
+      <c r="C27"/>
+      <c r="G27" t="s">
+        <v>180</v>
+      </c>
+      <c r="H27" s="3">
+        <f>_nr*(_L*1000/2)/_ep*H22</f>
+        <v>2259.5775141604267</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="1">
+        <v>7850</v>
+      </c>
+      <c r="C28"/>
+      <c r="D28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" t="s">
+        <v>181</v>
+      </c>
+      <c r="H28" s="26">
+        <f>MIN(H27/H26,1)</f>
+        <v>0.7780467767553837</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="31">
+        <f>_rho*_A*10^(-4)*9.81/1000</f>
+        <v>0.78009610500000004</v>
+      </c>
+      <c r="C29"/>
+      <c r="G29" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29">
+        <f>MAX(1-(355/_fy)*(0.75-0.03*_L),0.4)</f>
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C30"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="35"/>
+      <c r="C31" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="8">
+        <f>(2*(_h-2*_r)+2*_b+2*(_b-2*_r-_tw)+2*PI()*_r)/10</f>
+        <v>174.11468914507714</v>
+      </c>
+      <c r="D32" t="str">
+        <f>IF(C32&lt;&gt;"",(B32/C32-1)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="4">
+        <v>101.3</v>
+      </c>
+      <c r="C33" s="24">
+        <v>101.1</v>
+      </c>
+      <c r="D33" s="26">
+        <f t="shared" ref="D33:D68" si="0">IF(C33&lt;&gt;"",(B33/C33-1)*100,"")</f>
+        <v>0.19782393669633969</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="5">
+        <f>B33-2*_b*_tf/100+2*(_tw+2*_r)*_tf/2/100</f>
+        <v>50.607999999999997</v>
+      </c>
+      <c r="C34" s="24">
+        <v>50.4</v>
+      </c>
+      <c r="D34" s="26">
+        <f t="shared" si="0"/>
+        <v>0.41269841269842011</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="4">
+        <v>43014.311000000002</v>
+      </c>
+      <c r="C35" s="24">
+        <v>42933</v>
+      </c>
+      <c r="D35" s="26">
+        <f t="shared" si="0"/>
+        <v>0.18939044557799711</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="4">
+        <v>1939.511</v>
+      </c>
+      <c r="C36" s="24">
+        <v>1936</v>
+      </c>
+      <c r="D36" s="26">
+        <f t="shared" si="0"/>
+        <v>0.18135330578512576</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="5">
+        <f>B35/(_h/2/10)</f>
+        <v>1730.9581891348089</v>
+      </c>
+      <c r="C37" s="24">
+        <v>1728</v>
+      </c>
+      <c r="D37" s="26">
+        <f t="shared" si="0"/>
+        <v>0.17119150085700419</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="5">
+        <f>B36/(_b/2/10)</f>
+        <v>193.9511</v>
+      </c>
+      <c r="C38" s="24">
+        <v>193.6</v>
+      </c>
+      <c r="D38" s="26">
+        <f t="shared" si="0"/>
+        <v>0.18135330578512576</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="4">
+        <v>1949.546</v>
+      </c>
+      <c r="C39" s="24">
+        <v>1946</v>
+      </c>
+      <c r="D39" s="26">
+        <f t="shared" si="0"/>
+        <v>0.18221993833504868</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="4">
+        <v>301.74400000000003</v>
+      </c>
+      <c r="C40" s="24">
+        <v>298.3</v>
+      </c>
+      <c r="D40" s="26">
+        <f t="shared" si="0"/>
+        <v>1.1545424069728583</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="9"/>
+      <c r="D41" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B42" s="9">
+        <f>_rho*_A/10000</f>
+        <v>79.520499999999998</v>
+      </c>
+      <c r="C42" s="24">
+        <v>74.900000000000006</v>
+      </c>
+      <c r="D42" s="26">
+        <f t="shared" si="0"/>
+        <v>6.1688918558077344</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B43" s="9">
+        <f>B42*_L</f>
+        <v>994.00625000000002</v>
+      </c>
+      <c r="C43" s="24">
+        <v>992</v>
+      </c>
+      <c r="D43" s="26">
+        <f t="shared" si="0"/>
+        <v>0.20224294354838079</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="9"/>
+      <c r="D44" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" s="11">
+        <f>B32*_L*100</f>
+        <v>217643.36143134642</v>
+      </c>
+      <c r="C45" s="24">
+        <v>217643</v>
+      </c>
+      <c r="D45" s="26">
+        <f t="shared" si="0"/>
+        <v>1.6606614796632613E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="11">
+        <f>(B32-_b/10)*_L*100</f>
+        <v>192643.36143134642</v>
+      </c>
+      <c r="C46" s="24">
+        <v>192643</v>
+      </c>
+      <c r="D46" s="26">
+        <f t="shared" si="0"/>
+        <v>1.8761717084370133E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="9"/>
+      <c r="D47" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" s="9">
+        <f>B32/_A*100</f>
+        <v>171.88024594775629</v>
+      </c>
+      <c r="C48" s="24">
+        <v>172.2</v>
+      </c>
+      <c r="D48" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.18568760292897446</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" s="9">
+        <f>(B32-_b/10)/_A*100</f>
+        <v>152.13690932386689</v>
+      </c>
+      <c r="C49" s="24">
+        <v>152.4</v>
+      </c>
+      <c r="D49" s="26">
+        <f t="shared" si="0"/>
+        <v>-0.17263167725269923</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D50" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" s="35"/>
+      <c r="D51" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" s="13">
+        <f>_A*100*_fy/1000</f>
+        <v>3596.15</v>
+      </c>
+      <c r="C52" s="24">
+        <v>3589</v>
+      </c>
+      <c r="D52" s="26">
+        <f t="shared" si="0"/>
+        <v>0.19921983839510382</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="13">
+        <f>_Av*100*_fy/(1000*SQRT(3))</f>
+        <v>1037.2582560217745</v>
+      </c>
+      <c r="C53" s="24">
+        <v>1033</v>
+      </c>
+      <c r="D53" s="26">
+        <f t="shared" si="0"/>
+        <v>0.41222226735473377</v>
+      </c>
+      <c r="E53" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="F53" s="37"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" s="13">
+        <f>_Wel_y*1000*_fy*10^(-6)</f>
+        <v>614.49015714285713</v>
+      </c>
+      <c r="C54" s="24">
+        <v>613</v>
+      </c>
+      <c r="D54" s="26">
+        <f t="shared" si="0"/>
+        <v>0.2430925192262956</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" s="17">
+        <f>9*_epsilon</f>
+        <v>7.3225486212014435</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" s="13">
+        <f>_Wel_z*1000*_fy*10^(-6)</f>
+        <v>68.852640499999993</v>
+      </c>
+      <c r="D55" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="17">
+        <f>10*_epsilon</f>
+        <v>8.1361651346682713</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" s="13">
+        <f>_Wpl_y*1000*_fy*10^(-6)</f>
+        <v>692.08882999999992</v>
+      </c>
+      <c r="C56" s="24">
+        <v>691</v>
+      </c>
+      <c r="D56" s="26">
+        <f t="shared" si="0"/>
+        <v>0.15757308248913748</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F56" s="18">
+        <f>14*_epsilon</f>
+        <v>11.390631188535579</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" s="13">
+        <f>_Wpl_z*1000*_fy*10^(-6)</f>
+        <v>107.11912</v>
+      </c>
+      <c r="D57" s="26" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B58" s="13"/>
+      <c r="D58" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F58" s="22"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" s="12">
+        <f>_cf/_tf</f>
+        <v>5.1586206896551721</v>
+      </c>
+      <c r="D59" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F59" s="19">
+        <f>33*_epsilon</f>
+        <v>26.849344944405292</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="12">
+        <f>_cw/_tw</f>
+        <v>50.714285714285715</v>
+      </c>
+      <c r="D60" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="F60" s="19">
+        <f>38*_epsilon</f>
+        <v>30.917427511739429</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D61" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F61" s="20">
+        <f>42*_epsilon</f>
+        <v>34.171893565606737</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>34</v>
+      </c>
+      <c r="B62">
+        <f>IF(B59&lt;=F54,1,IF(B59&lt;=F55,2,IF(B59&lt;=F56,3,4)))</f>
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63">
+        <f>IF(B60&lt;=F59,1,IF(B60&lt;=F60,2,IF(B60&lt;=F61,3,4)))</f>
+        <v>4</v>
+      </c>
+      <c r="D63" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F63" s="22"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64">
+        <f>IF(B60&lt;=F64,1,IF(B60&lt;=F65,2,IF(B60&lt;=F66,3,4)))</f>
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E64" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F64" s="19">
+        <f>72*_epsilon</f>
+        <v>58.580388969611548</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D65" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="F65" s="19">
+        <f>83*_epsilon</f>
+        <v>67.530170617746649</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" s="3">
+        <f>_hw/_tw</f>
+        <v>55.714285714285715</v>
+      </c>
+      <c r="D66" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F66" s="20">
+        <f>124*_epsilon</f>
+        <v>100.88844766988656</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>51</v>
+      </c>
+      <c r="B67" s="23">
+        <f>124*_epsilon</f>
+        <v>100.88844766988656</v>
+      </c>
+      <c r="D67" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D68" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" s="35"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>183</v>
+      </c>
+      <c r="B70">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>87</v>
+      </c>
+      <c r="B71">
+        <f>_td+_h/2</f>
+        <v>388.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>184</v>
+      </c>
+      <c r="B72">
+        <f>_td+_zs_inf</f>
+        <v>562.5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B73" s="3">
+        <f>(_beff_mi_travee*1000*_tc^2/(2*_n_dalle)+_A*100*_za+_As_inf*100*_zs)/(_beff_mi_travee*1000*_tc/_n_dalle+_A*100+_As_inf*100)</f>
+        <v>131.594015157716</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74">
+        <f>_tc</f>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75">
+        <f>_td+_tf</f>
+        <v>154.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76" t="b">
+        <f>IF(B74&lt;=_zel,IF(_zel&lt;=B75,TRUE,FALSE),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77" s="5">
+        <f>(_Iy*10^4+_A*100*(_za-_zel)^2+_As_inf*100*(_zs-_zel)^2+_beff_mi_travee*1000*_tc/_n_dalle*(_tc^2/12+(_tc/2-_zel)^2))*10^(-4)</f>
+        <v>142488.53513587199</v>
+      </c>
+      <c r="C77" s="24">
+        <f>52814</f>
+        <v>52814</v>
+      </c>
+      <c r="D77">
+        <f>(B77/C77-1)*100</f>
+        <v>169.79311382563714</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>95</v>
+      </c>
+      <c r="B78" s="26">
+        <f>210000/_Ecm_dalle</f>
+        <v>6.6717909812633494</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B79" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="E79" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F79" s="22"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" s="1">
+        <f>50/100</f>
+        <v>0.5</v>
+      </c>
+      <c r="E80" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="F80" s="29">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>101</v>
+      </c>
+      <c r="B81" s="25">
+        <f>IF(E6&lt;=35,1+(1-B80)/(0.1*E5^(1/3)),FALSE)</f>
+        <v>1.8685939040970632</v>
+      </c>
+      <c r="E81" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F81" s="30">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>102</v>
+      </c>
+      <c r="B82" s="25">
+        <f>16.8/SQRT(_fcm_enrobage)</f>
+        <v>2.9245046200557239</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>103</v>
+      </c>
+      <c r="B83">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>104</v>
+      </c>
+      <c r="B84">
+        <v>18250</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" s="25">
+        <f>1/(0.1+B83^0.2)</f>
+        <v>0.42792578098028256</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>106</v>
+      </c>
+      <c r="B86" s="26">
+        <f>B81*B82*B85</f>
+        <v>2.3384909388400645</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>107</v>
+      </c>
+      <c r="B87" s="3">
+        <f>IF(_fck_enrobage&lt;=25,MIN(1.5*(1+(0.012*B80*100)^18+250),1500),FALSE)</f>
+        <v>376.50015233993503</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>108</v>
+      </c>
+      <c r="B88" s="26">
+        <f>((B84-B83)/(B87+B84-B83))^0.3</f>
+        <v>0.9938741085684526</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>109</v>
+      </c>
+      <c r="B89" s="25">
+        <f>B86*B88</f>
+        <v>2.3241655972350728</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>110</v>
+      </c>
+      <c r="B90" s="26">
+        <f>B78*(1+B79*B89)</f>
+        <v>23.728772758918403</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B92" s="35"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="B93" s="38">
+        <f>_tf*_b*_fy/1000</f>
+        <v>1029.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>112</v>
+      </c>
+      <c r="B94">
+        <f>_A*100*_fy/1000-2*B93</f>
+        <v>1537.15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>186</v>
+      </c>
+      <c r="B95">
+        <f>_eta*0.85*_beff_mi_travee*1000*_tc*_fck_dalle/(1000*1.5)</f>
+        <v>2259.5775141604267</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>119</v>
+      </c>
+      <c r="B96" s="23">
+        <f>B95/(0.85*_beff_mi_travee*1000*_fck_dalle/1000/1.5)</f>
+        <v>63.799835693941468</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>120</v>
+      </c>
+      <c r="B97">
+        <f>_tf+_r</f>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>121</v>
+      </c>
+      <c r="B98">
+        <f>_zs_inf</f>
+        <v>422.5</v>
+      </c>
+      <c r="D98" s="3"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>93</v>
+      </c>
+      <c r="B99" t="b">
+        <f>IF(B97&lt;=_zpl,IF(_zpl&lt;=B98,TRUE,FALSE),FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>122</v>
+      </c>
+      <c r="B100" s="23">
+        <f>_zpl-_tf-_r</f>
+        <v>28.299835693941468</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>123</v>
+      </c>
+      <c r="B101" s="3" t="e">
+        <f>((_Wpl_y*10^3-(_h/2-_zpl)^2*_tw)*_fy+#REF!*1000*(_zs_inf-_h/2)+0.85*B100*_bp*_fck_enrobage/1.5*(_h/2-_tf-_r-B100/2)+#REF!*1000*(_h/2-_tf-_r/2))*10^(-6)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="103" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="B103" s="35"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>130</v>
+      </c>
+      <c r="B104" s="26">
+        <f>_qProfile+_qEnrobage+_qBac+_qDalle</f>
+        <v>9.6760339528260868</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>132</v>
+      </c>
+      <c r="B105" s="3">
+        <f>B104*_L/2</f>
+        <v>60.475212205163039</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>131</v>
+      </c>
+      <c r="B106" s="3">
+        <f>B104*_L^2/8</f>
+        <v>188.98503814113451</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>135</v>
+      </c>
+      <c r="B107" s="3">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>136</v>
+      </c>
+      <c r="B108" s="3">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>137</v>
+      </c>
+      <c r="B109" s="3">
+        <f>B105+B107</f>
+        <v>73.775212205163044</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>138</v>
+      </c>
+      <c r="B110" s="3">
+        <f t="shared" ref="B110" si="1">B106+B108</f>
+        <v>234.28503814113452</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>139</v>
+      </c>
+      <c r="B111" s="3">
+        <f>1.35*B105+1.5*B107</f>
+        <v>101.59153647697011</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>140</v>
+      </c>
+      <c r="B112" s="3">
+        <f>1.35*B106+1.5*B108</f>
+        <v>323.07980149053162</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="114" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B114" s="35"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>141</v>
+      </c>
+      <c r="B115" s="26" t="e">
+        <f>B112/B101</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>142</v>
+      </c>
+      <c r="B116" s="26">
+        <f>B111/_VplRd</f>
+        <v>9.794237441561271E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>149</v>
+      </c>
+      <c r="B117" s="32">
+        <v>492.5</v>
+      </c>
+      <c r="C117" s="24" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>150</v>
+      </c>
+      <c r="B118" s="26">
+        <f>B112/B117</f>
+        <v>0.65599959693508958</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>143</v>
+      </c>
+      <c r="B119" s="3">
+        <f>5*B104*(_L*1000)^4/(384*210000*47199*10^(4))</f>
+        <v>31.033025872841279</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>144</v>
+      </c>
+      <c r="B120" s="33">
+        <v>6.476</v>
+      </c>
+      <c r="C120" s="24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>146</v>
+      </c>
+      <c r="B121" s="3">
+        <f>B119+B120</f>
+        <v>37.509025872841278</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>147</v>
+      </c>
+      <c r="B122">
+        <f>B119+0.2*B120</f>
+        <v>32.32822587284128</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>148</v>
+      </c>
+      <c r="B123">
+        <f>PI()/2*SQRT(210*52998*10/(B104*1000/9.81*_L*_L^4))</f>
+        <v>0.95514662218841706</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="G12:H12"/>
+  </mergeCells>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16">
+      <formula1>"Aucun,Perpendiculaire,Longitudinal"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -104,10 +104,13 @@
     <definedName name="_n" localSheetId="0">'Cas 2'!$B$69</definedName>
     <definedName name="_n_dalle" localSheetId="1">'Cas 3'!$B$70</definedName>
     <definedName name="_n_enrobage" localSheetId="1">'Cas 3'!#REF!</definedName>
-    <definedName name="_Nf" localSheetId="1">'Cas 3'!$B$93</definedName>
+    <definedName name="_Na" localSheetId="1">'Cas 3'!$H$23</definedName>
+    <definedName name="_Ncp" localSheetId="1">'Cas 3'!$B$104</definedName>
+    <definedName name="_Nf" localSheetId="1">'Cas 3'!$B$102</definedName>
     <definedName name="_nr" localSheetId="1">'Cas 3'!$H$16</definedName>
+    <definedName name="_Ns_inf" localSheetId="1">'Cas 3'!$H$24</definedName>
     <definedName name="_NtRd" localSheetId="0">'Cas 2'!$B$51</definedName>
-    <definedName name="_Nw" localSheetId="1">'Cas 3'!$B$94</definedName>
+    <definedName name="_Nw" localSheetId="1">'Cas 3'!$B$103</definedName>
     <definedName name="_qBac" localSheetId="0">'Cas 2'!$E$26</definedName>
     <definedName name="_qBac" localSheetId="1">'Cas 3'!$E$26</definedName>
     <definedName name="_qDalle" localSheetId="0">'Cas 2'!$H$10</definedName>
@@ -140,14 +143,15 @@
     <definedName name="_Wpl_z" localSheetId="0">'Cas 2'!$B$39</definedName>
     <definedName name="_Wpl_z" localSheetId="1">'Cas 3'!$B$40</definedName>
     <definedName name="_za" localSheetId="0">'Cas 2'!$B$74</definedName>
-    <definedName name="_za" localSheetId="1">'Cas 3'!$B$71</definedName>
+    <definedName name="_za" localSheetId="1">'Cas 3'!$B$73</definedName>
     <definedName name="_zcr" localSheetId="0">'Cas 2'!$B$73</definedName>
     <definedName name="_zcr" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_zel" localSheetId="0">'Cas 2'!$B$77</definedName>
-    <definedName name="_zel" localSheetId="1">'Cas 3'!$B$73</definedName>
+    <definedName name="_zel" localSheetId="1">'Cas 3'!$B$79</definedName>
     <definedName name="_zpl" localSheetId="0">'Cas 2'!$B$102</definedName>
-    <definedName name="_zpl" localSheetId="1">'Cas 3'!$B$96</definedName>
-    <definedName name="_zs" localSheetId="1">'Cas 3'!$B$72</definedName>
+    <definedName name="_zpl_a" localSheetId="1">'Cas 3'!$B$107</definedName>
+    <definedName name="_zpl_c" localSheetId="1">'Cas 3'!$B$105</definedName>
+    <definedName name="_zs" localSheetId="1">'Cas 3'!$B$74</definedName>
     <definedName name="_zs_inf" localSheetId="0">'Cas 2'!$E$11</definedName>
     <definedName name="_zs_inf" localSheetId="1">'Cas 3'!$E$11</definedName>
   </definedNames>
@@ -161,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="218">
   <si>
     <t>h (mm)</t>
   </si>
@@ -722,20 +726,114 @@
   </si>
   <si>
     <t>Ncp (kN)</t>
+  </si>
+  <si>
+    <t>n enrobage</t>
+  </si>
+  <si>
+    <t>Calcul coefficient équivalence LT</t>
+  </si>
+  <si>
+    <t>ANE dans la dalle</t>
+  </si>
+  <si>
+    <t>ANE dans section</t>
+  </si>
+  <si>
+    <t>Hypothèse</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>de (mm)</t>
+  </si>
+  <si>
+    <t>C (mm2)</t>
+  </si>
+  <si>
+    <t>zce (mm)</t>
+  </si>
+  <si>
+    <t>zpl,a (mm)</t>
+  </si>
+  <si>
+    <t>zpl,c (mm)</t>
+  </si>
+  <si>
+    <t>Moment dalle (kN.m)</t>
+  </si>
+  <si>
+    <t>Moment semelle sup (kN.m)</t>
+  </si>
+  <si>
+    <t>Moment âme (kN.m)</t>
+  </si>
+  <si>
+    <t>Moment semelle inf (kN.m)</t>
+  </si>
+  <si>
+    <t>Moment armatures inf (kN.m)</t>
+  </si>
+  <si>
+    <t>V(G2) (kN)</t>
+  </si>
+  <si>
+    <t>M(G2) (kN.m)</t>
+  </si>
+  <si>
+    <t>V(Q1) (kN)</t>
+  </si>
+  <si>
+    <t>M(Q1) (kN.m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dimensionnement armatures transversales </t>
+  </si>
+  <si>
+    <t>ved (MPa)</t>
+  </si>
+  <si>
+    <t>DFx/Dx (kN/m)</t>
+  </si>
+  <si>
+    <t>theta (°)</t>
+  </si>
+  <si>
+    <t>ved,lim (MPa)</t>
+  </si>
+  <si>
+    <t>nu</t>
+  </si>
+  <si>
+    <t>gamma sf</t>
+  </si>
+  <si>
+    <t>Asf/sf (cm2/m)</t>
+  </si>
+  <si>
+    <t>f(G2) (mm)</t>
+  </si>
+  <si>
+    <t>f(Q1) (mm)</t>
+  </si>
+  <si>
+    <t>f (SHC) (mm)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -765,6 +863,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -780,7 +891,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -902,12 +1013,51 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -960,8 +1110,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1289,8 +1460,8 @@
         <v>60</v>
       </c>
       <c r="H2" s="23">
-        <f>2*_tc*(1+_hp*_bm/(_ep*_tc))</f>
-        <v>209.67149758454107</v>
+        <f>IF(E16="Perpendiculaire",2*_tc,FALSE)</f>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2489,8 +2660,8 @@
         <v>107</v>
       </c>
       <c r="B91" s="3">
-        <f>IF(_fck_enrobage&lt;=25,MIN(1.5*(1+(0.012*B84*100)^18+250),1500),FALSE)</f>
-        <v>376.50015233993503</v>
+        <f>IF(_fcm_enrobage&lt;=35,MIN(B81*1.5*(1+(0.012*B80)^18)+250,1500),FALSE)</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -2499,7 +2670,7 @@
       </c>
       <c r="B92" s="26">
         <f>((B88-B87)/(B91+B88-B87))^0.3</f>
-        <v>0.9938741085684526</v>
+        <v>0.97651355707570364</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2508,7 +2679,7 @@
       </c>
       <c r="B93" s="25">
         <f>B90*B92</f>
-        <v>2.3241655972350728</v>
+        <v>2.283568104876013</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -2517,7 +2688,7 @@
       </c>
       <c r="B94" s="26">
         <f>B82*(1+B83*B93)</f>
-        <v>23.728772758918403</v>
+        <v>23.430828977197017</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -2831,12 +3002,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I123"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="24"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" style="24" customWidth="1"/>
     <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
@@ -2876,8 +3047,8 @@
         <v>60</v>
       </c>
       <c r="H2" s="23">
-        <f>2*_tc*(1+_hp*_bm/(_ep*_tc))</f>
-        <v>209.67149758454107</v>
+        <f>IF(E16="Perpendiculaire",2*_tc,FALSE)</f>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2937,7 +3108,7 @@
       <c r="D5" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="3">
         <f>_Ace*100/_hw</f>
         <v>190.74786324786325</v>
       </c>
@@ -4017,493 +4188,795 @@
       <c r="A70" t="s">
         <v>183</v>
       </c>
-      <c r="B70">
-        <v>6.77</v>
+      <c r="B70" s="32">
+        <v>25.2</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>187</v>
+      </c>
+      <c r="B71" s="32">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>191</v>
+      </c>
+      <c r="B72" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="C72" s="48" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>87</v>
       </c>
-      <c r="B71">
+      <c r="B73" s="39">
         <f>_td+_h/2</f>
         <v>388.5</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="C73" s="46">
+        <f>_za</f>
+        <v>388.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>184</v>
       </c>
-      <c r="B72">
+      <c r="B74" s="39">
         <f>_td+_zs_inf</f>
         <v>562.5</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="C74" s="46">
+        <f>_zs</f>
+        <v>562.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>88</v>
+      </c>
+      <c r="B75" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="C75" s="44">
+        <f>_A*100+_As_inf*100+_beff_mi_travee*1000*_tc/_n_dalle</f>
+        <v>18591.646270893973</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>193</v>
+      </c>
+      <c r="B76" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="C76" s="45">
+        <f>_Ace*100/(B71*_hw)</f>
+        <v>7.7225855565936534</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>194</v>
+      </c>
+      <c r="B77" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="C77" s="44">
+        <f>_A*100*(_h/2-_tf)+_As_inf*100*(_zs_inf-_tf)+_beff_mi_travee*1000*_tc/_n_dalle*(_tc/2-_tf-_td)</f>
+        <v>1580410.56741363</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>195</v>
+      </c>
+      <c r="B78" s="43" t="s">
+        <v>192</v>
+      </c>
+      <c r="C78" s="44">
+        <f>C75/C76*(-1+SQRT(1+2*C77*C76/C75^2))</f>
+        <v>83.556465257011979</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
         <v>90</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B79" s="51">
         <f>(_beff_mi_travee*1000*_tc^2/(2*_n_dalle)+_A*100*_za+_As_inf*100*_zs)/(_beff_mi_travee*1000*_tc/_n_dalle+_A*100+_As_inf*100)</f>
-        <v>131.594015157716</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+        <v>239.50648863397487</v>
+      </c>
+      <c r="C79" s="52">
+        <f>_td+_tf+C78</f>
+        <v>238.05646525701198</v>
+      </c>
+      <c r="D79">
+        <f>_zel-_td</f>
+        <v>99.506488633974868</v>
+      </c>
+      <c r="E79" s="3">
+        <f>C79-_td</f>
+        <v>98.056465257011979</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>91</v>
       </c>
-      <c r="B74">
+      <c r="B80" s="39">
         <f>_tc</f>
         <v>82</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="C80" s="46">
+        <f>_tc+_td</f>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>92</v>
       </c>
-      <c r="B75">
+      <c r="B81" s="39">
         <f>_td+_tf</f>
         <v>154.5</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="C81" s="46">
+        <f>C80+_h</f>
+        <v>719</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>93</v>
       </c>
-      <c r="B76" t="b">
-        <f>IF(B74&lt;=_zel,IF(_zel&lt;=B75,TRUE,FALSE),FALSE)</f>
+      <c r="B82" s="39" t="b">
+        <f>IF(B80&lt;=_zel,IF(_zel&lt;=B81,TRUE,FALSE),FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="C82" s="39" t="b">
+        <f>IF(C80&lt;=C79,IF(C79&lt;=C81,TRUE,FALSE),FALSE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>94</v>
       </c>
-      <c r="B77" s="5">
+      <c r="B83" s="53">
         <f>(_Iy*10^4+_A*100*(_za-_zel)^2+_As_inf*100*(_zs-_zel)^2+_beff_mi_travee*1000*_tc/_n_dalle*(_tc^2/12+(_tc/2-_zel)^2))*10^(-4)</f>
-        <v>142488.53513587199</v>
-      </c>
-      <c r="C77" s="24">
-        <f>52814</f>
-        <v>52814</v>
-      </c>
-      <c r="D77">
-        <f>(B77/C77-1)*100</f>
-        <v>169.79311382563714</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+        <v>101421.8641875779</v>
+      </c>
+      <c r="C83" s="54">
+        <f>(_Iy*10^4+_A*100*(_za-C79)^2+_As_inf*100*(_zs-C79)^2+_beff_mi_travee*1000*_tc/_n_dalle*(_tc^2/12+(_tc/2-C79)^2)+(_bc-_tw)*C78^3/(3*B71))*10^(-4)</f>
+        <v>101576.61353768932</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="41"/>
+      <c r="C84" s="40"/>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="B85" s="50"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>95</v>
       </c>
-      <c r="B78" s="26">
+      <c r="B86" s="26">
         <f>210000/_Ecm_dalle</f>
         <v>6.6717909812633494</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>96</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B87" s="1">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E79" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="F79" s="22"/>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>100</v>
       </c>
-      <c r="B80" s="1">
+      <c r="B88" s="1">
         <f>50/100</f>
         <v>0.5</v>
       </c>
-      <c r="E80" s="28" t="s">
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>60</v>
+      </c>
+      <c r="B89" s="32">
+        <f>H2</f>
+        <v>164</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="E89" s="22"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90" s="25">
+        <f>IF(E6&lt;=35,1+(1-B88)/(0.1*B89^(1/3)),FALSE)</f>
+        <v>1.9134582902287138</v>
+      </c>
+      <c r="D90" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="F80" s="29">
+      <c r="E90" s="29">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>101</v>
-      </c>
-      <c r="B81" s="25">
-        <f>IF(E6&lt;=35,1+(1-B80)/(0.1*E5^(1/3)),FALSE)</f>
-        <v>1.8685939040970632</v>
-      </c>
-      <c r="E81" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="F81" s="30">
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>102</v>
       </c>
-      <c r="B82" s="25">
+      <c r="B91" s="38">
         <f>16.8/SQRT(_fcm_enrobage)</f>
         <v>2.9245046200557239</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="D91" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="E91" s="30">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>103</v>
       </c>
-      <c r="B83">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="B92" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>104</v>
       </c>
-      <c r="B84">
+      <c r="B93">
         <v>18250</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>105</v>
       </c>
-      <c r="B85" s="25">
-        <f>1/(0.1+B83^0.2)</f>
-        <v>0.42792578098028256</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="B94" s="25">
+        <f>1/(0.1+B92^0.2)</f>
+        <v>0.48844954537902541</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>106</v>
       </c>
-      <c r="B86" s="26">
-        <f>B81*B82*B85</f>
-        <v>2.3384909388400645</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="B95" s="26">
+        <f>B90*B91*B94</f>
+        <v>2.7333234126112149</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>107</v>
       </c>
-      <c r="B87" s="3">
-        <f>IF(_fck_enrobage&lt;=25,MIN(1.5*(1+(0.012*B80*100)^18+250),1500),FALSE)</f>
-        <v>376.50015233993503</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="B96" s="3">
+        <f>IF(_fcm_enrobage&lt;=35,MIN(B89*1.5*(1+(0.012*B88)^18)+250,1500),FALSE)</f>
+        <v>496</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>108</v>
       </c>
-      <c r="B88" s="26">
-        <f>((B84-B83)/(B87+B84-B83))^0.3</f>
-        <v>0.9938741085684526</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="B97" s="26">
+        <f>((B93-B92)/(B96+B93-B92))^0.3</f>
+        <v>0.99197557722517693</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>109</v>
       </c>
-      <c r="B89" s="25">
-        <f>B86*B88</f>
-        <v>2.3241655972350728</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="B98" s="25">
+        <f>B95*B97</f>
+        <v>2.7113900699681004</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
         <v>110</v>
       </c>
-      <c r="B90" s="26">
-        <f>B78*(1+B79*B89)</f>
-        <v>23.728772758918403</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="92" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="34" t="s">
+      <c r="B99" s="26">
+        <f>B86*(1+B87*B98)</f>
+        <v>26.570601578313543</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="101" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="B92" s="35"/>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A93" s="7" t="s">
+      <c r="B101" s="35"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B93" s="38">
+      <c r="B102" s="55">
         <f>_tf*_b*_fy/1000</f>
         <v>1029.5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>112</v>
       </c>
-      <c r="B94">
-        <f>_A*100*_fy/1000-2*B93</f>
+      <c r="B103">
+        <f>_A*100*_fy/1000-2*B102</f>
         <v>1537.15</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>186</v>
       </c>
-      <c r="B95">
+      <c r="B104" s="23">
         <f>_eta*0.85*_beff_mi_travee*1000*_tc*_fck_dalle/(1000*1.5)</f>
         <v>2259.5775141604267</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>119</v>
-      </c>
-      <c r="B96" s="23">
-        <f>B95/(0.85*_beff_mi_travee*1000*_fck_dalle/1000/1.5)</f>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>197</v>
+      </c>
+      <c r="B105" s="23">
+        <f>B104/(0.85*_beff_mi_travee*1000*_fck_dalle/1000/1.5)</f>
         <v>63.799835693941468</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>118</v>
+      </c>
+      <c r="B106" s="26">
+        <f>(_Na+_Ns_inf-_Ncp)/(2*_Nf)</f>
+        <v>0.71812875676338395</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>196</v>
+      </c>
+      <c r="B107" s="23">
+        <f>_td+B106*_tf</f>
+        <v>150.41286697306907</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
         <v>120</v>
       </c>
-      <c r="B97">
-        <f>_tf+_r</f>
-        <v>35.5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="B108">
+        <f>_td</f>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>121</v>
       </c>
-      <c r="B98">
-        <f>_zs_inf</f>
-        <v>422.5</v>
-      </c>
-      <c r="D98" s="3"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="B109">
+        <f>_td+_tf</f>
+        <v>154.5</v>
+      </c>
+      <c r="D109" s="3"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
         <v>93</v>
       </c>
-      <c r="B99" t="b">
-        <f>IF(B97&lt;=_zpl,IF(_zpl&lt;=B98,TRUE,FALSE),FALSE)</f>
+      <c r="B110" t="b">
+        <f>IF(B108&lt;=_zpl_a,IF(_zpl_a&lt;=B109,TRUE,FALSE),FALSE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>122</v>
-      </c>
-      <c r="B100" s="23">
-        <f>_zpl-_tf-_r</f>
-        <v>28.299835693941468</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>198</v>
+      </c>
+      <c r="B111" s="23">
+        <f>_Ncp*(_zpl_a-_zpl_c/2)/1000</f>
+        <v>267.78919498217044</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>199</v>
+      </c>
+      <c r="B112" s="3">
+        <f>(B106^2+(1-B106)^2)*_Nf*_tf/2/1000</f>
+        <v>4.4422021517425065</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>200</v>
+      </c>
+      <c r="B113" s="23">
+        <f>_Nw*(_h/2+_td-_zpl_a)/1000</f>
+        <v>365.97563653234687</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>201</v>
+      </c>
+      <c r="B114" s="3">
+        <f>_Nf*(_h-_tf/2+_td-_zpl_a)/1000</f>
+        <v>493.47757845122544</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>202</v>
+      </c>
+      <c r="B115" s="3">
+        <f>_Ns_inf*(_zs_inf+_td-_zpl_a)/1000</f>
+        <v>58.538882875936423</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>123</v>
       </c>
-      <c r="B101" s="3" t="e">
-        <f>((_Wpl_y*10^3-(_h/2-_zpl)^2*_tw)*_fy+#REF!*1000*(_zs_inf-_h/2)+0.85*B100*_bp*_fck_enrobage/1.5*(_h/2-_tf-_r-B100/2)+#REF!*1000*(_h/2-_tf-_r/2))*10^(-6)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="103" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="34" t="s">
+      <c r="B116" s="3">
+        <f>SUM(B111:B115)</f>
+        <v>1190.2234949934218</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="118" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="B103" s="35"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="B118" s="35"/>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
         <v>130</v>
       </c>
-      <c r="B104" s="26">
+      <c r="B119" s="26">
         <f>_qProfile+_qEnrobage+_qBac+_qDalle</f>
         <v>9.6760339528260868</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>132</v>
       </c>
-      <c r="B105" s="3">
-        <f>B104*_L/2</f>
+      <c r="B120" s="3">
+        <f>B119*_L/2</f>
         <v>60.475212205163039</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
         <v>131</v>
       </c>
-      <c r="B106" s="3">
-        <f>B104*_L^2/8</f>
+      <c r="B121" s="3">
+        <f>B119*_L^2/8</f>
         <v>188.98503814113451</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>203</v>
+      </c>
+      <c r="B122" s="3">
+        <f>2.5*_L/2</f>
+        <v>15.625</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>204</v>
+      </c>
+      <c r="B123" s="3">
+        <f>2.5*_L^2/8</f>
+        <v>48.828125</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>205</v>
+      </c>
+      <c r="B124" s="3">
+        <f>6.25*_L/2</f>
+        <v>39.0625</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>206</v>
+      </c>
+      <c r="B125" s="3">
+        <f>6.25*_L^2/8</f>
+        <v>122.0703125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
         <v>135</v>
       </c>
-      <c r="B107" s="3">
+      <c r="B126" s="3">
         <v>13.3</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
         <v>136</v>
       </c>
-      <c r="B108" s="3">
+      <c r="B127" s="3">
         <v>45.3</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
         <v>137</v>
       </c>
-      <c r="B109" s="3">
-        <f>B105+B107</f>
-        <v>73.775212205163044</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="B128" s="3">
+        <f>B120+B122+B124</f>
+        <v>115.16271220516305</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
         <v>138</v>
       </c>
-      <c r="B110" s="3">
-        <f t="shared" ref="B110" si="1">B106+B108</f>
-        <v>234.28503814113452</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="B129" s="3">
+        <f>B121+B123+B125</f>
+        <v>359.88347564113451</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
         <v>139</v>
       </c>
-      <c r="B111" s="3">
-        <f>1.35*B105+1.5*B107</f>
-        <v>101.59153647697011</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+      <c r="B130" s="3">
+        <f>1.35*(B120+B122)+1.5*B124</f>
+        <v>161.32903647697012</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
         <v>140</v>
       </c>
-      <c r="B112" s="3">
-        <f>1.35*B106+1.5*B108</f>
-        <v>323.07980149053162</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="114" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="34" t="s">
+      <c r="B131" s="3">
+        <f>1.35*(B121+B123)+1.5*B125</f>
+        <v>504.15323899053163</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="B114" s="35"/>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
+      <c r="B133" s="35"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>141</v>
       </c>
-      <c r="B115" s="26" t="e">
-        <f>B112/B101</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
+      <c r="B134" s="26">
+        <f>B131/B116</f>
+        <v>0.42357863133370427</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
         <v>142</v>
       </c>
-      <c r="B116" s="26">
-        <f>B111/_VplRd</f>
-        <v>9.794237441561271E-2</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
+      <c r="B135" s="26">
+        <f>B130/_VplRd</f>
+        <v>0.15553410690190103</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>149</v>
       </c>
-      <c r="B117" s="32">
+      <c r="B136" s="32">
         <v>492.5</v>
       </c>
-      <c r="C117" s="24" t="s">
+      <c r="C136" s="24" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>150</v>
       </c>
-      <c r="B118" s="26">
-        <f>B112/B117</f>
-        <v>0.65599959693508958</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
+      <c r="B137" s="26">
+        <f>B131/B136</f>
+        <v>1.0236613989655465</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>143</v>
       </c>
-      <c r="B119" s="3">
-        <f>5*B104*(_L*1000)^4/(384*210000*47199*10^(4))</f>
+      <c r="B138" s="3">
+        <f>5*B119*(_L*1000)^4/(384*210000*47199*10^(4))</f>
         <v>31.033025872841279</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>215</v>
+      </c>
+      <c r="B139" s="26">
+        <f>5*2.5*(_L*1000)^4/(384*210000*99895*10^(4))</f>
+        <v>3.7883997101966984</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>216</v>
+      </c>
+      <c r="B140" s="26">
+        <f>5*6.25*(_L*1000)^4/(384*210000*142875*10^(4))</f>
+        <v>6.6219105695555411</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
         <v>144</v>
       </c>
-      <c r="B120" s="33">
+      <c r="B141" s="33">
         <v>6.476</v>
       </c>
-      <c r="C120" s="24" t="s">
+      <c r="C141" s="24" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>217</v>
+      </c>
+      <c r="B142" s="33">
+        <f>112.5*_L^2/(8*210000*101577)*10^8</f>
+        <v>10.300727175302621</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
         <v>146</v>
       </c>
-      <c r="B121" s="3">
-        <f>B119+B120</f>
+      <c r="B143" s="3">
+        <f>B138+B141</f>
         <v>37.509025872841278</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
         <v>147</v>
       </c>
-      <c r="B122">
-        <f>B119+0.2*B120</f>
-        <v>32.32822587284128</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
+      <c r="B144">
+        <f>B138+B139+0.2*B141</f>
+        <v>36.11662558303798</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>148</v>
       </c>
-      <c r="B123">
-        <f>PI()/2*SQRT(210*52998*10/(B104*1000/9.81*_L*_L^4))</f>
-        <v>0.95514662218841706</v>
+      <c r="B145">
+        <f>PI()/2*SQRT(210*142677*10/(B119*1000/9.81*_L*_L^4))</f>
+        <v>1.5671742538677766</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="147" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="B147" s="35"/>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>209</v>
+      </c>
+      <c r="B148" s="3">
+        <f>_nr*H22/(2*_ep/1000)</f>
+        <v>180.76620113283414</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>208</v>
+      </c>
+      <c r="B149" s="26">
+        <f>B148/1000/(_tc/1000)</f>
+        <v>2.2044658674735871</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>210</v>
+      </c>
+      <c r="B150" s="33">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>212</v>
+      </c>
+      <c r="B151" s="14">
+        <f>0.6*(1-_fck_dalle/250)</f>
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>211</v>
+      </c>
+      <c r="B152" s="26">
+        <f>B151*_fck_dalle/1.5*SIN(RADIANS(B150))*COS(RADIANS(B150))</f>
+        <v>3.6405764746872631</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>213</v>
+      </c>
+      <c r="B153" s="26">
+        <f>B149/B152</f>
+        <v>0.60552659250564367</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>214</v>
+      </c>
+      <c r="B154" s="26">
+        <f>B149*_tc*TAN(RADIANS(B150))/(500/1.15)*10</f>
+        <v>2.1184145373689756</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A114:B114"/>
+  <mergeCells count="15">
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A147:B147"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="D15:E15"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="A133:B133"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16">

--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -9,17 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15300" windowHeight="4260" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15300" windowHeight="4260" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Cas 2" sheetId="1" r:id="rId1"/>
     <sheet name="Cas 3" sheetId="2" r:id="rId2"/>
+    <sheet name="Cas 5" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_A" localSheetId="0">'Cas 2'!$B$32</definedName>
     <definedName name="_A" localSheetId="1">'Cas 3'!$B$33</definedName>
+    <definedName name="_A" localSheetId="2">'Cas 5'!$B$11</definedName>
     <definedName name="_A0" localSheetId="0">'Cas 2'!$B$75</definedName>
     <definedName name="_A0" localSheetId="1">'Cas 3'!#REF!</definedName>
+    <definedName name="_Ac" localSheetId="2">'Cas 5'!$H$5</definedName>
     <definedName name="_Ace" localSheetId="0">'Cas 2'!$E$4</definedName>
     <definedName name="_Ace" localSheetId="1">'Cas 3'!$E$4</definedName>
     <definedName name="_Acr" localSheetId="0">'Cas 2'!$B$71</definedName>
@@ -28,8 +31,12 @@
     <definedName name="_As_inf" localSheetId="1">'Cas 3'!$E$10</definedName>
     <definedName name="_Av" localSheetId="0">'Cas 2'!$B$33</definedName>
     <definedName name="_Av" localSheetId="1">'Cas 3'!$B$34</definedName>
+    <definedName name="_Av" localSheetId="2">'Cas 5'!$B$12</definedName>
     <definedName name="_b" localSheetId="0">'Cas 2'!$B$4</definedName>
     <definedName name="_b" localSheetId="1">'Cas 3'!$B$15</definedName>
+    <definedName name="_b" localSheetId="2">'Cas 5'!$E$3</definedName>
+    <definedName name="_b_Droite" localSheetId="2">'Cas 5'!$B$7</definedName>
+    <definedName name="_b_Gauche" localSheetId="2">'Cas 5'!$B$6</definedName>
     <definedName name="_B0" localSheetId="0">'Cas 2'!$B$76</definedName>
     <definedName name="_B0" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_bb" localSheetId="0">'Cas 2'!$E$21</definedName>
@@ -50,8 +57,10 @@
     <definedName name="_bt" localSheetId="0">'Cas 2'!$E$20</definedName>
     <definedName name="_cf" localSheetId="0">'Cas 2'!$B$11</definedName>
     <definedName name="_cf" localSheetId="1">'Cas 3'!$B$22</definedName>
+    <definedName name="_cf" localSheetId="2">'Cas 5'!$E$12</definedName>
     <definedName name="_cw" localSheetId="0">'Cas 2'!$B$12</definedName>
     <definedName name="_cw" localSheetId="1">'Cas 3'!$B$23</definedName>
+    <definedName name="_cw" localSheetId="2">'Cas 5'!$E$13</definedName>
     <definedName name="_d" localSheetId="0">'Cas 2'!$H$13</definedName>
     <definedName name="_dsc" localSheetId="1">'Cas 3'!$H$14</definedName>
     <definedName name="_dw" localSheetId="0">'Cas 2'!$B$9</definedName>
@@ -62,6 +71,7 @@
     <definedName name="_ep" localSheetId="1">'Cas 3'!$E$19</definedName>
     <definedName name="_epsilon" localSheetId="0">'Cas 2'!$B$15</definedName>
     <definedName name="_epsilon" localSheetId="1">'Cas 3'!$B$26</definedName>
+    <definedName name="_epsilon" localSheetId="2">'Cas 5'!$E$16</definedName>
     <definedName name="_eta" localSheetId="1">'Cas 3'!$H$28</definedName>
     <definedName name="_fck_dalle" localSheetId="0">'Cas 2'!$H$5</definedName>
     <definedName name="_fck_dalle" localSheetId="1">'Cas 3'!$H$5</definedName>
@@ -76,11 +86,13 @@
     <definedName name="_fusc" localSheetId="1">'Cas 3'!$H$15</definedName>
     <definedName name="_fy" localSheetId="0">'Cas 2'!$B$14</definedName>
     <definedName name="_fy" localSheetId="1">'Cas 3'!$B$25</definedName>
+    <definedName name="_fy" localSheetId="2">'Cas 5'!$E$15</definedName>
     <definedName name="_fyd" localSheetId="0">'Cas 2'!$E$12</definedName>
     <definedName name="_fyd" localSheetId="1">'Cas 3'!$E$12</definedName>
     <definedName name="_fyp" localSheetId="0">'Cas 2'!$E$24</definedName>
     <definedName name="_h" localSheetId="0">'Cas 2'!$B$3</definedName>
     <definedName name="_h" localSheetId="1">'Cas 3'!$B$14</definedName>
+    <definedName name="_h" localSheetId="2">'Cas 5'!$E$2</definedName>
     <definedName name="_hp" localSheetId="0">'Cas 2'!$E$17</definedName>
     <definedName name="_hp" localSheetId="1">'Cas 3'!$E$17</definedName>
     <definedName name="_hpg" localSheetId="0">'Cas 2'!$E$18</definedName>
@@ -88,15 +100,22 @@
     <definedName name="_hsc" localSheetId="1">'Cas 3'!$H$13</definedName>
     <definedName name="_hw" localSheetId="0">'Cas 2'!$B$8</definedName>
     <definedName name="_hw" localSheetId="1">'Cas 3'!$B$19</definedName>
+    <definedName name="_hw" localSheetId="2">'Cas 5'!$E$9</definedName>
     <definedName name="_Iy" localSheetId="0">'Cas 2'!$B$34</definedName>
     <definedName name="_Iy" localSheetId="1">'Cas 3'!$B$35</definedName>
+    <definedName name="_Iy" localSheetId="2">'Cas 5'!$B$13</definedName>
     <definedName name="_Iz" localSheetId="0">'Cas 2'!$B$35</definedName>
+    <definedName name="_Iz" localSheetId="2">'Cas 5'!$B$14</definedName>
     <definedName name="_kr" localSheetId="0">'Cas 2'!$B$72</definedName>
     <definedName name="_kr" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_kt" localSheetId="1">'Cas 3'!$H$21</definedName>
     <definedName name="_kt_max" localSheetId="1">'Cas 3'!$H$20</definedName>
     <definedName name="_L" localSheetId="0">'Cas 2'!$B$2</definedName>
     <definedName name="_L" localSheetId="1">'Cas 3'!$B$2</definedName>
+    <definedName name="_L_ConsoleD" localSheetId="2">'Cas 5'!$B$4</definedName>
+    <definedName name="_L_ConsoleG" localSheetId="2">'Cas 5'!$B$2</definedName>
+    <definedName name="_L_tot" localSheetId="2">'Cas 5'!$B$5</definedName>
+    <definedName name="_L_Travee" localSheetId="2">'Cas 5'!$B$3</definedName>
     <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$53</definedName>
     <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$54</definedName>
     <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$55</definedName>
@@ -121,27 +140,39 @@
     <definedName name="_qProfile" localSheetId="1">'Cas 3'!$B$29</definedName>
     <definedName name="_r" localSheetId="0">'Cas 2'!$B$7</definedName>
     <definedName name="_r" localSheetId="1">'Cas 3'!$B$18</definedName>
+    <definedName name="_r" localSheetId="2">'Cas 5'!$E$8</definedName>
     <definedName name="_rho" localSheetId="0">'Cas 2'!$B$17</definedName>
     <definedName name="_rho" localSheetId="1">'Cas 3'!$B$28</definedName>
+    <definedName name="_rhoA" localSheetId="2">'Cas 5'!$E$18</definedName>
+    <definedName name="_rhoC" localSheetId="2">'Cas 5'!$H$6</definedName>
     <definedName name="_tc" localSheetId="0">'Cas 2'!$H$4</definedName>
     <definedName name="_tc" localSheetId="1">'Cas 3'!$H$4</definedName>
     <definedName name="_td" localSheetId="0">'Cas 2'!$H$3</definedName>
     <definedName name="_td" localSheetId="1">'Cas 3'!$H$3</definedName>
+    <definedName name="_td" localSheetId="2">'Cas 5'!$H$2</definedName>
     <definedName name="_tf" localSheetId="0">'Cas 2'!$B$5</definedName>
     <definedName name="_tf" localSheetId="1">'Cas 3'!$B$16</definedName>
+    <definedName name="_tf" localSheetId="2">'Cas 5'!$E$4</definedName>
+    <definedName name="_th" localSheetId="2">'Cas 5'!$H$3</definedName>
+    <definedName name="_theta" localSheetId="2">'Cas 5'!$H$4</definedName>
     <definedName name="_tp" localSheetId="0">'Cas 2'!$E$23</definedName>
     <definedName name="_tw" localSheetId="0">'Cas 2'!$B$6</definedName>
     <definedName name="_tw" localSheetId="1">'Cas 3'!$B$17</definedName>
+    <definedName name="_tw" localSheetId="2">'Cas 5'!$E$5</definedName>
     <definedName name="_VplRd" localSheetId="0">'Cas 2'!$B$52</definedName>
     <definedName name="_VplRd" localSheetId="1">'Cas 3'!$B$53</definedName>
     <definedName name="_Wel_y" localSheetId="0">'Cas 2'!$B$36</definedName>
     <definedName name="_Wel_y" localSheetId="1">'Cas 3'!$B$37</definedName>
+    <definedName name="_Wel_y" localSheetId="2">'Cas 5'!$B$15</definedName>
     <definedName name="_Wel_z" localSheetId="0">'Cas 2'!$B$37</definedName>
     <definedName name="_Wel_z" localSheetId="1">'Cas 3'!$B$38</definedName>
+    <definedName name="_Wel_z" localSheetId="2">'Cas 5'!$B$16</definedName>
     <definedName name="_Wpl_y" localSheetId="0">'Cas 2'!$B$38</definedName>
     <definedName name="_Wpl_y" localSheetId="1">'Cas 3'!$B$39</definedName>
+    <definedName name="_Wpl_y" localSheetId="2">'Cas 5'!$B$17</definedName>
     <definedName name="_Wpl_z" localSheetId="0">'Cas 2'!$B$39</definedName>
     <definedName name="_Wpl_z" localSheetId="1">'Cas 3'!$B$40</definedName>
+    <definedName name="_Wpl_z" localSheetId="2">'Cas 5'!$B$18</definedName>
     <definedName name="_za" localSheetId="0">'Cas 2'!$B$74</definedName>
     <definedName name="_za" localSheetId="1">'Cas 3'!$B$73</definedName>
     <definedName name="_zcr" localSheetId="0">'Cas 2'!$B$73</definedName>
@@ -165,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="237">
   <si>
     <t>h (mm)</t>
   </si>
@@ -819,6 +850,63 @@
   </si>
   <si>
     <t>f (SHC) (mm)</t>
+  </si>
+  <si>
+    <t>L_ConsoleG (m)</t>
+  </si>
+  <si>
+    <t>L_travée (m)</t>
+  </si>
+  <si>
+    <t>L_ConsoleD (m)</t>
+  </si>
+  <si>
+    <t>Données profil acier</t>
+  </si>
+  <si>
+    <t>L tot (m)</t>
+  </si>
+  <si>
+    <t>bGauche (m)</t>
+  </si>
+  <si>
+    <t>bDroite (m)</t>
+  </si>
+  <si>
+    <t>th (mm)</t>
+  </si>
+  <si>
+    <t>Ac (mm2)</t>
+  </si>
+  <si>
+    <t>rho c (kg/m3)</t>
+  </si>
+  <si>
+    <t>V(G) (kN)</t>
+  </si>
+  <si>
+    <t>M(G) (kN.m)</t>
+  </si>
+  <si>
+    <t>V(Q1#1) (kN)</t>
+  </si>
+  <si>
+    <t>résultats obtenus sur RDM7</t>
+  </si>
+  <si>
+    <t>M(Q1#1) (kN.m)</t>
+  </si>
+  <si>
+    <t>V(Q1#2) (kN)</t>
+  </si>
+  <si>
+    <t>M(Q1#2) (kN.m)</t>
+  </si>
+  <si>
+    <t>V(Q1#3) (kN)</t>
+  </si>
+  <si>
+    <t>M(Q1#3) (kN.m)</t>
   </si>
 </sst>
 </file>
@@ -1098,6 +1186,24 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1110,29 +1216,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1427,20 +1515,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="35"/>
+      <c r="B1" s="51"/>
       <c r="C1"/>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="35"/>
+      <c r="E1" s="51"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -1702,10 +1790,10 @@
         <v>0.81361651346682706</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="35"/>
+      <c r="E15" s="51"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
@@ -1844,10 +1932,10 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="34" t="s">
+      <c r="A30" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="35"/>
+      <c r="B30" s="51"/>
       <c r="C30" s="24" t="s">
         <v>53</v>
       </c>
@@ -2115,10 +2203,10 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="34" t="s">
+      <c r="A50" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="35"/>
+      <c r="B50" s="51"/>
       <c r="D50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2155,10 +2243,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E52" s="36" t="s">
+      <c r="E52" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F52" s="37"/>
+      <c r="F52" s="53"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -2406,10 +2494,10 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="34" t="s">
+      <c r="A68" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="B68" s="35"/>
+      <c r="B68" s="51"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -2693,10 +2781,10 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="34" t="s">
+      <c r="A96" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="B96" s="35"/>
+      <c r="B96" s="51"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -2800,10 +2888,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="34" t="s">
+      <c r="A109" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="B109" s="35"/>
+      <c r="B109" s="51"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -2886,10 +2974,10 @@
     </row>
     <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="34" t="s">
+      <c r="A120" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="B120" s="35"/>
+      <c r="B120" s="51"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
@@ -3014,20 +3102,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="35"/>
+      <c r="B1" s="51"/>
       <c r="C1"/>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="35"/>
+      <c r="E1" s="51"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="35"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -3262,16 +3350,16 @@
         <f>500/1.15</f>
         <v>434.78260869565219</v>
       </c>
-      <c r="G12" s="34" t="s">
+      <c r="G12" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="51"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="35"/>
+      <c r="B13" s="51"/>
       <c r="C13"/>
       <c r="D13" t="s">
         <v>125</v>
@@ -3310,10 +3398,10 @@
         <v>200</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="35"/>
+      <c r="E15" s="51"/>
       <c r="G15" t="s">
         <v>166</v>
       </c>
@@ -3617,10 +3705,10 @@
       <c r="C30"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="34" t="s">
+      <c r="A31" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="51"/>
       <c r="C31" s="24" t="s">
         <v>53</v>
       </c>
@@ -3888,10 +3976,10 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="34" t="s">
+      <c r="A51" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="35"/>
+      <c r="B51" s="51"/>
       <c r="D51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3928,10 +4016,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E53" s="36" t="s">
+      <c r="E53" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="37"/>
+      <c r="F53" s="53"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -4179,10 +4267,10 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="34" t="s">
+      <c r="A69" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="35"/>
+      <c r="B69" s="51"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -4204,10 +4292,10 @@
       <c r="A72" t="s">
         <v>191</v>
       </c>
-      <c r="B72" s="47" t="s">
+      <c r="B72" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="C72" s="48" t="s">
+      <c r="C72" s="44" t="s">
         <v>190</v>
       </c>
     </row>
@@ -4215,11 +4303,11 @@
       <c r="A73" t="s">
         <v>87</v>
       </c>
-      <c r="B73" s="39">
+      <c r="B73" s="35">
         <f>_td+_h/2</f>
         <v>388.5</v>
       </c>
-      <c r="C73" s="46">
+      <c r="C73" s="42">
         <f>_za</f>
         <v>388.5</v>
       </c>
@@ -4228,11 +4316,11 @@
       <c r="A74" t="s">
         <v>184</v>
       </c>
-      <c r="B74" s="39">
+      <c r="B74" s="35">
         <f>_td+_zs_inf</f>
         <v>562.5</v>
       </c>
-      <c r="C74" s="46">
+      <c r="C74" s="42">
         <f>_zs</f>
         <v>562.5</v>
       </c>
@@ -4241,10 +4329,10 @@
       <c r="A75" t="s">
         <v>88</v>
       </c>
-      <c r="B75" s="42" t="s">
+      <c r="B75" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="C75" s="44">
+      <c r="C75" s="40">
         <f>_A*100+_As_inf*100+_beff_mi_travee*1000*_tc/_n_dalle</f>
         <v>18591.646270893973</v>
       </c>
@@ -4253,10 +4341,10 @@
       <c r="A76" t="s">
         <v>193</v>
       </c>
-      <c r="B76" s="42" t="s">
+      <c r="B76" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="C76" s="45">
+      <c r="C76" s="41">
         <f>_Ace*100/(B71*_hw)</f>
         <v>7.7225855565936534</v>
       </c>
@@ -4265,10 +4353,10 @@
       <c r="A77" t="s">
         <v>194</v>
       </c>
-      <c r="B77" s="42" t="s">
+      <c r="B77" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="C77" s="44">
+      <c r="C77" s="40">
         <f>_A*100*(_h/2-_tf)+_As_inf*100*(_zs_inf-_tf)+_beff_mi_travee*1000*_tc/_n_dalle*(_tc/2-_tf-_td)</f>
         <v>1580410.56741363</v>
       </c>
@@ -4277,10 +4365,10 @@
       <c r="A78" t="s">
         <v>195</v>
       </c>
-      <c r="B78" s="43" t="s">
+      <c r="B78" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="C78" s="44">
+      <c r="C78" s="40">
         <f>C75/C76*(-1+SQRT(1+2*C77*C76/C75^2))</f>
         <v>83.556465257011979</v>
       </c>
@@ -4289,11 +4377,11 @@
       <c r="A79" t="s">
         <v>90</v>
       </c>
-      <c r="B79" s="51">
+      <c r="B79" s="45">
         <f>(_beff_mi_travee*1000*_tc^2/(2*_n_dalle)+_A*100*_za+_As_inf*100*_zs)/(_beff_mi_travee*1000*_tc/_n_dalle+_A*100+_As_inf*100)</f>
         <v>239.50648863397487</v>
       </c>
-      <c r="C79" s="52">
+      <c r="C79" s="46">
         <f>_td+_tf+C78</f>
         <v>238.05646525701198</v>
       </c>
@@ -4310,11 +4398,11 @@
       <c r="A80" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="39">
+      <c r="B80" s="35">
         <f>_tc</f>
         <v>82</v>
       </c>
-      <c r="C80" s="46">
+      <c r="C80" s="42">
         <f>_tc+_td</f>
         <v>222</v>
       </c>
@@ -4323,11 +4411,11 @@
       <c r="A81" t="s">
         <v>92</v>
       </c>
-      <c r="B81" s="39">
+      <c r="B81" s="35">
         <f>_td+_tf</f>
         <v>154.5</v>
       </c>
-      <c r="C81" s="46">
+      <c r="C81" s="42">
         <f>C80+_h</f>
         <v>719</v>
       </c>
@@ -4336,11 +4424,11 @@
       <c r="A82" t="s">
         <v>93</v>
       </c>
-      <c r="B82" s="39" t="b">
+      <c r="B82" s="35" t="b">
         <f>IF(B80&lt;=_zel,IF(_zel&lt;=B81,TRUE,FALSE),FALSE)</f>
         <v>0</v>
       </c>
-      <c r="C82" s="39" t="b">
+      <c r="C82" s="35" t="b">
         <f>IF(C80&lt;=C79,IF(C79&lt;=C81,TRUE,FALSE),FALSE)</f>
         <v>1</v>
       </c>
@@ -4349,24 +4437,24 @@
       <c r="A83" t="s">
         <v>94</v>
       </c>
-      <c r="B83" s="53">
+      <c r="B83" s="47">
         <f>(_Iy*10^4+_A*100*(_za-_zel)^2+_As_inf*100*(_zs-_zel)^2+_beff_mi_travee*1000*_tc/_n_dalle*(_tc^2/12+(_tc/2-_zel)^2))*10^(-4)</f>
         <v>101421.8641875779</v>
       </c>
-      <c r="C83" s="54">
+      <c r="C83" s="48">
         <f>(_Iy*10^4+_A*100*(_za-C79)^2+_As_inf*100*(_zs-C79)^2+_beff_mi_travee*1000*_tc/_n_dalle*(_tc^2/12+(_tc/2-C79)^2)+(_bc-_tw)*C78^3/(3*B71))*10^(-4)</f>
         <v>101576.61353768932</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="41"/>
-      <c r="C84" s="40"/>
+      <c r="B84" s="37"/>
+      <c r="C84" s="36"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="49" t="s">
+      <c r="A85" s="54" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="50"/>
+      <c r="B85" s="55"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -4426,7 +4514,7 @@
       <c r="A91" t="s">
         <v>102</v>
       </c>
-      <c r="B91" s="38">
+      <c r="B91" s="34">
         <f>16.8/SQRT(_fcm_enrobage)</f>
         <v>2.9245046200557239</v>
       </c>
@@ -4509,16 +4597,16 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="34" t="s">
+      <c r="A101" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="B101" s="35"/>
+      <c r="B101" s="51"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B102" s="55">
+      <c r="B102" s="49">
         <f>_tf*_b*_fy/1000</f>
         <v>1029.5</v>
       </c>
@@ -4652,10 +4740,10 @@
     </row>
     <row r="117" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="118" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="34" t="s">
+      <c r="A118" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="B118" s="35"/>
+      <c r="B118" s="51"/>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
@@ -4774,10 +4862,10 @@
     </row>
     <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="34" t="s">
+      <c r="A133" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="B133" s="35"/>
+      <c r="B133" s="51"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
@@ -4893,10 +4981,10 @@
     </row>
     <row r="146" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="147" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="34" t="s">
+      <c r="A147" s="50" t="s">
         <v>207</v>
       </c>
-      <c r="B147" s="35"/>
+      <c r="B147" s="51"/>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
@@ -4962,16 +5050,16 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D15:E15"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="A147:B147"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D15:E15"/>
     <mergeCell ref="E53:F53"/>
     <mergeCell ref="A69:B69"/>
     <mergeCell ref="A101:B101"/>
@@ -4986,4 +5074,628 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="D1" s="50" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" s="51"/>
+      <c r="G1" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="51"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="10">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>497</v>
+      </c>
+      <c r="G2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" s="1">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1">
+        <v>200</v>
+      </c>
+      <c r="G3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>210</v>
+      </c>
+      <c r="H4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="1">
+        <f>_L_ConsoleG+_L_Travee+_L_ConsoleD</f>
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H5" s="23">
+        <f>(_b_Gauche+_b_Droite)*1000/2*_td+_th*_b+_th^2*TAN(RADIANS(_theta))</f>
+        <v>248923.76043070341</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="G6" t="s">
+        <v>227</v>
+      </c>
+      <c r="H6">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="G7" t="s">
+        <v>129</v>
+      </c>
+      <c r="H7" s="25">
+        <f>_rhoC*_Ac*10^(-6)*9.81/1000</f>
+        <v>6.1048552245630008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="51"/>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="6">
+        <f>_h-2*_tf</f>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="8">
+        <v>174.11468914507714</v>
+      </c>
+      <c r="D10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="6">
+        <f>_hw-2*_r</f>
+        <v>426</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4">
+        <v>101.3</v>
+      </c>
+      <c r="E11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5">
+        <v>50.607999999999997</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="6">
+        <f>(_b-2*_r-_tw)/2</f>
+        <v>74.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4">
+        <v>43014.311000000002</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="6">
+        <f>_hw-2*_r</f>
+        <v>426</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1939.511</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1730.9581891348089</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="5">
+        <v>193.9511</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="14">
+        <f>SQRT(235/_fy)</f>
+        <v>0.81361651346682706</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1949.546</v>
+      </c>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4">
+        <v>301.74400000000003</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="1">
+        <v>7850</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="31">
+        <f>_rhoA*_A*10^(-4)*9.81/1000</f>
+        <v>0.78009610500000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="9">
+        <f>_rhoA*_A/10000</f>
+        <v>79.520499999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="9">
+        <f>B20*_L_tot</f>
+        <v>1272.328</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="9"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="11">
+        <f>B10*_L_tot*100</f>
+        <v>278583.50263212342</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="11">
+        <f>(B10-_b/10)*_L_tot*100</f>
+        <v>246583.50263212342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="9"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="9">
+        <f>B10/_A*100</f>
+        <v>171.88024594775629</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="9">
+        <f>(B10-_b/10)/_A*100</f>
+        <v>152.13690932386689</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="51"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="23">
+        <f>_A*100*_fy/1000</f>
+        <v>3596.15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="23">
+        <f>_Av*100*_fy/(1000*SQRT(3))</f>
+        <v>1037.2582560217745</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="53"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="23">
+        <f>_Wel_y*1000*_fy*10^(-6)</f>
+        <v>614.49015714285713</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="17">
+        <f>9*_epsilon</f>
+        <v>7.3225486212014435</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>19</v>
+      </c>
+      <c r="B33" s="23">
+        <f>_Wel_z*1000*_fy*10^(-6)</f>
+        <v>68.852640499999993</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="17">
+        <f>10*_epsilon</f>
+        <v>8.1361651346682713</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="23">
+        <f>_Wpl_y*1000*_fy*10^(-6)</f>
+        <v>692.08882999999992</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="18">
+        <f>14*_epsilon</f>
+        <v>11.390631188535579</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" s="23">
+        <f>_Wpl_z*1000*_fy*10^(-6)</f>
+        <v>107.11912</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D36" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="22"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3">
+        <f>_cf/_tf</f>
+        <v>5.1586206896551721</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="19">
+        <f>33*_epsilon</f>
+        <v>26.849344944405292</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3">
+        <f>_cw/_tw</f>
+        <v>50.714285714285715</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="19">
+        <f>38*_epsilon</f>
+        <v>30.917427511739429</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D39" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E39" s="20">
+        <f>42*_epsilon</f>
+        <v>34.171893565606737</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40">
+        <f>IF(B37&lt;=E32,1,IF(B37&lt;=E33,2,IF(B37&lt;=E34,3,4)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41">
+        <f>IF(B38&lt;=E37,1,IF(B38&lt;=E38,2,IF(B38&lt;=E39,3,4)))</f>
+        <v>4</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="22"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42">
+        <f>IF(B38&lt;=E42,1,IF(B38&lt;=E43,2,IF(B38&lt;=E44,3,4)))</f>
+        <v>1</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="19">
+        <f>72*_epsilon</f>
+        <v>58.580388969611548</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D43" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="19">
+        <f>83*_epsilon</f>
+        <v>67.530170617746649</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="3">
+        <f>_hw/_tw</f>
+        <v>55.714285714285715</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" s="20">
+        <f>124*_epsilon</f>
+        <v>100.88844766988656</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="3">
+        <f>124*_epsilon</f>
+        <v>100.88844766988656</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="51"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="25">
+        <f>H7+E19</f>
+        <v>6.8849513295630009</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>228</v>
+      </c>
+      <c r="B49" s="3">
+        <f>B48*(_L_ConsoleG+_L_Travee/2)</f>
+        <v>55.079610636504007</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>229</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>236</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A29:B29"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -118,6 +118,7 @@
     <definedName name="_L_Travee" localSheetId="2">'Cas 5'!$B$3</definedName>
     <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$53</definedName>
     <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$54</definedName>
+    <definedName name="_Mpl_Rd" localSheetId="2">'Cas 5'!$B$69</definedName>
     <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$55</definedName>
     <definedName name="_Mpl_z_Rd" localSheetId="0">'Cas 2'!$B$56</definedName>
     <definedName name="_n" localSheetId="0">'Cas 2'!$B$69</definedName>
@@ -161,6 +162,7 @@
     <definedName name="_tw" localSheetId="2">'Cas 5'!$E$5</definedName>
     <definedName name="_VplRd" localSheetId="0">'Cas 2'!$B$52</definedName>
     <definedName name="_VplRd" localSheetId="1">'Cas 3'!$B$53</definedName>
+    <definedName name="_VplRd" localSheetId="2">'Cas 5'!$B$52</definedName>
     <definedName name="_Wel_y" localSheetId="0">'Cas 2'!$B$36</definedName>
     <definedName name="_Wel_y" localSheetId="1">'Cas 3'!$B$37</definedName>
     <definedName name="_Wel_y" localSheetId="2">'Cas 5'!$B$15</definedName>
@@ -196,7 +198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="257">
   <si>
     <t>h (mm)</t>
   </si>
@@ -894,9 +896,6 @@
     <t>résultats obtenus sur RDM7</t>
   </si>
   <si>
-    <t>M(Q1#1) (kN.m)</t>
-  </si>
-  <si>
     <t>V(Q1#2) (kN)</t>
   </si>
   <si>
@@ -907,19 +906,83 @@
   </si>
   <si>
     <t>M(Q1#3) (kN.m)</t>
+  </si>
+  <si>
+    <t>55,08/-30,98</t>
+  </si>
+  <si>
+    <t>V ELU 1 (kN)</t>
+  </si>
+  <si>
+    <t>V ELU 2 (kN)</t>
+  </si>
+  <si>
+    <t>V ELU 3 (kN)</t>
+  </si>
+  <si>
+    <t>M(Q1#1)+ (kN.m)</t>
+  </si>
+  <si>
+    <t>M(Q1#1)- (kN.m)</t>
+  </si>
+  <si>
+    <t>M ELU 1 + (kN.m)</t>
+  </si>
+  <si>
+    <t>M ELU 1 - (kN.m)</t>
+  </si>
+  <si>
+    <t>M ELU 2 + (kN.m)</t>
+  </si>
+  <si>
+    <t>M ELU 2 - (kN.m)</t>
+  </si>
+  <si>
+    <t>M ELU 3 + (kN.m)</t>
+  </si>
+  <si>
+    <t>M ELU 3 - (kN.m)</t>
+  </si>
+  <si>
+    <t>Vpl,Rd (kN)</t>
+  </si>
+  <si>
+    <t>ELU1</t>
+  </si>
+  <si>
+    <t>ELU2</t>
+  </si>
+  <si>
+    <t>ELU3</t>
+  </si>
+  <si>
+    <t>lambda</t>
+  </si>
+  <si>
+    <t>phi</t>
+  </si>
+  <si>
+    <t>khi</t>
+  </si>
+  <si>
+    <t>alpha ult</t>
+  </si>
+  <si>
+    <t>alpha cr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -979,7 +1042,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1140,12 +1203,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1222,6 +1305,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -5050,11 +5148,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D15:E15"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="G12:H12"/>
@@ -5065,6 +5158,11 @@
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A118:B118"/>
     <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D15:E15"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16">
@@ -5078,7 +5176,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
@@ -5111,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="1">
-        <v>497</v>
+        <v>450</v>
       </c>
       <c r="G2" t="s">
         <v>77</v>
@@ -5131,7 +5229,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="1">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="G3" t="s">
         <v>225</v>
@@ -5151,7 +5249,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="1">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="G4" t="s">
         <v>210</v>
@@ -5172,14 +5270,14 @@
         <v>3</v>
       </c>
       <c r="E5" s="1">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="G5" t="s">
         <v>226</v>
       </c>
       <c r="H5" s="23">
         <f>(_b_Gauche+_b_Droite)*1000/2*_td+_th*_b+_th^2*TAN(RADIANS(_theta))</f>
-        <v>248923.76043070341</v>
+        <v>248523.76043070341</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -5210,7 +5308,7 @@
       </c>
       <c r="H7" s="25">
         <f>_rhoC*_Ac*10^(-6)*9.81/1000</f>
-        <v>6.1048552245630008</v>
+        <v>6.0950452245630009</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5231,7 +5329,7 @@
       </c>
       <c r="E9" s="6">
         <f>_h-2*_tf</f>
-        <v>468</v>
+        <v>420.8</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -5239,22 +5337,24 @@
         <v>24</v>
       </c>
       <c r="B10" s="8">
-        <v>174.11468914507714</v>
+        <f>(2*(_h-2*_r)+2*_b+2*(_b-2*_r-_tw)+2*PI()*_r)/10</f>
+        <v>160.51468914507714</v>
       </c>
       <c r="D10" t="s">
         <v>113</v>
       </c>
       <c r="E10" s="6">
         <f>_hw-2*_r</f>
-        <v>426</v>
+        <v>378.8</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="4">
-        <v>101.3</v>
+      <c r="B11" s="9">
+        <f>(2*_b*_tf+(_h-2*_tf)*_tw+4*(1-PI()/4)*_r^2)/100</f>
+        <v>98.820776397669022</v>
       </c>
       <c r="E11" s="6"/>
     </row>
@@ -5262,15 +5362,16 @@
       <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="5">
-        <v>50.607999999999997</v>
+      <c r="B12" s="70">
+        <f>((_h-2*_tf)*_tw+4*(1-PI()/4)*_r^2+_tf*(_tw+2*_r))/100</f>
+        <v>50.845176397669007</v>
       </c>
       <c r="D12" t="s">
         <v>37</v>
       </c>
       <c r="E12" s="6">
         <f>(_b-2*_r-_tw)/2</f>
-        <v>74.8</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -5278,14 +5379,14 @@
         <v>9</v>
       </c>
       <c r="B13" s="4">
-        <v>43014.311000000002</v>
+        <v>33740</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
       </c>
       <c r="E13" s="6">
         <f>_hw-2*_r</f>
-        <v>426</v>
+        <v>378.8</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -5293,7 +5394,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="4">
-        <v>1939.511</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -5301,7 +5402,8 @@
         <v>12</v>
       </c>
       <c r="B15" s="5">
-        <v>1730.9581891348089</v>
+        <f>_Iy/(_h/10/2)</f>
+        <v>1499.5555555555557</v>
       </c>
       <c r="D15" t="s">
         <v>8</v>
@@ -5315,7 +5417,8 @@
         <v>13</v>
       </c>
       <c r="B16" s="5">
-        <v>193.9511</v>
+        <f>_Iz/(_b/10/2)</f>
+        <v>176.31578947368422</v>
       </c>
       <c r="D16" t="s">
         <v>33</v>
@@ -5330,7 +5433,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="4">
-        <v>1949.546</v>
+        <v>1701</v>
       </c>
       <c r="E17" s="6"/>
     </row>
@@ -5339,7 +5442,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="4">
-        <v>301.74400000000003</v>
+        <v>276.3</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
@@ -5354,7 +5457,7 @@
       </c>
       <c r="E19" s="31">
         <f>_rhoA*_A*10^(-4)*9.81/1000</f>
-        <v>0.78009610500000004</v>
+        <v>0.76100397592198954</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -5363,7 +5466,7 @@
       </c>
       <c r="B20" s="9">
         <f>_rhoA*_A/10000</f>
-        <v>79.520499999999998</v>
+        <v>77.574309472170185</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -5372,7 +5475,7 @@
       </c>
       <c r="B21" s="9">
         <f>B20*_L_tot</f>
-        <v>1272.328</v>
+        <v>1241.188951554723</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5384,7 +5487,7 @@
       </c>
       <c r="B23" s="11">
         <f>B10*_L_tot*100</f>
-        <v>278583.50263212342</v>
+        <v>256823.50263212342</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -5393,7 +5496,7 @@
       </c>
       <c r="B24" s="11">
         <f>(B10-_b/10)*_L_tot*100</f>
-        <v>246583.50263212342</v>
+        <v>226423.50263212342</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -5405,7 +5508,7 @@
       </c>
       <c r="B26" s="9">
         <f>B10/_A*100</f>
-        <v>171.88024594775629</v>
+        <v>162.43010326000976</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -5414,7 +5517,7 @@
       </c>
       <c r="B27" s="9">
         <f>(B10-_b/10)/_A*100</f>
-        <v>152.13690932386689</v>
+        <v>143.20337716797698</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -5430,7 +5533,7 @@
       </c>
       <c r="B30" s="23">
         <f>_A*100*_fy/1000</f>
-        <v>3596.15</v>
+        <v>3508.1375621172501</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -5439,7 +5542,7 @@
       </c>
       <c r="B31" s="23">
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
-        <v>1037.2582560217745</v>
+        <v>1042.1194079466816</v>
       </c>
       <c r="D31" s="52" t="s">
         <v>34</v>
@@ -5452,7 +5555,7 @@
       </c>
       <c r="B32" s="23">
         <f>_Wel_y*1000*_fy*10^(-6)</f>
-        <v>614.49015714285713</v>
+        <v>532.34222222222229</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>41</v>
@@ -5468,7 +5571,7 @@
       </c>
       <c r="B33" s="23">
         <f>_Wel_z*1000*_fy*10^(-6)</f>
-        <v>68.852640499999993</v>
+        <v>62.592105263157897</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>42</v>
@@ -5484,7 +5587,7 @@
       </c>
       <c r="B34" s="23">
         <f>_Wpl_y*1000*_fy*10^(-6)</f>
-        <v>692.08882999999992</v>
+        <v>603.85500000000002</v>
       </c>
       <c r="D34" s="16" t="s">
         <v>43</v>
@@ -5500,7 +5603,7 @@
       </c>
       <c r="B35" s="23">
         <f>_Wpl_z*1000*_fy*10^(-6)</f>
-        <v>107.11912</v>
+        <v>98.086500000000001</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -5515,7 +5618,7 @@
       </c>
       <c r="B37" s="3">
         <f>_cf/_tf</f>
-        <v>5.1586206896551721</v>
+        <v>4.7465753424657535</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>45</v>
@@ -5531,7 +5634,7 @@
       </c>
       <c r="B38" s="3">
         <f>_cw/_tw</f>
-        <v>50.714285714285715</v>
+        <v>40.297872340425535</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>46</v>
@@ -5603,7 +5706,7 @@
       </c>
       <c r="B44" s="3">
         <f>_hw/_tw</f>
-        <v>55.714285714285715</v>
+        <v>44.765957446808507</v>
       </c>
       <c r="D44" s="16" t="s">
         <v>51</v>
@@ -5635,67 +5738,372 @@
       </c>
       <c r="B48" s="25">
         <f>H7+E19</f>
-        <v>6.8849513295630009</v>
+        <v>6.8560492004849909</v>
+      </c>
+      <c r="C48" s="26">
+        <f>B48*1.35</f>
+        <v>9.2556664206547374</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="A49" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="B49" s="3">
-        <f>B48*(_L_ConsoleG+_L_Travee/2)</f>
-        <v>55.079610636504007</v>
+      <c r="B49" s="59">
+        <v>34.424999999999997</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="A50" s="16" t="s">
         <v>229</v>
+      </c>
+      <c r="B50" s="58" t="s">
+        <v>236</v>
       </c>
       <c r="D50" s="24" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+      <c r="A51" s="28" t="s">
         <v>230</v>
       </c>
+      <c r="B51" s="56">
+        <v>13.47</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="A52" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="B52" s="57">
+        <v>14.74</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="B53" s="57">
+        <v>-19.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="15" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="B54" s="57">
+        <v>11.67</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="15" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="B55" s="57">
+        <v>25.17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="15" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B56" s="57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="16" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>236</v>
+      <c r="B57" s="58">
+        <v>-19.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="B58" s="56">
+        <v>66.650000000000006</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="B59" s="57">
+        <v>96.16</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B60" s="57">
+        <v>-71.05</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B61" s="57">
+        <v>63.95</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="B62" s="57">
+        <v>111.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B63" s="57">
+        <v>-41.81</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="B64" s="57">
+        <v>49.15</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="60" t="s">
+        <v>246</v>
+      </c>
+      <c r="B65" s="57">
+        <v>58.96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B66" s="58">
+        <v>-71.06</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="B68" s="51"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>123</v>
+      </c>
+      <c r="B69" s="23">
+        <f>_Wpl_y*1000*_fy*10^(-6)</f>
+        <v>603.85500000000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>248</v>
+      </c>
+      <c r="B70" s="23">
+        <f>_Av*100*_fy/(1000*SQRT(3))</f>
+        <v>1042.1194079466816</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B71" s="23"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="21"/>
+      <c r="B72" s="68" t="s">
+        <v>249</v>
+      </c>
+      <c r="C72" s="69" t="s">
+        <v>250</v>
+      </c>
+      <c r="D72" s="22" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B73" s="65">
+        <f>MAX(B59,ABS(B60))/_Mpl_Rd</f>
+        <v>0.15924352700565533</v>
+      </c>
+      <c r="C73" s="61">
+        <f>MAX(B62,ABS(B63))/_Mpl_Rd</f>
+        <v>0.18530938718732146</v>
+      </c>
+      <c r="D73" s="17">
+        <f>MAX(B65,ABS(B66))/_Mpl_Rd</f>
+        <v>0.11767725695738215</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B74" s="65">
+        <f>B58/B70</f>
+        <v>6.3956202611486199E-2</v>
+      </c>
+      <c r="C74" s="61">
+        <f>B61/B70</f>
+        <v>6.1365328687239942E-2</v>
+      </c>
+      <c r="D74" s="17">
+        <f>B64/B70</f>
+        <v>4.7163501250630853E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B75" s="66">
+        <f>1/B73</f>
+        <v>6.2796900998336103</v>
+      </c>
+      <c r="C75" s="62">
+        <f t="shared" ref="C75:D75" si="0">1/C73</f>
+        <v>5.3963806970509385</v>
+      </c>
+      <c r="D75" s="63">
+        <f t="shared" si="0"/>
+        <v>8.4978187447227693</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B76" s="66">
+        <v>5.4870000000000001</v>
+      </c>
+      <c r="C76" s="62"/>
+      <c r="D76" s="63"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B77" s="65">
+        <f>SQRT(B75/B76)</f>
+        <v>1.0697976163788039</v>
+      </c>
+      <c r="C77" s="61">
+        <f>SQRT(_Mpl_Rd/C75)</f>
+        <v>10.578279633286312</v>
+      </c>
+      <c r="D77" s="17">
+        <f>SQRT(_Mpl_Rd/D75)</f>
+        <v>8.4297093662830402</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B78" s="66">
+        <v>0.21</v>
+      </c>
+      <c r="C78" s="62">
+        <v>1.21</v>
+      </c>
+      <c r="D78" s="63">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B79" s="65">
+        <f>0.5*(1+B78*(B77-0.2)+B77^2)</f>
+        <v>1.1635622197246596</v>
+      </c>
+      <c r="C79" s="61">
+        <f t="shared" ref="C79:D79" si="1">0.5*(1+C78*(C77-0.2)+C77^2)</f>
+        <v>62.728859178138222</v>
+      </c>
+      <c r="D79" s="17">
+        <f t="shared" si="1"/>
+        <v>45.123828849742765</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B80" s="65">
+        <f>1/(B79+SQRT(B79^2-B77^2))</f>
+        <v>0.61683628663191403</v>
+      </c>
+      <c r="C80" s="61">
+        <f t="shared" ref="C80:D80" si="2">1/(C79+SQRT(C79^2-C77^2))</f>
+        <v>8.0283012749364502E-3</v>
+      </c>
+      <c r="D80" s="17">
+        <f t="shared" si="2"/>
+        <v>1.1179020366719835E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B81" s="66">
+        <f>B80*_Mpl_Rd</f>
+        <v>372.47967586411448</v>
+      </c>
+      <c r="C81" s="62">
+        <f>C80*_Mpl_Rd</f>
+        <v>4.8479298663767505</v>
+      </c>
+      <c r="D81" s="63">
+        <f>D80*_Mpl_Rd</f>
+        <v>6.750507343545606</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B82" s="67">
+        <f>B73/B80</f>
+        <v>0.25816173668246117</v>
+      </c>
+      <c r="C82" s="64">
+        <f t="shared" ref="C82:D82" si="3">C73/C80</f>
+        <v>23.082017084465768</v>
+      </c>
+      <c r="D82" s="18">
+        <f t="shared" si="3"/>
+        <v>10.526616205809024</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -198,7 +198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="258">
   <si>
     <t>h (mm)</t>
   </si>
@@ -969,6 +969,9 @@
   </si>
   <si>
     <t>alpha cr</t>
+  </si>
+  <si>
+    <t>Mcr (kN.m)</t>
   </si>
 </sst>
 </file>
@@ -982,7 +985,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1042,7 +1045,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1223,12 +1226,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1287,6 +1299,21 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1305,21 +1332,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -1613,20 +1630,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="51"/>
+      <c r="B1" s="66"/>
       <c r="C1"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="51"/>
+      <c r="E1" s="66"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="51"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -1888,10 +1905,10 @@
         <v>0.81361651346682706</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="51"/>
+      <c r="E15" s="66"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
@@ -2030,10 +2047,10 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="50" t="s">
+      <c r="A30" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="51"/>
+      <c r="B30" s="66"/>
       <c r="C30" s="24" t="s">
         <v>53</v>
       </c>
@@ -2301,10 +2318,10 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="50" t="s">
+      <c r="A50" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="51"/>
+      <c r="B50" s="66"/>
       <c r="D50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2341,10 +2358,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E52" s="52" t="s">
+      <c r="E52" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="F52" s="53"/>
+      <c r="F52" s="68"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -2592,10 +2609,10 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="50" t="s">
+      <c r="A68" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="B68" s="51"/>
+      <c r="B68" s="66"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -2879,10 +2896,10 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="50" t="s">
+      <c r="A96" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="B96" s="51"/>
+      <c r="B96" s="66"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -2986,10 +3003,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="50" t="s">
+      <c r="A109" s="65" t="s">
         <v>133</v>
       </c>
-      <c r="B109" s="51"/>
+      <c r="B109" s="66"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -3072,10 +3089,10 @@
     </row>
     <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="50" t="s">
+      <c r="A120" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="B120" s="51"/>
+      <c r="B120" s="66"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
@@ -3200,20 +3217,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="51"/>
+      <c r="B1" s="66"/>
       <c r="C1"/>
-      <c r="D1" s="50" t="s">
+      <c r="D1" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="51"/>
+      <c r="E1" s="66"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="51"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -3448,16 +3465,16 @@
         <f>500/1.15</f>
         <v>434.78260869565219</v>
       </c>
-      <c r="G12" s="50" t="s">
+      <c r="G12" s="65" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="51"/>
+      <c r="H12" s="66"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="50" t="s">
+      <c r="A13" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="51"/>
+      <c r="B13" s="66"/>
       <c r="C13"/>
       <c r="D13" t="s">
         <v>125</v>
@@ -3496,10 +3513,10 @@
         <v>200</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="51"/>
+      <c r="E15" s="66"/>
       <c r="G15" t="s">
         <v>166</v>
       </c>
@@ -3803,10 +3820,10 @@
       <c r="C30"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="51"/>
+      <c r="B31" s="66"/>
       <c r="C31" s="24" t="s">
         <v>53</v>
       </c>
@@ -4074,10 +4091,10 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="50" t="s">
+      <c r="A51" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="51"/>
+      <c r="B51" s="66"/>
       <c r="D51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4114,10 +4131,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E53" s="52" t="s">
+      <c r="E53" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="53"/>
+      <c r="F53" s="68"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -4365,10 +4382,10 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="50" t="s">
+      <c r="A69" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="51"/>
+      <c r="B69" s="66"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -4549,10 +4566,10 @@
       <c r="C84" s="36"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="54" t="s">
+      <c r="A85" s="69" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="55"/>
+      <c r="B85" s="70"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -4695,10 +4712,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="50" t="s">
+      <c r="A101" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="B101" s="51"/>
+      <c r="B101" s="66"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
@@ -4838,10 +4855,10 @@
     </row>
     <row r="117" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="118" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="50" t="s">
+      <c r="A118" s="65" t="s">
         <v>133</v>
       </c>
-      <c r="B118" s="51"/>
+      <c r="B118" s="66"/>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
@@ -4960,10 +4977,10 @@
     </row>
     <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="50" t="s">
+      <c r="A133" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="B133" s="51"/>
+      <c r="B133" s="66"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
@@ -5079,10 +5096,10 @@
     </row>
     <row r="146" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="147" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="50" t="s">
+      <c r="A147" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="B147" s="51"/>
+      <c r="B147" s="66"/>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
@@ -5148,6 +5165,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D15:E15"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="G12:H12"/>
@@ -5158,11 +5180,6 @@
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A118:B118"/>
     <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D15:E15"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16">
@@ -5176,7 +5193,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
@@ -5185,18 +5202,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="65" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="D1" s="50" t="s">
+      <c r="B1" s="66"/>
+      <c r="D1" s="65" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="G1" s="50" t="s">
+      <c r="E1" s="66"/>
+      <c r="G1" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="51"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -5320,10 +5337,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="51"/>
+      <c r="B9" s="66"/>
       <c r="D9" t="s">
         <v>32</v>
       </c>
@@ -5362,7 +5379,7 @@
       <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="70">
+      <c r="B12" s="64">
         <f>((_h-2*_tf)*_tw+4*(1-PI()/4)*_r^2+_tf*(_tw+2*_r))/100</f>
         <v>50.845176397669007</v>
       </c>
@@ -5522,10 +5539,10 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="50" t="s">
+      <c r="A29" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="51"/>
+      <c r="B29" s="66"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -5544,10 +5561,10 @@
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>1042.1194079466816</v>
       </c>
-      <c r="D31" s="52" t="s">
+      <c r="D31" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="53"/>
+      <c r="E31" s="68"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -5727,10 +5744,10 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="50" t="s">
+      <c r="A47" s="65" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="51"/>
+      <c r="B47" s="66"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -5749,7 +5766,7 @@
       <c r="A49" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="B49" s="59">
+      <c r="B49" s="53">
         <v>34.424999999999997</v>
       </c>
     </row>
@@ -5757,7 +5774,7 @@
       <c r="A50" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="B50" s="58" t="s">
+      <c r="B50" s="52" t="s">
         <v>236</v>
       </c>
       <c r="D50" s="24" t="s">
@@ -5768,7 +5785,7 @@
       <c r="A51" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="B51" s="56">
+      <c r="B51" s="50">
         <v>13.47</v>
       </c>
     </row>
@@ -5776,7 +5793,7 @@
       <c r="A52" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="B52" s="57">
+      <c r="B52" s="51">
         <v>14.74</v>
       </c>
     </row>
@@ -5784,7 +5801,7 @@
       <c r="A53" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="B53" s="57">
+      <c r="B53" s="51">
         <v>-19.5</v>
       </c>
     </row>
@@ -5792,7 +5809,7 @@
       <c r="A54" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="B54" s="57">
+      <c r="B54" s="51">
         <v>11.67</v>
       </c>
     </row>
@@ -5800,7 +5817,7 @@
       <c r="A55" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="B55" s="57">
+      <c r="B55" s="51">
         <v>25.17</v>
       </c>
     </row>
@@ -5808,7 +5825,7 @@
       <c r="A56" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="B56" s="57">
+      <c r="B56" s="51">
         <v>12</v>
       </c>
     </row>
@@ -5816,7 +5833,7 @@
       <c r="A57" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="B57" s="58">
+      <c r="B57" s="52">
         <v>-19.5</v>
       </c>
     </row>
@@ -5824,7 +5841,7 @@
       <c r="A58" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="B58" s="56">
+      <c r="B58" s="50">
         <v>66.650000000000006</v>
       </c>
     </row>
@@ -5832,7 +5849,7 @@
       <c r="A59" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="B59" s="57">
+      <c r="B59" s="51">
         <v>96.16</v>
       </c>
     </row>
@@ -5840,7 +5857,7 @@
       <c r="A60" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B60" s="57">
+      <c r="B60" s="51">
         <v>-71.05</v>
       </c>
     </row>
@@ -5848,7 +5865,7 @@
       <c r="A61" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="B61" s="57">
+      <c r="B61" s="51">
         <v>63.95</v>
       </c>
     </row>
@@ -5856,7 +5873,7 @@
       <c r="A62" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="B62" s="57">
+      <c r="B62" s="51">
         <v>111.9</v>
       </c>
     </row>
@@ -5864,7 +5881,7 @@
       <c r="A63" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="B63" s="57">
+      <c r="B63" s="51">
         <v>-41.81</v>
       </c>
     </row>
@@ -5872,34 +5889,34 @@
       <c r="A64" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B64" s="57">
+      <c r="B64" s="51">
         <v>49.15</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="60" t="s">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="B65" s="57">
+      <c r="B65" s="51">
         <v>58.96</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="B66" s="58">
+      <c r="B66" s="52">
         <v>-71.06</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="50" t="s">
+    <row r="67" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="51"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B68" s="66"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>123</v>
       </c>
@@ -5908,7 +5925,7 @@
         <v>603.85500000000002</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>248</v>
       </c>
@@ -5917,30 +5934,40 @@
         <v>1042.1194079466816</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B71" s="23"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="21"/>
-      <c r="B72" s="68" t="s">
+      <c r="B72" s="62" t="s">
         <v>249</v>
       </c>
-      <c r="C72" s="69" t="s">
+      <c r="C72" s="63" t="s">
         <v>250</v>
       </c>
       <c r="D72" s="22" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F72" s="21"/>
+      <c r="G72" s="71" t="s">
+        <v>249</v>
+      </c>
+      <c r="H72" s="72" t="s">
+        <v>250</v>
+      </c>
+      <c r="I72" s="29" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B73" s="65">
+      <c r="B73" s="59">
         <f>MAX(B59,ABS(B60))/_Mpl_Rd</f>
         <v>0.15924352700565533</v>
       </c>
-      <c r="C73" s="61">
+      <c r="C73" s="55">
         <f>MAX(B62,ABS(B63))/_Mpl_Rd</f>
         <v>0.18530938718732146</v>
       </c>
@@ -5948,16 +5975,31 @@
         <f>MAX(B65,ABS(B66))/_Mpl_Rd</f>
         <v>0.11767725695738215</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F73" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="G73" s="73">
+        <f>B73</f>
+        <v>0.15924352700565533</v>
+      </c>
+      <c r="H73" s="74">
+        <f t="shared" ref="H73:I73" si="0">C73</f>
+        <v>0.18530938718732146</v>
+      </c>
+      <c r="I73" s="75">
+        <f t="shared" si="0"/>
+        <v>0.11767725695738215</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="B74" s="65">
+      <c r="B74" s="59">
         <f>B58/B70</f>
         <v>6.3956202611486199E-2</v>
       </c>
-      <c r="C74" s="61">
+      <c r="C74" s="55">
         <f>B61/B70</f>
         <v>6.1365328687239942E-2</v>
       </c>
@@ -5965,131 +6007,255 @@
         <f>B64/B70</f>
         <v>4.7163501250630853E-2</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F74" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="G74" s="59">
+        <f>B74</f>
+        <v>6.3956202611486199E-2</v>
+      </c>
+      <c r="H74" s="55">
+        <f t="shared" ref="H74" si="1">C74</f>
+        <v>6.1365328687239942E-2</v>
+      </c>
+      <c r="I74" s="17">
+        <f t="shared" ref="I74" si="2">D74</f>
+        <v>4.7163501250630853E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="B75" s="66">
+      <c r="B75" s="60">
         <f>1/B73</f>
         <v>6.2796900998336103</v>
       </c>
-      <c r="C75" s="62">
-        <f t="shared" ref="C75:D75" si="0">1/C73</f>
+      <c r="C75" s="56">
+        <f t="shared" ref="C75:D75" si="3">1/C73</f>
         <v>5.3963806970509385</v>
       </c>
-      <c r="D75" s="63">
-        <f t="shared" si="0"/>
+      <c r="D75" s="57">
+        <f t="shared" si="3"/>
         <v>8.4978187447227693</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="F75" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="G75" s="60">
+        <v>521.97</v>
+      </c>
+      <c r="H75" s="56">
+        <v>546.22</v>
+      </c>
+      <c r="I75" s="57">
+        <v>496.55</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="B76" s="66">
+      <c r="B76" s="60">
         <v>5.4870000000000001</v>
       </c>
-      <c r="C76" s="62"/>
-      <c r="D76" s="63"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C76" s="56">
+        <v>4.9240000000000004</v>
+      </c>
+      <c r="D76" s="57">
+        <v>6.9660000000000002</v>
+      </c>
+      <c r="F76" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="G76" s="59">
+        <f>SQRT(_Mpl_Rd/G75)</f>
+        <v>1.0755820898480224</v>
+      </c>
+      <c r="H76" s="55">
+        <f>SQRT(_Mpl_Rd/H75)</f>
+        <v>1.0514352535543854</v>
+      </c>
+      <c r="I76" s="17">
+        <f>SQRT(_Mpl_Rd/I75)</f>
+        <v>1.1027697391446936</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="B77" s="65">
+      <c r="B77" s="59">
         <f>SQRT(B75/B76)</f>
         <v>1.0697976163788039</v>
       </c>
-      <c r="C77" s="61">
-        <f>SQRT(_Mpl_Rd/C75)</f>
-        <v>10.578279633286312</v>
+      <c r="C77" s="55">
+        <f t="shared" ref="C77:D77" si="4">SQRT(C75/C76)</f>
+        <v>1.0468688272173641</v>
       </c>
       <c r="D77" s="17">
-        <f>SQRT(_Mpl_Rd/D75)</f>
-        <v>8.4297093662830402</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" si="4"/>
+        <v>1.1044905303869459</v>
+      </c>
+      <c r="F77" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="G77" s="60">
+        <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+      <c r="H77" s="56">
+        <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+      <c r="I77" s="57">
+        <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B78" s="66">
-        <v>0.21</v>
-      </c>
-      <c r="C78" s="62">
-        <v>1.21</v>
-      </c>
-      <c r="D78" s="63">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B78" s="60">
+        <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+      <c r="C78" s="56">
+        <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+      <c r="D78" s="57">
+        <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+      <c r="F78" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="G78" s="59">
+        <f>0.5*(1+G77*(G76-0.2)+G76^2)</f>
+        <v>1.2272873712750836</v>
+      </c>
+      <c r="H78" s="55">
+        <f t="shared" ref="H78:I78" si="5">0.5*(1+H77*(H76-0.2)+H76^2)</f>
+        <v>1.1975020393127329</v>
+      </c>
+      <c r="I78" s="17">
+        <f t="shared" si="5"/>
+        <v>1.2615214044412257</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="B79" s="65">
+      <c r="B79" s="59">
         <f>0.5*(1+B78*(B77-0.2)+B77^2)</f>
-        <v>1.1635622197246596</v>
-      </c>
-      <c r="C79" s="61">
-        <f t="shared" ref="C79:D79" si="1">0.5*(1+C78*(C77-0.2)+C77^2)</f>
-        <v>62.728859178138222</v>
+        <v>1.2200990647892818</v>
+      </c>
+      <c r="C79" s="55">
+        <f t="shared" ref="C79:D79" si="6">0.5*(1+C78*(C77-0.2)+C77^2)</f>
+        <v>1.1919348713266817</v>
       </c>
       <c r="D79" s="17">
-        <f t="shared" si="1"/>
-        <v>45.123828849742765</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>1.2637130560229994</v>
+      </c>
+      <c r="F79" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="G79" s="59">
+        <f>1/(G78+SQRT(G78^2-G76^2))</f>
+        <v>0.54994850835187725</v>
+      </c>
+      <c r="H79" s="55">
+        <f t="shared" ref="H79:I79" si="7">1/(H78+SQRT(H78^2-H76^2))</f>
+        <v>0.56476533795169126</v>
+      </c>
+      <c r="I79" s="17">
+        <f t="shared" si="7"/>
+        <v>0.53357025759830123</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="B80" s="65">
+      <c r="B80" s="59">
         <f>1/(B79+SQRT(B79^2-B77^2))</f>
-        <v>0.61683628663191403</v>
-      </c>
-      <c r="C80" s="61">
-        <f t="shared" ref="C80:D80" si="2">1/(C79+SQRT(C79^2-C77^2))</f>
-        <v>8.0283012749364502E-3</v>
+        <v>0.55347596700576529</v>
+      </c>
+      <c r="C80" s="55">
+        <f t="shared" ref="C80:D80" si="8">1/(C79+SQRT(C79^2-C77^2))</f>
+        <v>0.56759336517890635</v>
       </c>
       <c r="D80" s="17">
-        <f t="shared" si="2"/>
-        <v>1.1179020366719835E-2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>0.5325453315503752</v>
+      </c>
+      <c r="F80" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="G80" s="60">
+        <f>G79*_Mpl_Rd</f>
+        <v>332.08915651082287</v>
+      </c>
+      <c r="H80" s="56">
+        <f>H79*_Mpl_Rd</f>
+        <v>341.03637314881854</v>
+      </c>
+      <c r="I80" s="57">
+        <f>I79*_Mpl_Rd</f>
+        <v>322.19906790202219</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B81" s="66">
+      <c r="B81" s="60">
         <f>B80*_Mpl_Rd</f>
-        <v>372.47967586411448</v>
-      </c>
-      <c r="C81" s="62">
+        <v>334.21923005626638</v>
+      </c>
+      <c r="C81" s="56">
         <f>C80*_Mpl_Rd</f>
-        <v>4.8479298663767505</v>
-      </c>
-      <c r="D81" s="63">
+        <v>342.74409153010851</v>
+      </c>
+      <c r="D81" s="57">
         <f>D80*_Mpl_Rd</f>
-        <v>6.750507343545606</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+        <v>321.58016118335183</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="G81" s="61">
+        <f>G73/G79</f>
+        <v>0.28956079448762767</v>
+      </c>
+      <c r="H81" s="58">
+        <f>H73/H79</f>
+        <v>0.32811749364684345</v>
+      </c>
+      <c r="I81" s="18">
+        <f>I73/I79</f>
+        <v>0.2205468825924993</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B82" s="67">
+      <c r="B82" s="61">
         <f>B73/B80</f>
-        <v>0.25816173668246117</v>
-      </c>
-      <c r="C82" s="64">
-        <f t="shared" ref="C82:D82" si="3">C73/C80</f>
-        <v>23.082017084465768</v>
+        <v>0.28771534176477903</v>
+      </c>
+      <c r="C82" s="58">
+        <f t="shared" ref="C82:D82" si="9">C73/C80</f>
+        <v>0.3264826521164701</v>
       </c>
       <c r="D82" s="18">
-        <f t="shared" si="3"/>
-        <v>10.526616205809024</v>
+        <f t="shared" si="9"/>
+        <v>0.22097134269263738</v>
       </c>
     </row>
   </sheetData>

--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -9,20 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15300" windowHeight="4260" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15300" windowHeight="4260"/>
   </bookViews>
   <sheets>
     <sheet name="Cas 2" sheetId="1" r:id="rId1"/>
     <sheet name="Cas 3" sheetId="2" r:id="rId2"/>
-    <sheet name="Cas 5" sheetId="3" r:id="rId3"/>
+    <sheet name="Cas 4" sheetId="4" r:id="rId3"/>
+    <sheet name="Cas 5" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_A" localSheetId="0">'Cas 2'!$B$32</definedName>
     <definedName name="_A" localSheetId="1">'Cas 3'!$B$33</definedName>
-    <definedName name="_A" localSheetId="2">'Cas 5'!$B$11</definedName>
+    <definedName name="_A" localSheetId="3">'Cas 5'!$B$11</definedName>
     <definedName name="_A0" localSheetId="0">'Cas 2'!$B$75</definedName>
     <definedName name="_A0" localSheetId="1">'Cas 3'!#REF!</definedName>
-    <definedName name="_Ac" localSheetId="2">'Cas 5'!$H$5</definedName>
+    <definedName name="_Ac" localSheetId="3">'Cas 5'!$H$5</definedName>
     <definedName name="_Ace" localSheetId="0">'Cas 2'!$E$4</definedName>
     <definedName name="_Ace" localSheetId="1">'Cas 3'!$E$4</definedName>
     <definedName name="_Acr" localSheetId="0">'Cas 2'!$B$71</definedName>
@@ -31,12 +32,12 @@
     <definedName name="_As_inf" localSheetId="1">'Cas 3'!$E$10</definedName>
     <definedName name="_Av" localSheetId="0">'Cas 2'!$B$33</definedName>
     <definedName name="_Av" localSheetId="1">'Cas 3'!$B$34</definedName>
-    <definedName name="_Av" localSheetId="2">'Cas 5'!$B$12</definedName>
+    <definedName name="_Av" localSheetId="3">'Cas 5'!$B$12</definedName>
     <definedName name="_b" localSheetId="0">'Cas 2'!$B$4</definedName>
     <definedName name="_b" localSheetId="1">'Cas 3'!$B$15</definedName>
-    <definedName name="_b" localSheetId="2">'Cas 5'!$E$3</definedName>
-    <definedName name="_b_Droite" localSheetId="2">'Cas 5'!$B$7</definedName>
-    <definedName name="_b_Gauche" localSheetId="2">'Cas 5'!$B$6</definedName>
+    <definedName name="_b" localSheetId="3">'Cas 5'!$E$3</definedName>
+    <definedName name="_b_Droite" localSheetId="3">'Cas 5'!$B$7</definedName>
+    <definedName name="_b_Gauche" localSheetId="3">'Cas 5'!$B$6</definedName>
     <definedName name="_B0" localSheetId="0">'Cas 2'!$B$76</definedName>
     <definedName name="_B0" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_bb" localSheetId="0">'Cas 2'!$E$21</definedName>
@@ -57,10 +58,10 @@
     <definedName name="_bt" localSheetId="0">'Cas 2'!$E$20</definedName>
     <definedName name="_cf" localSheetId="0">'Cas 2'!$B$11</definedName>
     <definedName name="_cf" localSheetId="1">'Cas 3'!$B$22</definedName>
-    <definedName name="_cf" localSheetId="2">'Cas 5'!$E$12</definedName>
+    <definedName name="_cf" localSheetId="3">'Cas 5'!$E$12</definedName>
     <definedName name="_cw" localSheetId="0">'Cas 2'!$B$12</definedName>
     <definedName name="_cw" localSheetId="1">'Cas 3'!$B$23</definedName>
-    <definedName name="_cw" localSheetId="2">'Cas 5'!$E$13</definedName>
+    <definedName name="_cw" localSheetId="3">'Cas 5'!$E$13</definedName>
     <definedName name="_d" localSheetId="0">'Cas 2'!$H$13</definedName>
     <definedName name="_dsc" localSheetId="1">'Cas 3'!$H$14</definedName>
     <definedName name="_dw" localSheetId="0">'Cas 2'!$B$9</definedName>
@@ -71,7 +72,7 @@
     <definedName name="_ep" localSheetId="1">'Cas 3'!$E$19</definedName>
     <definedName name="_epsilon" localSheetId="0">'Cas 2'!$B$15</definedName>
     <definedName name="_epsilon" localSheetId="1">'Cas 3'!$B$26</definedName>
-    <definedName name="_epsilon" localSheetId="2">'Cas 5'!$E$16</definedName>
+    <definedName name="_epsilon" localSheetId="3">'Cas 5'!$E$16</definedName>
     <definedName name="_eta" localSheetId="1">'Cas 3'!$H$28</definedName>
     <definedName name="_fck_dalle" localSheetId="0">'Cas 2'!$H$5</definedName>
     <definedName name="_fck_dalle" localSheetId="1">'Cas 3'!$H$5</definedName>
@@ -86,13 +87,13 @@
     <definedName name="_fusc" localSheetId="1">'Cas 3'!$H$15</definedName>
     <definedName name="_fy" localSheetId="0">'Cas 2'!$B$14</definedName>
     <definedName name="_fy" localSheetId="1">'Cas 3'!$B$25</definedName>
-    <definedName name="_fy" localSheetId="2">'Cas 5'!$E$15</definedName>
+    <definedName name="_fy" localSheetId="3">'Cas 5'!$E$15</definedName>
     <definedName name="_fyd" localSheetId="0">'Cas 2'!$E$12</definedName>
     <definedName name="_fyd" localSheetId="1">'Cas 3'!$E$12</definedName>
     <definedName name="_fyp" localSheetId="0">'Cas 2'!$E$24</definedName>
     <definedName name="_h" localSheetId="0">'Cas 2'!$B$3</definedName>
     <definedName name="_h" localSheetId="1">'Cas 3'!$B$14</definedName>
-    <definedName name="_h" localSheetId="2">'Cas 5'!$E$2</definedName>
+    <definedName name="_h" localSheetId="3">'Cas 5'!$E$2</definedName>
     <definedName name="_hp" localSheetId="0">'Cas 2'!$E$17</definedName>
     <definedName name="_hp" localSheetId="1">'Cas 3'!$E$17</definedName>
     <definedName name="_hpg" localSheetId="0">'Cas 2'!$E$18</definedName>
@@ -100,25 +101,25 @@
     <definedName name="_hsc" localSheetId="1">'Cas 3'!$H$13</definedName>
     <definedName name="_hw" localSheetId="0">'Cas 2'!$B$8</definedName>
     <definedName name="_hw" localSheetId="1">'Cas 3'!$B$19</definedName>
-    <definedName name="_hw" localSheetId="2">'Cas 5'!$E$9</definedName>
+    <definedName name="_hw" localSheetId="3">'Cas 5'!$E$9</definedName>
     <definedName name="_Iy" localSheetId="0">'Cas 2'!$B$34</definedName>
     <definedName name="_Iy" localSheetId="1">'Cas 3'!$B$35</definedName>
-    <definedName name="_Iy" localSheetId="2">'Cas 5'!$B$13</definedName>
+    <definedName name="_Iy" localSheetId="3">'Cas 5'!$B$13</definedName>
     <definedName name="_Iz" localSheetId="0">'Cas 2'!$B$35</definedName>
-    <definedName name="_Iz" localSheetId="2">'Cas 5'!$B$14</definedName>
+    <definedName name="_Iz" localSheetId="3">'Cas 5'!$B$14</definedName>
     <definedName name="_kr" localSheetId="0">'Cas 2'!$B$72</definedName>
     <definedName name="_kr" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_kt" localSheetId="1">'Cas 3'!$H$21</definedName>
     <definedName name="_kt_max" localSheetId="1">'Cas 3'!$H$20</definedName>
     <definedName name="_L" localSheetId="0">'Cas 2'!$B$2</definedName>
     <definedName name="_L" localSheetId="1">'Cas 3'!$B$2</definedName>
-    <definedName name="_L_ConsoleD" localSheetId="2">'Cas 5'!$B$4</definedName>
-    <definedName name="_L_ConsoleG" localSheetId="2">'Cas 5'!$B$2</definedName>
-    <definedName name="_L_tot" localSheetId="2">'Cas 5'!$B$5</definedName>
-    <definedName name="_L_Travee" localSheetId="2">'Cas 5'!$B$3</definedName>
+    <definedName name="_L_ConsoleD" localSheetId="3">'Cas 5'!$B$4</definedName>
+    <definedName name="_L_ConsoleG" localSheetId="3">'Cas 5'!$B$2</definedName>
+    <definedName name="_L_tot" localSheetId="3">'Cas 5'!$B$5</definedName>
+    <definedName name="_L_Travee" localSheetId="3">'Cas 5'!$B$3</definedName>
     <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$53</definedName>
     <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$54</definedName>
-    <definedName name="_Mpl_Rd" localSheetId="2">'Cas 5'!$B$69</definedName>
+    <definedName name="_Mpl_Rd" localSheetId="3">'Cas 5'!$B$69</definedName>
     <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$55</definedName>
     <definedName name="_Mpl_z_Rd" localSheetId="0">'Cas 2'!$B$56</definedName>
     <definedName name="_n" localSheetId="0">'Cas 2'!$B$69</definedName>
@@ -141,40 +142,40 @@
     <definedName name="_qProfile" localSheetId="1">'Cas 3'!$B$29</definedName>
     <definedName name="_r" localSheetId="0">'Cas 2'!$B$7</definedName>
     <definedName name="_r" localSheetId="1">'Cas 3'!$B$18</definedName>
-    <definedName name="_r" localSheetId="2">'Cas 5'!$E$8</definedName>
+    <definedName name="_r" localSheetId="3">'Cas 5'!$E$8</definedName>
     <definedName name="_rho" localSheetId="0">'Cas 2'!$B$17</definedName>
     <definedName name="_rho" localSheetId="1">'Cas 3'!$B$28</definedName>
-    <definedName name="_rhoA" localSheetId="2">'Cas 5'!$E$18</definedName>
-    <definedName name="_rhoC" localSheetId="2">'Cas 5'!$H$6</definedName>
+    <definedName name="_rhoA" localSheetId="3">'Cas 5'!$E$18</definedName>
+    <definedName name="_rhoC" localSheetId="3">'Cas 5'!$H$6</definedName>
     <definedName name="_tc" localSheetId="0">'Cas 2'!$H$4</definedName>
     <definedName name="_tc" localSheetId="1">'Cas 3'!$H$4</definedName>
     <definedName name="_td" localSheetId="0">'Cas 2'!$H$3</definedName>
     <definedName name="_td" localSheetId="1">'Cas 3'!$H$3</definedName>
-    <definedName name="_td" localSheetId="2">'Cas 5'!$H$2</definedName>
+    <definedName name="_td" localSheetId="3">'Cas 5'!$H$2</definedName>
     <definedName name="_tf" localSheetId="0">'Cas 2'!$B$5</definedName>
     <definedName name="_tf" localSheetId="1">'Cas 3'!$B$16</definedName>
-    <definedName name="_tf" localSheetId="2">'Cas 5'!$E$4</definedName>
-    <definedName name="_th" localSheetId="2">'Cas 5'!$H$3</definedName>
-    <definedName name="_theta" localSheetId="2">'Cas 5'!$H$4</definedName>
+    <definedName name="_tf" localSheetId="3">'Cas 5'!$E$4</definedName>
+    <definedName name="_th" localSheetId="3">'Cas 5'!$H$3</definedName>
+    <definedName name="_theta" localSheetId="3">'Cas 5'!$H$4</definedName>
     <definedName name="_tp" localSheetId="0">'Cas 2'!$E$23</definedName>
     <definedName name="_tw" localSheetId="0">'Cas 2'!$B$6</definedName>
     <definedName name="_tw" localSheetId="1">'Cas 3'!$B$17</definedName>
-    <definedName name="_tw" localSheetId="2">'Cas 5'!$E$5</definedName>
+    <definedName name="_tw" localSheetId="3">'Cas 5'!$E$5</definedName>
     <definedName name="_VplRd" localSheetId="0">'Cas 2'!$B$52</definedName>
     <definedName name="_VplRd" localSheetId="1">'Cas 3'!$B$53</definedName>
-    <definedName name="_VplRd" localSheetId="2">'Cas 5'!$B$52</definedName>
+    <definedName name="_VplRd" localSheetId="3">'Cas 5'!$B$52</definedName>
     <definedName name="_Wel_y" localSheetId="0">'Cas 2'!$B$36</definedName>
     <definedName name="_Wel_y" localSheetId="1">'Cas 3'!$B$37</definedName>
-    <definedName name="_Wel_y" localSheetId="2">'Cas 5'!$B$15</definedName>
+    <definedName name="_Wel_y" localSheetId="3">'Cas 5'!$B$15</definedName>
     <definedName name="_Wel_z" localSheetId="0">'Cas 2'!$B$37</definedName>
     <definedName name="_Wel_z" localSheetId="1">'Cas 3'!$B$38</definedName>
-    <definedName name="_Wel_z" localSheetId="2">'Cas 5'!$B$16</definedName>
+    <definedName name="_Wel_z" localSheetId="3">'Cas 5'!$B$16</definedName>
     <definedName name="_Wpl_y" localSheetId="0">'Cas 2'!$B$38</definedName>
     <definedName name="_Wpl_y" localSheetId="1">'Cas 3'!$B$39</definedName>
-    <definedName name="_Wpl_y" localSheetId="2">'Cas 5'!$B$17</definedName>
+    <definedName name="_Wpl_y" localSheetId="3">'Cas 5'!$B$17</definedName>
     <definedName name="_Wpl_z" localSheetId="0">'Cas 2'!$B$39</definedName>
     <definedName name="_Wpl_z" localSheetId="1">'Cas 3'!$B$40</definedName>
-    <definedName name="_Wpl_z" localSheetId="2">'Cas 5'!$B$18</definedName>
+    <definedName name="_Wpl_z" localSheetId="3">'Cas 5'!$B$18</definedName>
     <definedName name="_za" localSheetId="0">'Cas 2'!$B$74</definedName>
     <definedName name="_za" localSheetId="1">'Cas 3'!$B$73</definedName>
     <definedName name="_zcr" localSheetId="0">'Cas 2'!$B$73</definedName>
@@ -198,7 +199,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="259">
   <si>
     <t>h (mm)</t>
   </si>
@@ -972,6 +973,9 @@
   </si>
   <si>
     <t>Mcr (kN.m)</t>
+  </si>
+  <si>
+    <t>Sans objet, l'ensemble des résultats sont dans l'article RCM 2022 n°3</t>
   </si>
 </sst>
 </file>
@@ -1314,6 +1318,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1332,11 +1341,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -1630,20 +1634,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="66"/>
+      <c r="B1" s="71"/>
       <c r="C1"/>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="66"/>
+      <c r="E1" s="71"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="65" t="s">
+      <c r="G1" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="66"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -1905,10 +1909,10 @@
         <v>0.81361651346682706</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="66"/>
+      <c r="E15" s="71"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
@@ -2047,10 +2051,10 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="65" t="s">
+      <c r="A30" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="66"/>
+      <c r="B30" s="71"/>
       <c r="C30" s="24" t="s">
         <v>53</v>
       </c>
@@ -2318,10 +2322,10 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="65" t="s">
+      <c r="A50" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="66"/>
+      <c r="B50" s="71"/>
       <c r="D50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2358,10 +2362,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E52" s="67" t="s">
+      <c r="E52" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="F52" s="68"/>
+      <c r="F52" s="73"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -2609,10 +2613,10 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="65" t="s">
+      <c r="A68" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="B68" s="66"/>
+      <c r="B68" s="71"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -2896,10 +2900,10 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="65" t="s">
+      <c r="A96" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="B96" s="66"/>
+      <c r="B96" s="71"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -3003,10 +3007,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="65" t="s">
+      <c r="A109" s="70" t="s">
         <v>133</v>
       </c>
-      <c r="B109" s="66"/>
+      <c r="B109" s="71"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -3089,10 +3093,10 @@
     </row>
     <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="65" t="s">
+      <c r="A120" s="70" t="s">
         <v>134</v>
       </c>
-      <c r="B120" s="66"/>
+      <c r="B120" s="71"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
@@ -3217,20 +3221,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="66"/>
+      <c r="B1" s="71"/>
       <c r="C1"/>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="66"/>
+      <c r="E1" s="71"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="65" t="s">
+      <c r="G1" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="66"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -3465,16 +3469,16 @@
         <f>500/1.15</f>
         <v>434.78260869565219</v>
       </c>
-      <c r="G12" s="65" t="s">
+      <c r="G12" s="70" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="66"/>
+      <c r="H12" s="71"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="66"/>
+      <c r="B13" s="71"/>
       <c r="C13"/>
       <c r="D13" t="s">
         <v>125</v>
@@ -3513,10 +3517,10 @@
         <v>200</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="65" t="s">
+      <c r="D15" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="66"/>
+      <c r="E15" s="71"/>
       <c r="G15" t="s">
         <v>166</v>
       </c>
@@ -3820,10 +3824,10 @@
       <c r="C30"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="66"/>
+      <c r="B31" s="71"/>
       <c r="C31" s="24" t="s">
         <v>53</v>
       </c>
@@ -4091,10 +4095,10 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="66"/>
+      <c r="B51" s="71"/>
       <c r="D51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4131,10 +4135,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E53" s="67" t="s">
+      <c r="E53" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="68"/>
+      <c r="F53" s="73"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -4382,10 +4386,10 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="65" t="s">
+      <c r="A69" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="66"/>
+      <c r="B69" s="71"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -4566,10 +4570,10 @@
       <c r="C84" s="36"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="69" t="s">
+      <c r="A85" s="74" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="70"/>
+      <c r="B85" s="75"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -4712,10 +4716,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="65" t="s">
+      <c r="A101" s="70" t="s">
         <v>111</v>
       </c>
-      <c r="B101" s="66"/>
+      <c r="B101" s="71"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
@@ -4855,10 +4859,10 @@
     </row>
     <row r="117" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="118" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="65" t="s">
+      <c r="A118" s="70" t="s">
         <v>133</v>
       </c>
-      <c r="B118" s="66"/>
+      <c r="B118" s="71"/>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
@@ -4977,10 +4981,10 @@
     </row>
     <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="65" t="s">
+      <c r="A133" s="70" t="s">
         <v>134</v>
       </c>
-      <c r="B133" s="66"/>
+      <c r="B133" s="71"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
@@ -5096,10 +5100,10 @@
     </row>
     <row r="146" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="147" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="65" t="s">
+      <c r="A147" s="70" t="s">
         <v>207</v>
       </c>
-      <c r="B147" s="66"/>
+      <c r="B147" s="71"/>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
@@ -5165,11 +5169,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D15:E15"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="G12:H12"/>
@@ -5180,6 +5179,11 @@
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A118:B118"/>
     <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D15:E15"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16">
@@ -5193,6 +5197,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>258</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5202,18 +5222,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="70" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="D1" s="65" t="s">
+      <c r="B1" s="71"/>
+      <c r="D1" s="70" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="66"/>
-      <c r="G1" s="65" t="s">
+      <c r="E1" s="71"/>
+      <c r="G1" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="66"/>
+      <c r="H1" s="71"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -5337,10 +5357,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="66"/>
+      <c r="B9" s="71"/>
       <c r="D9" t="s">
         <v>32</v>
       </c>
@@ -5539,10 +5559,10 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="65" t="s">
+      <c r="A29" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="66"/>
+      <c r="B29" s="71"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -5561,10 +5581,10 @@
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>1042.1194079466816</v>
       </c>
-      <c r="D31" s="67" t="s">
+      <c r="D31" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="68"/>
+      <c r="E31" s="73"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -5744,10 +5764,10 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="65" t="s">
+      <c r="A47" s="70" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="66"/>
+      <c r="B47" s="71"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -5911,10 +5931,10 @@
     </row>
     <row r="67" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="65" t="s">
+      <c r="A68" s="70" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="66"/>
+      <c r="B68" s="71"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -5949,10 +5969,10 @@
         <v>251</v>
       </c>
       <c r="F72" s="21"/>
-      <c r="G72" s="71" t="s">
+      <c r="G72" s="65" t="s">
         <v>249</v>
       </c>
-      <c r="H72" s="72" t="s">
+      <c r="H72" s="66" t="s">
         <v>250</v>
       </c>
       <c r="I72" s="29" t="s">
@@ -5978,15 +5998,15 @@
       <c r="F73" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="G73" s="73">
+      <c r="G73" s="67">
         <f>B73</f>
         <v>0.15924352700565533</v>
       </c>
-      <c r="H73" s="74">
+      <c r="H73" s="68">
         <f t="shared" ref="H73:I73" si="0">C73</f>
         <v>0.18530938718732146</v>
       </c>
-      <c r="I73" s="75">
+      <c r="I73" s="69">
         <f t="shared" si="0"/>
         <v>0.11767725695738215</v>
       </c>

--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -9,47 +9,65 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15300" windowHeight="4260"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15300" windowHeight="4260" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Cas 2" sheetId="1" r:id="rId1"/>
     <sheet name="Cas 3" sheetId="2" r:id="rId2"/>
     <sheet name="Cas 4" sheetId="4" r:id="rId3"/>
     <sheet name="Cas 5" sheetId="3" r:id="rId4"/>
+    <sheet name="Cas 6" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_A" localSheetId="0">'Cas 2'!$B$32</definedName>
     <definedName name="_A" localSheetId="1">'Cas 3'!$B$33</definedName>
     <definedName name="_A" localSheetId="3">'Cas 5'!$B$11</definedName>
+    <definedName name="_A" localSheetId="4">'Cas 6'!$B$15</definedName>
     <definedName name="_A0" localSheetId="0">'Cas 2'!$B$75</definedName>
     <definedName name="_A0" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_Ac" localSheetId="3">'Cas 5'!$H$5</definedName>
+    <definedName name="_Ac_brute" localSheetId="4">'Cas 6'!$H$5</definedName>
     <definedName name="_Ace" localSheetId="0">'Cas 2'!$E$4</definedName>
     <definedName name="_Ace" localSheetId="1">'Cas 3'!$E$4</definedName>
+    <definedName name="_Ace" localSheetId="4">'Cas 6'!$E$4</definedName>
     <definedName name="_Acr" localSheetId="0">'Cas 2'!$B$71</definedName>
     <definedName name="_Acr" localSheetId="1">'Cas 3'!#REF!</definedName>
+    <definedName name="_Ah" localSheetId="4">'Cas 6'!$B$94</definedName>
     <definedName name="_As_inf" localSheetId="0">'Cas 2'!$E$10</definedName>
     <definedName name="_As_inf" localSheetId="1">'Cas 3'!$E$10</definedName>
+    <definedName name="_As_inf" localSheetId="4">'Cas 6'!$E$10</definedName>
     <definedName name="_Av" localSheetId="0">'Cas 2'!$B$33</definedName>
     <definedName name="_Av" localSheetId="1">'Cas 3'!$B$34</definedName>
     <definedName name="_Av" localSheetId="3">'Cas 5'!$B$12</definedName>
+    <definedName name="_Av" localSheetId="4">'Cas 6'!$B$16</definedName>
     <definedName name="_b" localSheetId="0">'Cas 2'!$B$4</definedName>
     <definedName name="_b" localSheetId="1">'Cas 3'!$B$15</definedName>
     <definedName name="_b" localSheetId="3">'Cas 5'!$E$3</definedName>
     <definedName name="_b_Droite" localSheetId="3">'Cas 5'!$B$7</definedName>
+    <definedName name="_b_Droite" localSheetId="4">'Cas 6'!$B$4</definedName>
     <definedName name="_b_Gauche" localSheetId="3">'Cas 5'!$B$6</definedName>
+    <definedName name="_b_Gauche" localSheetId="4">'Cas 6'!$B$3</definedName>
     <definedName name="_B0" localSheetId="0">'Cas 2'!$B$76</definedName>
     <definedName name="_B0" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_bb" localSheetId="0">'Cas 2'!$E$21</definedName>
     <definedName name="_bc" localSheetId="0">'Cas 2'!$E$3</definedName>
     <definedName name="_bc" localSheetId="1">'Cas 3'!$E$3</definedName>
+    <definedName name="_bc" localSheetId="4">'Cas 6'!$E$3</definedName>
     <definedName name="_bdroite" localSheetId="1">'Cas 3'!$B$4</definedName>
     <definedName name="_be1" localSheetId="1">'Cas 3'!$B$6</definedName>
+    <definedName name="_be1" localSheetId="4">'Cas 6'!$B$3</definedName>
     <definedName name="_be2" localSheetId="1">'Cas 3'!$B$7</definedName>
+    <definedName name="_be2" localSheetId="4">'Cas 6'!$B$4</definedName>
+    <definedName name="_beff" localSheetId="4">'Cas 6'!$B$90</definedName>
     <definedName name="_beff_appui" localSheetId="1">'Cas 3'!$B$11</definedName>
     <definedName name="_beff_mi_travee" localSheetId="1">'Cas 3'!$B$10</definedName>
+    <definedName name="_beff_mi_travee" localSheetId="4">'Cas 6'!$B$10</definedName>
     <definedName name="_beta1" localSheetId="1">'Cas 3'!$B$8</definedName>
+    <definedName name="_beta1" localSheetId="4">'Cas 6'!$B$8</definedName>
     <definedName name="_beta2" localSheetId="1">'Cas 3'!$B$9</definedName>
+    <definedName name="_beta2" localSheetId="4">'Cas 6'!$B$9</definedName>
+    <definedName name="_bfi">'Cas 6'!$E$5</definedName>
+    <definedName name="_bfs" localSheetId="4">'Cas 6'!$E$3</definedName>
     <definedName name="_bgauche" localSheetId="1">'Cas 3'!$B$3</definedName>
     <definedName name="_bm" localSheetId="0">'Cas 2'!$E$22</definedName>
     <definedName name="_bm" localSheetId="1">'Cas 3'!$E$22</definedName>
@@ -59,79 +77,102 @@
     <definedName name="_cf" localSheetId="0">'Cas 2'!$B$11</definedName>
     <definedName name="_cf" localSheetId="1">'Cas 3'!$B$22</definedName>
     <definedName name="_cf" localSheetId="3">'Cas 5'!$E$12</definedName>
+    <definedName name="_cf_sup" localSheetId="4">'Cas 6'!$E$12</definedName>
     <definedName name="_cw" localSheetId="0">'Cas 2'!$B$12</definedName>
     <definedName name="_cw" localSheetId="1">'Cas 3'!$B$23</definedName>
     <definedName name="_cw" localSheetId="3">'Cas 5'!$E$13</definedName>
+    <definedName name="_cw" localSheetId="4">'Cas 6'!$E$13</definedName>
     <definedName name="_d" localSheetId="0">'Cas 2'!$H$13</definedName>
     <definedName name="_dsc" localSheetId="1">'Cas 3'!$H$14</definedName>
+    <definedName name="_dsc" localSheetId="4">'Cas 6'!$H$16</definedName>
     <definedName name="_dw" localSheetId="0">'Cas 2'!$B$9</definedName>
     <definedName name="_dw" localSheetId="1">'Cas 3'!$B$20</definedName>
     <definedName name="_Ecm_dalle" localSheetId="0">'Cas 2'!$H$8</definedName>
     <definedName name="_Ecm_dalle" localSheetId="1">'Cas 3'!$H$8</definedName>
+    <definedName name="_Ecm_dalle" localSheetId="4">'Cas 6'!$H$10</definedName>
     <definedName name="_ep" localSheetId="0">'Cas 2'!$E$19</definedName>
     <definedName name="_ep" localSheetId="1">'Cas 3'!$E$19</definedName>
     <definedName name="_epsilon" localSheetId="0">'Cas 2'!$B$15</definedName>
     <definedName name="_epsilon" localSheetId="1">'Cas 3'!$B$26</definedName>
     <definedName name="_epsilon" localSheetId="3">'Cas 5'!$E$16</definedName>
+    <definedName name="_epsilon" localSheetId="4">'Cas 6'!$E$16</definedName>
     <definedName name="_eta" localSheetId="1">'Cas 3'!$H$28</definedName>
     <definedName name="_fck_dalle" localSheetId="0">'Cas 2'!$H$5</definedName>
     <definedName name="_fck_dalle" localSheetId="1">'Cas 3'!$H$5</definedName>
+    <definedName name="_fck_dalle" localSheetId="4">'Cas 6'!$H$7</definedName>
     <definedName name="_fck_enrobage" localSheetId="0">'Cas 2'!$E$6</definedName>
     <definedName name="_fck_enrobage" localSheetId="1">'Cas 3'!$E$6</definedName>
     <definedName name="_fcm_dalle" localSheetId="0">'Cas 2'!$H$6</definedName>
+    <definedName name="_fcm_dalle" localSheetId="4">'Cas 6'!$H$8</definedName>
     <definedName name="_fcm_enrobage" localSheetId="0">'Cas 2'!$E$7</definedName>
     <definedName name="_fcm_enrobage" localSheetId="1">'Cas 3'!$E$7</definedName>
     <definedName name="_fctm_dalle" localSheetId="0">'Cas 2'!$H$7</definedName>
+    <definedName name="_fctm_dalle" localSheetId="4">'Cas 6'!$H$9</definedName>
     <definedName name="_fctm_enrobage" localSheetId="0">'Cas 2'!$E$8</definedName>
     <definedName name="_fusc" localSheetId="0">'Cas 2'!$H$14</definedName>
     <definedName name="_fusc" localSheetId="1">'Cas 3'!$H$15</definedName>
+    <definedName name="_fusc" localSheetId="4">'Cas 6'!$H$17</definedName>
     <definedName name="_fy" localSheetId="0">'Cas 2'!$B$14</definedName>
     <definedName name="_fy" localSheetId="1">'Cas 3'!$B$25</definedName>
     <definedName name="_fy" localSheetId="3">'Cas 5'!$E$15</definedName>
+    <definedName name="_fy" localSheetId="4">'Cas 6'!$E$15</definedName>
     <definedName name="_fyd" localSheetId="0">'Cas 2'!$E$12</definedName>
     <definedName name="_fyd" localSheetId="1">'Cas 3'!$E$12</definedName>
     <definedName name="_fyp" localSheetId="0">'Cas 2'!$E$24</definedName>
     <definedName name="_h" localSheetId="0">'Cas 2'!$B$3</definedName>
     <definedName name="_h" localSheetId="1">'Cas 3'!$B$14</definedName>
     <definedName name="_h" localSheetId="3">'Cas 5'!$E$2</definedName>
+    <definedName name="_h" localSheetId="4">'Cas 6'!$E$2</definedName>
+    <definedName name="_h0_dalle" localSheetId="4">'Cas 6'!$H$2</definedName>
     <definedName name="_hp" localSheetId="0">'Cas 2'!$E$17</definedName>
     <definedName name="_hp" localSheetId="1">'Cas 3'!$E$17</definedName>
     <definedName name="_hpg" localSheetId="0">'Cas 2'!$E$18</definedName>
     <definedName name="_hsc" localSheetId="0">'Cas 2'!$H$12</definedName>
     <definedName name="_hsc" localSheetId="1">'Cas 3'!$H$13</definedName>
+    <definedName name="_hsc" localSheetId="4">'Cas 6'!$H$15</definedName>
     <definedName name="_hw" localSheetId="0">'Cas 2'!$B$8</definedName>
     <definedName name="_hw" localSheetId="1">'Cas 3'!$B$19</definedName>
     <definedName name="_hw" localSheetId="3">'Cas 5'!$E$9</definedName>
+    <definedName name="_hw" localSheetId="4">'Cas 6'!$E$8</definedName>
     <definedName name="_Iy" localSheetId="0">'Cas 2'!$B$34</definedName>
     <definedName name="_Iy" localSheetId="1">'Cas 3'!$B$35</definedName>
     <definedName name="_Iy" localSheetId="3">'Cas 5'!$B$13</definedName>
+    <definedName name="_Iy" localSheetId="4">'Cas 6'!$B$17</definedName>
     <definedName name="_Iz" localSheetId="0">'Cas 2'!$B$35</definedName>
     <definedName name="_Iz" localSheetId="3">'Cas 5'!$B$14</definedName>
+    <definedName name="_Iz" localSheetId="4">'Cas 6'!$B$18</definedName>
     <definedName name="_kr" localSheetId="0">'Cas 2'!$B$72</definedName>
     <definedName name="_kr" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_kt" localSheetId="1">'Cas 3'!$H$21</definedName>
     <definedName name="_kt_max" localSheetId="1">'Cas 3'!$H$20</definedName>
     <definedName name="_L" localSheetId="0">'Cas 2'!$B$2</definedName>
     <definedName name="_L" localSheetId="1">'Cas 3'!$B$2</definedName>
+    <definedName name="_L" localSheetId="4">'Cas 6'!$B$2</definedName>
     <definedName name="_L_ConsoleD" localSheetId="3">'Cas 5'!$B$4</definedName>
     <definedName name="_L_ConsoleG" localSheetId="3">'Cas 5'!$B$2</definedName>
     <definedName name="_L_tot" localSheetId="3">'Cas 5'!$B$5</definedName>
     <definedName name="_L_Travee" localSheetId="3">'Cas 5'!$B$3</definedName>
+    <definedName name="_L_Travee" localSheetId="4">'Cas 6'!$B$2</definedName>
     <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$53</definedName>
     <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$54</definedName>
     <definedName name="_Mpl_Rd" localSheetId="3">'Cas 5'!$B$69</definedName>
+    <definedName name="_Mpl_Rd" localSheetId="4">'Cas 6'!$B$103</definedName>
     <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$55</definedName>
     <definedName name="_Mpl_z_Rd" localSheetId="0">'Cas 2'!$B$56</definedName>
     <definedName name="_n" localSheetId="0">'Cas 2'!$B$69</definedName>
     <definedName name="_n_dalle" localSheetId="1">'Cas 3'!$B$70</definedName>
+    <definedName name="_n_dalle" localSheetId="4">'Cas 6'!$B$89</definedName>
     <definedName name="_n_enrobage" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_Na" localSheetId="1">'Cas 3'!$H$23</definedName>
+    <definedName name="_Na" localSheetId="4">'Cas 6'!$H$24</definedName>
     <definedName name="_Ncp" localSheetId="1">'Cas 3'!$B$104</definedName>
     <definedName name="_Nf" localSheetId="1">'Cas 3'!$B$102</definedName>
     <definedName name="_nr" localSheetId="1">'Cas 3'!$H$16</definedName>
+    <definedName name="_nr" localSheetId="4">'Cas 6'!$H$18</definedName>
     <definedName name="_Ns_inf" localSheetId="1">'Cas 3'!$H$24</definedName>
     <definedName name="_NtRd" localSheetId="0">'Cas 2'!$B$51</definedName>
     <definedName name="_Nw" localSheetId="1">'Cas 3'!$B$103</definedName>
+    <definedName name="_PRd" localSheetId="4">'Cas 6'!$H$23</definedName>
     <definedName name="_qBac" localSheetId="0">'Cas 2'!$E$26</definedName>
     <definedName name="_qBac" localSheetId="1">'Cas 3'!$E$26</definedName>
     <definedName name="_qDalle" localSheetId="0">'Cas 2'!$H$10</definedName>
@@ -143,51 +184,70 @@
     <definedName name="_r" localSheetId="0">'Cas 2'!$B$7</definedName>
     <definedName name="_r" localSheetId="1">'Cas 3'!$B$18</definedName>
     <definedName name="_r" localSheetId="3">'Cas 5'!$E$8</definedName>
+    <definedName name="_r" localSheetId="4">'Cas 6'!$E$10</definedName>
     <definedName name="_rho" localSheetId="0">'Cas 2'!$B$17</definedName>
     <definedName name="_rho" localSheetId="1">'Cas 3'!$B$28</definedName>
     <definedName name="_rhoA" localSheetId="3">'Cas 5'!$E$18</definedName>
+    <definedName name="_rhoA" localSheetId="4">'Cas 6'!$E$18</definedName>
     <definedName name="_rhoC" localSheetId="3">'Cas 5'!$H$6</definedName>
+    <definedName name="_rhoC" localSheetId="4">'Cas 6'!$H$6</definedName>
+    <definedName name="_sx" localSheetId="4">'Cas 6'!$H$19</definedName>
     <definedName name="_tc" localSheetId="0">'Cas 2'!$H$4</definedName>
     <definedName name="_tc" localSheetId="1">'Cas 3'!$H$4</definedName>
     <definedName name="_td" localSheetId="0">'Cas 2'!$H$3</definedName>
     <definedName name="_td" localSheetId="1">'Cas 3'!$H$3</definedName>
     <definedName name="_td" localSheetId="3">'Cas 5'!$H$2</definedName>
+    <definedName name="_td" localSheetId="4">'Cas 6'!$H$3</definedName>
     <definedName name="_tf" localSheetId="0">'Cas 2'!$B$5</definedName>
     <definedName name="_tf" localSheetId="1">'Cas 3'!$B$16</definedName>
     <definedName name="_tf" localSheetId="3">'Cas 5'!$E$4</definedName>
+    <definedName name="_tf" localSheetId="4">'Cas 6'!$B$16</definedName>
+    <definedName name="_tfi" localSheetId="4">'Cas 6'!$E$6</definedName>
+    <definedName name="_tfs" localSheetId="4">'Cas 6'!$E$4</definedName>
     <definedName name="_th" localSheetId="3">'Cas 5'!$H$3</definedName>
     <definedName name="_theta" localSheetId="3">'Cas 5'!$H$4</definedName>
+    <definedName name="_tj" localSheetId="4">'Cas 6'!$H$4</definedName>
     <definedName name="_tp" localSheetId="0">'Cas 2'!$E$23</definedName>
     <definedName name="_tw" localSheetId="0">'Cas 2'!$B$6</definedName>
     <definedName name="_tw" localSheetId="1">'Cas 3'!$B$17</definedName>
     <definedName name="_tw" localSheetId="3">'Cas 5'!$E$5</definedName>
+    <definedName name="_tw" localSheetId="4">'Cas 6'!$E$7</definedName>
     <definedName name="_VplRd" localSheetId="0">'Cas 2'!$B$52</definedName>
     <definedName name="_VplRd" localSheetId="1">'Cas 3'!$B$53</definedName>
     <definedName name="_VplRd" localSheetId="3">'Cas 5'!$B$52</definedName>
+    <definedName name="_VplRd" localSheetId="4">'Cas 6'!$B$56</definedName>
     <definedName name="_Wel_y" localSheetId="0">'Cas 2'!$B$36</definedName>
     <definedName name="_Wel_y" localSheetId="1">'Cas 3'!$B$37</definedName>
     <definedName name="_Wel_y" localSheetId="3">'Cas 5'!$B$15</definedName>
+    <definedName name="_Wel_y" localSheetId="4">'Cas 6'!$B$19</definedName>
     <definedName name="_Wel_z" localSheetId="0">'Cas 2'!$B$37</definedName>
     <definedName name="_Wel_z" localSheetId="1">'Cas 3'!$B$38</definedName>
     <definedName name="_Wel_z" localSheetId="3">'Cas 5'!$B$16</definedName>
+    <definedName name="_Wel_z" localSheetId="4">'Cas 6'!$B$20</definedName>
     <definedName name="_Wpl_y" localSheetId="0">'Cas 2'!$B$38</definedName>
     <definedName name="_Wpl_y" localSheetId="1">'Cas 3'!$B$39</definedName>
     <definedName name="_Wpl_y" localSheetId="3">'Cas 5'!$B$17</definedName>
+    <definedName name="_Wpl_y" localSheetId="4">'Cas 6'!$B$21</definedName>
     <definedName name="_Wpl_z" localSheetId="0">'Cas 2'!$B$39</definedName>
     <definedName name="_Wpl_z" localSheetId="1">'Cas 3'!$B$40</definedName>
     <definedName name="_Wpl_z" localSheetId="3">'Cas 5'!$B$18</definedName>
+    <definedName name="_Wpl_z" localSheetId="4">'Cas 6'!$B$22</definedName>
     <definedName name="_za" localSheetId="0">'Cas 2'!$B$74</definedName>
     <definedName name="_za" localSheetId="1">'Cas 3'!$B$73</definedName>
     <definedName name="_zcr" localSheetId="0">'Cas 2'!$B$73</definedName>
     <definedName name="_zcr" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_zel" localSheetId="0">'Cas 2'!$B$77</definedName>
     <definedName name="_zel" localSheetId="1">'Cas 3'!$B$79</definedName>
+    <definedName name="_zel" localSheetId="4">'Cas 6'!$B$79</definedName>
+    <definedName name="_zp" localSheetId="4">'Cas 6'!$B$93</definedName>
     <definedName name="_zpl" localSheetId="0">'Cas 2'!$B$102</definedName>
     <definedName name="_zpl_a" localSheetId="1">'Cas 3'!$B$107</definedName>
     <definedName name="_zpl_c" localSheetId="1">'Cas 3'!$B$105</definedName>
     <definedName name="_zs" localSheetId="1">'Cas 3'!$B$74</definedName>
+    <definedName name="_zs" localSheetId="4">'Cas 6'!$B$74</definedName>
     <definedName name="_zs_inf" localSheetId="0">'Cas 2'!$E$11</definedName>
     <definedName name="_zs_inf" localSheetId="1">'Cas 3'!$E$11</definedName>
+    <definedName name="_zs_inf" localSheetId="4">'Cas 6'!$E$11</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -199,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="272">
   <si>
     <t>h (mm)</t>
   </si>
@@ -976,6 +1036,45 @@
   </si>
   <si>
     <t>Sans objet, l'ensemble des résultats sont dans l'article RCM 2022 n°3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PropSection section seule </t>
+  </si>
+  <si>
+    <t>tj (mm)</t>
+  </si>
+  <si>
+    <t>Ac, brute (mm2)</t>
+  </si>
+  <si>
+    <t>sx (mm)</t>
+  </si>
+  <si>
+    <t>bfs (mm)</t>
+  </si>
+  <si>
+    <t>tfs (mm)</t>
+  </si>
+  <si>
+    <t>bfi (mm)</t>
+  </si>
+  <si>
+    <t>tfi (mm)</t>
+  </si>
+  <si>
+    <t>cf ,sup</t>
+  </si>
+  <si>
+    <t>Classe semelle sup</t>
+  </si>
+  <si>
+    <t>beff (m)</t>
+  </si>
+  <si>
+    <t>Ah (mm2)</t>
+  </si>
+  <si>
+    <t>zp (mm)</t>
   </si>
 </sst>
 </file>
@@ -1244,7 +1343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1341,6 +1440,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -6292,4 +6404,1541 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I116"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="70" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="D1" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" s="71"/>
+      <c r="G1" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="71"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="1">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>300</v>
+      </c>
+      <c r="G2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="23">
+        <f>1/(1/_td-_bfs/(2*(_b_Gauche+_b_Droite)*1000*_td))</f>
+        <v>123.71134020618557</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E3" s="1">
+        <v>120</v>
+      </c>
+      <c r="G3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E4" s="1">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>260</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5">
+        <f>_L/8</f>
+        <v>1.25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E5" s="1">
+        <v>150</v>
+      </c>
+      <c r="G5" t="s">
+        <v>261</v>
+      </c>
+      <c r="H5" s="23">
+        <f>(_b_Gauche+_b_Droite)*1000*(_td-_tj)</f>
+        <v>220000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6">
+        <f>MIN(_b_Gauche,B5)</f>
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>227</v>
+      </c>
+      <c r="H6">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B7">
+        <f>MIN(_b_Droite,B5)</f>
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8">
+        <f>MIN(1,0.55+0.025*_L/_be1)</f>
+        <v>0.8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="6">
+        <f>_h-_tfs-_tfi</f>
+        <v>283.3</v>
+      </c>
+      <c r="G8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8">
+        <f>_fck_dalle+8</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9">
+        <f>MIN(1,0.55+0.025*_L/_be2)</f>
+        <v>0.8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="6">
+        <f>_hw-2*_r</f>
+        <v>283.3</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+      <c r="H9" s="26">
+        <f>0.3*_fck_dalle^(2/3)</f>
+        <v>2.5649639200150443</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="26">
+        <f>_be1+_be2</f>
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="13">
+        <f>22*(_fcm_dalle/10)^0.3*1000</f>
+        <v>31475.806210019346</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="26">
+        <f>_be1*_beta1+_be2*_beta2</f>
+        <v>1.6</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="G11" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" s="25">
+        <f>_rhoC*_Ac_brute*10^(-6)*9.81/1000</f>
+        <v>5.3955000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>267</v>
+      </c>
+      <c r="E12" s="6">
+        <f>(_bfs-2*_r-_tw)/2</f>
+        <v>56.45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="70" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="71"/>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="6">
+        <f>_hw-2*_r</f>
+        <v>283.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="79">
+        <f>(2*(_h-2*_r)+_bfs+_bfi+(_bfs-2*_r-_tw)+(_bfi-2*_r-_tw)+2*PI()*_r)/10</f>
+        <v>112.58</v>
+      </c>
+      <c r="G14" s="70" t="s">
+        <v>162</v>
+      </c>
+      <c r="H14" s="71"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="9">
+        <f>(_bfs*_tfs+_bfi*_tfi+(_h-_tfs-_tfi)*_tw+4*(1-PI()/4)*_r^2)/100</f>
+        <v>43.3643</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1">
+        <v>355</v>
+      </c>
+      <c r="G15" t="s">
+        <v>163</v>
+      </c>
+      <c r="H15" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="64">
+        <f>((_h-_tfs-_tfi)*_tw)/100</f>
+        <v>20.1143</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="14">
+        <f>SQRT(235/_fy)</f>
+        <v>0.81361651346682706</v>
+      </c>
+      <c r="G16" t="s">
+        <v>164</v>
+      </c>
+      <c r="H16" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="4">
+        <v>5921.277</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="G17" t="s">
+        <v>166</v>
+      </c>
+      <c r="H17" s="10">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="4">
+        <v>332.58</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="1">
+        <v>7850</v>
+      </c>
+      <c r="G18" t="s">
+        <v>171</v>
+      </c>
+      <c r="H18" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="4">
+        <f>_Iy/(_h/10/2)</f>
+        <v>394.7518</v>
+      </c>
+      <c r="D19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" s="31">
+        <f>_rhoA*_A*10^(-4)*9.81/1000</f>
+        <v>0.33394196965500006</v>
+      </c>
+      <c r="G19" t="s">
+        <v>262</v>
+      </c>
+      <c r="H19" s="10">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="4">
+        <v>51.758000000000003</v>
+      </c>
+      <c r="G20" t="s">
+        <v>165</v>
+      </c>
+      <c r="H20" s="3">
+        <f>0.8*_fusc*PI()*_dsc^2/4/(1000*1.25)</f>
+        <v>81.656276252105897</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="4">
+        <v>454.96199999999999</v>
+      </c>
+      <c r="G21" t="s">
+        <v>167</v>
+      </c>
+      <c r="H21" s="3">
+        <f>IF(_hsc/_dsc&gt;=4,1,FALSE)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="4">
+        <v>85.24</v>
+      </c>
+      <c r="G22" t="s">
+        <v>168</v>
+      </c>
+      <c r="H22" s="3">
+        <f>0.29*H21*_dsc^2*SQRT(_fck_dalle*_Ecm_dalle)/(1000*1.25)</f>
+        <v>74.293979654469197</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>172</v>
+      </c>
+      <c r="H23" s="26">
+        <f>MIN(H20,H22)</f>
+        <v>74.293979654469197</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="9">
+        <f>_rhoA*_A/10000</f>
+        <v>34.040975500000002</v>
+      </c>
+      <c r="G24" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="23">
+        <f>_A*100*_fy/1000</f>
+        <v>1539.4326500000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="9">
+        <f>B24*_L</f>
+        <v>340.40975500000002</v>
+      </c>
+      <c r="G25" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="23">
+        <f>0.85*_beff_mi_travee*1000*(_td-_tj)*_fck_dalle/1.5/1000</f>
+        <v>3116.6666666666665</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="9"/>
+      <c r="G26" t="s">
+        <v>179</v>
+      </c>
+      <c r="H26" s="23">
+        <f>MIN(H25,H24)</f>
+        <v>1539.4326500000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="11">
+        <f>B14*_L*100</f>
+        <v>112580</v>
+      </c>
+      <c r="G27" t="s">
+        <v>180</v>
+      </c>
+      <c r="H27" s="3">
+        <f>_nr*(_L*1000/2)/_sx*_PRd</f>
+        <v>1955.1047277491894</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="11">
+        <f>(B14-_bfs/10)*_L*100</f>
+        <v>100580</v>
+      </c>
+      <c r="G28" t="s">
+        <v>181</v>
+      </c>
+      <c r="H28" s="26">
+        <f>MIN(H27/H26,1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="9"/>
+      <c r="G29" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29">
+        <f>MAX(1-(355/_fy)*(0.75-0.03*_L),0.4)</f>
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="9">
+        <f>B14/_A*100</f>
+        <v>259.61447550173762</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="9">
+        <f>(B14-_bfs/10)/_A*100</f>
+        <v>231.9419430268677</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="71"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>17</v>
+      </c>
+      <c r="B34" s="23">
+        <f>_A*100*_fy/1000</f>
+        <v>1539.4326500000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="23">
+        <f>_Av*100*_fy/(1000*SQRT(3))</f>
+        <v>412.26137644441161</v>
+      </c>
+      <c r="D35" s="72" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="73"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="23">
+        <f>_Wel_y*1000*_fy*10^(-6)</f>
+        <v>140.136889</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="17">
+        <f>9*_epsilon</f>
+        <v>7.3225486212014435</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" s="23">
+        <f>_Wel_z*1000*_fy*10^(-6)</f>
+        <v>18.374089999999999</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" s="17">
+        <f>10*_epsilon</f>
+        <v>8.1361651346682713</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="23">
+        <f>_Wpl_y*1000*_fy*10^(-6)</f>
+        <v>161.51150999999999</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="18">
+        <f>14*_epsilon</f>
+        <v>11.390631188535579</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="23">
+        <f>_Wpl_z*1000*_fy*10^(-6)</f>
+        <v>30.260199999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D40" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E40" s="22"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3">
+        <f>_cf_sup/_tfs</f>
+        <v>9.4083333333333332</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="19">
+        <f>33*_epsilon</f>
+        <v>26.849344944405292</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3">
+        <f>_cw/_tw</f>
+        <v>39.901408450704231</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" s="19">
+        <f>38*_epsilon</f>
+        <v>30.917427511739429</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D43" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E43" s="20">
+        <f>42*_epsilon</f>
+        <v>34.171893565606737</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>268</v>
+      </c>
+      <c r="B44">
+        <f>IF(B41&lt;=E36,1,IF(B41&lt;=E37,2,IF(B41&lt;=E38,3,4)))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45">
+        <f>IF(B42&lt;=E41,1,IF(B42&lt;=E42,2,IF(B42&lt;=E43,3,4)))</f>
+        <v>4</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="22"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46">
+        <f>IF(B42&lt;=E46,1,IF(B42&lt;=E47,2,IF(B42&lt;=E48,3,4)))</f>
+        <v>1</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E46" s="19">
+        <f>72*_epsilon</f>
+        <v>58.580388969611548</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D47" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" s="19">
+        <f>83*_epsilon</f>
+        <v>67.530170617746649</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48" s="3">
+        <f>_hw/_tw</f>
+        <v>39.901408450704231</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="20">
+        <f>124*_epsilon</f>
+        <v>100.88844766988656</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B49" s="3">
+        <f>124*_epsilon</f>
+        <v>100.88844766988656</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="70" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="71"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>130</v>
+      </c>
+      <c r="B52" s="25">
+        <f>H11+E19</f>
+        <v>5.7294419696550003</v>
+      </c>
+      <c r="C52" s="26">
+        <f>B52*1.35</f>
+        <v>7.7347466590342506</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="28" t="s">
+        <v>228</v>
+      </c>
+      <c r="B53" s="53">
+        <v>34.424999999999997</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="B54" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="D54" s="24" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="B55" s="50">
+        <v>13.47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="B56" s="51">
+        <v>14.74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="B57" s="51">
+        <v>-19.5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B58" s="51">
+        <v>11.67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B59" s="51">
+        <v>25.17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B60" s="51">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B61" s="52">
+        <v>-19.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="B62" s="50">
+        <v>66.650000000000006</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="B63" s="51">
+        <v>96.16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B64" s="51">
+        <v>-71.05</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B65" s="51">
+        <v>63.95</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="B66" s="51">
+        <v>111.9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B67" s="51">
+        <v>-41.81</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="B68" s="51">
+        <v>49.15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="54" t="s">
+        <v>246</v>
+      </c>
+      <c r="B69" s="51">
+        <v>58.96</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B70" s="52">
+        <v>-71.06</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="54"/>
+      <c r="B71" s="76"/>
+    </row>
+    <row r="72" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="77" t="s">
+        <v>188</v>
+      </c>
+      <c r="B72" s="78"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>95</v>
+      </c>
+      <c r="B73" s="26">
+        <f>210000/_Ecm_dalle</f>
+        <v>6.6717909812633494</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>100</v>
+      </c>
+      <c r="B75" s="1">
+        <f>50/100</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>60</v>
+      </c>
+      <c r="B76" s="32">
+        <f>_h0_dalle</f>
+        <v>123.71134020618557</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>101</v>
+      </c>
+      <c r="B77" s="25">
+        <f>IF(_fck_dalle&lt;=35,1+(1-B75)/(0.1*B76^(1/3)),FALSE)</f>
+        <v>2.0034602351846282</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>102</v>
+      </c>
+      <c r="B78" s="34">
+        <f>16.8/SQRT(_fcm_dalle)</f>
+        <v>2.9245046200557239</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>103</v>
+      </c>
+      <c r="B79" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>104</v>
+      </c>
+      <c r="B80">
+        <v>18250</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>105</v>
+      </c>
+      <c r="B81" s="25">
+        <f>1/(0.1+B79^0.2)</f>
+        <v>0.48844954537902541</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>106</v>
+      </c>
+      <c r="B82" s="26">
+        <f>B77*B78*B81</f>
+        <v>2.8618887566193885</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>107</v>
+      </c>
+      <c r="B83" s="3">
+        <f>IF(_fcm_dalle&lt;=35,MIN(B76*1.5*(1+(0.012*B75)^18)+250,1500),FALSE)</f>
+        <v>435.56701030927832</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>108</v>
+      </c>
+      <c r="B84" s="26">
+        <f>((B80-B79)/(B83+B80-B79))^0.3</f>
+        <v>0.99293840715187665</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>109</v>
+      </c>
+      <c r="B85" s="25">
+        <f>B82*B84</f>
+        <v>2.8416792634435204</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>110</v>
+      </c>
+      <c r="B86" s="26">
+        <f>B73*(1+B74*B85)</f>
+        <v>27.526790070897466</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="54"/>
+      <c r="B87" s="76"/>
+    </row>
+    <row r="88" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="70" t="s">
+        <v>79</v>
+      </c>
+      <c r="B88" s="71"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>183</v>
+      </c>
+      <c r="B89" s="32">
+        <v>25.2</v>
+      </c>
+      <c r="C89" s="24"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>269</v>
+      </c>
+      <c r="B90" s="32">
+        <f>_beff_mi_travee</f>
+        <v>2</v>
+      </c>
+      <c r="C90" s="24"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B91" s="14"/>
+      <c r="C91" s="24"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>191</v>
+      </c>
+      <c r="B92" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="C92" s="44" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>271</v>
+      </c>
+      <c r="B93" s="35">
+        <f>_td+_h/2</f>
+        <v>270</v>
+      </c>
+      <c r="C93" s="42">
+        <f>B93</f>
+        <v>270</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>270</v>
+      </c>
+      <c r="B94" s="80">
+        <f>_A*100+_beff*1000*(_td-_tj)/B89</f>
+        <v>13066.58873015873</v>
+      </c>
+      <c r="C94" s="40">
+        <f>B94</f>
+        <v>13066.58873015873</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>90</v>
+      </c>
+      <c r="B95" s="45">
+        <f>(B89*_A*100/(_beff*1000))*(-1+SQRT(1+2*_zp/(B89*_A*100/(_beff*1000))))</f>
+        <v>125.61217341909804</v>
+      </c>
+      <c r="C95" s="46">
+        <f>_zp*_A*100/_Ah+_beff*1000*(_td-_tj)^2/(2*B89*_Ah)</f>
+        <v>126.35239879771393</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>91</v>
+      </c>
+      <c r="B96" s="35">
+        <f>_tj</f>
+        <v>10</v>
+      </c>
+      <c r="C96" s="42">
+        <f>-_h</f>
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>92</v>
+      </c>
+      <c r="B97" s="35">
+        <f>_td</f>
+        <v>120</v>
+      </c>
+      <c r="C97" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>93</v>
+      </c>
+      <c r="B98" s="35" t="b">
+        <f>IF(B96&lt;=_zel,IF(_zel&lt;=B97,TRUE,FALSE),FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="C98" s="35" t="b">
+        <f>IF(C96&lt;=C95,IF(C95&lt;=C97,TRUE,FALSE),FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>94</v>
+      </c>
+      <c r="B99" s="47">
+        <f>(_Iy*10^4+_A*100*(_zp-C95)^2+_beff*1000*B95^3/(3*B89))*10^(-4)</f>
+        <v>20112.625407572665</v>
+      </c>
+      <c r="C99" s="48">
+        <f>(_Iy*10^4+_A*100*(_zp-C95)^2+_beff*1000*(_td-_tj)/(3*B89)*((_td-_tj)^2+3*C95*(C95-(_td-_tj))))*10^(-4)</f>
+        <v>20194.300001846041</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B100" s="81"/>
+      <c r="C100" s="82"/>
+    </row>
+    <row r="101" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="102" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="70" t="s">
+        <v>134</v>
+      </c>
+      <c r="B102" s="71"/>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>123</v>
+      </c>
+      <c r="B103" s="23">
+        <f>_Wpl_y*1000*_fy*10^(-6)</f>
+        <v>161.51150999999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>248</v>
+      </c>
+      <c r="B104" s="23">
+        <f>_Av*100*_fy/(1000*SQRT(3))</f>
+        <v>412.26137644441161</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B105" s="23"/>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="21"/>
+      <c r="B106" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="C106" s="63" t="s">
+        <v>250</v>
+      </c>
+      <c r="D106" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="F106" s="21"/>
+      <c r="G106" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="H106" s="66" t="s">
+        <v>250</v>
+      </c>
+      <c r="I106" s="29" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B107" s="59">
+        <f>MAX(B63,ABS(B64))/_Mpl_Rd</f>
+        <v>0.59537552462979271</v>
+      </c>
+      <c r="C107" s="55">
+        <f>MAX(B66,ABS(B67))/_Mpl_Rd</f>
+        <v>0.69282987943088403</v>
+      </c>
+      <c r="D107" s="17">
+        <f>MAX(B69,ABS(B70))/_Mpl_Rd</f>
+        <v>0.43996864372080979</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="G107" s="67">
+        <f>B107</f>
+        <v>0.59537552462979271</v>
+      </c>
+      <c r="H107" s="68">
+        <f t="shared" ref="H107:I108" si="0">C107</f>
+        <v>0.69282987943088403</v>
+      </c>
+      <c r="I107" s="69">
+        <f t="shared" si="0"/>
+        <v>0.43996864372080979</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B108" s="59">
+        <f>B62/B104</f>
+        <v>0.16166928023873936</v>
+      </c>
+      <c r="C108" s="55">
+        <f>B65/B104</f>
+        <v>0.15512003707828032</v>
+      </c>
+      <c r="D108" s="17">
+        <f>B68/B104</f>
+        <v>0.11922048197650471</v>
+      </c>
+      <c r="F108" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="G108" s="59">
+        <f>B108</f>
+        <v>0.16166928023873936</v>
+      </c>
+      <c r="H108" s="55">
+        <f t="shared" si="0"/>
+        <v>0.15512003707828032</v>
+      </c>
+      <c r="I108" s="17">
+        <f t="shared" si="0"/>
+        <v>0.11922048197650471</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B109" s="60">
+        <f>1/B107</f>
+        <v>1.6796122088186354</v>
+      </c>
+      <c r="C109" s="56">
+        <f t="shared" ref="C109:D109" si="1">1/C107</f>
+        <v>1.4433557640750667</v>
+      </c>
+      <c r="D109" s="57">
+        <f t="shared" si="1"/>
+        <v>2.2728892485223753</v>
+      </c>
+      <c r="F109" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="G109" s="60">
+        <v>521.97</v>
+      </c>
+      <c r="H109" s="56">
+        <v>546.22</v>
+      </c>
+      <c r="I109" s="57">
+        <v>496.55</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B110" s="60">
+        <v>5.4870000000000001</v>
+      </c>
+      <c r="C110" s="56">
+        <v>4.9240000000000004</v>
+      </c>
+      <c r="D110" s="57">
+        <v>6.9660000000000002</v>
+      </c>
+      <c r="F110" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="G110" s="59">
+        <f>SQRT(_Mpl_Rd/G109)</f>
+        <v>0.55626145483781619</v>
+      </c>
+      <c r="H110" s="55">
+        <f>SQRT(_Mpl_Rd/H109)</f>
+        <v>0.54377337567286188</v>
+      </c>
+      <c r="I110" s="17">
+        <f>SQRT(_Mpl_Rd/I109)</f>
+        <v>0.57032215879907633</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B111" s="59">
+        <f>SQRT(B109/B110)</f>
+        <v>0.55326988435906932</v>
+      </c>
+      <c r="C111" s="55">
+        <f t="shared" ref="C111:D111" si="2">SQRT(C109/C110)</f>
+        <v>0.54141174564795125</v>
+      </c>
+      <c r="D111" s="17">
+        <f t="shared" si="2"/>
+        <v>0.57121210467017469</v>
+      </c>
+      <c r="F111" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="G111" s="60">
+        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+      <c r="H111" s="56">
+        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+      <c r="I111" s="57">
+        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B112" s="60">
+        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+      <c r="C112" s="56">
+        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+      <c r="D112" s="57">
+        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
+        <v>0.34</v>
+      </c>
+      <c r="F112" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="G112" s="59">
+        <f>0.5*(1+G111*(G110-0.2)+G110^2)</f>
+        <v>0.71527785039157066</v>
+      </c>
+      <c r="H112" s="55">
+        <f t="shared" ref="H112:I112" si="3">0.5*(1+H111*(H110-0.2)+H110^2)</f>
+        <v>0.70628621590971619</v>
+      </c>
+      <c r="I112" s="17">
+        <f t="shared" si="3"/>
+        <v>0.72558844940446243</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B113" s="59">
+        <f>0.5*(1+B112*(B111-0.2)+B111^2)</f>
+        <v>0.71310966281039079</v>
+      </c>
+      <c r="C113" s="55">
+        <f t="shared" ref="C113:D113" si="4">0.5*(1+C112*(C111-0.2)+C111^2)</f>
+        <v>0.70460333592293267</v>
+      </c>
+      <c r="D113" s="17">
+        <f t="shared" si="4"/>
+        <v>0.72624769205479511</v>
+      </c>
+      <c r="F113" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="G113" s="59">
+        <f>1/(G112+SQRT(G112^2-G110^2))</f>
+        <v>0.85841367892050768</v>
+      </c>
+      <c r="H113" s="55">
+        <f t="shared" ref="H113:I113" si="5">1/(H112+SQRT(H112^2-H110^2))</f>
+        <v>0.86429775508559659</v>
+      </c>
+      <c r="I113" s="17">
+        <f t="shared" si="5"/>
+        <v>0.85167689179151895</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B114" s="59">
+        <f>1/(B113+SQRT(B113^2-B111^2))</f>
+        <v>0.85983166175255588</v>
+      </c>
+      <c r="C114" s="55">
+        <f t="shared" ref="C114:D114" si="6">1/(C113+SQRT(C113^2-C111^2))</f>
+        <v>0.8654001614839576</v>
+      </c>
+      <c r="D114" s="17">
+        <f t="shared" si="6"/>
+        <v>0.85124646326009779</v>
+      </c>
+      <c r="F114" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="G114" s="60">
+        <f>G113*_Mpl_Rd</f>
+        <v>138.64368948710634</v>
+      </c>
+      <c r="H114" s="56">
+        <f>H113*_Mpl_Rd</f>
+        <v>139.59403551348487</v>
+      </c>
+      <c r="I114" s="57">
+        <f>I113*_Mpl_Rd</f>
+        <v>137.55562082535482</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B115" s="60">
+        <f>B114*_Mpl_Rd</f>
+        <v>138.87271003546454</v>
+      </c>
+      <c r="C115" s="56">
+        <f>C114*_Mpl_Rd</f>
+        <v>139.77208683551783</v>
+      </c>
+      <c r="D115" s="57">
+        <f>D114*_Mpl_Rd</f>
+        <v>137.48610166329792</v>
+      </c>
+      <c r="F115" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="G115" s="61">
+        <f>G107/G113</f>
+        <v>0.69357646464639655</v>
+      </c>
+      <c r="H115" s="58">
+        <f>H107/H113</f>
+        <v>0.80161018046641686</v>
+      </c>
+      <c r="I115" s="18">
+        <f>I107/I113</f>
+        <v>0.51659103113074623</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B116" s="61">
+        <f>B107/B114</f>
+        <v>0.6924326599188797</v>
+      </c>
+      <c r="C116" s="58">
+        <f t="shared" ref="C116:D116" si="7">C107/C114</f>
+        <v>0.80058903414444005</v>
+      </c>
+      <c r="D116" s="18">
+        <f t="shared" si="7"/>
+        <v>0.51685224281087871</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A88:B88"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_Ace" localSheetId="4">'Cas 6'!$E$4</definedName>
     <definedName name="_Acr" localSheetId="0">'Cas 2'!$B$71</definedName>
     <definedName name="_Acr" localSheetId="1">'Cas 3'!#REF!</definedName>
-    <definedName name="_Ah" localSheetId="4">'Cas 6'!$B$94</definedName>
+    <definedName name="_Ah" localSheetId="4">'Cas 6'!$B$102</definedName>
     <definedName name="_As_inf" localSheetId="0">'Cas 2'!$E$10</definedName>
     <definedName name="_As_inf" localSheetId="1">'Cas 3'!$E$10</definedName>
     <definedName name="_As_inf" localSheetId="4">'Cas 6'!$E$10</definedName>
@@ -58,7 +58,7 @@
     <definedName name="_be1" localSheetId="4">'Cas 6'!$B$3</definedName>
     <definedName name="_be2" localSheetId="1">'Cas 3'!$B$7</definedName>
     <definedName name="_be2" localSheetId="4">'Cas 6'!$B$4</definedName>
-    <definedName name="_beff" localSheetId="4">'Cas 6'!$B$90</definedName>
+    <definedName name="_beff" localSheetId="4">'Cas 6'!$B$98</definedName>
     <definedName name="_beff_appui" localSheetId="1">'Cas 3'!$B$11</definedName>
     <definedName name="_beff_mi_travee" localSheetId="1">'Cas 3'!$B$10</definedName>
     <definedName name="_beff_mi_travee" localSheetId="4">'Cas 6'!$B$10</definedName>
@@ -156,12 +156,12 @@
     <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$53</definedName>
     <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$54</definedName>
     <definedName name="_Mpl_Rd" localSheetId="3">'Cas 5'!$B$69</definedName>
-    <definedName name="_Mpl_Rd" localSheetId="4">'Cas 6'!$B$103</definedName>
+    <definedName name="_Mpl_Rd" localSheetId="4">'Cas 6'!$B$111</definedName>
     <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$55</definedName>
     <definedName name="_Mpl_z_Rd" localSheetId="0">'Cas 2'!$B$56</definedName>
     <definedName name="_n" localSheetId="0">'Cas 2'!$B$69</definedName>
     <definedName name="_n_dalle" localSheetId="1">'Cas 3'!$B$70</definedName>
-    <definedName name="_n_dalle" localSheetId="4">'Cas 6'!$B$89</definedName>
+    <definedName name="_n_dalle" localSheetId="4">'Cas 6'!$B$97</definedName>
     <definedName name="_n_enrobage" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_Na" localSheetId="1">'Cas 3'!$H$23</definedName>
     <definedName name="_Na" localSheetId="4">'Cas 6'!$H$24</definedName>
@@ -215,7 +215,7 @@
     <definedName name="_VplRd" localSheetId="0">'Cas 2'!$B$52</definedName>
     <definedName name="_VplRd" localSheetId="1">'Cas 3'!$B$53</definedName>
     <definedName name="_VplRd" localSheetId="3">'Cas 5'!$B$52</definedName>
-    <definedName name="_VplRd" localSheetId="4">'Cas 6'!$B$56</definedName>
+    <definedName name="_VplRd" localSheetId="4">'Cas 6'!$B$64</definedName>
     <definedName name="_Wel_y" localSheetId="0">'Cas 2'!$B$36</definedName>
     <definedName name="_Wel_y" localSheetId="1">'Cas 3'!$B$37</definedName>
     <definedName name="_Wel_y" localSheetId="3">'Cas 5'!$B$15</definedName>
@@ -238,13 +238,13 @@
     <definedName name="_zcr" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_zel" localSheetId="0">'Cas 2'!$B$77</definedName>
     <definedName name="_zel" localSheetId="1">'Cas 3'!$B$79</definedName>
-    <definedName name="_zel" localSheetId="4">'Cas 6'!$B$79</definedName>
-    <definedName name="_zp" localSheetId="4">'Cas 6'!$B$93</definedName>
+    <definedName name="_zel" localSheetId="4">'Cas 6'!$B$87</definedName>
+    <definedName name="_zp" localSheetId="4">'Cas 6'!$B$101</definedName>
     <definedName name="_zpl" localSheetId="0">'Cas 2'!$B$102</definedName>
     <definedName name="_zpl_a" localSheetId="1">'Cas 3'!$B$107</definedName>
     <definedName name="_zpl_c" localSheetId="1">'Cas 3'!$B$105</definedName>
     <definedName name="_zs" localSheetId="1">'Cas 3'!$B$74</definedName>
-    <definedName name="_zs" localSheetId="4">'Cas 6'!$B$74</definedName>
+    <definedName name="_zs" localSheetId="4">'Cas 6'!$B$82</definedName>
     <definedName name="_zs_inf" localSheetId="0">'Cas 2'!$E$11</definedName>
     <definedName name="_zs_inf" localSheetId="1">'Cas 3'!$E$11</definedName>
     <definedName name="_zs_inf" localSheetId="4">'Cas 6'!$E$11</definedName>
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="287">
   <si>
     <t>h (mm)</t>
   </si>
@@ -1075,6 +1075,51 @@
   </si>
   <si>
     <t>zp (mm)</t>
+  </si>
+  <si>
+    <t>Classe section flexion pure</t>
+  </si>
+  <si>
+    <t>Classe section compression pure</t>
+  </si>
+  <si>
+    <t>zCDG par rapport arase inf (mm)</t>
+  </si>
+  <si>
+    <t>zANP par rapport arase inf (mm)</t>
+  </si>
+  <si>
+    <t>psi</t>
+  </si>
+  <si>
+    <t>456 epsilon/(13alpha-1)</t>
+  </si>
+  <si>
+    <t>396 epsilon/(13alpha-1)</t>
+  </si>
+  <si>
+    <t>36 epsilon/alpha</t>
+  </si>
+  <si>
+    <t>41,5 epsilon/alpha</t>
+  </si>
+  <si>
+    <t>Classe ame plast. N+M (alpha&gt;0,5)</t>
+  </si>
+  <si>
+    <t>Classe ame plast. N+M (alpha&lt;=0,5)</t>
+  </si>
+  <si>
+    <t>Classe ame élast. N+M (psi&gt;-1)</t>
+  </si>
+  <si>
+    <t>42 epsilon/(0,67+0,33psi)</t>
+  </si>
+  <si>
+    <t>Classe ame élast. N+M (psi&lt;=-1)</t>
+  </si>
+  <si>
+    <t>62 epsilon(1-psi)*racine(-psi)</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1388,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1422,6 +1467,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1440,19 +1492,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -1746,20 +1793,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="71"/>
+      <c r="B1" s="76"/>
       <c r="C1"/>
-      <c r="D1" s="70" t="s">
+      <c r="D1" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="71"/>
+      <c r="E1" s="76"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="70" t="s">
+      <c r="G1" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="71"/>
+      <c r="H1" s="76"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -2021,10 +2068,10 @@
         <v>0.81361651346682706</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="70" t="s">
+      <c r="D15" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="71"/>
+      <c r="E15" s="76"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
@@ -2163,10 +2210,10 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="70" t="s">
+      <c r="A30" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="71"/>
+      <c r="B30" s="76"/>
       <c r="C30" s="24" t="s">
         <v>53</v>
       </c>
@@ -2434,10 +2481,10 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="70" t="s">
+      <c r="A50" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="71"/>
+      <c r="B50" s="76"/>
       <c r="D50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2474,10 +2521,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E52" s="72" t="s">
+      <c r="E52" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="F52" s="73"/>
+      <c r="F52" s="78"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -2725,10 +2772,10 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="70" t="s">
+      <c r="A68" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="B68" s="71"/>
+      <c r="B68" s="76"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -3012,10 +3059,10 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="70" t="s">
+      <c r="A96" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="B96" s="71"/>
+      <c r="B96" s="76"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -3119,10 +3166,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="70" t="s">
+      <c r="A109" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B109" s="71"/>
+      <c r="B109" s="76"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -3205,10 +3252,10 @@
     </row>
     <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="70" t="s">
+      <c r="A120" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="B120" s="71"/>
+      <c r="B120" s="76"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
@@ -3333,20 +3380,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="75" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="71"/>
+      <c r="B1" s="76"/>
       <c r="C1"/>
-      <c r="D1" s="70" t="s">
+      <c r="D1" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="71"/>
+      <c r="E1" s="76"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="70" t="s">
+      <c r="G1" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="71"/>
+      <c r="H1" s="76"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -3581,16 +3628,16 @@
         <f>500/1.15</f>
         <v>434.78260869565219</v>
       </c>
-      <c r="G12" s="70" t="s">
+      <c r="G12" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="71"/>
+      <c r="H12" s="76"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="71"/>
+      <c r="B13" s="76"/>
       <c r="C13"/>
       <c r="D13" t="s">
         <v>125</v>
@@ -3629,10 +3676,10 @@
         <v>200</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="70" t="s">
+      <c r="D15" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="71"/>
+      <c r="E15" s="76"/>
       <c r="G15" t="s">
         <v>166</v>
       </c>
@@ -3936,10 +3983,10 @@
       <c r="C30"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="70" t="s">
+      <c r="A31" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="71"/>
+      <c r="B31" s="76"/>
       <c r="C31" s="24" t="s">
         <v>53</v>
       </c>
@@ -4207,10 +4254,10 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="70" t="s">
+      <c r="A51" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="71"/>
+      <c r="B51" s="76"/>
       <c r="D51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4247,10 +4294,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E53" s="72" t="s">
+      <c r="E53" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="73"/>
+      <c r="F53" s="78"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -4498,10 +4545,10 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="70" t="s">
+      <c r="A69" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="71"/>
+      <c r="B69" s="76"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -4682,10 +4729,10 @@
       <c r="C84" s="36"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="74" t="s">
+      <c r="A85" s="79" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="75"/>
+      <c r="B85" s="80"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -4828,10 +4875,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="70" t="s">
+      <c r="A101" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="B101" s="71"/>
+      <c r="B101" s="76"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
@@ -4971,10 +5018,10 @@
     </row>
     <row r="117" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="118" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="70" t="s">
+      <c r="A118" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B118" s="71"/>
+      <c r="B118" s="76"/>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
@@ -5093,10 +5140,10 @@
     </row>
     <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="70" t="s">
+      <c r="A133" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="B133" s="71"/>
+      <c r="B133" s="76"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
@@ -5212,10 +5259,10 @@
     </row>
     <row r="146" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="147" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="70" t="s">
+      <c r="A147" s="75" t="s">
         <v>207</v>
       </c>
-      <c r="B147" s="71"/>
+      <c r="B147" s="76"/>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
@@ -5281,6 +5328,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D15:E15"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="G12:H12"/>
@@ -5291,11 +5343,6 @@
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A118:B118"/>
     <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D15:E15"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16">
@@ -5334,18 +5381,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="75" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="D1" s="70" t="s">
+      <c r="B1" s="76"/>
+      <c r="D1" s="75" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="G1" s="70" t="s">
+      <c r="E1" s="76"/>
+      <c r="G1" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="71"/>
+      <c r="H1" s="76"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -5469,10 +5516,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="75" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="71"/>
+      <c r="B9" s="76"/>
       <c r="D9" t="s">
         <v>32</v>
       </c>
@@ -5671,10 +5718,10 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="70" t="s">
+      <c r="A29" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="71"/>
+      <c r="B29" s="76"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -5693,10 +5740,10 @@
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>1042.1194079466816</v>
       </c>
-      <c r="D31" s="72" t="s">
+      <c r="D31" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="73"/>
+      <c r="E31" s="78"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -5876,10 +5923,10 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="70" t="s">
+      <c r="A47" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="71"/>
+      <c r="B47" s="76"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -6043,10 +6090,10 @@
     </row>
     <row r="67" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="70" t="s">
+      <c r="A68" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="71"/>
+      <c r="B68" s="76"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -6408,28 +6455,30 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="75" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="D1" s="70" t="s">
+      <c r="B1" s="76"/>
+      <c r="D1" s="75" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="G1" s="70" t="s">
+      <c r="E1" s="76"/>
+      <c r="G1" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="71"/>
+      <c r="H1" s="76"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -6651,10 +6700,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="75" t="s">
         <v>259</v>
       </c>
-      <c r="B13" s="71"/>
+      <c r="B13" s="76"/>
       <c r="D13" t="s">
         <v>38</v>
       </c>
@@ -6667,14 +6716,14 @@
       <c r="A14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="79">
+      <c r="B14" s="71">
         <f>(2*(_h-2*_r)+_bfs+_bfi+(_bfs-2*_r-_tw)+(_bfi-2*_r-_tw)+2*PI()*_r)/10</f>
         <v>112.58</v>
       </c>
-      <c r="G14" s="70" t="s">
+      <c r="G14" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="H14" s="71"/>
+      <c r="H14" s="76"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -6688,7 +6737,7 @@
         <v>8</v>
       </c>
       <c r="E15" s="1">
-        <v>355</v>
+        <v>420</v>
       </c>
       <c r="G15" t="s">
         <v>163</v>
@@ -6710,7 +6759,7 @@
       </c>
       <c r="E16" s="14">
         <f>SQRT(235/_fy)</f>
-        <v>0.81361651346682706</v>
+        <v>0.74801324154309567</v>
       </c>
       <c r="G16" t="s">
         <v>164</v>
@@ -6739,7 +6788,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="4">
-        <v>332.58</v>
+        <v>388.18299999999999</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
@@ -6759,8 +6808,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="4">
-        <f>_Iy/(_h/10/2)</f>
-        <v>394.7518</v>
+        <v>332.58</v>
       </c>
       <c r="D19" t="s">
         <v>124</v>
@@ -6843,7 +6891,7 @@
       </c>
       <c r="H24" s="23">
         <f>_A*100*_fy/1000</f>
-        <v>1539.4326500000002</v>
+        <v>1821.3006</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -6869,7 +6917,7 @@
       </c>
       <c r="H26" s="23">
         <f>MIN(H25,H24)</f>
-        <v>1539.4326500000002</v>
+        <v>1821.3006</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -6911,7 +6959,7 @@
       </c>
       <c r="H29">
         <f>MAX(1-(355/_fy)*(0.75-0.03*_L),0.4)</f>
-        <v>0.55000000000000004</v>
+        <v>0.61964285714285716</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -6933,98 +6981,148 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="70" t="s">
+    <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="71"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="76"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>17</v>
       </c>
       <c r="B34" s="23">
         <f>_A*100*_fy/1000</f>
-        <v>1539.4326500000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1821.3006</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>22</v>
       </c>
       <c r="B35" s="23">
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
-        <v>412.26137644441161</v>
-      </c>
-      <c r="D35" s="72" t="s">
+        <v>487.74585382155738</v>
+      </c>
+      <c r="D35" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="73"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E35" s="78"/>
+      <c r="G35" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="H35" s="22"/>
+      <c r="J35" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="K35" s="22"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>18</v>
       </c>
       <c r="B36" s="23">
         <f>_Wel_y*1000*_fy*10^(-6)</f>
-        <v>140.136889</v>
+        <v>139.68359999999998</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>41</v>
       </c>
       <c r="E36" s="17">
         <f>9*_epsilon</f>
-        <v>7.3225486212014435</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6.7321191738878614</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H36" s="19">
+        <f>33*_epsilon</f>
+        <v>24.684436970922157</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36" s="19">
+        <f>72*_epsilon</f>
+        <v>53.856953391102891</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>19</v>
       </c>
       <c r="B37" s="23">
         <f>_Wel_z*1000*_fy*10^(-6)</f>
-        <v>18.374089999999999</v>
+        <v>21.73836</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>42</v>
       </c>
       <c r="E37" s="17">
         <f>10*_epsilon</f>
-        <v>8.1361651346682713</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7.4801324154309565</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H37" s="19">
+        <f>38*_epsilon</f>
+        <v>28.424503178637636</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="K37" s="19">
+        <f>83*_epsilon</f>
+        <v>62.085099048076941</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>20</v>
       </c>
       <c r="B38" s="23">
         <f>_Wpl_y*1000*_fy*10^(-6)</f>
-        <v>161.51150999999999</v>
+        <v>191.08403999999999</v>
       </c>
       <c r="D38" s="16" t="s">
         <v>43</v>
       </c>
       <c r="E38" s="18">
         <f>14*_epsilon</f>
-        <v>11.390631188535579</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10.472185381603339</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H38" s="20">
+        <f>42*_epsilon</f>
+        <v>31.41655614481002</v>
+      </c>
+      <c r="J38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="K38" s="20">
+        <f>124*_epsilon</f>
+        <v>92.753641951343866</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>21</v>
       </c>
       <c r="B39" s="23">
         <f>_Wpl_z*1000*_fy*10^(-6)</f>
-        <v>30.260199999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D40" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40" s="22"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>35.800799999999995</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J40" s="77" t="s">
+        <v>281</v>
+      </c>
+      <c r="K40" s="78"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -7032,15 +7130,15 @@
         <f>_cf_sup/_tfs</f>
         <v>9.4083333333333332</v>
       </c>
-      <c r="D41" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E41" s="19">
-        <f>33*_epsilon</f>
-        <v>26.849344944405292</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="J41" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="K41" s="83">
+        <f>396*_epsilon/(13*B46-1)</f>
+        <v>35.433373133731216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -7048,895 +7146,963 @@
         <f>_cw/_tw</f>
         <v>39.901408450704231</v>
       </c>
-      <c r="D42" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="E42" s="19">
-        <f>38*_epsilon</f>
-        <v>30.917427511739429</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D43" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E43" s="20">
-        <f>42*_epsilon</f>
-        <v>34.171893565606737</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="J42" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="K42" s="20">
+        <f>456*_epsilon/(13*B46-1)</f>
+        <v>40.802066032781397</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>274</v>
+      </c>
+      <c r="B44" s="3">
+        <v>121.96</v>
+      </c>
+      <c r="C44" s="3">
+        <f>B44-300</f>
+        <v>-178.04000000000002</v>
+      </c>
+      <c r="J44" s="77" t="s">
+        <v>282</v>
+      </c>
+      <c r="K44" s="78"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>275</v>
+      </c>
+      <c r="B45" s="3">
+        <f>B44-31.93</f>
+        <v>90.03</v>
+      </c>
+      <c r="C45" s="3">
+        <f>-300+B45</f>
+        <v>-209.97</v>
+      </c>
+      <c r="J45" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="K45" s="83">
+        <f>36*_epsilon/B46</f>
+        <v>37.401762258419005</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>167</v>
+      </c>
+      <c r="B46" s="26">
+        <f>(_h-B45-_tfs)/_hw</f>
+        <v>0.71997882103776911</v>
+      </c>
+      <c r="J46" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="K46" s="20">
+        <f>41.5*_epsilon/B46</f>
+        <v>43.115920381233018</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>276</v>
+      </c>
+      <c r="B47" s="26">
+        <f>-(B44-_tfi)/(_hw-B44+_tfi)</f>
+        <v>-0.64671006742617987</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J48" s="77" t="s">
+        <v>283</v>
+      </c>
+      <c r="K48" s="78"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>268</v>
       </c>
-      <c r="B44">
+      <c r="B49">
         <f>IF(B41&lt;=E36,1,IF(B41&lt;=E37,2,IF(B41&lt;=E38,3,4)))</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+      <c r="J49" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="K49" s="84">
+        <f>42*_epsilon/(0.67+0.33*B47)</f>
+        <v>68.807581305815532</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>35</v>
       </c>
-      <c r="B45">
-        <f>IF(B42&lt;=E41,1,IF(B42&lt;=E42,2,IF(B42&lt;=E43,3,4)))</f>
+      <c r="B50">
+        <f>IF(B42&lt;=H36,1,IF(B42&lt;=H37,2,IF(B42&lt;=H38,3,4)))</f>
         <v>4</v>
       </c>
-      <c r="D45" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="E45" s="22"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>36</v>
       </c>
-      <c r="B46">
-        <f>IF(B42&lt;=E46,1,IF(B42&lt;=E47,2,IF(B42&lt;=E48,3,4)))</f>
-        <v>1</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E46" s="19">
-        <f>72*_epsilon</f>
-        <v>58.580388969611548</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D47" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E47" s="19">
-        <f>83*_epsilon</f>
-        <v>67.530170617746649</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="B51">
+        <f>IF(B46&gt;0.5,IF(B42&lt;=K41,1,IF(B42&lt;=K42,2,IF(B47&gt;-1,IF(B42&lt;=K49,3,4),IF(B42&lt;=K52,3,4)))),IF(B42&lt;=K45,1,IF(B42&lt;=K46,2,IF(B47&gt;-1,IF(B42&lt;=K49,3,4),IF(B42&lt;=K52,3,4)))))</f>
+        <v>2</v>
+      </c>
+      <c r="J51" s="77" t="s">
+        <v>285</v>
+      </c>
+      <c r="K51" s="78"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="J52" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="K52" s="84">
+        <f>62*_epsilon*(1-B47)*SQRT(-B47)</f>
+        <v>61.414783744295001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B56" s="3">
         <f>_hw/_tw</f>
         <v>39.901408450704231</v>
       </c>
-      <c r="D48" s="16" t="s">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>51</v>
       </c>
-      <c r="E48" s="20">
+      <c r="B57" s="3">
         <f>124*_epsilon</f>
-        <v>100.88844766988656</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>51</v>
-      </c>
-      <c r="B49" s="3">
-        <f>124*_epsilon</f>
-        <v>100.88844766988656</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="70" t="s">
+        <v>92.753641951343866</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="B51" s="71"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="B59" s="76"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>130</v>
       </c>
-      <c r="B52" s="25">
+      <c r="B60" s="25">
         <f>H11+E19</f>
         <v>5.7294419696550003</v>
       </c>
-      <c r="C52" s="26">
-        <f>B52*1.35</f>
+      <c r="C60" s="26">
+        <f>B60*1.35</f>
         <v>7.7347466590342506</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="28" t="s">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="B53" s="53">
+      <c r="B61" s="53">
         <v>34.424999999999997</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="B54" s="52" t="s">
+      <c r="B62" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="D54" s="24" t="s">
+      <c r="D62" s="24" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="28" t="s">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="B55" s="50">
+      <c r="B63" s="50">
         <v>13.47</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="15" t="s">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="B56" s="51">
+      <c r="B64" s="51">
         <v>14.74</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="B57" s="51">
-        <v>-19.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="B58" s="51">
-        <v>11.67</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="B59" s="51">
-        <v>25.17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="B60" s="51">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="B61" s="52">
-        <v>-19.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="B62" s="50">
-        <v>66.650000000000006</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="B63" s="51">
-        <v>96.16</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="B64" s="51">
-        <v>-71.05</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B65" s="51">
-        <v>63.95</v>
+        <v>-19.5</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="15" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="B66" s="51">
-        <v>111.9</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B67" s="51">
-        <v>-41.81</v>
+        <v>25.17</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B68" s="51">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B69" s="52">
+        <v>-19.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="B70" s="50">
+        <v>66.650000000000006</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="B71" s="51">
+        <v>96.16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B72" s="51">
+        <v>-71.05</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B73" s="51">
+        <v>63.95</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="B74" s="51">
+        <v>111.9</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B75" s="51">
+        <v>-41.81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="B68" s="51">
+      <c r="B76" s="51">
         <v>49.15</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="54" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="54" t="s">
         <v>246</v>
       </c>
-      <c r="B69" s="51">
+      <c r="B77" s="51">
         <v>58.96</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="16" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="B70" s="52">
+      <c r="B78" s="52">
         <v>-71.06</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="54"/>
-      <c r="B71" s="76"/>
-    </row>
-    <row r="72" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="77" t="s">
+    <row r="79" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="54"/>
+      <c r="B79" s="70"/>
+    </row>
+    <row r="80" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="81" t="s">
         <v>188</v>
       </c>
-      <c r="B72" s="78"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="B80" s="82"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>95</v>
       </c>
-      <c r="B73" s="26">
+      <c r="B81" s="26">
         <f>210000/_Ecm_dalle</f>
         <v>6.6717909812633494</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
         <v>96</v>
       </c>
-      <c r="B74" s="1">
+      <c r="B82" s="1">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
         <v>100</v>
       </c>
-      <c r="B75" s="1">
+      <c r="B83" s="1">
         <f>50/100</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
         <v>60</v>
       </c>
-      <c r="B76" s="32">
+      <c r="B84" s="32">
         <f>_h0_dalle</f>
         <v>123.71134020618557</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>101</v>
       </c>
-      <c r="B77" s="25">
-        <f>IF(_fck_dalle&lt;=35,1+(1-B75)/(0.1*B76^(1/3)),FALSE)</f>
+      <c r="B85" s="25">
+        <f>IF(_fck_dalle&lt;=35,1+(1-B83)/(0.1*B84^(1/3)),FALSE)</f>
         <v>2.0034602351846282</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
         <v>102</v>
       </c>
-      <c r="B78" s="34">
+      <c r="B86" s="34">
         <f>16.8/SQRT(_fcm_dalle)</f>
         <v>2.9245046200557239</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
         <v>103</v>
       </c>
-      <c r="B79" s="1">
+      <c r="B87" s="1">
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
         <v>104</v>
       </c>
-      <c r="B80">
+      <c r="B88">
         <v>18250</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
         <v>105</v>
       </c>
-      <c r="B81" s="25">
-        <f>1/(0.1+B79^0.2)</f>
+      <c r="B89" s="25">
+        <f>1/(0.1+B87^0.2)</f>
         <v>0.48844954537902541</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>106</v>
       </c>
-      <c r="B82" s="26">
-        <f>B77*B78*B81</f>
+      <c r="B90" s="26">
+        <f>B85*B86*B89</f>
         <v>2.8618887566193885</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>107</v>
       </c>
-      <c r="B83" s="3">
-        <f>IF(_fcm_dalle&lt;=35,MIN(B76*1.5*(1+(0.012*B75)^18)+250,1500),FALSE)</f>
+      <c r="B91" s="3">
+        <f>IF(_fcm_dalle&lt;=35,MIN(B84*1.5*(1+(0.012*B83)^18)+250,1500),FALSE)</f>
         <v>435.56701030927832</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>108</v>
       </c>
-      <c r="B84" s="26">
-        <f>((B80-B79)/(B83+B80-B79))^0.3</f>
+      <c r="B92" s="26">
+        <f>((B88-B87)/(B91+B88-B87))^0.3</f>
         <v>0.99293840715187665</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>109</v>
       </c>
-      <c r="B85" s="25">
-        <f>B82*B84</f>
+      <c r="B93" s="25">
+        <f>B90*B92</f>
         <v>2.8416792634435204</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
         <v>110</v>
       </c>
-      <c r="B86" s="26">
-        <f>B73*(1+B74*B85)</f>
+      <c r="B94" s="26">
+        <f>B81*(1+B82*B93)</f>
         <v>27.526790070897466</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="54"/>
-      <c r="B87" s="76"/>
-    </row>
-    <row r="88" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="70" t="s">
+    <row r="95" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="54"/>
+      <c r="B95" s="70"/>
+    </row>
+    <row r="96" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="B88" s="71"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="B96" s="76"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>183</v>
       </c>
-      <c r="B89" s="32">
+      <c r="B97" s="32">
         <v>25.2</v>
       </c>
-      <c r="C89" s="24"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="C97" s="24"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>269</v>
       </c>
-      <c r="B90" s="32">
+      <c r="B98" s="32">
         <f>_beff_mi_travee</f>
         <v>2</v>
       </c>
-      <c r="C90" s="24"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="14"/>
-      <c r="C91" s="24"/>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="C98" s="24"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B99" s="14"/>
+      <c r="C99" s="24"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
         <v>191</v>
       </c>
-      <c r="B92" s="43" t="s">
+      <c r="B100" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="C92" s="44" t="s">
+      <c r="C100" s="44" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
         <v>271</v>
       </c>
-      <c r="B93" s="35">
+      <c r="B101" s="35">
         <f>_td+_h/2</f>
         <v>270</v>
       </c>
-      <c r="C93" s="42">
-        <f>B93</f>
+      <c r="C101" s="42">
+        <f>B101</f>
         <v>270</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
         <v>270</v>
       </c>
-      <c r="B94" s="80">
-        <f>_A*100+_beff*1000*(_td-_tj)/B89</f>
+      <c r="B102" s="72">
+        <f>_A*100+_beff*1000*(_td-_tj)/B97</f>
         <v>13066.58873015873</v>
       </c>
-      <c r="C94" s="40">
-        <f>B94</f>
+      <c r="C102" s="40">
+        <f>B102</f>
         <v>13066.58873015873</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
         <v>90</v>
       </c>
-      <c r="B95" s="45">
-        <f>(B89*_A*100/(_beff*1000))*(-1+SQRT(1+2*_zp/(B89*_A*100/(_beff*1000))))</f>
+      <c r="B103" s="45">
+        <f>(B97*_A*100/(_beff*1000))*(-1+SQRT(1+2*_zp/(B97*_A*100/(_beff*1000))))</f>
         <v>125.61217341909804</v>
       </c>
-      <c r="C95" s="46">
-        <f>_zp*_A*100/_Ah+_beff*1000*(_td-_tj)^2/(2*B89*_Ah)</f>
+      <c r="C103" s="46">
+        <f>_zp*_A*100/_Ah+_beff*1000*(_td-_tj)^2/(2*B97*_Ah)</f>
         <v>126.35239879771393</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>91</v>
       </c>
-      <c r="B96" s="35">
+      <c r="B104" s="35">
         <f>_tj</f>
         <v>10</v>
       </c>
-      <c r="C96" s="42">
+      <c r="C104" s="42">
         <f>-_h</f>
         <v>-300</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
         <v>92</v>
       </c>
-      <c r="B97" s="35">
+      <c r="B105" s="35">
         <f>_td</f>
         <v>120</v>
       </c>
-      <c r="C97" s="42">
+      <c r="C105" s="42">
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
         <v>93</v>
       </c>
-      <c r="B98" s="35" t="b">
-        <f>IF(B96&lt;=_zel,IF(_zel&lt;=B97,TRUE,FALSE),FALSE)</f>
+      <c r="B106" s="35" t="b">
+        <f>IF(B104&lt;=_zel,IF(_zel&lt;=B105,TRUE,FALSE),FALSE)</f>
         <v>1</v>
       </c>
-      <c r="C98" s="35" t="b">
-        <f>IF(C96&lt;=C95,IF(C95&lt;=C97,TRUE,FALSE),FALSE)</f>
+      <c r="C106" s="35" t="b">
+        <f>IF(C104&lt;=C103,IF(C103&lt;=C105,TRUE,FALSE),FALSE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
         <v>94</v>
       </c>
-      <c r="B99" s="47">
-        <f>(_Iy*10^4+_A*100*(_zp-C95)^2+_beff*1000*B95^3/(3*B89))*10^(-4)</f>
+      <c r="B107" s="47">
+        <f>(_Iy*10^4+_A*100*(_zp-C103)^2+_beff*1000*B103^3/(3*B97))*10^(-4)</f>
         <v>20112.625407572665</v>
       </c>
-      <c r="C99" s="48">
-        <f>(_Iy*10^4+_A*100*(_zp-C95)^2+_beff*1000*(_td-_tj)/(3*B89)*((_td-_tj)^2+3*C95*(C95-(_td-_tj))))*10^(-4)</f>
+      <c r="C107" s="48">
+        <f>(_Iy*10^4+_A*100*(_zp-C103)^2+_beff*1000*(_td-_tj)/(3*B97)*((_td-_tj)^2+3*C103*(C103-(_td-_tj))))*10^(-4)</f>
         <v>20194.300001846041</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B100" s="81"/>
-      <c r="C100" s="82"/>
-    </row>
-    <row r="101" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="102" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="70" t="s">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B108" s="73"/>
+      <c r="C108" s="74"/>
+    </row>
+    <row r="109" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="B102" s="71"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="B110" s="76"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>123</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B111" s="23">
         <f>_Wpl_y*1000*_fy*10^(-6)</f>
-        <v>161.51150999999999</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+        <v>191.08403999999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>248</v>
       </c>
-      <c r="B104" s="23">
+      <c r="B112" s="23">
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
-        <v>412.26137644441161</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B105" s="23"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="21"/>
-      <c r="B106" s="62" t="s">
+        <v>487.74585382155738</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B113" s="23"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="21"/>
+      <c r="B114" s="62" t="s">
         <v>249</v>
       </c>
-      <c r="C106" s="63" t="s">
+      <c r="C114" s="63" t="s">
         <v>250</v>
       </c>
-      <c r="D106" s="22" t="s">
+      <c r="D114" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="F106" s="21"/>
-      <c r="G106" s="65" t="s">
+      <c r="F114" s="21"/>
+      <c r="G114" s="65" t="s">
         <v>249</v>
       </c>
-      <c r="H106" s="66" t="s">
+      <c r="H114" s="66" t="s">
         <v>250</v>
       </c>
-      <c r="I106" s="29" t="s">
+      <c r="I114" s="29" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="15" t="s">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B107" s="59">
-        <f>MAX(B63,ABS(B64))/_Mpl_Rd</f>
-        <v>0.59537552462979271</v>
-      </c>
-      <c r="C107" s="55">
-        <f>MAX(B66,ABS(B67))/_Mpl_Rd</f>
-        <v>0.69282987943088403</v>
-      </c>
-      <c r="D107" s="17">
-        <f>MAX(B69,ABS(B70))/_Mpl_Rd</f>
-        <v>0.43996864372080979</v>
-      </c>
-      <c r="F107" s="15" t="s">
+      <c r="B115" s="59">
+        <f>MAX(B71,ABS(B72))/_Mpl_Rd</f>
+        <v>0.50323407438946766</v>
+      </c>
+      <c r="C115" s="55">
+        <f>MAX(B74,ABS(B75))/_Mpl_Rd</f>
+        <v>0.58560620761419957</v>
+      </c>
+      <c r="D115" s="17">
+        <f>MAX(B77,ABS(B78))/_Mpl_Rd</f>
+        <v>0.37187825838306543</v>
+      </c>
+      <c r="F115" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="G107" s="67">
-        <f>B107</f>
-        <v>0.59537552462979271</v>
-      </c>
-      <c r="H107" s="68">
-        <f t="shared" ref="H107:I108" si="0">C107</f>
-        <v>0.69282987943088403</v>
-      </c>
-      <c r="I107" s="69">
+      <c r="G115" s="67">
+        <f>B115</f>
+        <v>0.50323407438946766</v>
+      </c>
+      <c r="H115" s="68">
+        <f t="shared" ref="H115:I116" si="0">C115</f>
+        <v>0.58560620761419957</v>
+      </c>
+      <c r="I115" s="69">
         <f t="shared" si="0"/>
-        <v>0.43996864372080979</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="15" t="s">
+        <v>0.37187825838306543</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="B108" s="59">
-        <f>B62/B104</f>
-        <v>0.16166928023873936</v>
-      </c>
-      <c r="C108" s="55">
-        <f>B65/B104</f>
-        <v>0.15512003707828032</v>
-      </c>
-      <c r="D108" s="17">
-        <f>B68/B104</f>
-        <v>0.11922048197650471</v>
-      </c>
-      <c r="F108" s="15" t="s">
+      <c r="B116" s="59">
+        <f>B70/B112</f>
+        <v>0.1366490344875059</v>
+      </c>
+      <c r="C116" s="55">
+        <f>B73/B112</f>
+        <v>0.13111336467330836</v>
+      </c>
+      <c r="D116" s="17">
+        <f>B76/B112</f>
+        <v>0.10076969309918851</v>
+      </c>
+      <c r="F116" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="G108" s="59">
-        <f>B108</f>
-        <v>0.16166928023873936</v>
-      </c>
-      <c r="H108" s="55">
+      <c r="G116" s="59">
+        <f>B116</f>
+        <v>0.1366490344875059</v>
+      </c>
+      <c r="H116" s="55">
         <f t="shared" si="0"/>
-        <v>0.15512003707828032</v>
-      </c>
-      <c r="I108" s="17">
+        <v>0.13111336467330836</v>
+      </c>
+      <c r="I116" s="17">
         <f t="shared" si="0"/>
-        <v>0.11922048197650471</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="15" t="s">
+        <v>0.10076969309918851</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="B109" s="60">
-        <f>1/B107</f>
-        <v>1.6796122088186354</v>
-      </c>
-      <c r="C109" s="56">
-        <f t="shared" ref="C109:D109" si="1">1/C107</f>
-        <v>1.4433557640750667</v>
-      </c>
-      <c r="D109" s="57">
+      <c r="B117" s="60">
+        <f>1/B115</f>
+        <v>1.9871468386023292</v>
+      </c>
+      <c r="C117" s="56">
+        <f t="shared" ref="C117:D117" si="1">1/C115</f>
+        <v>1.7076321715817693</v>
+      </c>
+      <c r="D117" s="57">
         <f t="shared" si="1"/>
-        <v>2.2728892485223753</v>
-      </c>
-      <c r="F109" s="15" t="s">
+        <v>2.6890520686743593</v>
+      </c>
+      <c r="F117" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="G109" s="60">
+      <c r="G117" s="60">
         <v>521.97</v>
       </c>
-      <c r="H109" s="56">
+      <c r="H117" s="56">
         <v>546.22</v>
       </c>
-      <c r="I109" s="57">
+      <c r="I117" s="57">
         <v>496.55</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="15" t="s">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="B110" s="60">
+      <c r="B118" s="60">
         <v>5.4870000000000001</v>
       </c>
-      <c r="C110" s="56">
+      <c r="C118" s="56">
         <v>4.9240000000000004</v>
       </c>
-      <c r="D110" s="57">
+      <c r="D118" s="57">
         <v>6.9660000000000002</v>
       </c>
-      <c r="F110" s="15" t="s">
+      <c r="F118" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="G110" s="59">
-        <f>SQRT(_Mpl_Rd/G109)</f>
-        <v>0.55626145483781619</v>
-      </c>
-      <c r="H110" s="55">
-        <f>SQRT(_Mpl_Rd/H109)</f>
-        <v>0.54377337567286188</v>
-      </c>
-      <c r="I110" s="17">
-        <f>SQRT(_Mpl_Rd/I109)</f>
-        <v>0.57032215879907633</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="15" t="s">
+      <c r="G118" s="59">
+        <f>SQRT(_Mpl_Rd/G117)</f>
+        <v>0.60504745146955252</v>
+      </c>
+      <c r="H118" s="55">
+        <f>SQRT(_Mpl_Rd/H117)</f>
+        <v>0.59146412584669672</v>
+      </c>
+      <c r="I118" s="17">
+        <f>SQRT(_Mpl_Rd/I117)</f>
+        <v>0.62034132636172667</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="B111" s="59">
-        <f>SQRT(B109/B110)</f>
-        <v>0.55326988435906932</v>
-      </c>
-      <c r="C111" s="55">
-        <f t="shared" ref="C111:D111" si="2">SQRT(C109/C110)</f>
-        <v>0.54141174564795125</v>
-      </c>
-      <c r="D111" s="17">
+      <c r="B119" s="59">
+        <f>SQRT(B117/B118)</f>
+        <v>0.60179351021887739</v>
+      </c>
+      <c r="C119" s="55">
+        <f t="shared" ref="C119:D119" si="2">SQRT(C117/C118)</f>
+        <v>0.58889537294199867</v>
+      </c>
+      <c r="D119" s="17">
         <f t="shared" si="2"/>
-        <v>0.57121210467017469</v>
-      </c>
-      <c r="F111" s="15" t="s">
+        <v>0.62130932347274503</v>
+      </c>
+      <c r="F119" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G111" s="60">
+      <c r="G119" s="60">
         <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
-      <c r="H111" s="56">
+      <c r="H119" s="56">
         <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
-      <c r="I111" s="57">
+      <c r="I119" s="57">
         <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="15" t="s">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B112" s="60">
+      <c r="B120" s="60">
         <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
-      <c r="C112" s="56">
+      <c r="C120" s="56">
         <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
-      <c r="D112" s="57">
+      <c r="D120" s="57">
         <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
-      <c r="F112" s="15" t="s">
+      <c r="F120" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="G112" s="59">
-        <f>0.5*(1+G111*(G110-0.2)+G110^2)</f>
-        <v>0.71527785039157066</v>
-      </c>
-      <c r="H112" s="55">
-        <f t="shared" ref="H112:I112" si="3">0.5*(1+H111*(H110-0.2)+H110^2)</f>
-        <v>0.70628621590971619</v>
-      </c>
-      <c r="I112" s="17">
+      <c r="G120" s="59">
+        <f>0.5*(1+G119*(G118-0.2)+G118^2)</f>
+        <v>0.75189927601472428</v>
+      </c>
+      <c r="H120" s="55">
+        <f t="shared" ref="H120:I120" si="3">0.5*(1+H119*(H118-0.2)+H118^2)</f>
+        <v>0.74146380747573692</v>
+      </c>
+      <c r="I120" s="17">
         <f t="shared" si="3"/>
-        <v>0.72558844940446243</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="15" t="s">
+        <v>0.76386970607760662</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="B113" s="59">
-        <f>0.5*(1+B112*(B111-0.2)+B111^2)</f>
-        <v>0.71310966281039079</v>
-      </c>
-      <c r="C113" s="55">
-        <f t="shared" ref="C113:D113" si="4">0.5*(1+C112*(C111-0.2)+C111^2)</f>
-        <v>0.70460333592293267</v>
-      </c>
-      <c r="D113" s="17">
+      <c r="B121" s="59">
+        <f>0.5*(1+B120*(B119-0.2)+B119^2)</f>
+        <v>0.74938261120798821</v>
+      </c>
+      <c r="C121" s="55">
+        <f t="shared" ref="C121:D121" si="4">0.5*(1+C120*(C119-0.2)+C119^2)</f>
+        <v>0.73951109353638755</v>
+      </c>
+      <c r="D121" s="17">
         <f t="shared" si="4"/>
-        <v>0.72624769205479511</v>
-      </c>
-      <c r="F113" s="15" t="s">
+        <v>0.76463522270744666</v>
+      </c>
+      <c r="F121" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="G113" s="59">
-        <f>1/(G112+SQRT(G112^2-G110^2))</f>
-        <v>0.85841367892050768</v>
-      </c>
-      <c r="H113" s="55">
-        <f t="shared" ref="H113:I113" si="5">1/(H112+SQRT(H112^2-H110^2))</f>
-        <v>0.86429775508559659</v>
-      </c>
-      <c r="I113" s="17">
+      <c r="G121" s="59">
+        <f>1/(G120+SQRT(G120^2-G118^2))</f>
+        <v>0.83451829669193112</v>
+      </c>
+      <c r="H121" s="55">
+        <f t="shared" ref="H121:I121" si="5">1/(H120+SQRT(H120^2-H118^2))</f>
+        <v>0.84131960481121948</v>
+      </c>
+      <c r="I121" s="17">
         <f t="shared" si="5"/>
-        <v>0.85167689179151895</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="15" t="s">
+        <v>0.82672105507651716</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="B114" s="59">
-        <f>1/(B113+SQRT(B113^2-B111^2))</f>
-        <v>0.85983166175255588</v>
-      </c>
-      <c r="C114" s="55">
-        <f t="shared" ref="C114:D114" si="6">1/(C113+SQRT(C113^2-C111^2))</f>
-        <v>0.8654001614839576</v>
-      </c>
-      <c r="D114" s="17">
+      <c r="B122" s="59">
+        <f>1/(B121+SQRT(B121^2-B119^2))</f>
+        <v>0.83615814738565442</v>
+      </c>
+      <c r="C122" s="55">
+        <f t="shared" ref="C122:D122" si="6">1/(C121+SQRT(C121^2-C119^2))</f>
+        <v>0.84259280326221675</v>
+      </c>
+      <c r="D122" s="17">
         <f t="shared" si="6"/>
-        <v>0.85124646326009779</v>
-      </c>
-      <c r="F114" s="15" t="s">
+        <v>0.82622254561044939</v>
+      </c>
+      <c r="F122" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="G114" s="60">
-        <f>G113*_Mpl_Rd</f>
-        <v>138.64368948710634</v>
-      </c>
-      <c r="H114" s="56">
-        <f>H113*_Mpl_Rd</f>
-        <v>139.59403551348487</v>
-      </c>
-      <c r="I114" s="57">
-        <f>I113*_Mpl_Rd</f>
-        <v>137.55562082535482</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="15" t="s">
+      <c r="G122" s="60">
+        <f>G121*_Mpl_Rd</f>
+        <v>159.46312758581283</v>
+      </c>
+      <c r="H122" s="56">
+        <f>H121*_Mpl_Rd</f>
+        <v>160.76274901853125</v>
+      </c>
+      <c r="I122" s="57">
+        <f>I121*_Mpl_Rd</f>
+        <v>157.9731991570834</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B115" s="60">
-        <f>B114*_Mpl_Rd</f>
-        <v>138.87271003546454</v>
-      </c>
-      <c r="C115" s="56">
-        <f>C114*_Mpl_Rd</f>
-        <v>139.77208683551783</v>
-      </c>
-      <c r="D115" s="57">
-        <f>D114*_Mpl_Rd</f>
-        <v>137.48610166329792</v>
-      </c>
-      <c r="F115" s="16" t="s">
+      <c r="B123" s="60">
+        <f>B122*_Mpl_Rd</f>
+        <v>159.77647688136628</v>
+      </c>
+      <c r="C123" s="56">
+        <f>C122*_Mpl_Rd</f>
+        <v>161.00603692226954</v>
+      </c>
+      <c r="D123" s="57">
+        <f>D122*_Mpl_Rd</f>
+        <v>157.87794195432892</v>
+      </c>
+      <c r="F123" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="G115" s="61">
-        <f>G107/G113</f>
-        <v>0.69357646464639655</v>
-      </c>
-      <c r="H115" s="58">
-        <f>H107/H113</f>
-        <v>0.80161018046641686</v>
-      </c>
-      <c r="I115" s="18">
-        <f>I107/I113</f>
-        <v>0.51659103113074623</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="16" t="s">
+      <c r="G123" s="61">
+        <f>G115/G121</f>
+        <v>0.60302341648386937</v>
+      </c>
+      <c r="H123" s="58">
+        <f>H115/H121</f>
+        <v>0.69605677113111075</v>
+      </c>
+      <c r="I123" s="18">
+        <f>I115/I121</f>
+        <v>0.44982313695717624</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B116" s="61">
-        <f>B107/B114</f>
-        <v>0.6924326599188797</v>
-      </c>
-      <c r="C116" s="58">
-        <f t="shared" ref="C116:D116" si="7">C107/C114</f>
-        <v>0.80058903414444005</v>
-      </c>
-      <c r="D116" s="18">
+      <c r="B124" s="61">
+        <f>B115/B122</f>
+        <v>0.60184078330503321</v>
+      </c>
+      <c r="C124" s="58">
+        <f t="shared" ref="C124:D124" si="7">C115/C122</f>
+        <v>0.69500499570722962</v>
+      </c>
+      <c r="D124" s="18">
         <f t="shared" si="7"/>
-        <v>0.51685224281087871</v>
+        <v>0.45009454215305333</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A102:B102"/>
+  <mergeCells count="15">
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A110:B110"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A80:B80"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A96:B96"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_Ace" localSheetId="4">'Cas 6'!$E$4</definedName>
     <definedName name="_Acr" localSheetId="0">'Cas 2'!$B$71</definedName>
     <definedName name="_Acr" localSheetId="1">'Cas 3'!#REF!</definedName>
-    <definedName name="_Ah" localSheetId="4">'Cas 6'!$B$102</definedName>
+    <definedName name="_Ah" localSheetId="4">'Cas 6'!#REF!</definedName>
     <definedName name="_As_inf" localSheetId="0">'Cas 2'!$E$10</definedName>
     <definedName name="_As_inf" localSheetId="1">'Cas 3'!$E$10</definedName>
     <definedName name="_As_inf" localSheetId="4">'Cas 6'!$E$10</definedName>
@@ -58,7 +58,7 @@
     <definedName name="_be1" localSheetId="4">'Cas 6'!$B$3</definedName>
     <definedName name="_be2" localSheetId="1">'Cas 3'!$B$7</definedName>
     <definedName name="_be2" localSheetId="4">'Cas 6'!$B$4</definedName>
-    <definedName name="_beff" localSheetId="4">'Cas 6'!$B$98</definedName>
+    <definedName name="_beff" localSheetId="4">'Cas 6'!$B$81</definedName>
     <definedName name="_beff_appui" localSheetId="1">'Cas 3'!$B$11</definedName>
     <definedName name="_beff_mi_travee" localSheetId="1">'Cas 3'!$B$10</definedName>
     <definedName name="_beff_mi_travee" localSheetId="4">'Cas 6'!$B$10</definedName>
@@ -66,7 +66,7 @@
     <definedName name="_beta1" localSheetId="4">'Cas 6'!$B$8</definedName>
     <definedName name="_beta2" localSheetId="1">'Cas 3'!$B$9</definedName>
     <definedName name="_beta2" localSheetId="4">'Cas 6'!$B$9</definedName>
-    <definedName name="_bfi">'Cas 6'!$E$5</definedName>
+    <definedName name="_bfi" localSheetId="4">'Cas 6'!$E$5</definedName>
     <definedName name="_bfs" localSheetId="4">'Cas 6'!$E$3</definedName>
     <definedName name="_bgauche" localSheetId="1">'Cas 3'!$B$3</definedName>
     <definedName name="_bm" localSheetId="0">'Cas 2'!$E$22</definedName>
@@ -77,6 +77,7 @@
     <definedName name="_cf" localSheetId="0">'Cas 2'!$B$11</definedName>
     <definedName name="_cf" localSheetId="1">'Cas 3'!$B$22</definedName>
     <definedName name="_cf" localSheetId="3">'Cas 5'!$E$12</definedName>
+    <definedName name="_cf_inf" localSheetId="4">'Cas 6'!$E$14</definedName>
     <definedName name="_cf_sup" localSheetId="4">'Cas 6'!$E$12</definedName>
     <definedName name="_cw" localSheetId="0">'Cas 2'!$B$12</definedName>
     <definedName name="_cw" localSheetId="1">'Cas 3'!$B$23</definedName>
@@ -95,7 +96,7 @@
     <definedName name="_epsilon" localSheetId="0">'Cas 2'!$B$15</definedName>
     <definedName name="_epsilon" localSheetId="1">'Cas 3'!$B$26</definedName>
     <definedName name="_epsilon" localSheetId="3">'Cas 5'!$E$16</definedName>
-    <definedName name="_epsilon" localSheetId="4">'Cas 6'!$E$16</definedName>
+    <definedName name="_epsilon" localSheetId="4">'Cas 6'!$E$17</definedName>
     <definedName name="_eta" localSheetId="1">'Cas 3'!$H$28</definedName>
     <definedName name="_fck_dalle" localSheetId="0">'Cas 2'!$H$5</definedName>
     <definedName name="_fck_dalle" localSheetId="1">'Cas 3'!$H$5</definedName>
@@ -115,7 +116,7 @@
     <definedName name="_fy" localSheetId="0">'Cas 2'!$B$14</definedName>
     <definedName name="_fy" localSheetId="1">'Cas 3'!$B$25</definedName>
     <definedName name="_fy" localSheetId="3">'Cas 5'!$E$15</definedName>
-    <definedName name="_fy" localSheetId="4">'Cas 6'!$E$15</definedName>
+    <definedName name="_fy" localSheetId="4">'Cas 6'!$E$16</definedName>
     <definedName name="_fyd" localSheetId="0">'Cas 2'!$E$12</definedName>
     <definedName name="_fyd" localSheetId="1">'Cas 3'!$E$12</definedName>
     <definedName name="_fyp" localSheetId="0">'Cas 2'!$E$24</definedName>
@@ -147,6 +148,7 @@
     <definedName name="_kt_max" localSheetId="1">'Cas 3'!$H$20</definedName>
     <definedName name="_L" localSheetId="0">'Cas 2'!$B$2</definedName>
     <definedName name="_L" localSheetId="1">'Cas 3'!$B$2</definedName>
+    <definedName name="_L" localSheetId="3">'Cas 5'!$B$2</definedName>
     <definedName name="_L" localSheetId="4">'Cas 6'!$B$2</definedName>
     <definedName name="_L_ConsoleD" localSheetId="3">'Cas 5'!$B$4</definedName>
     <definedName name="_L_ConsoleG" localSheetId="3">'Cas 5'!$B$2</definedName>
@@ -155,13 +157,13 @@
     <definedName name="_L_Travee" localSheetId="4">'Cas 6'!$B$2</definedName>
     <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$53</definedName>
     <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$54</definedName>
-    <definedName name="_Mpl_Rd" localSheetId="3">'Cas 5'!$B$69</definedName>
-    <definedName name="_Mpl_Rd" localSheetId="4">'Cas 6'!$B$111</definedName>
+    <definedName name="_Mpl_Rd" localSheetId="3">'Cas 5'!$B$70</definedName>
+    <definedName name="_Mpl_Rd" localSheetId="4">'Cas 6'!$B$134</definedName>
     <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$55</definedName>
     <definedName name="_Mpl_z_Rd" localSheetId="0">'Cas 2'!$B$56</definedName>
     <definedName name="_n" localSheetId="0">'Cas 2'!$B$69</definedName>
     <definedName name="_n_dalle" localSheetId="1">'Cas 3'!$B$70</definedName>
-    <definedName name="_n_dalle" localSheetId="4">'Cas 6'!$B$97</definedName>
+    <definedName name="_n_dalle" localSheetId="4">'Cas 6'!$B$80</definedName>
     <definedName name="_n_enrobage" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_Na" localSheetId="1">'Cas 3'!$H$23</definedName>
     <definedName name="_Na" localSheetId="4">'Cas 6'!$H$24</definedName>
@@ -188,7 +190,7 @@
     <definedName name="_rho" localSheetId="0">'Cas 2'!$B$17</definedName>
     <definedName name="_rho" localSheetId="1">'Cas 3'!$B$28</definedName>
     <definedName name="_rhoA" localSheetId="3">'Cas 5'!$E$18</definedName>
-    <definedName name="_rhoA" localSheetId="4">'Cas 6'!$E$18</definedName>
+    <definedName name="_rhoA" localSheetId="4">'Cas 6'!$E$19</definedName>
     <definedName name="_rhoC" localSheetId="3">'Cas 5'!$H$6</definedName>
     <definedName name="_rhoC" localSheetId="4">'Cas 6'!$H$6</definedName>
     <definedName name="_sx" localSheetId="4">'Cas 6'!$H$19</definedName>
@@ -214,8 +216,8 @@
     <definedName name="_tw" localSheetId="4">'Cas 6'!$E$7</definedName>
     <definedName name="_VplRd" localSheetId="0">'Cas 2'!$B$52</definedName>
     <definedName name="_VplRd" localSheetId="1">'Cas 3'!$B$53</definedName>
-    <definedName name="_VplRd" localSheetId="3">'Cas 5'!$B$52</definedName>
-    <definedName name="_VplRd" localSheetId="4">'Cas 6'!$B$64</definedName>
+    <definedName name="_VplRd" localSheetId="3">'Cas 5'!$B$53</definedName>
+    <definedName name="_VplRd" localSheetId="4">'Cas 6'!#REF!</definedName>
     <definedName name="_Wel_y" localSheetId="0">'Cas 2'!$B$36</definedName>
     <definedName name="_Wel_y" localSheetId="1">'Cas 3'!$B$37</definedName>
     <definedName name="_Wel_y" localSheetId="3">'Cas 5'!$B$15</definedName>
@@ -238,13 +240,13 @@
     <definedName name="_zcr" localSheetId="1">'Cas 3'!#REF!</definedName>
     <definedName name="_zel" localSheetId="0">'Cas 2'!$B$77</definedName>
     <definedName name="_zel" localSheetId="1">'Cas 3'!$B$79</definedName>
-    <definedName name="_zel" localSheetId="4">'Cas 6'!$B$87</definedName>
-    <definedName name="_zp" localSheetId="4">'Cas 6'!$B$101</definedName>
+    <definedName name="_zel" localSheetId="4">'Cas 6'!$B$70</definedName>
+    <definedName name="_zp" localSheetId="4">'Cas 6'!#REF!</definedName>
     <definedName name="_zpl" localSheetId="0">'Cas 2'!$B$102</definedName>
     <definedName name="_zpl_a" localSheetId="1">'Cas 3'!$B$107</definedName>
     <definedName name="_zpl_c" localSheetId="1">'Cas 3'!$B$105</definedName>
     <definedName name="_zs" localSheetId="1">'Cas 3'!$B$74</definedName>
-    <definedName name="_zs" localSheetId="4">'Cas 6'!$B$82</definedName>
+    <definedName name="_zs" localSheetId="4">'Cas 6'!$B$65</definedName>
     <definedName name="_zs_inf" localSheetId="0">'Cas 2'!$E$11</definedName>
     <definedName name="_zs_inf" localSheetId="1">'Cas 3'!$E$11</definedName>
     <definedName name="_zs_inf" localSheetId="4">'Cas 6'!$E$11</definedName>
@@ -259,7 +261,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="337">
   <si>
     <t>h (mm)</t>
   </si>
@@ -945,12 +947,6 @@
     <t>rho c (kg/m3)</t>
   </si>
   <si>
-    <t>V(G) (kN)</t>
-  </si>
-  <si>
-    <t>M(G) (kN.m)</t>
-  </si>
-  <si>
     <t>V(Q1#1) (kN)</t>
   </si>
   <si>
@@ -969,9 +965,6 @@
     <t>M(Q1#3) (kN.m)</t>
   </si>
   <si>
-    <t>55,08/-30,98</t>
-  </si>
-  <si>
     <t>V ELU 1 (kN)</t>
   </si>
   <si>
@@ -1071,12 +1064,6 @@
     <t>beff (m)</t>
   </si>
   <si>
-    <t>Ah (mm2)</t>
-  </si>
-  <si>
-    <t>zp (mm)</t>
-  </si>
-  <si>
     <t>Classe section flexion pure</t>
   </si>
   <si>
@@ -1120,13 +1107,178 @@
   </si>
   <si>
     <t>62 epsilon(1-psi)*racine(-psi)</t>
+  </si>
+  <si>
+    <t>cf,sup/tf,sup</t>
+  </si>
+  <si>
+    <t>cf,inf/tf,inf</t>
+  </si>
+  <si>
+    <t>cf ,inf</t>
+  </si>
+  <si>
+    <t>Classe semelle inf</t>
+  </si>
+  <si>
+    <t>72 epsilon / eta</t>
+  </si>
+  <si>
+    <t>Elements</t>
+  </si>
+  <si>
+    <t>Dalle</t>
+  </si>
+  <si>
+    <t>Semelle sup</t>
+  </si>
+  <si>
+    <t>Ame</t>
+  </si>
+  <si>
+    <t>Semelle inf</t>
+  </si>
+  <si>
+    <t>t (mm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zel (mm) </t>
+  </si>
+  <si>
+    <t>zG (mm)</t>
+  </si>
+  <si>
+    <t>A (mm2)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>S (mm3)</t>
+  </si>
+  <si>
+    <t>Iy (mm4)</t>
+  </si>
+  <si>
+    <t>A(z-zg)²</t>
+  </si>
+  <si>
+    <t>IY (mm4)</t>
+  </si>
+  <si>
+    <t>IY (cm4)</t>
+  </si>
+  <si>
+    <t>(Hypothèse)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zpl (mm) </t>
+  </si>
+  <si>
+    <t>Ni,Rd (kN) +</t>
+  </si>
+  <si>
+    <t>Ni,Rd (kN) -</t>
+  </si>
+  <si>
+    <t>h+ (mm)</t>
+  </si>
+  <si>
+    <t>h- (mm)</t>
+  </si>
+  <si>
+    <t>arase sup (mm)</t>
+  </si>
+  <si>
+    <t>arase inf (mm)</t>
+  </si>
+  <si>
+    <t>arase sup comp (mm)</t>
+  </si>
+  <si>
+    <t>arase inf comp (mm)</t>
+  </si>
+  <si>
+    <t>arase sup trac (mm)</t>
+  </si>
+  <si>
+    <t>arase inf trac (mm)</t>
+  </si>
+  <si>
+    <t>fd + (MPa)</t>
+  </si>
+  <si>
+    <t>fd - (MPa)</t>
+  </si>
+  <si>
+    <t>Mi,Rd (kN.m) +</t>
+  </si>
+  <si>
+    <t>Mi,Rd (kN.m) -</t>
+  </si>
+  <si>
+    <t>NRd (kN)</t>
+  </si>
+  <si>
+    <t>MRd (kN.m)</t>
+  </si>
+  <si>
+    <t>(z,sup - xpl)/h (%)</t>
+  </si>
+  <si>
+    <t>beta</t>
+  </si>
+  <si>
+    <t>qG2 (kPa)</t>
+  </si>
+  <si>
+    <t>M(Qc) (kN.m)</t>
+  </si>
+  <si>
+    <t>M(G1) + (kN.m)</t>
+  </si>
+  <si>
+    <t>M(G1) - (kN.m)</t>
+  </si>
+  <si>
+    <t>epsilon cs</t>
+  </si>
+  <si>
+    <t>Ey (MPa)</t>
+  </si>
+  <si>
+    <t>nLT</t>
+  </si>
+  <si>
+    <t>Nr (kN)</t>
+  </si>
+  <si>
+    <t>zLT (mm)</t>
+  </si>
+  <si>
+    <t>Mr (kN.m)</t>
+  </si>
+  <si>
+    <t>MEd (kN.m)</t>
+  </si>
+  <si>
+    <t>VEd (kN)</t>
+  </si>
+  <si>
+    <t>Ved, const (kN)</t>
+  </si>
+  <si>
+    <t>MEd, const (kN.m)</t>
+  </si>
+  <si>
+    <t>Répartition plastique (acier entierement tendu)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -1134,6 +1286,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="0.000000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1193,7 +1346,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1383,12 +1536,152 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1471,9 +1764,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1498,8 +1797,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -1793,20 +2125,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="76"/>
+      <c r="B1" s="78"/>
       <c r="C1"/>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="76"/>
+      <c r="E1" s="78"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="76"/>
+      <c r="H1" s="78"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -2068,10 +2400,10 @@
         <v>0.81361651346682706</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="75" t="s">
+      <c r="D15" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="76"/>
+      <c r="E15" s="78"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
@@ -2210,10 +2542,10 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="75" t="s">
+      <c r="A30" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="76"/>
+      <c r="B30" s="78"/>
       <c r="C30" s="24" t="s">
         <v>53</v>
       </c>
@@ -2481,10 +2813,10 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="75" t="s">
+      <c r="A50" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="76"/>
+      <c r="B50" s="78"/>
       <c r="D50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2521,10 +2853,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E52" s="77" t="s">
+      <c r="E52" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="F52" s="78"/>
+      <c r="F52" s="80"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -2772,10 +3104,10 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="75" t="s">
+      <c r="A68" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B68" s="76"/>
+      <c r="B68" s="78"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -3059,10 +3391,10 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="75" t="s">
+      <c r="A96" s="77" t="s">
         <v>111</v>
       </c>
-      <c r="B96" s="76"/>
+      <c r="B96" s="78"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -3166,10 +3498,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="75" t="s">
+      <c r="A109" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="B109" s="76"/>
+      <c r="B109" s="78"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -3252,10 +3584,10 @@
     </row>
     <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="75" t="s">
+      <c r="A120" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="B120" s="76"/>
+      <c r="B120" s="78"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
@@ -3380,20 +3712,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="76"/>
+      <c r="B1" s="78"/>
       <c r="C1"/>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="76"/>
+      <c r="E1" s="78"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="76"/>
+      <c r="H1" s="78"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -3628,16 +3960,16 @@
         <f>500/1.15</f>
         <v>434.78260869565219</v>
       </c>
-      <c r="G12" s="75" t="s">
+      <c r="G12" s="77" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="76"/>
+      <c r="H12" s="78"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="77" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="76"/>
+      <c r="B13" s="78"/>
       <c r="C13"/>
       <c r="D13" t="s">
         <v>125</v>
@@ -3676,10 +4008,10 @@
         <v>200</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="75" t="s">
+      <c r="D15" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="76"/>
+      <c r="E15" s="78"/>
       <c r="G15" t="s">
         <v>166</v>
       </c>
@@ -3983,10 +4315,10 @@
       <c r="C30"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="75" t="s">
+      <c r="A31" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="76"/>
+      <c r="B31" s="78"/>
       <c r="C31" s="24" t="s">
         <v>53</v>
       </c>
@@ -4254,10 +4586,10 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="75" t="s">
+      <c r="A51" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="76"/>
+      <c r="B51" s="78"/>
       <c r="D51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4294,10 +4626,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E53" s="77" t="s">
+      <c r="E53" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="78"/>
+      <c r="F53" s="80"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -4545,10 +4877,10 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="75" t="s">
+      <c r="A69" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="76"/>
+      <c r="B69" s="78"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -4729,10 +5061,10 @@
       <c r="C84" s="36"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="79" t="s">
+      <c r="A85" s="81" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="80"/>
+      <c r="B85" s="82"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -4875,10 +5207,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="75" t="s">
+      <c r="A101" s="77" t="s">
         <v>111</v>
       </c>
-      <c r="B101" s="76"/>
+      <c r="B101" s="78"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
@@ -5018,10 +5350,10 @@
     </row>
     <row r="117" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="118" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="75" t="s">
+      <c r="A118" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="B118" s="76"/>
+      <c r="B118" s="78"/>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
@@ -5140,10 +5472,10 @@
     </row>
     <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="75" t="s">
+      <c r="A133" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="B133" s="76"/>
+      <c r="B133" s="78"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
@@ -5259,10 +5591,10 @@
     </row>
     <row r="146" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="147" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="75" t="s">
+      <c r="A147" s="77" t="s">
         <v>207</v>
       </c>
-      <c r="B147" s="76"/>
+      <c r="B147" s="78"/>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
@@ -5361,7 +5693,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -5372,7 +5704,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
@@ -5381,18 +5713,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="D1" s="75" t="s">
+      <c r="B1" s="78"/>
+      <c r="D1" s="77" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="76"/>
-      <c r="G1" s="75" t="s">
+      <c r="E1" s="78"/>
+      <c r="G1" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="76"/>
+      <c r="H1" s="78"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -5516,10 +5848,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="76"/>
+      <c r="B9" s="78"/>
       <c r="D9" t="s">
         <v>32</v>
       </c>
@@ -5718,10 +6050,10 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="75" t="s">
+      <c r="A29" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="76"/>
+      <c r="B29" s="78"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -5740,10 +6072,10 @@
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>1042.1194079466816</v>
       </c>
-      <c r="D31" s="77" t="s">
+      <c r="D31" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="78"/>
+      <c r="E31" s="80"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -5923,516 +6255,520 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="75" t="s">
+      <c r="A47" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="76"/>
+      <c r="B47" s="78"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="A48" s="114" t="s">
         <v>130</v>
       </c>
-      <c r="B48" s="25">
-        <f>H7+E19</f>
+      <c r="B48" s="115">
+        <f>E19+H7</f>
         <v>6.8560492004849909</v>
-      </c>
-      <c r="C48" s="26">
-        <f>B48*1.35</f>
-        <v>9.2556664206547374</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="B49" s="53">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="B50" s="113">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="B51" s="110">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="B49" s="53">
-        <v>34.424999999999997</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="B50" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="D50" s="24" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="B51" s="50">
+      <c r="B52" s="50">
         <v>13.47</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="B52" s="51">
-        <v>14.74</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B53" s="51">
-        <v>-19.5</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="15" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B54" s="51">
-        <v>11.67</v>
+        <v>-19.5</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B55" s="51">
-        <v>25.17</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="B56" s="51">
+        <v>25.17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B57" s="51">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="B58" s="52">
+        <v>-19.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="B56" s="51">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="B57" s="52">
-        <v>-19.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="B58" s="50">
+      <c r="B59" s="50">
         <v>66.650000000000006</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="B59" s="51">
-        <v>96.16</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B60" s="51">
-        <v>-71.05</v>
+        <v>96.16</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B61" s="51">
-        <v>63.95</v>
+        <v>-71.05</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B62" s="51">
-        <v>111.9</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B63" s="51">
-        <v>-41.81</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B64" s="51">
+        <v>-41.81</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B65" s="51">
         <v>49.15</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="54" t="s">
-        <v>246</v>
-      </c>
-      <c r="B65" s="51">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="54" t="s">
+        <v>243</v>
+      </c>
+      <c r="B66" s="51">
         <v>58.96</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="B66" s="52">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="B67" s="52">
         <v>-71.06</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="75" t="s">
+    <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="76"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B69" s="78"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>123</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <f>_Wpl_y*1000*_fy*10^(-6)</f>
         <v>603.85500000000002</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>248</v>
-      </c>
-      <c r="B70" s="23">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>245</v>
+      </c>
+      <c r="B71" s="23">
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>1042.1194079466816</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B71" s="23"/>
-    </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="21"/>
-      <c r="B72" s="62" t="s">
-        <v>249</v>
-      </c>
-      <c r="C72" s="63" t="s">
-        <v>250</v>
-      </c>
-      <c r="D72" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="F72" s="21"/>
-      <c r="G72" s="65" t="s">
-        <v>249</v>
-      </c>
-      <c r="H72" s="66" t="s">
-        <v>250</v>
-      </c>
-      <c r="I72" s="29" t="s">
-        <v>251</v>
-      </c>
+      <c r="B72" s="23"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="15" t="s">
+      <c r="A73" s="21"/>
+      <c r="B73" s="62" t="s">
+        <v>246</v>
+      </c>
+      <c r="C73" s="63" t="s">
+        <v>247</v>
+      </c>
+      <c r="D73" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="F73" s="21"/>
+      <c r="G73" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="H73" s="66" t="s">
+        <v>247</v>
+      </c>
+      <c r="I73" s="29" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B73" s="59">
-        <f>MAX(B59,ABS(B60))/_Mpl_Rd</f>
+      <c r="B74" s="59">
+        <f>MAX(B60,ABS(B61))/_Mpl_Rd</f>
         <v>0.15924352700565533</v>
       </c>
-      <c r="C73" s="55">
-        <f>MAX(B62,ABS(B63))/_Mpl_Rd</f>
+      <c r="C74" s="55">
+        <f>MAX(B63,ABS(B64))/_Mpl_Rd</f>
         <v>0.18530938718732146</v>
       </c>
-      <c r="D73" s="17">
-        <f>MAX(B65,ABS(B66))/_Mpl_Rd</f>
+      <c r="D74" s="17">
+        <f>MAX(B66,ABS(B67))/_Mpl_Rd</f>
         <v>0.11767725695738215</v>
       </c>
-      <c r="F73" s="15" t="s">
+      <c r="F74" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="G73" s="67">
-        <f>B73</f>
+      <c r="G74" s="67">
+        <f>B74</f>
         <v>0.15924352700565533</v>
       </c>
-      <c r="H73" s="68">
-        <f t="shared" ref="H73:I73" si="0">C73</f>
+      <c r="H74" s="68">
+        <f t="shared" ref="H74:I74" si="0">C74</f>
         <v>0.18530938718732146</v>
       </c>
-      <c r="I73" s="69">
+      <c r="I74" s="69">
         <f t="shared" si="0"/>
         <v>0.11767725695738215</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="B74" s="59">
-        <f>B58/B70</f>
-        <v>6.3956202611486199E-2</v>
-      </c>
-      <c r="C74" s="55">
-        <f>B61/B70</f>
-        <v>6.1365328687239942E-2</v>
-      </c>
-      <c r="D74" s="17">
-        <f>B64/B70</f>
-        <v>4.7163501250630853E-2</v>
-      </c>
-      <c r="F74" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="G74" s="59">
-        <f>B74</f>
-        <v>6.3956202611486199E-2</v>
-      </c>
-      <c r="H74" s="55">
-        <f t="shared" ref="H74" si="1">C74</f>
-        <v>6.1365328687239942E-2</v>
-      </c>
-      <c r="I74" s="17">
-        <f t="shared" ref="I74" si="2">D74</f>
-        <v>4.7163501250630853E-2</v>
-      </c>
-    </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="B75" s="60">
-        <f>1/B73</f>
+        <v>142</v>
+      </c>
+      <c r="B75" s="59">
+        <f>B59/B71</f>
+        <v>6.3956202611486199E-2</v>
+      </c>
+      <c r="C75" s="55">
+        <f>B62/B71</f>
+        <v>6.1365328687239942E-2</v>
+      </c>
+      <c r="D75" s="17">
+        <f>B65/B71</f>
+        <v>4.7163501250630853E-2</v>
+      </c>
+      <c r="F75" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="G75" s="59">
+        <f>B75</f>
+        <v>6.3956202611486199E-2</v>
+      </c>
+      <c r="H75" s="55">
+        <f t="shared" ref="H75" si="1">C75</f>
+        <v>6.1365328687239942E-2</v>
+      </c>
+      <c r="I75" s="17">
+        <f t="shared" ref="I75" si="2">D75</f>
+        <v>4.7163501250630853E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="B76" s="60">
+        <f>1/B74</f>
         <v>6.2796900998336103</v>
       </c>
-      <c r="C75" s="56">
-        <f t="shared" ref="C75:D75" si="3">1/C73</f>
+      <c r="C76" s="56">
+        <f t="shared" ref="C76:D76" si="3">1/C74</f>
         <v>5.3963806970509385</v>
       </c>
-      <c r="D75" s="57">
+      <c r="D76" s="57">
         <f t="shared" si="3"/>
         <v>8.4978187447227693</v>
       </c>
-      <c r="F75" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="G75" s="60">
+      <c r="F76" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="G76" s="60">
         <v>521.97</v>
       </c>
-      <c r="H75" s="56">
+      <c r="H76" s="56">
         <v>546.22</v>
       </c>
-      <c r="I75" s="57">
+      <c r="I76" s="57">
         <v>496.55</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="B76" s="60">
-        <v>5.4870000000000001</v>
-      </c>
-      <c r="C76" s="56">
-        <v>4.9240000000000004</v>
-      </c>
-      <c r="D76" s="57">
-        <v>6.9660000000000002</v>
-      </c>
-      <c r="F76" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="G76" s="59">
-        <f>SQRT(_Mpl_Rd/G75)</f>
-        <v>1.0755820898480224</v>
-      </c>
-      <c r="H76" s="55">
-        <f>SQRT(_Mpl_Rd/H75)</f>
-        <v>1.0514352535543854</v>
-      </c>
-      <c r="I76" s="17">
-        <f>SQRT(_Mpl_Rd/I75)</f>
-        <v>1.1027697391446936</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="B77" s="59">
-        <f>SQRT(B75/B76)</f>
+        <v>253</v>
+      </c>
+      <c r="B77" s="60">
+        <v>5.4870000000000001</v>
+      </c>
+      <c r="C77" s="56">
+        <v>4.9240000000000004</v>
+      </c>
+      <c r="D77" s="57">
+        <v>6.9660000000000002</v>
+      </c>
+      <c r="F77" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="G77" s="59">
+        <f>SQRT(_Mpl_Rd/G76)</f>
+        <v>1.0755820898480224</v>
+      </c>
+      <c r="H77" s="55">
+        <f>SQRT(_Mpl_Rd/H76)</f>
+        <v>1.0514352535543854</v>
+      </c>
+      <c r="I77" s="17">
+        <f>SQRT(_Mpl_Rd/I76)</f>
+        <v>1.1027697391446936</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="B78" s="59">
+        <f>SQRT(B76/B77)</f>
         <v>1.0697976163788039</v>
       </c>
-      <c r="C77" s="55">
-        <f t="shared" ref="C77:D77" si="4">SQRT(C75/C76)</f>
+      <c r="C78" s="55">
+        <f t="shared" ref="C78:D78" si="4">SQRT(C76/C77)</f>
         <v>1.0468688272173641</v>
       </c>
-      <c r="D77" s="17">
+      <c r="D78" s="17">
         <f t="shared" si="4"/>
         <v>1.1044905303869459</v>
       </c>
-      <c r="F77" s="15" t="s">
+      <c r="F78" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G77" s="60">
+      <c r="G78" s="60">
         <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
-      <c r="H77" s="56">
+      <c r="H78" s="56">
         <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
-      <c r="I77" s="57">
+      <c r="I78" s="57">
         <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="15" t="s">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="B78" s="60">
+      <c r="B79" s="60">
         <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
-      <c r="C78" s="56">
+      <c r="C79" s="56">
         <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
-      <c r="D78" s="57">
+      <c r="D79" s="57">
         <f>IF(_h/_b&lt;=2,0.21,0.34)</f>
         <v>0.34</v>
       </c>
-      <c r="F78" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="G78" s="59">
-        <f>0.5*(1+G77*(G76-0.2)+G76^2)</f>
+      <c r="F79" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="G79" s="59">
+        <f>0.5*(1+G78*(G77-0.2)+G77^2)</f>
         <v>1.2272873712750836</v>
       </c>
-      <c r="H78" s="55">
-        <f t="shared" ref="H78:I78" si="5">0.5*(1+H77*(H76-0.2)+H76^2)</f>
+      <c r="H79" s="55">
+        <f t="shared" ref="H79:I79" si="5">0.5*(1+H78*(H77-0.2)+H77^2)</f>
         <v>1.1975020393127329</v>
       </c>
-      <c r="I78" s="17">
+      <c r="I79" s="17">
         <f t="shared" si="5"/>
         <v>1.2615214044412257</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="B79" s="59">
-        <f>0.5*(1+B78*(B77-0.2)+B77^2)</f>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="B80" s="59">
+        <f>0.5*(1+B79*(B78-0.2)+B78^2)</f>
         <v>1.2200990647892818</v>
       </c>
-      <c r="C79" s="55">
-        <f t="shared" ref="C79:D79" si="6">0.5*(1+C78*(C77-0.2)+C77^2)</f>
+      <c r="C80" s="55">
+        <f t="shared" ref="C80:D80" si="6">0.5*(1+C79*(C78-0.2)+C78^2)</f>
         <v>1.1919348713266817</v>
       </c>
-      <c r="D79" s="17">
+      <c r="D80" s="17">
         <f t="shared" si="6"/>
         <v>1.2637130560229994</v>
       </c>
-      <c r="F79" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="G79" s="59">
-        <f>1/(G78+SQRT(G78^2-G76^2))</f>
+      <c r="F80" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="G80" s="59">
+        <f>1/(G79+SQRT(G79^2-G77^2))</f>
         <v>0.54994850835187725</v>
       </c>
-      <c r="H79" s="55">
-        <f t="shared" ref="H79:I79" si="7">1/(H78+SQRT(H78^2-H76^2))</f>
+      <c r="H80" s="55">
+        <f t="shared" ref="H80:I80" si="7">1/(H79+SQRT(H79^2-H77^2))</f>
         <v>0.56476533795169126</v>
       </c>
-      <c r="I79" s="17">
+      <c r="I80" s="17">
         <f t="shared" si="7"/>
         <v>0.53357025759830123</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="B80" s="59">
-        <f>1/(B79+SQRT(B79^2-B77^2))</f>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="B81" s="59">
+        <f>1/(B80+SQRT(B80^2-B78^2))</f>
         <v>0.55347596700576529</v>
       </c>
-      <c r="C80" s="55">
-        <f t="shared" ref="C80:D80" si="8">1/(C79+SQRT(C79^2-C77^2))</f>
+      <c r="C81" s="55">
+        <f t="shared" ref="C81:D81" si="8">1/(C80+SQRT(C80^2-C78^2))</f>
         <v>0.56759336517890635</v>
       </c>
-      <c r="D80" s="17">
+      <c r="D81" s="17">
         <f t="shared" si="8"/>
         <v>0.5325453315503752</v>
       </c>
-      <c r="F80" s="15" t="s">
+      <c r="F81" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="G80" s="60">
-        <f>G79*_Mpl_Rd</f>
+      <c r="G81" s="60">
+        <f>G80*_Mpl_Rd</f>
         <v>332.08915651082287</v>
       </c>
-      <c r="H80" s="56">
-        <f>H79*_Mpl_Rd</f>
+      <c r="H81" s="56">
+        <f>H80*_Mpl_Rd</f>
         <v>341.03637314881854</v>
       </c>
-      <c r="I80" s="57">
-        <f>I79*_Mpl_Rd</f>
+      <c r="I81" s="57">
+        <f>I80*_Mpl_Rd</f>
         <v>322.19906790202219</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="15" t="s">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B81" s="60">
-        <f>B80*_Mpl_Rd</f>
+      <c r="B82" s="60">
+        <f>B81*_Mpl_Rd</f>
         <v>334.21923005626638</v>
       </c>
-      <c r="C81" s="56">
-        <f>C80*_Mpl_Rd</f>
+      <c r="C82" s="56">
+        <f>C81*_Mpl_Rd</f>
         <v>342.74409153010851</v>
       </c>
-      <c r="D81" s="57">
-        <f>D80*_Mpl_Rd</f>
+      <c r="D82" s="57">
+        <f>D81*_Mpl_Rd</f>
         <v>321.58016118335183</v>
       </c>
-      <c r="F81" s="16" t="s">
+      <c r="F82" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="G81" s="61">
-        <f>G73/G79</f>
+      <c r="G82" s="61">
+        <f>G74/G80</f>
         <v>0.28956079448762767</v>
       </c>
-      <c r="H81" s="58">
-        <f>H73/H79</f>
+      <c r="H82" s="58">
+        <f>H74/H80</f>
         <v>0.32811749364684345</v>
       </c>
-      <c r="I81" s="18">
-        <f>I73/I79</f>
+      <c r="I82" s="18">
+        <f>I74/I80</f>
         <v>0.2205468825924993</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="16" t="s">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B82" s="61">
-        <f>B73/B80</f>
+      <c r="B83" s="61">
+        <f>B74/B81</f>
         <v>0.28771534176477903</v>
       </c>
-      <c r="C82" s="58">
-        <f t="shared" ref="C82:D82" si="9">C73/C80</f>
+      <c r="C83" s="58">
+        <f t="shared" ref="C83:D83" si="9">C74/C81</f>
         <v>0.3264826521164701</v>
       </c>
-      <c r="D82" s="18">
+      <c r="D83" s="18">
         <f t="shared" si="9"/>
         <v>0.22097134269263738</v>
       </c>
@@ -6441,7 +6777,7 @@
   <mergeCells count="8">
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A69:B69"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A1:B1"/>
@@ -6455,30 +6791,35 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:Q137"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="D1" s="75" t="s">
+      <c r="B1" s="78"/>
+      <c r="D1" s="77" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="76"/>
-      <c r="G1" s="75" t="s">
+      <c r="E1" s="78"/>
+      <c r="G1" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="76"/>
+      <c r="H1" s="78"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -6496,7 +6837,7 @@
       <c r="G2" t="s">
         <v>60</v>
       </c>
-      <c r="H2" s="23">
+      <c r="H2" s="26">
         <f>1/(1/_td-_bfs/(2*(_b_Gauche+_b_Droite)*1000*_td))</f>
         <v>123.71134020618557</v>
       </c>
@@ -6509,7 +6850,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E3" s="1">
         <v>120</v>
@@ -6529,13 +6870,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E4" s="1">
         <v>6</v>
       </c>
       <c r="G4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -6550,17 +6891,17 @@
         <v>1.25</v>
       </c>
       <c r="D5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E5" s="1">
         <v>150</v>
       </c>
       <c r="G5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H5" s="23">
-        <f>(_b_Gauche+_b_Droite)*1000*(_td-_tj)</f>
-        <v>220000</v>
+        <f>(_b_Gauche+_b_Droite)*1000*_td</f>
+        <v>240000</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -6572,7 +6913,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E6" s="1">
         <v>10.7</v>
@@ -6602,7 +6943,7 @@
         <v>62</v>
       </c>
       <c r="H7" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -6625,7 +6966,7 @@
       </c>
       <c r="H8">
         <f>_fck_dalle+8</f>
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -6648,7 +6989,7 @@
       </c>
       <c r="H9" s="26">
         <f>0.3*_fck_dalle^(2/3)</f>
-        <v>2.5649639200150443</v>
+        <v>2.2104188991842313</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -6670,7 +7011,7 @@
       </c>
       <c r="H10" s="13">
         <f>22*(_fcm_dalle/10)^0.3*1000</f>
-        <v>31475.806210019346</v>
+        <v>29961.951054640311</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -6687,12 +7028,12 @@
       </c>
       <c r="H11" s="25">
         <f>_rhoC*_Ac_brute*10^(-6)*9.81/1000</f>
-        <v>5.3955000000000002</v>
+        <v>5.8860000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E12" s="6">
         <f>(_bfs-2*_r-_tw)/2</f>
@@ -6700,10 +7041,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="B13" s="76"/>
+      <c r="A13" s="77" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" s="78"/>
       <c r="D13" t="s">
         <v>38</v>
       </c>
@@ -6720,10 +7061,17 @@
         <f>(2*(_h-2*_r)+_bfs+_bfi+(_bfs-2*_r-_tw)+(_bfi-2*_r-_tw)+2*PI()*_r)/10</f>
         <v>112.58</v>
       </c>
-      <c r="G14" s="75" t="s">
+      <c r="D14" t="s">
+        <v>284</v>
+      </c>
+      <c r="E14" s="6">
+        <f>(_bfi-2*_r-_tw)/2</f>
+        <v>71.45</v>
+      </c>
+      <c r="G14" s="77" t="s">
         <v>162</v>
       </c>
-      <c r="H14" s="76"/>
+      <c r="H14" s="78"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -6733,12 +7081,6 @@
         <f>(_bfs*_tfs+_bfi*_tfi+(_h-_tfs-_tfi)*_tw+4*(1-PI()/4)*_r^2)/100</f>
         <v>43.3643</v>
       </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1">
-        <v>420</v>
-      </c>
       <c r="G15" t="s">
         <v>163</v>
       </c>
@@ -6755,11 +7097,10 @@
         <v>20.1143</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" s="14">
-        <f>SQRT(235/_fy)</f>
-        <v>0.74801324154309567</v>
+        <v>8</v>
+      </c>
+      <c r="E16" s="1">
+        <v>420</v>
       </c>
       <c r="G16" t="s">
         <v>164</v>
@@ -6775,7 +7116,13 @@
       <c r="B17" s="4">
         <v>5921.277</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="D17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="14">
+        <f>SQRT(235/_fy)</f>
+        <v>0.74801324154309567</v>
+      </c>
       <c r="G17" t="s">
         <v>166</v>
       </c>
@@ -6790,12 +7137,7 @@
       <c r="B18" s="4">
         <v>388.18299999999999</v>
       </c>
-      <c r="D18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="1">
-        <v>7850</v>
-      </c>
+      <c r="E18" s="6"/>
       <c r="G18" t="s">
         <v>171</v>
       </c>
@@ -6811,14 +7153,13 @@
         <v>332.58</v>
       </c>
       <c r="D19" t="s">
-        <v>124</v>
-      </c>
-      <c r="E19" s="31">
-        <f>_rhoA*_A*10^(-4)*9.81/1000</f>
-        <v>0.33394196965500006</v>
+        <v>23</v>
+      </c>
+      <c r="E19" s="1">
+        <v>7850</v>
       </c>
       <c r="G19" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H19" s="10">
         <v>190</v>
@@ -6831,6 +7172,13 @@
       <c r="B20" s="4">
         <v>51.758000000000003</v>
       </c>
+      <c r="D20" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="31">
+        <f>_rhoA*_A*10^(-4)*9.81/1000</f>
+        <v>0.33394196965500006</v>
+      </c>
       <c r="G20" t="s">
         <v>165</v>
       </c>
@@ -6866,7 +7214,7 @@
       </c>
       <c r="H22" s="3">
         <f>0.29*H21*_dsc^2*SQRT(_fck_dalle*_Ecm_dalle)/(1000*1.25)</f>
-        <v>74.293979654469197</v>
+        <v>64.832867388792735</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -6875,7 +7223,7 @@
       </c>
       <c r="H23" s="26">
         <f>MIN(H20,H22)</f>
-        <v>74.293979654469197</v>
+        <v>64.832867388792735</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -6907,7 +7255,7 @@
       </c>
       <c r="H25" s="23">
         <f>0.85*_beff_mi_travee*1000*(_td-_tj)*_fck_dalle/1.5/1000</f>
-        <v>3116.6666666666665</v>
+        <v>2493.3333333333335</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -6933,7 +7281,7 @@
       </c>
       <c r="H27" s="3">
         <f>_nr*(_L*1000/2)/_sx*_PRd</f>
-        <v>1955.1047277491894</v>
+        <v>1706.128089178756</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -6949,7 +7297,7 @@
       </c>
       <c r="H28" s="26">
         <f>MIN(H27/H26,1)</f>
-        <v>1</v>
+        <v>0.93676359035886547</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -6982,10 +7330,10 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="75" t="s">
+      <c r="A33" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="76"/>
+      <c r="B33" s="78"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -7004,10 +7352,10 @@
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>487.74585382155738</v>
       </c>
-      <c r="D35" s="77" t="s">
+      <c r="D35" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="78"/>
+      <c r="E35" s="80"/>
       <c r="G35" s="21" t="s">
         <v>44</v>
       </c>
@@ -7117,24 +7465,24 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J40" s="77" t="s">
-        <v>281</v>
-      </c>
-      <c r="K40" s="78"/>
+      <c r="J40" s="79" t="s">
+        <v>276</v>
+      </c>
+      <c r="K40" s="80"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>282</v>
       </c>
       <c r="B41" s="3">
         <f>_cf_sup/_tfs</f>
         <v>9.4083333333333332</v>
       </c>
       <c r="J41" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="K41" s="83">
-        <f>396*_epsilon/(13*B46-1)</f>
+        <v>273</v>
+      </c>
+      <c r="K41" s="74">
+        <f>396*_epsilon/(13*B47-1)</f>
         <v>35.433373133731216</v>
       </c>
     </row>
@@ -7147,961 +7495,1255 @@
         <v>39.901408450704231</v>
       </c>
       <c r="J42" s="16" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="K42" s="20">
-        <f>456*_epsilon/(13*B46-1)</f>
+        <f>456*_epsilon/(13*B47-1)</f>
         <v>40.802066032781397</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B43" s="3"/>
+      <c r="A43" t="s">
+        <v>283</v>
+      </c>
+      <c r="B43" s="26">
+        <f>_cf_inf/_tfi</f>
+        <v>6.6775700934579447</v>
+      </c>
+      <c r="J43" s="54"/>
+      <c r="K43" s="76"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>274</v>
-      </c>
-      <c r="B44" s="3">
-        <v>121.96</v>
-      </c>
-      <c r="C44" s="3">
-        <f>B44-300</f>
-        <v>-178.04000000000002</v>
-      </c>
-      <c r="J44" s="77" t="s">
-        <v>282</v>
-      </c>
-      <c r="K44" s="78"/>
+      <c r="B44" s="3"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>275</v>
-      </c>
-      <c r="B45" s="3">
-        <f>B44-31.93</f>
-        <v>90.03</v>
+        <v>269</v>
+      </c>
+      <c r="B45" s="33">
+        <v>121.96</v>
       </c>
       <c r="C45" s="3">
-        <f>-300+B45</f>
-        <v>-209.97</v>
-      </c>
-      <c r="J45" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="K45" s="83">
-        <f>36*_epsilon/B46</f>
-        <v>37.401762258419005</v>
-      </c>
+        <f>B45-300</f>
+        <v>-178.04000000000002</v>
+      </c>
+      <c r="J45" s="79" t="s">
+        <v>277</v>
+      </c>
+      <c r="K45" s="80"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>167</v>
-      </c>
-      <c r="B46" s="26">
-        <f>(_h-B45-_tfs)/_hw</f>
-        <v>0.71997882103776911</v>
-      </c>
-      <c r="J46" s="16" t="s">
-        <v>280</v>
-      </c>
-      <c r="K46" s="20">
-        <f>41.5*_epsilon/B46</f>
-        <v>43.115920381233018</v>
+        <v>270</v>
+      </c>
+      <c r="B46" s="33">
+        <f>B45-31.93</f>
+        <v>90.03</v>
+      </c>
+      <c r="C46" s="3">
+        <f>-300+B46</f>
+        <v>-209.97</v>
+      </c>
+      <c r="J46" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="K46" s="74">
+        <f>36*_epsilon/B47</f>
+        <v>37.401762258419005</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>276</v>
+        <v>167</v>
       </c>
       <c r="B47" s="26">
-        <f>-(B44-_tfi)/(_hw-B44+_tfi)</f>
+        <f>(_h-B46-_tfs)/_hw</f>
+        <v>0.71997882103776911</v>
+      </c>
+      <c r="J47" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="K47" s="20">
+        <f>41.5*_epsilon/B47</f>
+        <v>43.115920381233018</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>271</v>
+      </c>
+      <c r="B48" s="26">
+        <f>-(B45-_tfi)/(_hw-B45+_tfi)</f>
         <v>-0.64671006742617987</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J48" s="77" t="s">
-        <v>283</v>
-      </c>
-      <c r="K48" s="78"/>
-    </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>268</v>
-      </c>
-      <c r="B49">
+      <c r="J49" s="79" t="s">
+        <v>278</v>
+      </c>
+      <c r="K49" s="80"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>265</v>
+      </c>
+      <c r="B50">
         <f>IF(B41&lt;=E36,1,IF(B41&lt;=E37,2,IF(B41&lt;=E38,3,4)))</f>
         <v>3</v>
       </c>
-      <c r="J49" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="K49" s="84">
-        <f>42*_epsilon/(0.67+0.33*B47)</f>
+      <c r="J50" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="K50" s="75">
+        <f>42*_epsilon/(0.67+0.33*B48)</f>
         <v>68.807581305815532</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>35</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <f>IF(B42&lt;=H36,1,IF(B42&lt;=H37,2,IF(B42&lt;=H38,3,4)))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>36</v>
       </c>
-      <c r="B51">
-        <f>IF(B46&gt;0.5,IF(B42&lt;=K41,1,IF(B42&lt;=K42,2,IF(B47&gt;-1,IF(B42&lt;=K49,3,4),IF(B42&lt;=K52,3,4)))),IF(B42&lt;=K45,1,IF(B42&lt;=K46,2,IF(B47&gt;-1,IF(B42&lt;=K49,3,4),IF(B42&lt;=K52,3,4)))))</f>
+      <c r="B52">
+        <f>IF(B47&gt;0.5,IF(B42&lt;=K41,1,IF(B42&lt;=K42,2,IF(B48&gt;-1,IF(B42&lt;=K50,3,4),IF(B42&lt;=K54,3,4)))),IF(B42&lt;=K46,1,IF(B42&lt;=K47,2,IF(B48&gt;-1,IF(B42&lt;=K50,3,4),IF(B42&lt;=K54,3,4)))))</f>
         <v>2</v>
       </c>
-      <c r="J51" s="77" t="s">
-        <v>285</v>
-      </c>
-      <c r="K51" s="78"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J52" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="K52" s="84">
-        <f>62*_epsilon*(1-B47)*SQRT(-B47)</f>
-        <v>61.414783744295001</v>
-      </c>
+      <c r="J52" s="79" t="s">
+        <v>280</v>
+      </c>
+      <c r="K52" s="80"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>272</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="B53">
+        <f>IF(B43&lt;=E36,1,IF(B43&lt;=E37,2,IF(B43&lt;=E38,3,4)))</f>
+        <v>1</v>
+      </c>
+      <c r="J53" s="72"/>
+      <c r="K53" s="73"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>273</v>
+      <c r="J54" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="K54" s="75">
+        <f>62*_epsilon*(1-B48)*SQRT(-B48)</f>
+        <v>61.414783744295001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="3">
+      <c r="B58" s="3">
         <f>_hw/_tw</f>
         <v>39.901408450704231</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>286</v>
+      </c>
+      <c r="B59" s="3">
+        <f>72*_epsilon/1</f>
+        <v>53.856953391102891</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>51</v>
       </c>
-      <c r="B57" s="3">
+      <c r="B60" s="3">
         <f>124*_epsilon</f>
         <v>92.753641951343866</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="75" t="s">
-        <v>133</v>
-      </c>
-      <c r="B59" s="76"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>130</v>
-      </c>
-      <c r="B60" s="25">
-        <f>H11+E19</f>
-        <v>5.7294419696550003</v>
-      </c>
-      <c r="C60" s="26">
-        <f>B60*1.35</f>
-        <v>7.7347466590342506</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="B61" s="53">
-        <v>34.424999999999997</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="B62" s="52" t="s">
-        <v>236</v>
-      </c>
-      <c r="D62" s="24" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="B63" s="50">
-        <v>13.47</v>
-      </c>
+    <row r="62" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="54"/>
+      <c r="B62" s="70"/>
+    </row>
+    <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="83" t="s">
+        <v>188</v>
+      </c>
+      <c r="B63" s="84"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="B64" s="51">
-        <v>14.74</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="B65" s="51">
-        <v>-19.5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="B66" s="51">
-        <v>11.67</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="B67" s="51">
-        <v>25.17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="B68" s="51">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="16" t="s">
-        <v>235</v>
-      </c>
-      <c r="B69" s="52">
-        <v>-19.5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="B70" s="50">
-        <v>66.650000000000006</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="B71" s="51">
-        <v>96.16</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="B72" s="51">
-        <v>-71.05</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="B73" s="51">
-        <v>63.95</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="B74" s="51">
-        <v>111.9</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="B75" s="51">
-        <v>-41.81</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="B76" s="51">
-        <v>49.15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="54" t="s">
-        <v>246</v>
-      </c>
-      <c r="B77" s="51">
-        <v>58.96</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="B78" s="52">
-        <v>-71.06</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="54"/>
-      <c r="B79" s="70"/>
-    </row>
-    <row r="80" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="81" t="s">
-        <v>188</v>
-      </c>
-      <c r="B80" s="82"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A64" t="s">
         <v>95</v>
       </c>
-      <c r="B81" s="26">
+      <c r="B64" s="26">
         <f>210000/_Ecm_dalle</f>
-        <v>6.6717909812633494</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+        <v>7.008889361611736</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>96</v>
       </c>
-      <c r="B82" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="B65" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="E65" s="22"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>100</v>
       </c>
-      <c r="B83" s="1">
+      <c r="B66" s="1">
         <f>50/100</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="D66" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E66" s="29">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>60</v>
       </c>
-      <c r="B84" s="32">
+      <c r="B67" s="32">
         <f>_h0_dalle</f>
         <v>123.71134020618557</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="D67" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="E67" s="30">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>101</v>
       </c>
-      <c r="B85" s="25">
-        <f>IF(_fck_dalle&lt;=35,1+(1-B83)/(0.1*B84^(1/3)),FALSE)</f>
+      <c r="B68" s="25">
+        <f>IF(_fck_dalle&lt;=35,1+(1-B66)/(0.1*B67^(1/3)),FALSE)</f>
         <v>2.0034602351846282</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>102</v>
       </c>
-      <c r="B86" s="34">
+      <c r="B69" s="34">
         <f>16.8/SQRT(_fcm_dalle)</f>
-        <v>2.9245046200557239</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+        <v>3.1749015732775088</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>103</v>
       </c>
-      <c r="B87" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="B70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>104</v>
       </c>
-      <c r="B88">
+      <c r="B71">
         <v>18250</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
         <v>105</v>
       </c>
-      <c r="B89" s="25">
-        <f>1/(0.1+B87^0.2)</f>
-        <v>0.48844954537902541</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="B72" s="25">
+        <f>1/(0.1+B70^0.2)</f>
+        <v>0.90909090909090906</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>106</v>
       </c>
-      <c r="B90" s="26">
-        <f>B85*B86*B89</f>
-        <v>2.8618887566193885</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="B73" s="26">
+        <f>B68*B69*B72</f>
+        <v>5.782535502442367</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
         <v>107</v>
       </c>
-      <c r="B91" s="3">
-        <f>IF(_fcm_dalle&lt;=35,MIN(B84*1.5*(1+(0.012*B83)^18)+250,1500),FALSE)</f>
+      <c r="B74" s="3">
+        <f>IF(_fcm_dalle&lt;=35,MIN(B67*1.5*(1+(0.012*B66)^18)+250,1500),FALSE)</f>
         <v>435.56701030927832</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
         <v>108</v>
       </c>
-      <c r="B92" s="26">
-        <f>((B88-B87)/(B91+B88-B87))^0.3</f>
-        <v>0.99293840715187665</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="B75" s="26">
+        <f>((B71-B70)/(B74+B71-B70))^0.3</f>
+        <v>0.99294869626582294</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
         <v>109</v>
       </c>
-      <c r="B93" s="25">
-        <f>B90*B92</f>
-        <v>2.8416792634435204</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="B76" s="25">
+        <f>B73*B75</f>
+        <v>5.7417610882609837</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>110</v>
       </c>
-      <c r="B94" s="26">
-        <f>B81*(1+B82*B93)</f>
-        <v>27.526790070897466</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="54"/>
-      <c r="B95" s="70"/>
-    </row>
-    <row r="96" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="75" t="s">
+      <c r="B77" s="26">
+        <f>B64*(1+B65*B76)</f>
+        <v>29.142741876247484</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="54"/>
+      <c r="B78" s="70"/>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B96" s="76"/>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="B79" s="78"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
         <v>183</v>
       </c>
-      <c r="B97" s="32">
-        <v>25.2</v>
-      </c>
-      <c r="C97" s="24"/>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>269</v>
-      </c>
-      <c r="B98" s="32">
+      <c r="B80" s="32">
+        <f>B77</f>
+        <v>29.142741876247484</v>
+      </c>
+      <c r="C80" s="24"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>266</v>
+      </c>
+      <c r="B81" s="32">
         <f>_beff_mi_travee</f>
         <v>2</v>
       </c>
-      <c r="C98" s="24"/>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B99" s="14"/>
-      <c r="C99" s="24"/>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>191</v>
-      </c>
-      <c r="B100" s="43" t="s">
-        <v>189</v>
-      </c>
-      <c r="C100" s="44" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>271</v>
-      </c>
-      <c r="B101" s="35">
-        <f>_td+_h/2</f>
-        <v>270</v>
-      </c>
-      <c r="C101" s="42">
-        <f>B101</f>
-        <v>270</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>270</v>
-      </c>
-      <c r="B102" s="72">
-        <f>_A*100+_beff*1000*(_td-_tj)/B97</f>
-        <v>13066.58873015873</v>
-      </c>
-      <c r="C102" s="40">
-        <f>B102</f>
-        <v>13066.58873015873</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="C81" s="24"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B82" s="14"/>
+      <c r="C82" s="24"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>293</v>
+      </c>
+      <c r="B83" s="32">
+        <v>-22</v>
+      </c>
+      <c r="C83" s="24" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="90" t="s">
+        <v>287</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85" s="63" t="s">
+        <v>292</v>
+      </c>
+      <c r="D85" s="63" t="s">
+        <v>294</v>
+      </c>
+      <c r="E85" s="63" t="s">
+        <v>295</v>
+      </c>
+      <c r="F85" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="G85" s="63" t="s">
+        <v>298</v>
+      </c>
+      <c r="H85" s="22" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="B86" s="91">
+        <f>_beff*1000/_n_dalle</f>
+        <v>68.627722418599234</v>
+      </c>
+      <c r="C86" s="54">
+        <f>MIN(MAX(_td-B83,0),_td)</f>
+        <v>120</v>
+      </c>
+      <c r="D86" s="54">
+        <f>_td-C86/2</f>
+        <v>60</v>
+      </c>
+      <c r="E86" s="76">
+        <f>B86*C86</f>
+        <v>8235.3266902319083</v>
+      </c>
+      <c r="F86" s="92">
+        <f>E86*D86</f>
+        <v>494119.60141391447</v>
+      </c>
+      <c r="G86" s="54">
+        <f>B86*C86^3/12</f>
+        <v>9882392.0282782894</v>
+      </c>
+      <c r="H86" s="88">
+        <f>E86*(D86-$F$92)^2</f>
+        <v>55520822.984722495</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="35" t="s">
+        <v>289</v>
+      </c>
+      <c r="B87" s="15">
+        <v>120</v>
+      </c>
+      <c r="C87" s="54">
+        <v>6</v>
+      </c>
+      <c r="D87" s="54">
+        <f>-C87/2</f>
+        <v>-3</v>
+      </c>
+      <c r="E87" s="76">
+        <f t="shared" ref="E87:E89" si="0">B87*C87</f>
+        <v>720</v>
+      </c>
+      <c r="F87" s="92">
+        <f t="shared" ref="F87:F89" si="1">E87*D87</f>
+        <v>-2160</v>
+      </c>
+      <c r="G87" s="54">
+        <f t="shared" ref="G87:G89" si="2">B87*C87^3/12</f>
+        <v>2160</v>
+      </c>
+      <c r="H87" s="88">
+        <f>E87*(D87-$F$92)^2</f>
+        <v>262893.98340079188</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="B88" s="15">
+        <v>7.1</v>
+      </c>
+      <c r="C88" s="54">
+        <f>_hw</f>
+        <v>283.3</v>
+      </c>
+      <c r="D88" s="54">
+        <f>-C87-C88/2</f>
+        <v>-147.65</v>
+      </c>
+      <c r="E88" s="76">
+        <f t="shared" si="0"/>
+        <v>2011.43</v>
+      </c>
+      <c r="F88" s="92">
+        <f t="shared" si="1"/>
+        <v>-296987.63950000005</v>
+      </c>
+      <c r="G88" s="54">
+        <f t="shared" si="2"/>
+        <v>13452928.259391665</v>
+      </c>
+      <c r="H88" s="88">
+        <f>E88*(D88-$F$92)^2</f>
+        <v>31701536.910552371</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="B89" s="15">
+        <v>150</v>
+      </c>
+      <c r="C89" s="54">
+        <v>10.7</v>
+      </c>
+      <c r="D89" s="54">
+        <f>-C87-C88-C89/2</f>
+        <v>-294.65000000000003</v>
+      </c>
+      <c r="E89" s="76">
+        <f t="shared" si="0"/>
+        <v>1605</v>
+      </c>
+      <c r="F89" s="92">
+        <f t="shared" si="1"/>
+        <v>-472913.25000000006</v>
+      </c>
+      <c r="G89" s="54">
+        <f t="shared" si="2"/>
+        <v>15313.037499999997</v>
+      </c>
+      <c r="H89" s="88">
+        <f>E89*(D89-$F$92)^2</f>
+        <v>119217682.1577512</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="90" t="s">
+        <v>296</v>
+      </c>
+      <c r="B90" s="21"/>
+      <c r="C90" s="93"/>
+      <c r="D90" s="63"/>
+      <c r="E90" s="94">
+        <f>SUM(E86:E89)</f>
+        <v>12571.756690231909</v>
+      </c>
+      <c r="F90" s="22"/>
+      <c r="G90" s="63"/>
+      <c r="H90" s="22"/>
+    </row>
+    <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E92" s="85" t="s">
         <v>90</v>
       </c>
-      <c r="B103" s="45">
-        <f>(B97*_A*100/(_beff*1000))*(-1+SQRT(1+2*_zp/(B97*_A*100/(_beff*1000))))</f>
-        <v>125.61217341909804</v>
-      </c>
-      <c r="C103" s="46">
-        <f>_zp*_A*100/_Ah+_beff*1000*(_td-_tj)^2/(2*B97*_Ah)</f>
-        <v>126.35239879771393</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>91</v>
-      </c>
-      <c r="B104" s="35">
-        <f>_tj</f>
-        <v>10</v>
-      </c>
-      <c r="C104" s="42">
+      <c r="F92" s="95">
+        <f>SUM(F86:F89)/E90</f>
+        <v>-22.108389060857533</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C93">
+        <f>SUM(E87:E89)*_fy/1000</f>
+        <v>1821.3006</v>
+      </c>
+      <c r="E93" s="86" t="s">
+        <v>300</v>
+      </c>
+      <c r="F93" s="96">
+        <f>SUM(G86:H89)</f>
+        <v>230055729.36159682</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E94" s="87" t="s">
+        <v>301</v>
+      </c>
+      <c r="F94" s="97">
+        <f>F93*10^(-4)</f>
+        <v>23005.572936159682</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="B96" s="78"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>303</v>
+      </c>
+      <c r="B97" s="32">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="C97" s="24" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" s="90" t="s">
+        <v>287</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" s="63" t="s">
+        <v>292</v>
+      </c>
+      <c r="D99" s="98" t="s">
+        <v>308</v>
+      </c>
+      <c r="E99" s="98" t="s">
+        <v>309</v>
+      </c>
+      <c r="F99" s="102" t="s">
+        <v>314</v>
+      </c>
+      <c r="G99" s="99" t="s">
+        <v>315</v>
+      </c>
+      <c r="H99" s="102" t="s">
+        <v>310</v>
+      </c>
+      <c r="I99" s="98" t="s">
+        <v>311</v>
+      </c>
+      <c r="J99" s="98" t="s">
+        <v>306</v>
+      </c>
+      <c r="K99" s="98" t="s">
+        <v>304</v>
+      </c>
+      <c r="L99" s="99" t="s">
+        <v>316</v>
+      </c>
+      <c r="M99" s="102" t="s">
+        <v>312</v>
+      </c>
+      <c r="N99" s="98" t="s">
+        <v>313</v>
+      </c>
+      <c r="O99" s="98" t="s">
+        <v>307</v>
+      </c>
+      <c r="P99" s="98" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q99" s="99" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="B100" s="91">
+        <f>_beff*1000</f>
+        <v>2000</v>
+      </c>
+      <c r="C100" s="54">
+        <v>120</v>
+      </c>
+      <c r="D100" s="54">
+        <f>_td</f>
+        <v>120</v>
+      </c>
+      <c r="E100" s="54">
+        <v>0</v>
+      </c>
+      <c r="F100" s="101">
+        <f>0.85*_fck_dalle/1.5</f>
+        <v>11.333333333333334</v>
+      </c>
+      <c r="G100" s="88">
+        <v>0</v>
+      </c>
+      <c r="H100" s="59">
+        <f>D100</f>
+        <v>120</v>
+      </c>
+      <c r="I100" s="55">
+        <f>IF($B$97&gt;=D100,D100,IF($B$97&lt;=E100,E100,$B$97))</f>
+        <v>39.700000000000003</v>
+      </c>
+      <c r="J100" s="55">
+        <f>H100-I100</f>
+        <v>80.3</v>
+      </c>
+      <c r="K100" s="54">
+        <f>J100*B100*F100/1000</f>
+        <v>1820.1333333333334</v>
+      </c>
+      <c r="L100" s="88">
+        <f>K100*((H100+I100)/2-$B$97)/1000</f>
+        <v>73.078353333333311</v>
+      </c>
+      <c r="M100" s="59">
+        <f>I100</f>
+        <v>39.700000000000003</v>
+      </c>
+      <c r="N100" s="54">
+        <f>E100</f>
+        <v>0</v>
+      </c>
+      <c r="O100" s="55">
+        <f>M100-N100</f>
+        <v>39.700000000000003</v>
+      </c>
+      <c r="P100" s="54">
+        <f>O100*B100*G100/1000</f>
+        <v>0</v>
+      </c>
+      <c r="Q100" s="88">
+        <f>P100*((M100+N100)/2-$B$97)/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101" s="35" t="s">
+        <v>289</v>
+      </c>
+      <c r="B101" s="15">
+        <v>120</v>
+      </c>
+      <c r="C101" s="54">
+        <v>6</v>
+      </c>
+      <c r="D101" s="54">
+        <v>0</v>
+      </c>
+      <c r="E101" s="54">
+        <f>-_tfs</f>
+        <v>-6</v>
+      </c>
+      <c r="F101" s="15">
+        <f>_fy</f>
+        <v>420</v>
+      </c>
+      <c r="G101" s="88">
+        <f>_fy</f>
+        <v>420</v>
+      </c>
+      <c r="H101" s="59">
+        <f t="shared" ref="H101:H103" si="3">D101</f>
+        <v>0</v>
+      </c>
+      <c r="I101" s="55">
+        <f t="shared" ref="I101:I103" si="4">IF($B$97&gt;=D101,D101,IF($B$97&lt;=E101,E101,$B$97))</f>
+        <v>0</v>
+      </c>
+      <c r="J101" s="55">
+        <f t="shared" ref="J101:J103" si="5">H101-I101</f>
+        <v>0</v>
+      </c>
+      <c r="K101" s="54">
+        <f>J101*B101*F101/1000</f>
+        <v>0</v>
+      </c>
+      <c r="L101" s="88">
+        <f t="shared" ref="L101:L103" si="6">K101*((H101+I101)/2-$B$97)/1000</f>
+        <v>0</v>
+      </c>
+      <c r="M101" s="59">
+        <f>I101</f>
+        <v>0</v>
+      </c>
+      <c r="N101" s="54">
+        <f>E101</f>
+        <v>-6</v>
+      </c>
+      <c r="O101" s="55">
+        <f>MIN(MAX(($B$97-E101),0),C101)</f>
+        <v>6</v>
+      </c>
+      <c r="P101" s="54">
+        <f>-O101*B101*F101/1000</f>
+        <v>-302.39999999999998</v>
+      </c>
+      <c r="Q101" s="88">
+        <f t="shared" ref="Q101:Q103" si="7">P101*((M101+N101)/2-$B$97)/1000</f>
+        <v>12.91248</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="B102" s="15">
+        <v>7.1</v>
+      </c>
+      <c r="C102" s="54">
+        <f>_hw</f>
+        <v>283.3</v>
+      </c>
+      <c r="D102" s="54">
+        <f>-_tfs</f>
+        <v>-6</v>
+      </c>
+      <c r="E102" s="54">
+        <f>-_tfs-_hw</f>
+        <v>-289.3</v>
+      </c>
+      <c r="F102" s="15">
+        <f>_fy</f>
+        <v>420</v>
+      </c>
+      <c r="G102" s="88">
+        <f>_fy</f>
+        <v>420</v>
+      </c>
+      <c r="H102" s="59">
+        <f t="shared" si="3"/>
+        <v>-6</v>
+      </c>
+      <c r="I102" s="55">
+        <f t="shared" si="4"/>
+        <v>-6</v>
+      </c>
+      <c r="J102" s="55">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K102" s="54">
+        <f>MIN(MAX((D102-$B$97),0),C102)*B102*F102/1000</f>
+        <v>0</v>
+      </c>
+      <c r="L102" s="88">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M102" s="59">
+        <f>I102</f>
+        <v>-6</v>
+      </c>
+      <c r="N102" s="54">
+        <f>E102</f>
+        <v>-289.3</v>
+      </c>
+      <c r="O102" s="55">
+        <f>MIN(MAX(($B$97-E102),0),C102)</f>
+        <v>283.3</v>
+      </c>
+      <c r="P102" s="54">
+        <f>-MIN(MAX(($B$97-E102),0),C102)*B102*F102/1000</f>
+        <v>-844.80060000000003</v>
+      </c>
+      <c r="Q102" s="88">
+        <f t="shared" si="7"/>
+        <v>158.27339241000004</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="B103" s="15">
+        <v>150</v>
+      </c>
+      <c r="C103" s="54">
+        <v>10.7</v>
+      </c>
+      <c r="D103" s="54">
+        <f>-_tfs-_hw</f>
+        <v>-289.3</v>
+      </c>
+      <c r="E103" s="54">
         <f>-_h</f>
         <v>-300</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>92</v>
-      </c>
-      <c r="B105" s="35">
-        <f>_td</f>
-        <v>120</v>
-      </c>
-      <c r="C105" s="42">
+      <c r="F103" s="15">
+        <f>_fy</f>
+        <v>420</v>
+      </c>
+      <c r="G103" s="88">
+        <f>_fy</f>
+        <v>420</v>
+      </c>
+      <c r="H103" s="61">
+        <f t="shared" si="3"/>
+        <v>-289.3</v>
+      </c>
+      <c r="I103" s="58">
+        <f t="shared" si="4"/>
+        <v>-289.3</v>
+      </c>
+      <c r="J103" s="58">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>93</v>
-      </c>
-      <c r="B106" s="35" t="b">
-        <f>IF(B104&lt;=_zel,IF(_zel&lt;=B105,TRUE,FALSE),FALSE)</f>
-        <v>1</v>
-      </c>
-      <c r="C106" s="35" t="b">
-        <f>IF(C104&lt;=C103,IF(C103&lt;=C105,TRUE,FALSE),FALSE)</f>
+      <c r="K103" s="89">
+        <f>MIN(MAX((D103-$B$97),0),C103)*B103*F103/1000</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>94</v>
-      </c>
-      <c r="B107" s="47">
-        <f>(_Iy*10^4+_A*100*(_zp-C103)^2+_beff*1000*B103^3/(3*B97))*10^(-4)</f>
-        <v>20112.625407572665</v>
-      </c>
-      <c r="C107" s="48">
-        <f>(_Iy*10^4+_A*100*(_zp-C103)^2+_beff*1000*(_td-_tj)/(3*B97)*((_td-_tj)^2+3*C103*(C103-(_td-_tj))))*10^(-4)</f>
-        <v>20194.300001846041</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B108" s="73"/>
-      <c r="C108" s="74"/>
-    </row>
-    <row r="109" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="75" t="s">
+      <c r="L103" s="30">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M103" s="61">
+        <f>I103</f>
+        <v>-289.3</v>
+      </c>
+      <c r="N103" s="89">
+        <f>E103</f>
+        <v>-300</v>
+      </c>
+      <c r="O103" s="58">
+        <f>MIN(MAX(($B$97-E103),0),C103)</f>
+        <v>10.7</v>
+      </c>
+      <c r="P103" s="89">
+        <f>-MIN(MAX(($B$97-E103),0),C103)*B103*F103/1000</f>
+        <v>-674.1</v>
+      </c>
+      <c r="Q103" s="30">
+        <f t="shared" si="7"/>
+        <v>225.385335</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" s="90" t="s">
+        <v>296</v>
+      </c>
+      <c r="B104" s="21"/>
+      <c r="C104" s="93"/>
+      <c r="D104" s="63"/>
+      <c r="E104" s="63"/>
+      <c r="F104" s="21"/>
+      <c r="G104" s="22"/>
+      <c r="H104" s="16"/>
+      <c r="I104" s="89"/>
+      <c r="J104" s="89"/>
+      <c r="K104" s="103">
+        <f>SUM(K100:K103)</f>
+        <v>1820.1333333333334</v>
+      </c>
+      <c r="L104" s="104">
+        <f>SUM(L100:L103)</f>
+        <v>73.078353333333311</v>
+      </c>
+      <c r="M104" s="109"/>
+      <c r="N104" s="103"/>
+      <c r="O104" s="103"/>
+      <c r="P104" s="103">
+        <f>SUM(P100:P103)</f>
+        <v>-1821.3006</v>
+      </c>
+      <c r="Q104" s="104">
+        <f>SUM(Q100:Q103)</f>
+        <v>396.57120741000006</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P105" s="54"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D106" s="105" t="s">
+        <v>318</v>
+      </c>
+      <c r="E106" s="106">
+        <f>K104+P104</f>
+        <v>-1.1672666666665918</v>
+      </c>
+      <c r="G106" t="s">
+        <v>320</v>
+      </c>
+      <c r="H106" s="23">
+        <f>(_td-B97)/(_h+_td)*100</f>
+        <v>19.11904761904762</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D107" s="107" t="s">
+        <v>319</v>
+      </c>
+      <c r="E107" s="108">
+        <f>L104+Q104</f>
+        <v>469.64956074333338</v>
+      </c>
+      <c r="G107" t="s">
+        <v>321</v>
+      </c>
+      <c r="H107" s="25">
+        <f>IF(H106&lt;=15,1,IF(H106&gt;=40,0.85,1+(H106-15)/(40-15)*(0.85-1)))</f>
+        <v>0.97528571428571431</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="110" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="77" t="s">
+        <v>133</v>
+      </c>
+      <c r="B110" s="78"/>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>130</v>
+      </c>
+      <c r="B111" s="27">
+        <f>H11+E20</f>
+        <v>6.2199419696550002</v>
+      </c>
+      <c r="C111" s="26">
+        <f>B111*1.35</f>
+        <v>8.3969216590342501</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>322</v>
+      </c>
+      <c r="B112" s="27">
+        <v>2</v>
+      </c>
+      <c r="C112" s="26"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="B113" s="111">
+        <f>B111*_L/2</f>
+        <v>31.099709848275001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B114" s="112">
+        <f>B111*_L^2/8</f>
+        <v>77.749274620687501</v>
+      </c>
+      <c r="D114" s="24"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="B115" s="111">
+        <f>B112*(_b_Gauche+_b_Droite)*_L/2</f>
+        <v>20</v>
+      </c>
+      <c r="D115" s="24"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="B116" s="112">
+        <f>B112*(_b_Gauche+_b_Droite)*_L^2/8</f>
+        <v>50</v>
+      </c>
+      <c r="D116" s="24"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="B117" s="53">
+        <v>0.5</v>
+      </c>
+      <c r="D117" s="24"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="B118" s="110">
+        <f>B117*_L/2</f>
+        <v>2.5</v>
+      </c>
+      <c r="D118" s="24"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="B119" s="53">
+        <f>4*(_L-4)/_L</f>
+        <v>2.4</v>
+      </c>
+      <c r="D119" s="24"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="B120" s="110">
+        <f>B119*_L/2</f>
+        <v>12</v>
+      </c>
+      <c r="D120" s="24"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="100" t="s">
+        <v>326</v>
+      </c>
+      <c r="B121" s="117">
+        <f>325*10^(-6)</f>
+        <v>3.2499999999999999E-4</v>
+      </c>
+      <c r="D121" s="24"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="116" t="s">
+        <v>327</v>
+      </c>
+      <c r="B122" s="118">
+        <v>210000</v>
+      </c>
+      <c r="D122" s="24"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="116" t="s">
+        <v>226</v>
+      </c>
+      <c r="B123" s="88">
+        <f>_Ac_brute</f>
+        <v>240000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="116" t="s">
+        <v>328</v>
+      </c>
+      <c r="B124" s="57">
+        <v>29.142741876247484</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="116" t="s">
+        <v>330</v>
+      </c>
+      <c r="B125" s="57">
+        <v>-22.108000000000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="116" t="s">
+        <v>329</v>
+      </c>
+      <c r="B126" s="19">
+        <f>B121*B122*B123/(1000*B124)</f>
+        <v>562.06104660832773</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="119" t="s">
+        <v>331</v>
+      </c>
+      <c r="B127" s="20">
+        <f>B126*((_td-_tj)/2+_tj-B125)/1000</f>
+        <v>48.960013647958213</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="100" t="s">
+        <v>333</v>
+      </c>
+      <c r="B128" s="74">
+        <f>1.35*B113+1.35*B115+1.5*B117</f>
+        <v>69.734608295171256</v>
+      </c>
+      <c r="C128" s="24" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="119" t="s">
+        <v>332</v>
+      </c>
+      <c r="B129" s="20">
+        <f>1.35*B114+1.35*B116+1.5*B118</f>
+        <v>176.21152073792814</v>
+      </c>
+      <c r="C129" s="24"/>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="100" t="s">
+        <v>334</v>
+      </c>
+      <c r="B130" s="74">
+        <f>1.35*B113+1.5*B119</f>
+        <v>45.584608295171257</v>
+      </c>
+      <c r="C130" s="24" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="119" t="s">
+        <v>335</v>
+      </c>
+      <c r="B131" s="20">
+        <f>1.35*B114+1.5*B120</f>
+        <v>122.96152073792814</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="B110" s="76"/>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="B133" s="78"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
         <v>123</v>
       </c>
-      <c r="B111" s="23">
-        <f>_Wpl_y*1000*_fy*10^(-6)</f>
-        <v>191.08403999999999</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>248</v>
-      </c>
-      <c r="B112" s="23">
+      <c r="B134" s="23">
+        <f>H107*E107</f>
+        <v>458.04250731353386</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>245</v>
+      </c>
+      <c r="B135" s="23">
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>487.74585382155738</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B113" s="23"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="21"/>
-      <c r="B114" s="62" t="s">
-        <v>249</v>
-      </c>
-      <c r="C114" s="63" t="s">
-        <v>250</v>
-      </c>
-      <c r="D114" s="22" t="s">
-        <v>251</v>
-      </c>
-      <c r="F114" s="21"/>
-      <c r="G114" s="65" t="s">
-        <v>249</v>
-      </c>
-      <c r="H114" s="66" t="s">
-        <v>250</v>
-      </c>
-      <c r="I114" s="29" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="15" t="s">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B136" s="23"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>141</v>
       </c>
-      <c r="B115" s="59">
-        <f>MAX(B71,ABS(B72))/_Mpl_Rd</f>
-        <v>0.50323407438946766</v>
-      </c>
-      <c r="C115" s="55">
-        <f>MAX(B74,ABS(B75))/_Mpl_Rd</f>
-        <v>0.58560620761419957</v>
-      </c>
-      <c r="D115" s="17">
-        <f>MAX(B77,ABS(B78))/_Mpl_Rd</f>
-        <v>0.37187825838306543</v>
-      </c>
-      <c r="F115" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G115" s="67">
-        <f>B115</f>
-        <v>0.50323407438946766</v>
-      </c>
-      <c r="H115" s="68">
-        <f t="shared" ref="H115:I116" si="0">C115</f>
-        <v>0.58560620761419957</v>
-      </c>
-      <c r="I115" s="69">
-        <f t="shared" si="0"/>
-        <v>0.37187825838306543</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="B116" s="59">
-        <f>B70/B112</f>
-        <v>0.1366490344875059</v>
-      </c>
-      <c r="C116" s="55">
-        <f>B73/B112</f>
-        <v>0.13111336467330836</v>
-      </c>
-      <c r="D116" s="17">
-        <f>B76/B112</f>
-        <v>0.10076969309918851</v>
-      </c>
-      <c r="F116" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="G116" s="59">
-        <f>B116</f>
-        <v>0.1366490344875059</v>
-      </c>
-      <c r="H116" s="55">
-        <f t="shared" si="0"/>
-        <v>0.13111336467330836</v>
-      </c>
-      <c r="I116" s="17">
-        <f t="shared" si="0"/>
-        <v>0.10076969309918851</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="B117" s="60">
-        <f>1/B115</f>
-        <v>1.9871468386023292</v>
-      </c>
-      <c r="C117" s="56">
-        <f t="shared" ref="C117:D117" si="1">1/C115</f>
-        <v>1.7076321715817693</v>
-      </c>
-      <c r="D117" s="57">
-        <f t="shared" si="1"/>
-        <v>2.6890520686743593</v>
-      </c>
-      <c r="F117" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="G117" s="60">
-        <v>521.97</v>
-      </c>
-      <c r="H117" s="56">
-        <v>546.22</v>
-      </c>
-      <c r="I117" s="57">
-        <v>496.55</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="B118" s="60">
-        <v>5.4870000000000001</v>
-      </c>
-      <c r="C118" s="56">
-        <v>4.9240000000000004</v>
-      </c>
-      <c r="D118" s="57">
-        <v>6.9660000000000002</v>
-      </c>
-      <c r="F118" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="G118" s="59">
-        <f>SQRT(_Mpl_Rd/G117)</f>
-        <v>0.60504745146955252</v>
-      </c>
-      <c r="H118" s="55">
-        <f>SQRT(_Mpl_Rd/H117)</f>
-        <v>0.59146412584669672</v>
-      </c>
-      <c r="I118" s="17">
-        <f>SQRT(_Mpl_Rd/I117)</f>
-        <v>0.62034132636172667</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="B119" s="59">
-        <f>SQRT(B117/B118)</f>
-        <v>0.60179351021887739</v>
-      </c>
-      <c r="C119" s="55">
-        <f t="shared" ref="C119:D119" si="2">SQRT(C117/C118)</f>
-        <v>0.58889537294199867</v>
-      </c>
-      <c r="D119" s="17">
-        <f t="shared" si="2"/>
-        <v>0.62130932347274503</v>
-      </c>
-      <c r="F119" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="G119" s="60">
-        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
-        <v>0.34</v>
-      </c>
-      <c r="H119" s="56">
-        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
-        <v>0.34</v>
-      </c>
-      <c r="I119" s="57">
-        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="B120" s="60">
-        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
-        <v>0.34</v>
-      </c>
-      <c r="C120" s="56">
-        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
-        <v>0.34</v>
-      </c>
-      <c r="D120" s="57">
-        <f>IF(_h/_bfs&lt;=2,0.21,0.34)</f>
-        <v>0.34</v>
-      </c>
-      <c r="F120" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="G120" s="59">
-        <f>0.5*(1+G119*(G118-0.2)+G118^2)</f>
-        <v>0.75189927601472428</v>
-      </c>
-      <c r="H120" s="55">
-        <f t="shared" ref="H120:I120" si="3">0.5*(1+H119*(H118-0.2)+H118^2)</f>
-        <v>0.74146380747573692</v>
-      </c>
-      <c r="I120" s="17">
-        <f t="shared" si="3"/>
-        <v>0.76386970607760662</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="B121" s="59">
-        <f>0.5*(1+B120*(B119-0.2)+B119^2)</f>
-        <v>0.74938261120798821</v>
-      </c>
-      <c r="C121" s="55">
-        <f t="shared" ref="C121:D121" si="4">0.5*(1+C120*(C119-0.2)+C119^2)</f>
-        <v>0.73951109353638755</v>
-      </c>
-      <c r="D121" s="17">
-        <f t="shared" si="4"/>
-        <v>0.76463522270744666</v>
-      </c>
-      <c r="F121" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="G121" s="59">
-        <f>1/(G120+SQRT(G120^2-G118^2))</f>
-        <v>0.83451829669193112</v>
-      </c>
-      <c r="H121" s="55">
-        <f t="shared" ref="H121:I121" si="5">1/(H120+SQRT(H120^2-H118^2))</f>
-        <v>0.84131960481121948</v>
-      </c>
-      <c r="I121" s="17">
-        <f t="shared" si="5"/>
-        <v>0.82672105507651716</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="B122" s="59">
-        <f>1/(B121+SQRT(B121^2-B119^2))</f>
-        <v>0.83615814738565442</v>
-      </c>
-      <c r="C122" s="55">
-        <f t="shared" ref="C122:D122" si="6">1/(C121+SQRT(C121^2-C119^2))</f>
-        <v>0.84259280326221675</v>
-      </c>
-      <c r="D122" s="17">
-        <f t="shared" si="6"/>
-        <v>0.82622254561044939</v>
-      </c>
-      <c r="F122" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="G122" s="60">
-        <f>G121*_Mpl_Rd</f>
-        <v>159.46312758581283</v>
-      </c>
-      <c r="H122" s="56">
-        <f>H121*_Mpl_Rd</f>
-        <v>160.76274901853125</v>
-      </c>
-      <c r="I122" s="57">
-        <f>I121*_Mpl_Rd</f>
-        <v>157.9731991570834</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B123" s="60">
-        <f>B122*_Mpl_Rd</f>
-        <v>159.77647688136628</v>
-      </c>
-      <c r="C123" s="56">
-        <f>C122*_Mpl_Rd</f>
-        <v>161.00603692226954</v>
-      </c>
-      <c r="D123" s="57">
-        <f>D122*_Mpl_Rd</f>
-        <v>157.87794195432892</v>
-      </c>
-      <c r="F123" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="G123" s="61">
-        <f>G115/G121</f>
-        <v>0.60302341648386937</v>
-      </c>
-      <c r="H123" s="58">
-        <f>H115/H121</f>
-        <v>0.69605677113111075</v>
-      </c>
-      <c r="I123" s="18">
-        <f>I115/I121</f>
-        <v>0.44982313695717624</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="B124" s="61">
-        <f>B115/B122</f>
-        <v>0.60184078330503321</v>
-      </c>
-      <c r="C124" s="58">
-        <f t="shared" ref="C124:D124" si="7">C115/C122</f>
-        <v>0.69500499570722962</v>
-      </c>
-      <c r="D124" s="18">
-        <f t="shared" si="7"/>
-        <v>0.45009454215305333</v>
+      <c r="B137">
+        <f>B129/_Mpl_Rd</f>
+        <v>0.38470560684733546</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J52:K52"/>
     <mergeCell ref="A110:B110"/>
+    <mergeCell ref="A133:B133"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A79:B79"/>
     <mergeCell ref="A96:B96"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -60,6 +60,7 @@
     <definedName name="_be2" localSheetId="4">'Cas 6'!$B$4</definedName>
     <definedName name="_beff" localSheetId="4">'Cas 6'!$B$81</definedName>
     <definedName name="_beff_appui" localSheetId="1">'Cas 3'!$B$11</definedName>
+    <definedName name="_beff_appuis" localSheetId="4">'Cas 6'!$B$11</definedName>
     <definedName name="_beff_mi_travee" localSheetId="1">'Cas 3'!$B$10</definedName>
     <definedName name="_beff_mi_travee" localSheetId="4">'Cas 6'!$B$10</definedName>
     <definedName name="_beta1" localSheetId="1">'Cas 3'!$B$8</definedName>
@@ -158,7 +159,7 @@
     <definedName name="_Mel_y_Rd" localSheetId="0">'Cas 2'!$B$53</definedName>
     <definedName name="_Mel_z_Rd" localSheetId="0">'Cas 2'!$B$54</definedName>
     <definedName name="_Mpl_Rd" localSheetId="3">'Cas 5'!$B$70</definedName>
-    <definedName name="_Mpl_Rd" localSheetId="4">'Cas 6'!$B$134</definedName>
+    <definedName name="_Mpl_Rd" localSheetId="4">'Cas 6'!#REF!</definedName>
     <definedName name="_Mpl_y_Rd" localSheetId="0">'Cas 2'!$B$55</definedName>
     <definedName name="_Mpl_z_Rd" localSheetId="0">'Cas 2'!$B$56</definedName>
     <definedName name="_n" localSheetId="0">'Cas 2'!$B$69</definedName>
@@ -261,7 +262,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="370">
   <si>
     <t>h (mm)</t>
   </si>
@@ -1272,13 +1273,112 @@
   </si>
   <si>
     <t>Répartition plastique (acier entierement tendu)</t>
+  </si>
+  <si>
+    <t>Flexion obtenue sur RDM7</t>
+  </si>
+  <si>
+    <t>Propriétés plastiques pour x = 0,5 m (eta)</t>
+  </si>
+  <si>
+    <t>L/4 (m)</t>
+  </si>
+  <si>
+    <t>x (m)</t>
+  </si>
+  <si>
+    <t>Delta Rd (kN)</t>
+  </si>
+  <si>
+    <t>Nc,Rd (kN)</t>
+  </si>
+  <si>
+    <t>t dalle (mm)</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>SHC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critere sigma </t>
+  </si>
+  <si>
+    <t>critere sup profilé</t>
+  </si>
+  <si>
+    <t>critere  inf profilé</t>
+  </si>
+  <si>
+    <t>Travail de la dalle ?</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>sigma sup dalle (MPa)</t>
+  </si>
+  <si>
+    <t>sigma sup profilé (MPa)</t>
+  </si>
+  <si>
+    <t>sigma inf profilé (MPa)</t>
+  </si>
+  <si>
+    <t>ELU</t>
+  </si>
+  <si>
+    <t>Critere MV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beta </t>
+  </si>
+  <si>
+    <t>Le calcul prend en compte le fluage car Cl3</t>
+  </si>
+  <si>
+    <t>flux cisaillement connecteur (kN/m)</t>
+  </si>
+  <si>
+    <t>Sh,i (mm3)</t>
+  </si>
+  <si>
+    <t>Ved (kN)</t>
+  </si>
+  <si>
+    <t>PRd/sx (kN/m)</t>
+  </si>
+  <si>
+    <t>IY (cm4) mi travee</t>
+  </si>
+  <si>
+    <t>zel (mm) mi travee</t>
+  </si>
+  <si>
+    <t>IY (cm4) appuis</t>
+  </si>
+  <si>
+    <t>zel (mm) appuis</t>
+  </si>
+  <si>
+    <t>Propriétés plastiques à mi travée (eta)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
@@ -1287,6 +1387,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="0.000000"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0.0\ _€_-;\-* #,##0.0\ _€_-;_-* &quot;-&quot;?\ _€_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1346,7 +1447,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1676,12 +1777,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1773,28 +1887,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
@@ -1832,6 +1925,125 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Milliers" xfId="1" builtinId="3"/>
@@ -2125,20 +2337,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="78"/>
+      <c r="B1" s="114"/>
       <c r="C1"/>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="78"/>
+      <c r="E1" s="114"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="78"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -2400,10 +2612,10 @@
         <v>0.81361651346682706</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="77" t="s">
+      <c r="D15" s="113" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="78"/>
+      <c r="E15" s="114"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
@@ -2542,10 +2754,10 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="77" t="s">
+      <c r="A30" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="78"/>
+      <c r="B30" s="114"/>
       <c r="C30" s="24" t="s">
         <v>53</v>
       </c>
@@ -2813,10 +3025,10 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="77" t="s">
+      <c r="A50" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="78"/>
+      <c r="B50" s="114"/>
       <c r="D50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2853,10 +3065,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E52" s="79" t="s">
+      <c r="E52" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="F52" s="80"/>
+      <c r="F52" s="116"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -3104,10 +3316,10 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="77" t="s">
+      <c r="A68" s="113" t="s">
         <v>79</v>
       </c>
-      <c r="B68" s="78"/>
+      <c r="B68" s="114"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -3391,10 +3603,10 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="77" t="s">
+      <c r="A96" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="B96" s="78"/>
+      <c r="B96" s="114"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -3498,10 +3710,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="77" t="s">
+      <c r="A109" s="113" t="s">
         <v>133</v>
       </c>
-      <c r="B109" s="78"/>
+      <c r="B109" s="114"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -3584,10 +3796,10 @@
     </row>
     <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="77" t="s">
+      <c r="A120" s="113" t="s">
         <v>134</v>
       </c>
-      <c r="B120" s="78"/>
+      <c r="B120" s="114"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
@@ -3712,20 +3924,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="113" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="78"/>
+      <c r="B1" s="114"/>
       <c r="C1"/>
-      <c r="D1" s="77" t="s">
+      <c r="D1" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="78"/>
+      <c r="E1" s="114"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="77" t="s">
+      <c r="G1" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="78"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -3960,16 +4172,16 @@
         <f>500/1.15</f>
         <v>434.78260869565219</v>
       </c>
-      <c r="G12" s="77" t="s">
+      <c r="G12" s="113" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="78"/>
+      <c r="H12" s="114"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="78"/>
+      <c r="B13" s="114"/>
       <c r="C13"/>
       <c r="D13" t="s">
         <v>125</v>
@@ -4008,10 +4220,10 @@
         <v>200</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="77" t="s">
+      <c r="D15" s="113" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="78"/>
+      <c r="E15" s="114"/>
       <c r="G15" t="s">
         <v>166</v>
       </c>
@@ -4315,10 +4527,10 @@
       <c r="C30"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="77" t="s">
+      <c r="A31" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="78"/>
+      <c r="B31" s="114"/>
       <c r="C31" s="24" t="s">
         <v>53</v>
       </c>
@@ -4586,10 +4798,10 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="77" t="s">
+      <c r="A51" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="78"/>
+      <c r="B51" s="114"/>
       <c r="D51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4626,10 +4838,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E53" s="79" t="s">
+      <c r="E53" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="80"/>
+      <c r="F53" s="116"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -4877,10 +5089,10 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="77" t="s">
+      <c r="A69" s="113" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="78"/>
+      <c r="B69" s="114"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -5061,10 +5273,10 @@
       <c r="C84" s="36"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="81" t="s">
+      <c r="A85" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="82"/>
+      <c r="B85" s="118"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -5207,10 +5419,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="77" t="s">
+      <c r="A101" s="113" t="s">
         <v>111</v>
       </c>
-      <c r="B101" s="78"/>
+      <c r="B101" s="114"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
@@ -5350,10 +5562,10 @@
     </row>
     <row r="117" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="118" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="77" t="s">
+      <c r="A118" s="113" t="s">
         <v>133</v>
       </c>
-      <c r="B118" s="78"/>
+      <c r="B118" s="114"/>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
@@ -5472,10 +5684,10 @@
     </row>
     <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="77" t="s">
+      <c r="A133" s="113" t="s">
         <v>134</v>
       </c>
-      <c r="B133" s="78"/>
+      <c r="B133" s="114"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
@@ -5591,10 +5803,10 @@
     </row>
     <row r="146" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="147" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="77" t="s">
+      <c r="A147" s="113" t="s">
         <v>207</v>
       </c>
-      <c r="B147" s="78"/>
+      <c r="B147" s="114"/>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
@@ -5660,11 +5872,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D15:E15"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="G12:H12"/>
@@ -5675,6 +5882,11 @@
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A118:B118"/>
     <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D15:E15"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16">
@@ -5713,18 +5925,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="113" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="114"/>
+      <c r="D1" s="113" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="G1" s="77" t="s">
+      <c r="E1" s="114"/>
+      <c r="G1" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="78"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -5848,10 +6060,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="78"/>
+      <c r="B9" s="114"/>
       <c r="D9" t="s">
         <v>32</v>
       </c>
@@ -6050,10 +6262,10 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="77" t="s">
+      <c r="A29" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="78"/>
+      <c r="B29" s="114"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -6072,10 +6284,10 @@
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>1042.1194079466816</v>
       </c>
-      <c r="D31" s="79" t="s">
+      <c r="D31" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="80"/>
+      <c r="E31" s="116"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -6255,16 +6467,16 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="77" t="s">
+      <c r="A47" s="113" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="78"/>
+      <c r="B47" s="114"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="114" t="s">
+      <c r="A48" s="107" t="s">
         <v>130</v>
       </c>
-      <c r="B48" s="115">
+      <c r="B48" s="108">
         <f>E19+H7</f>
         <v>6.8560492004849909</v>
       </c>
@@ -6284,7 +6496,7 @@
       <c r="A50" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="B50" s="113">
+      <c r="B50" s="106">
         <v>55.1</v>
       </c>
     </row>
@@ -6292,7 +6504,7 @@
       <c r="A51" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="B51" s="110">
+      <c r="B51" s="103">
         <v>55.1</v>
       </c>
     </row>
@@ -6426,10 +6638,10 @@
     </row>
     <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="77" t="s">
+      <c r="A69" s="113" t="s">
         <v>134</v>
       </c>
-      <c r="B69" s="78"/>
+      <c r="B69" s="114"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -6791,10 +7003,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q137"/>
+  <dimension ref="A1:Q186"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
@@ -6808,18 +7020,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="113" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="D1" s="77" t="s">
+      <c r="B1" s="114"/>
+      <c r="D1" s="113" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="78"/>
-      <c r="G1" s="77" t="s">
+      <c r="E1" s="114"/>
+      <c r="G1" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="78"/>
+      <c r="H1" s="114"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -7041,10 +7253,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="77" t="s">
+      <c r="A13" s="113" t="s">
         <v>256</v>
       </c>
-      <c r="B13" s="78"/>
+      <c r="B13" s="114"/>
       <c r="D13" t="s">
         <v>38</v>
       </c>
@@ -7068,10 +7280,10 @@
         <f>(_bfi-2*_r-_tw)/2</f>
         <v>71.45</v>
       </c>
-      <c r="G14" s="77" t="s">
+      <c r="G14" s="113" t="s">
         <v>162</v>
       </c>
-      <c r="H14" s="78"/>
+      <c r="H14" s="114"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -7330,10 +7542,10 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="77" t="s">
+      <c r="A33" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="78"/>
+      <c r="B33" s="114"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -7352,10 +7564,10 @@
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>487.74585382155738</v>
       </c>
-      <c r="D35" s="79" t="s">
+      <c r="D35" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="80"/>
+      <c r="E35" s="116"/>
       <c r="G35" s="21" t="s">
         <v>44</v>
       </c>
@@ -7465,10 +7677,10 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J40" s="79" t="s">
+      <c r="J40" s="115" t="s">
         <v>276</v>
       </c>
-      <c r="K40" s="80"/>
+      <c r="K40" s="116"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -7527,10 +7739,10 @@
         <f>B45-300</f>
         <v>-178.04000000000002</v>
       </c>
-      <c r="J45" s="79" t="s">
+      <c r="J45" s="115" t="s">
         <v>277</v>
       </c>
-      <c r="K45" s="80"/>
+      <c r="K45" s="116"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -7578,10 +7790,10 @@
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J49" s="79" t="s">
+      <c r="J49" s="115" t="s">
         <v>278</v>
       </c>
-      <c r="K49" s="80"/>
+      <c r="K49" s="116"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -7616,10 +7828,10 @@
         <f>IF(B47&gt;0.5,IF(B42&lt;=K41,1,IF(B42&lt;=K42,2,IF(B48&gt;-1,IF(B42&lt;=K50,3,4),IF(B42&lt;=K54,3,4)))),IF(B42&lt;=K46,1,IF(B42&lt;=K47,2,IF(B48&gt;-1,IF(B42&lt;=K50,3,4),IF(B42&lt;=K54,3,4)))))</f>
         <v>2</v>
       </c>
-      <c r="J52" s="79" t="s">
+      <c r="J52" s="115" t="s">
         <v>280</v>
       </c>
-      <c r="K52" s="80"/>
+      <c r="K52" s="116"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -7683,10 +7895,10 @@
       <c r="B62" s="70"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="83" t="s">
+      <c r="A63" s="119" t="s">
         <v>188</v>
       </c>
-      <c r="B63" s="84"/>
+      <c r="B63" s="120"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -7832,18 +8044,17 @@
       <c r="B78" s="70"/>
     </row>
     <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="77" t="s">
+      <c r="A79" s="113" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="78"/>
+      <c r="B79" s="114"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>183</v>
       </c>
       <c r="B80" s="32">
-        <f>B77</f>
-        <v>29.142741876247484</v>
+        <v>29.1</v>
       </c>
       <c r="C80" s="24"/>
     </row>
@@ -7852,8 +8063,7 @@
         <v>266</v>
       </c>
       <c r="B81" s="32">
-        <f>_beff_mi_travee</f>
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="C81" s="24"/>
     </row>
@@ -7866,14 +8076,14 @@
         <v>293</v>
       </c>
       <c r="B83" s="32">
-        <v>-22</v>
+        <v>-34</v>
       </c>
       <c r="C83" s="24" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="90" t="s">
+      <c r="A85" s="83" t="s">
         <v>287</v>
       </c>
       <c r="B85" s="21" t="s">
@@ -7902,9 +8112,9 @@
       <c r="A86" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="B86" s="91">
+      <c r="B86" s="84">
         <f>_beff*1000/_n_dalle</f>
-        <v>68.627722418599234</v>
+        <v>54.982817869415804</v>
       </c>
       <c r="C86" s="54">
         <f>MIN(MAX(_td-B83,0),_td)</f>
@@ -7916,19 +8126,19 @@
       </c>
       <c r="E86" s="76">
         <f>B86*C86</f>
-        <v>8235.3266902319083</v>
-      </c>
-      <c r="F86" s="92">
+        <v>6597.9381443298962</v>
+      </c>
+      <c r="F86" s="85">
         <f>E86*D86</f>
-        <v>494119.60141391447</v>
+        <v>395876.28865979379</v>
       </c>
       <c r="G86" s="54">
         <f>B86*C86^3/12</f>
-        <v>9882392.0282782894</v>
-      </c>
-      <c r="H86" s="88">
+        <v>7917525.7731958749</v>
+      </c>
+      <c r="H86" s="81">
         <f>E86*(D86-$F$92)^2</f>
-        <v>55520822.984722495</v>
+        <v>58801425.338739321</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -7949,7 +8159,7 @@
         <f t="shared" ref="E87:E89" si="0">B87*C87</f>
         <v>720</v>
       </c>
-      <c r="F87" s="92">
+      <c r="F87" s="85">
         <f t="shared" ref="F87:F89" si="1">E87*D87</f>
         <v>-2160</v>
       </c>
@@ -7957,9 +8167,9 @@
         <f t="shared" ref="G87:G89" si="2">B87*C87^3/12</f>
         <v>2160</v>
       </c>
-      <c r="H87" s="88">
+      <c r="H87" s="81">
         <f>E87*(D87-$F$92)^2</f>
-        <v>262893.98340079188</v>
+        <v>710066.2821910996</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -7981,7 +8191,7 @@
         <f t="shared" si="0"/>
         <v>2011.43</v>
       </c>
-      <c r="F88" s="92">
+      <c r="F88" s="85">
         <f t="shared" si="1"/>
         <v>-296987.63950000005</v>
       </c>
@@ -7989,9 +8199,9 @@
         <f t="shared" si="2"/>
         <v>13452928.259391665</v>
       </c>
-      <c r="H88" s="88">
+      <c r="H88" s="81">
         <f>E88*(D88-$F$92)^2</f>
-        <v>31701536.910552371</v>
+        <v>25795957.219251785</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -8012,7 +8222,7 @@
         <f t="shared" si="0"/>
         <v>1605</v>
       </c>
-      <c r="F89" s="92">
+      <c r="F89" s="85">
         <f t="shared" si="1"/>
         <v>-472913.25000000006</v>
       </c>
@@ -8020,21 +8230,21 @@
         <f t="shared" si="2"/>
         <v>15313.037499999997</v>
       </c>
-      <c r="H89" s="88">
+      <c r="H89" s="81">
         <f>E89*(D89-$F$92)^2</f>
-        <v>119217682.1577512</v>
+        <v>108703515.74962555</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="90" t="s">
+      <c r="A90" s="83" t="s">
         <v>296</v>
       </c>
       <c r="B90" s="21"/>
-      <c r="C90" s="93"/>
+      <c r="C90" s="86"/>
       <c r="D90" s="63"/>
-      <c r="E90" s="94">
+      <c r="E90" s="87">
         <f>SUM(E86:E89)</f>
-        <v>12571.756690231909</v>
+        <v>10934.368144329896</v>
       </c>
       <c r="F90" s="22"/>
       <c r="G90" s="63"/>
@@ -8042,12 +8252,12 @@
     </row>
     <row r="91" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E92" s="85" t="s">
+      <c r="E92" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="F92" s="95">
+      <c r="F92" s="88">
         <f>SUM(F86:F89)/E90</f>
-        <v>-22.108389060857533</v>
+        <v>-34.40387189041919</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -8055,686 +8265,1615 @@
         <f>SUM(E87:E89)*_fy/1000</f>
         <v>1821.3006</v>
       </c>
-      <c r="E93" s="86" t="s">
+      <c r="E93" s="79" t="s">
         <v>300</v>
       </c>
-      <c r="F93" s="96">
+      <c r="F93" s="89">
         <f>SUM(G86:H89)</f>
-        <v>230055729.36159682</v>
+        <v>215398891.6598953</v>
       </c>
     </row>
     <row r="94" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E94" s="87" t="s">
+      <c r="E94" s="80" t="s">
         <v>301</v>
       </c>
-      <c r="F94" s="97">
+      <c r="F94" s="90">
         <f>F93*10^(-4)</f>
-        <v>23005.572936159682</v>
+        <v>21539.889165989531</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="77" t="s">
-        <v>111</v>
-      </c>
-      <c r="B96" s="78"/>
+      <c r="A96" s="113" t="s">
+        <v>369</v>
+      </c>
+      <c r="B96" s="114"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="A97" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="B97" s="121">
+        <f>_L/4</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B98" s="122">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B99" s="121">
+        <f>IF(B98&lt;=B97,_beff_appuis+(_beff_mi_travee-_beff_appuis)/B97*B98,_beff_mi_travee)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100" s="123" t="s">
+        <v>341</v>
+      </c>
+      <c r="B100" s="14">
+        <f>_PRd*B98*1000/_sx</f>
+        <v>1706.1280891787565</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101" s="123" t="s">
+        <v>342</v>
+      </c>
+      <c r="B101" s="14">
+        <f>B99*1000*(_td-_tj)*0.85*_fck_dalle/1.5/1000</f>
+        <v>2493.3333333333335</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102" s="123" t="s">
+        <v>343</v>
+      </c>
+      <c r="B102" s="14">
+        <f>MIN(B100:B101)*1000/(0.85*_fck_dalle/1.5*B99*1000)</f>
+        <v>75.270356875533366</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" s="121"/>
+      <c r="B103" s="121"/>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>303</v>
       </c>
-      <c r="B97" s="32">
-        <v>39.700000000000003</v>
-      </c>
-      <c r="C97" s="24" t="s">
+      <c r="B104" s="32">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="C104" s="24" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A99" s="90" t="s">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106" s="83" t="s">
         <v>287</v>
       </c>
-      <c r="B99" s="21" t="s">
+      <c r="B106" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="63" t="s">
+      <c r="C106" s="63" t="s">
         <v>292</v>
       </c>
-      <c r="D99" s="98" t="s">
+      <c r="D106" s="91" t="s">
         <v>308</v>
       </c>
-      <c r="E99" s="98" t="s">
+      <c r="E106" s="91" t="s">
         <v>309</v>
       </c>
-      <c r="F99" s="102" t="s">
+      <c r="F106" s="95" t="s">
         <v>314</v>
       </c>
-      <c r="G99" s="99" t="s">
+      <c r="G106" s="92" t="s">
         <v>315</v>
       </c>
-      <c r="H99" s="102" t="s">
+      <c r="H106" s="95" t="s">
         <v>310</v>
       </c>
-      <c r="I99" s="98" t="s">
+      <c r="I106" s="91" t="s">
         <v>311</v>
       </c>
-      <c r="J99" s="98" t="s">
+      <c r="J106" s="91" t="s">
         <v>306</v>
       </c>
-      <c r="K99" s="98" t="s">
+      <c r="K106" s="91" t="s">
         <v>304</v>
       </c>
-      <c r="L99" s="99" t="s">
+      <c r="L106" s="92" t="s">
         <v>316</v>
       </c>
-      <c r="M99" s="102" t="s">
+      <c r="M106" s="95" t="s">
         <v>312</v>
       </c>
-      <c r="N99" s="98" t="s">
+      <c r="N106" s="91" t="s">
         <v>313</v>
       </c>
-      <c r="O99" s="98" t="s">
+      <c r="O106" s="91" t="s">
         <v>307</v>
       </c>
-      <c r="P99" s="98" t="s">
+      <c r="P106" s="91" t="s">
         <v>305</v>
       </c>
-      <c r="Q99" s="99" t="s">
+      <c r="Q106" s="92" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100" s="35" t="s">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="B100" s="91">
-        <f>_beff*1000</f>
+      <c r="B107" s="84">
+        <f>_beff_mi_travee*1000</f>
         <v>2000</v>
       </c>
-      <c r="C100" s="54">
+      <c r="C107" s="54">
         <v>120</v>
       </c>
-      <c r="D100" s="54">
+      <c r="D107" s="54">
         <f>_td</f>
         <v>120</v>
       </c>
-      <c r="E100" s="54">
-        <v>0</v>
-      </c>
-      <c r="F100" s="101">
+      <c r="E107" s="55">
+        <f>C107-B102</f>
+        <v>44.729643124466634</v>
+      </c>
+      <c r="F107" s="94">
         <f>0.85*_fck_dalle/1.5</f>
         <v>11.333333333333334</v>
       </c>
-      <c r="G100" s="88">
+      <c r="G107" s="81">
         <v>0</v>
       </c>
-      <c r="H100" s="59">
-        <f>D100</f>
+      <c r="H107" s="59">
+        <f>D107</f>
         <v>120</v>
       </c>
-      <c r="I100" s="55">
-        <f>IF($B$97&gt;=D100,D100,IF($B$97&lt;=E100,E100,$B$97))</f>
-        <v>39.700000000000003</v>
-      </c>
-      <c r="J100" s="55">
-        <f>H100-I100</f>
-        <v>80.3</v>
-      </c>
-      <c r="K100" s="54">
-        <f>J100*B100*F100/1000</f>
-        <v>1820.1333333333334</v>
-      </c>
-      <c r="L100" s="88">
-        <f>K100*((H100+I100)/2-$B$97)/1000</f>
-        <v>73.078353333333311</v>
-      </c>
-      <c r="M100" s="59">
-        <f>I100</f>
-        <v>39.700000000000003</v>
-      </c>
-      <c r="N100" s="54">
-        <f>E100</f>
+      <c r="I107" s="55">
+        <f>IF($B$104&gt;=D107,D107,IF($B$104&lt;=E107,E107,$B$104))</f>
+        <v>44.729643124466634</v>
+      </c>
+      <c r="J107" s="55">
+        <f>H107-I107</f>
+        <v>75.270356875533366</v>
+      </c>
+      <c r="K107" s="54">
+        <f>J107*B107*F107/1000</f>
+        <v>1706.1280891787565</v>
+      </c>
+      <c r="L107" s="81">
+        <f>K107*((H107+I107)/2-$B$104)/1000</f>
+        <v>142.48698293007794</v>
+      </c>
+      <c r="M107" s="59">
+        <f>I107</f>
+        <v>44.729643124466634</v>
+      </c>
+      <c r="N107" s="54">
+        <f>E107</f>
+        <v>44.729643124466634</v>
+      </c>
+      <c r="O107" s="55">
+        <f>M107-N107</f>
         <v>0</v>
       </c>
-      <c r="O100" s="55">
-        <f>M100-N100</f>
-        <v>39.700000000000003</v>
-      </c>
-      <c r="P100" s="54">
-        <f>O100*B100*G100/1000</f>
+      <c r="P107" s="54">
+        <f>O107*B107*G107/1000</f>
         <v>0</v>
       </c>
-      <c r="Q100" s="88">
-        <f>P100*((M100+N100)/2-$B$97)/1000</f>
+      <c r="Q107" s="81">
+        <f>P107*((M107+N107)/2-$B$104)/1000</f>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A101" s="35" t="s">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="B101" s="15">
+      <c r="B108" s="15">
         <v>120</v>
       </c>
-      <c r="C101" s="54">
+      <c r="C108" s="54">
         <v>6</v>
       </c>
-      <c r="D101" s="54">
+      <c r="D108" s="54">
         <v>0</v>
       </c>
-      <c r="E101" s="54">
+      <c r="E108" s="54">
         <f>-_tfs</f>
         <v>-6</v>
       </c>
-      <c r="F101" s="15">
-        <f>_fy</f>
+      <c r="F108" s="15">
+        <f t="shared" ref="F108:G110" si="3">_fy</f>
         <v>420</v>
       </c>
-      <c r="G101" s="88">
-        <f>_fy</f>
+      <c r="G108" s="81">
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
-      <c r="H101" s="59">
-        <f t="shared" ref="H101:H103" si="3">D101</f>
+      <c r="H108" s="59">
+        <f t="shared" ref="H108:H110" si="4">D108</f>
         <v>0</v>
       </c>
-      <c r="I101" s="55">
-        <f t="shared" ref="I101:I103" si="4">IF($B$97&gt;=D101,D101,IF($B$97&lt;=E101,E101,$B$97))</f>
-        <v>0</v>
-      </c>
-      <c r="J101" s="55">
-        <f t="shared" ref="J101:J103" si="5">H101-I101</f>
-        <v>0</v>
-      </c>
-      <c r="K101" s="54">
-        <f>J101*B101*F101/1000</f>
-        <v>0</v>
-      </c>
-      <c r="L101" s="88">
-        <f t="shared" ref="L101:L103" si="6">K101*((H101+I101)/2-$B$97)/1000</f>
-        <v>0</v>
-      </c>
-      <c r="M101" s="59">
-        <f>I101</f>
-        <v>0</v>
-      </c>
-      <c r="N101" s="54">
-        <f>E101</f>
+      <c r="I108" s="55">
+        <f t="shared" ref="I108:I110" si="5">IF($B$104&gt;=D108,D108,IF($B$104&lt;=E108,E108,$B$104))</f>
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="J108" s="55">
+        <f t="shared" ref="J108:J110" si="6">H108-I108</f>
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K108" s="54">
+        <f t="shared" ref="K108:K110" si="7">J108*B108*F108/1000</f>
+        <v>57.96</v>
+      </c>
+      <c r="L108" s="81">
+        <f t="shared" ref="L108:L110" si="8">K108*((H108+I108)/2-$B$104)/1000</f>
+        <v>3.3326999999999996E-2</v>
+      </c>
+      <c r="M108" s="59">
+        <f t="shared" ref="M108:M110" si="9">I108</f>
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="N108" s="54">
+        <f t="shared" ref="N108:N110" si="10">E108</f>
         <v>-6</v>
       </c>
-      <c r="O101" s="55">
-        <f>MIN(MAX(($B$97-E101),0),C101)</f>
-        <v>6</v>
-      </c>
-      <c r="P101" s="54">
-        <f>-O101*B101*F101/1000</f>
-        <v>-302.39999999999998</v>
-      </c>
-      <c r="Q101" s="88">
-        <f t="shared" ref="Q101:Q103" si="7">P101*((M101+N101)/2-$B$97)/1000</f>
-        <v>12.91248</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102" s="35" t="s">
+      <c r="O108" s="55">
+        <f t="shared" ref="O108:O110" si="11">M108-N108</f>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="P108" s="54">
+        <f t="shared" ref="P108:P110" si="12">O108*B108*G108/1000</f>
+        <v>244.44</v>
+      </c>
+      <c r="Q108" s="81">
+        <f t="shared" ref="Q108:Q110" si="13">P108*((M108+N108)/2-$B$104)/1000</f>
+        <v>-0.59276700000000004</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="B102" s="15">
+      <c r="B109" s="15">
         <v>7.1</v>
       </c>
-      <c r="C102" s="54">
+      <c r="C109" s="54">
         <f>_hw</f>
         <v>283.3</v>
       </c>
-      <c r="D102" s="54">
+      <c r="D109" s="54">
         <f>-_tfs</f>
         <v>-6</v>
       </c>
-      <c r="E102" s="54">
+      <c r="E109" s="54">
         <f>-_tfs-_hw</f>
         <v>-289.3</v>
       </c>
-      <c r="F102" s="15">
-        <f>_fy</f>
+      <c r="F109" s="15">
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
-      <c r="G102" s="88">
-        <f>_fy</f>
+      <c r="G109" s="81">
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
-      <c r="H102" s="59">
-        <f t="shared" si="3"/>
-        <v>-6</v>
-      </c>
-      <c r="I102" s="55">
+      <c r="H109" s="59">
         <f t="shared" si="4"/>
         <v>-6</v>
       </c>
-      <c r="J102" s="55">
+      <c r="I109" s="55">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K102" s="54">
-        <f>MIN(MAX((D102-$B$97),0),C102)*B102*F102/1000</f>
-        <v>0</v>
-      </c>
-      <c r="L102" s="88">
+        <v>-6</v>
+      </c>
+      <c r="J109" s="55">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M102" s="59">
-        <f>I102</f>
+      <c r="K109" s="54">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L109" s="81">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M109" s="59">
+        <f t="shared" si="9"/>
         <v>-6</v>
       </c>
-      <c r="N102" s="54">
-        <f>E102</f>
+      <c r="N109" s="54">
+        <f t="shared" si="10"/>
         <v>-289.3</v>
       </c>
-      <c r="O102" s="55">
-        <f>MIN(MAX(($B$97-E102),0),C102)</f>
+      <c r="O109" s="55">
+        <f t="shared" si="11"/>
         <v>283.3</v>
       </c>
-      <c r="P102" s="54">
-        <f>-MIN(MAX(($B$97-E102),0),C102)*B102*F102/1000</f>
-        <v>-844.80060000000003</v>
-      </c>
-      <c r="Q102" s="88">
-        <f t="shared" si="7"/>
-        <v>158.27339241000004</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A103" s="35" t="s">
+      <c r="P109" s="54">
+        <f t="shared" si="12"/>
+        <v>844.80060000000003</v>
+      </c>
+      <c r="Q109" s="81">
+        <f t="shared" si="13"/>
+        <v>-123.76328790000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" s="35" t="s">
         <v>291</v>
       </c>
-      <c r="B103" s="15">
+      <c r="B110" s="15">
         <v>150</v>
       </c>
-      <c r="C103" s="54">
+      <c r="C110" s="54">
         <v>10.7</v>
       </c>
-      <c r="D103" s="54">
+      <c r="D110" s="54">
         <f>-_tfs-_hw</f>
         <v>-289.3</v>
       </c>
-      <c r="E103" s="54">
+      <c r="E110" s="54">
         <f>-_h</f>
         <v>-300</v>
       </c>
-      <c r="F103" s="15">
-        <f>_fy</f>
+      <c r="F110" s="15">
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
-      <c r="G103" s="88">
-        <f>_fy</f>
+      <c r="G110" s="81">
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
-      <c r="H103" s="61">
-        <f t="shared" si="3"/>
-        <v>-289.3</v>
-      </c>
-      <c r="I103" s="58">
+      <c r="H110" s="61">
         <f t="shared" si="4"/>
         <v>-289.3</v>
       </c>
-      <c r="J103" s="58">
+      <c r="I110" s="58">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K103" s="89">
-        <f>MIN(MAX((D103-$B$97),0),C103)*B103*F103/1000</f>
-        <v>0</v>
-      </c>
-      <c r="L103" s="30">
+        <v>-289.3</v>
+      </c>
+      <c r="J110" s="55">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="M103" s="61">
-        <f>I103</f>
+      <c r="K110" s="54">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L110" s="81">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="59">
+        <f t="shared" si="9"/>
         <v>-289.3</v>
       </c>
-      <c r="N103" s="89">
-        <f>E103</f>
+      <c r="N110" s="54">
+        <f t="shared" si="10"/>
         <v>-300</v>
       </c>
-      <c r="O103" s="58">
-        <f>MIN(MAX(($B$97-E103),0),C103)</f>
+      <c r="O110" s="55">
+        <f t="shared" si="11"/>
+        <v>10.699999999999989</v>
+      </c>
+      <c r="P110" s="54">
+        <f t="shared" si="12"/>
+        <v>674.09999999999923</v>
+      </c>
+      <c r="Q110" s="81">
+        <f t="shared" si="13"/>
+        <v>-197.84834999999978</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" s="83" t="s">
+        <v>296</v>
+      </c>
+      <c r="B111" s="21"/>
+      <c r="C111" s="86"/>
+      <c r="D111" s="63"/>
+      <c r="E111" s="63"/>
+      <c r="F111" s="21"/>
+      <c r="G111" s="22"/>
+      <c r="H111" s="16"/>
+      <c r="I111" s="82"/>
+      <c r="J111" s="82"/>
+      <c r="K111" s="96">
+        <f>SUM(K107:K110)</f>
+        <v>1764.0880891787565</v>
+      </c>
+      <c r="L111" s="97">
+        <f>SUM(L107:L110)</f>
+        <v>142.52030993007796</v>
+      </c>
+      <c r="M111" s="102"/>
+      <c r="N111" s="96"/>
+      <c r="O111" s="96"/>
+      <c r="P111" s="96">
+        <f>SUM(P107:P110)</f>
+        <v>1763.3405999999993</v>
+      </c>
+      <c r="Q111" s="97">
+        <f>SUM(Q107:Q110)</f>
+        <v>-322.20440489999976</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P112" s="54"/>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D113" s="98" t="s">
+        <v>318</v>
+      </c>
+      <c r="E113" s="99">
+        <f>K111-P111</f>
+        <v>0.7474891787571778</v>
+      </c>
+      <c r="G113" t="s">
+        <v>320</v>
+      </c>
+      <c r="H113" s="23">
+        <f>(_td-B104)/(_h+_td)*100</f>
+        <v>28.845238095238095</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D114" s="100" t="s">
+        <v>319</v>
+      </c>
+      <c r="E114" s="101">
+        <f>ABS(L111)+ABS(Q111)</f>
+        <v>464.72471483007769</v>
+      </c>
+      <c r="G114" t="s">
+        <v>321</v>
+      </c>
+      <c r="H114" s="25">
+        <f>IF(H113&lt;=15,1,IF(H113&gt;=40,0.85,1+(H113-15)/(40-15)*(0.85-1)))</f>
+        <v>0.91692857142857143</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="116" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="113" t="s">
+        <v>338</v>
+      </c>
+      <c r="B116" s="114"/>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="B117" s="121">
+        <f>_L/4</f>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B118" s="122">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="B119" s="121">
+        <f>IF(B118&lt;=B117,_beff_appuis+(_beff_mi_travee-_beff_appuis)/B117*B118,_beff_mi_travee)</f>
+        <v>1.6800000000000002</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120" s="123" t="s">
+        <v>341</v>
+      </c>
+      <c r="B120" s="14">
+        <f>_PRd*B118*1000/_sx</f>
+        <v>170.61280891787561</v>
+      </c>
+      <c r="C120" s="24"/>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121" s="123" t="s">
+        <v>342</v>
+      </c>
+      <c r="B121" s="14">
+        <f>B119*1000*(_td-_tj)*0.85*_fck_dalle/1.5/1000</f>
+        <v>2094.4</v>
+      </c>
+      <c r="C121" s="24"/>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122" s="123" t="s">
+        <v>343</v>
+      </c>
+      <c r="B122" s="14">
+        <f>MIN(B120:B121)*1000/(0.85*_fck_dalle/1.5*B119*1000)</f>
+        <v>8.9607567708968254</v>
+      </c>
+      <c r="C122" s="24"/>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123" s="123"/>
+      <c r="B123" s="14"/>
+      <c r="C123" s="24"/>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>303</v>
+      </c>
+      <c r="B124" s="32">
+        <v>-181.5</v>
+      </c>
+      <c r="C124" s="24" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126" s="83" t="s">
+        <v>287</v>
+      </c>
+      <c r="B126" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C126" s="63" t="s">
+        <v>292</v>
+      </c>
+      <c r="D126" s="91" t="s">
+        <v>308</v>
+      </c>
+      <c r="E126" s="91" t="s">
+        <v>309</v>
+      </c>
+      <c r="F126" s="95" t="s">
+        <v>314</v>
+      </c>
+      <c r="G126" s="92" t="s">
+        <v>315</v>
+      </c>
+      <c r="H126" s="95" t="s">
+        <v>310</v>
+      </c>
+      <c r="I126" s="91" t="s">
+        <v>311</v>
+      </c>
+      <c r="J126" s="91" t="s">
+        <v>306</v>
+      </c>
+      <c r="K126" s="91" t="s">
+        <v>304</v>
+      </c>
+      <c r="L126" s="92" t="s">
+        <v>316</v>
+      </c>
+      <c r="M126" s="95" t="s">
+        <v>312</v>
+      </c>
+      <c r="N126" s="91" t="s">
+        <v>313</v>
+      </c>
+      <c r="O126" s="91" t="s">
+        <v>307</v>
+      </c>
+      <c r="P126" s="91" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q126" s="92" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A127" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="B127" s="84">
+        <f>B119*1000</f>
+        <v>1680.0000000000002</v>
+      </c>
+      <c r="C127" s="54">
+        <v>120</v>
+      </c>
+      <c r="D127" s="54">
+        <f>_td</f>
+        <v>120</v>
+      </c>
+      <c r="E127" s="55">
+        <f>C127-B122</f>
+        <v>111.03924322910318</v>
+      </c>
+      <c r="F127" s="94">
+        <f>0.85*_fck_dalle/1.5</f>
+        <v>11.333333333333334</v>
+      </c>
+      <c r="G127" s="81">
+        <v>0</v>
+      </c>
+      <c r="H127" s="59">
+        <f>D127</f>
+        <v>120</v>
+      </c>
+      <c r="I127" s="55">
+        <f>IF($B$124&gt;=D127,D127,IF($B$124&lt;=E127,E127,$B$124))</f>
+        <v>111.03924322910318</v>
+      </c>
+      <c r="J127" s="55">
+        <f>H127-I127</f>
+        <v>8.9607567708968219</v>
+      </c>
+      <c r="K127" s="54">
+        <f>J127*B127*F127/1000</f>
+        <v>170.61280891787553</v>
+      </c>
+      <c r="L127" s="81">
+        <f>K127*((H127+I127)/2-$B$124)/1000</f>
+        <v>50.675351947383191</v>
+      </c>
+      <c r="M127" s="59">
+        <f>I127</f>
+        <v>111.03924322910318</v>
+      </c>
+      <c r="N127" s="55">
+        <f>E127</f>
+        <v>111.03924322910318</v>
+      </c>
+      <c r="O127" s="55">
+        <f>M127-N127</f>
+        <v>0</v>
+      </c>
+      <c r="P127" s="54">
+        <f>O127*B127*G127/1000</f>
+        <v>0</v>
+      </c>
+      <c r="Q127" s="81">
+        <f>P127*((M127+N127)/2-$B$124)/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A128" s="35" t="s">
+        <v>289</v>
+      </c>
+      <c r="B128" s="15">
+        <v>120</v>
+      </c>
+      <c r="C128" s="54">
+        <v>6</v>
+      </c>
+      <c r="D128" s="54">
+        <v>0</v>
+      </c>
+      <c r="E128" s="54">
+        <f>-_tfs</f>
+        <v>-6</v>
+      </c>
+      <c r="F128" s="15">
+        <f t="shared" ref="F128:G130" si="14">_fy</f>
+        <v>420</v>
+      </c>
+      <c r="G128" s="81">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+      <c r="H128" s="59">
+        <f t="shared" ref="H128:H130" si="15">D128</f>
+        <v>0</v>
+      </c>
+      <c r="I128" s="55">
+        <f>IF($B$124&gt;=D128,D128,IF($B$124&lt;=E128,E128,$B$124))</f>
+        <v>-6</v>
+      </c>
+      <c r="J128" s="55">
+        <f t="shared" ref="J128:J130" si="16">H128-I128</f>
+        <v>6</v>
+      </c>
+      <c r="K128" s="54">
+        <f t="shared" ref="K128:K130" si="17">J128*B128*F128/1000</f>
+        <v>302.39999999999998</v>
+      </c>
+      <c r="L128" s="81">
+        <f>K128*((H128+I128)/2-$B$124)/1000</f>
+        <v>53.978399999999993</v>
+      </c>
+      <c r="M128" s="59">
+        <f t="shared" ref="M128:M130" si="18">I128</f>
+        <v>-6</v>
+      </c>
+      <c r="N128" s="54">
+        <f t="shared" ref="N128:N130" si="19">E128</f>
+        <v>-6</v>
+      </c>
+      <c r="O128" s="55">
+        <f t="shared" ref="O128:O130" si="20">M128-N128</f>
+        <v>0</v>
+      </c>
+      <c r="P128" s="54">
+        <f t="shared" ref="P128:P130" si="21">O128*B128*G128/1000</f>
+        <v>0</v>
+      </c>
+      <c r="Q128" s="81">
+        <f>P128*((M128+N128)/2-$B$124)/1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A129" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="B129" s="15">
+        <v>7.1</v>
+      </c>
+      <c r="C129" s="54">
+        <f>_hw</f>
+        <v>283.3</v>
+      </c>
+      <c r="D129" s="54">
+        <f>-_tfs</f>
+        <v>-6</v>
+      </c>
+      <c r="E129" s="54">
+        <f>-_tfs-_hw</f>
+        <v>-289.3</v>
+      </c>
+      <c r="F129" s="15">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+      <c r="G129" s="81">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+      <c r="H129" s="59">
+        <f t="shared" si="15"/>
+        <v>-6</v>
+      </c>
+      <c r="I129" s="55">
+        <f>IF($B$124&gt;=D129,D129,IF($B$124&lt;=E129,E129,$B$124))</f>
+        <v>-181.5</v>
+      </c>
+      <c r="J129" s="55">
+        <f t="shared" si="16"/>
+        <v>175.5</v>
+      </c>
+      <c r="K129" s="54">
+        <f t="shared" si="17"/>
+        <v>523.34100000000001</v>
+      </c>
+      <c r="L129" s="81">
+        <f>K129*((H129+I129)/2-$B$124)/1000</f>
+        <v>45.923172749999999</v>
+      </c>
+      <c r="M129" s="59">
+        <f t="shared" si="18"/>
+        <v>-181.5</v>
+      </c>
+      <c r="N129" s="54">
+        <f t="shared" si="19"/>
+        <v>-289.3</v>
+      </c>
+      <c r="O129" s="55">
+        <f t="shared" si="20"/>
+        <v>107.80000000000001</v>
+      </c>
+      <c r="P129" s="54">
+        <f t="shared" si="21"/>
+        <v>321.45959999999997</v>
+      </c>
+      <c r="Q129" s="81">
+        <f>P129*((M129+N129)/2-$B$124)/1000</f>
+        <v>-17.326672439999999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="B130" s="15">
+        <v>150</v>
+      </c>
+      <c r="C130" s="54">
         <v>10.7</v>
       </c>
-      <c r="P103" s="89">
-        <f>-MIN(MAX(($B$97-E103),0),C103)*B103*F103/1000</f>
-        <v>-674.1</v>
-      </c>
-      <c r="Q103" s="30">
-        <f t="shared" si="7"/>
-        <v>225.385335</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A104" s="90" t="s">
+      <c r="D130" s="54">
+        <f>-_tfs-_hw</f>
+        <v>-289.3</v>
+      </c>
+      <c r="E130" s="54">
+        <f>-_h</f>
+        <v>-300</v>
+      </c>
+      <c r="F130" s="15">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+      <c r="G130" s="81">
+        <f t="shared" si="14"/>
+        <v>420</v>
+      </c>
+      <c r="H130" s="59">
+        <f t="shared" si="15"/>
+        <v>-289.3</v>
+      </c>
+      <c r="I130" s="55">
+        <f>IF($B$124&gt;=D130,D130,IF($B$124&lt;=E130,E130,$B$124))</f>
+        <v>-289.3</v>
+      </c>
+      <c r="J130" s="55">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K130" s="54">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="L130" s="81">
+        <f>K130*((H130+I130)/2-$B$124)/1000</f>
+        <v>0</v>
+      </c>
+      <c r="M130" s="59">
+        <f t="shared" si="18"/>
+        <v>-289.3</v>
+      </c>
+      <c r="N130" s="54">
+        <f t="shared" si="19"/>
+        <v>-300</v>
+      </c>
+      <c r="O130" s="55">
+        <f t="shared" si="20"/>
+        <v>10.699999999999989</v>
+      </c>
+      <c r="P130" s="54">
+        <f t="shared" si="21"/>
+        <v>674.09999999999923</v>
+      </c>
+      <c r="Q130" s="81">
+        <f>P130*((M130+N130)/2-$B$124)/1000</f>
+        <v>-76.274414999999891</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A131" s="83" t="s">
         <v>296</v>
       </c>
-      <c r="B104" s="21"/>
-      <c r="C104" s="93"/>
-      <c r="D104" s="63"/>
-      <c r="E104" s="63"/>
-      <c r="F104" s="21"/>
-      <c r="G104" s="22"/>
-      <c r="H104" s="16"/>
-      <c r="I104" s="89"/>
-      <c r="J104" s="89"/>
-      <c r="K104" s="103">
-        <f>SUM(K100:K103)</f>
-        <v>1820.1333333333334</v>
-      </c>
-      <c r="L104" s="104">
-        <f>SUM(L100:L103)</f>
-        <v>73.078353333333311</v>
-      </c>
-      <c r="M104" s="109"/>
-      <c r="N104" s="103"/>
-      <c r="O104" s="103"/>
-      <c r="P104" s="103">
-        <f>SUM(P100:P103)</f>
-        <v>-1821.3006</v>
-      </c>
-      <c r="Q104" s="104">
-        <f>SUM(Q100:Q103)</f>
-        <v>396.57120741000006</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P105" s="54"/>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="D106" s="105" t="s">
+      <c r="B131" s="21"/>
+      <c r="C131" s="86"/>
+      <c r="D131" s="63"/>
+      <c r="E131" s="63"/>
+      <c r="F131" s="21"/>
+      <c r="G131" s="22"/>
+      <c r="H131" s="16"/>
+      <c r="I131" s="82"/>
+      <c r="J131" s="82"/>
+      <c r="K131" s="96">
+        <f>SUM(K127:K130)</f>
+        <v>996.35380891787554</v>
+      </c>
+      <c r="L131" s="97">
+        <f>SUM(L127:L130)</f>
+        <v>150.57692469738319</v>
+      </c>
+      <c r="M131" s="102"/>
+      <c r="N131" s="96"/>
+      <c r="O131" s="96"/>
+      <c r="P131" s="96">
+        <f>SUM(P127:P130)</f>
+        <v>995.55959999999914</v>
+      </c>
+      <c r="Q131" s="97">
+        <f>SUM(Q127:Q130)</f>
+        <v>-93.601087439999887</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P132" s="54"/>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="D133" s="98" t="s">
         <v>318</v>
       </c>
-      <c r="E106" s="106">
-        <f>K104+P104</f>
-        <v>-1.1672666666665918</v>
-      </c>
-      <c r="G106" t="s">
+      <c r="E133" s="99">
+        <f>K131-P131</f>
+        <v>0.79420891787640358</v>
+      </c>
+      <c r="G133" t="s">
         <v>320</v>
       </c>
-      <c r="H106" s="23">
-        <f>(_td-B97)/(_h+_td)*100</f>
-        <v>19.11904761904762</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D107" s="107" t="s">
+      <c r="H133" s="23">
+        <f>(_td-B124)/(_h+_td)*100</f>
+        <v>71.785714285714292</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D134" s="100" t="s">
         <v>319</v>
       </c>
-      <c r="E107" s="108">
-        <f>L104+Q104</f>
-        <v>469.64956074333338</v>
-      </c>
-      <c r="G107" t="s">
+      <c r="E134" s="101">
+        <f>L131+Q131</f>
+        <v>56.975837257383304</v>
+      </c>
+      <c r="G134" t="s">
         <v>321</v>
       </c>
-      <c r="H107" s="25">
-        <f>IF(H106&lt;=15,1,IF(H106&gt;=40,0.85,1+(H106-15)/(40-15)*(0.85-1)))</f>
-        <v>0.97528571428571431</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="110" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="77" t="s">
+      <c r="H134" s="25">
+        <f>IF(H133&lt;=15,1,IF(H133&gt;=40,0.85,1+(H133-15)/(40-15)*(0.85-1)))</f>
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="136" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="113" t="s">
         <v>133</v>
       </c>
-      <c r="B110" s="78"/>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
+      <c r="B136" s="114"/>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>130</v>
       </c>
-      <c r="B111" s="27">
+      <c r="B137" s="27">
         <f>H11+E20</f>
         <v>6.2199419696550002</v>
       </c>
-      <c r="C111" s="26">
-        <f>B111*1.35</f>
+      <c r="C137" s="25">
+        <f>B137*1.35</f>
         <v>8.3969216590342501</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>322</v>
       </c>
-      <c r="B112" s="27">
+      <c r="B138" s="27">
         <v>2</v>
       </c>
-      <c r="C112" s="26"/>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="28" t="s">
+      <c r="C138" s="26"/>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A139" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="B113" s="111">
-        <f>B111*_L/2</f>
+      <c r="B139" s="104">
+        <f>B137*_L/2</f>
         <v>31.099709848275001</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="16" t="s">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A140" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B114" s="112">
-        <f>B111*_L^2/8</f>
+      <c r="B140" s="105">
+        <f>B137*_L^2/8</f>
         <v>77.749274620687501</v>
       </c>
-      <c r="D114" s="24"/>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="28" t="s">
+      <c r="D140" s="24"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A141" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="B115" s="111">
-        <f>B112*(_b_Gauche+_b_Droite)*_L/2</f>
+      <c r="B141" s="104">
+        <f>B138*(_b_Gauche+_b_Droite)*_L/2</f>
         <v>20</v>
       </c>
-      <c r="D115" s="24"/>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="16" t="s">
+      <c r="D141" s="24"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A142" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="B116" s="112">
-        <f>B112*(_b_Gauche+_b_Droite)*_L^2/8</f>
+      <c r="B142" s="105">
+        <f>B138*(_b_Gauche+_b_Droite)*_L^2/8</f>
         <v>50</v>
       </c>
-      <c r="D116" s="24"/>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="28" t="s">
+      <c r="D142" s="24"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A143" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="B117" s="53">
+      <c r="B143" s="53">
         <v>0.5</v>
       </c>
-      <c r="D117" s="24"/>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="16" t="s">
+      <c r="D143" s="24"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A144" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="B118" s="110">
-        <f>B117*_L/2</f>
+      <c r="B144" s="103">
+        <f>B143*_L/2</f>
         <v>2.5</v>
       </c>
-      <c r="D118" s="24"/>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="28" t="s">
+      <c r="D144" s="24"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="B119" s="53">
+      <c r="B145" s="53">
         <f>4*(_L-4)/_L</f>
         <v>2.4</v>
       </c>
-      <c r="D119" s="24"/>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="16" t="s">
+      <c r="D145" s="24"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="B120" s="110">
-        <f>B119*_L/2</f>
-        <v>12</v>
-      </c>
-      <c r="D120" s="24"/>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="100" t="s">
+      <c r="B146" s="103">
+        <f>B145*4</f>
+        <v>9.6</v>
+      </c>
+      <c r="D146" s="24"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="93" t="s">
         <v>326</v>
       </c>
-      <c r="B121" s="117">
+      <c r="B147" s="110">
         <f>325*10^(-6)</f>
         <v>3.2499999999999999E-4</v>
       </c>
-      <c r="D121" s="24"/>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="116" t="s">
+      <c r="D147" s="24"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="109" t="s">
         <v>327</v>
       </c>
-      <c r="B122" s="118">
+      <c r="B148" s="111">
         <v>210000</v>
       </c>
-      <c r="D122" s="24"/>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="116" t="s">
+      <c r="D148" s="24"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="109" t="s">
         <v>226</v>
       </c>
-      <c r="B123" s="88">
+      <c r="B149" s="81">
         <f>_Ac_brute</f>
         <v>240000</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="116" t="s">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="109" t="s">
         <v>328</v>
       </c>
-      <c r="B124" s="57">
+      <c r="B150" s="57">
         <v>29.142741876247484</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="116" t="s">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="109" t="s">
         <v>330</v>
       </c>
-      <c r="B125" s="57">
+      <c r="B151" s="57">
         <v>-22.108000000000001</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="116" t="s">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="109" t="s">
         <v>329</v>
       </c>
-      <c r="B126" s="19">
-        <f>B121*B122*B123/(1000*B124)</f>
+      <c r="B152" s="19">
+        <f>B147*B148*B149/(1000*B150)</f>
         <v>562.06104660832773</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="119" t="s">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="112" t="s">
         <v>331</v>
       </c>
-      <c r="B127" s="20">
-        <f>B126*((_td-_tj)/2+_tj-B125)/1000</f>
+      <c r="B153" s="20">
+        <f>B152*((_td-_tj)/2+_tj-B151)/1000</f>
         <v>48.960013647958213</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="100" t="s">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A154" s="93" t="s">
         <v>333</v>
       </c>
-      <c r="B128" s="74">
-        <f>1.35*B113+1.35*B115+1.5*B117</f>
+      <c r="B154" s="74">
+        <f>1.35*B139+1.35*B141+1.5*B143</f>
         <v>69.734608295171256</v>
       </c>
-      <c r="C128" s="24" t="s">
+      <c r="C154" s="24" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="119" t="s">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A155" s="112" t="s">
         <v>332</v>
       </c>
-      <c r="B129" s="20">
-        <f>1.35*B114+1.35*B116+1.5*B118</f>
-        <v>176.21152073792814</v>
-      </c>
-      <c r="C129" s="24"/>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="100" t="s">
+      <c r="B155" s="20">
+        <f>1.35*B140+1.35*B142+1.5*B144+1.35*B153</f>
+        <v>242.30753916267173</v>
+      </c>
+      <c r="C155" s="24"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A156" s="93" t="s">
         <v>334</v>
       </c>
-      <c r="B130" s="74">
-        <f>1.35*B113+1.5*B119</f>
+      <c r="B156" s="74">
+        <f>1.35*B139+1.5*B145</f>
         <v>45.584608295171257</v>
       </c>
-      <c r="C130" s="24" t="s">
+      <c r="C156" s="24" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="119" t="s">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A157" s="112" t="s">
         <v>335</v>
       </c>
-      <c r="B131" s="20">
-        <f>1.35*B114+1.5*B120</f>
-        <v>122.96152073792814</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="77" t="s">
+      <c r="B157" s="20">
+        <v>117.3</v>
+      </c>
+      <c r="C157" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="159" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="113" t="s">
         <v>134</v>
       </c>
-      <c r="B133" s="78"/>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>123</v>
-      </c>
-      <c r="B134" s="23">
-        <f>H107*E107</f>
-        <v>458.04250731353386</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
+      <c r="B159" s="114"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A160" s="121"/>
+      <c r="B160" s="121"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="121"/>
+      <c r="B161" s="77" t="s">
+        <v>344</v>
+      </c>
+      <c r="C161" s="63" t="s">
+        <v>345</v>
+      </c>
+      <c r="D161" s="63" t="s">
+        <v>346</v>
+      </c>
+      <c r="E161" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="F161" s="83" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="132" t="s">
+        <v>328</v>
+      </c>
+      <c r="B162" s="139"/>
+      <c r="C162" s="66">
+        <v>30.8</v>
+      </c>
+      <c r="D162" s="66">
+        <v>7.01</v>
+      </c>
+      <c r="E162" s="29">
+        <v>29.1</v>
+      </c>
+      <c r="F162" s="127"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="28" t="s">
+        <v>365</v>
+      </c>
+      <c r="B163" s="155">
+        <v>5921</v>
+      </c>
+      <c r="C163" s="154">
+        <v>22581</v>
+      </c>
+      <c r="D163" s="154">
+        <v>31404</v>
+      </c>
+      <c r="E163" s="156">
+        <v>22952</v>
+      </c>
+      <c r="F163" s="127"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="134" t="s">
+        <v>366</v>
+      </c>
+      <c r="B164" s="152">
+        <v>-178</v>
+      </c>
+      <c r="C164" s="82">
+        <v>-26.8</v>
+      </c>
+      <c r="D164" s="82">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="E164" s="30">
+        <v>-23.7</v>
+      </c>
+      <c r="F164" s="135"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="28" t="s">
+        <v>367</v>
+      </c>
+      <c r="B165" s="155">
+        <v>5921</v>
+      </c>
+      <c r="C165" s="154">
+        <v>21530.096266744444</v>
+      </c>
+      <c r="D165" s="154">
+        <v>30234.112325995633</v>
+      </c>
+      <c r="E165" s="156">
+        <v>21539.889165989531</v>
+      </c>
+      <c r="F165" s="127"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="134" t="s">
+        <v>368</v>
+      </c>
+      <c r="B166" s="152">
+        <v>-178</v>
+      </c>
+      <c r="C166" s="96">
+        <v>-34.487492252446586</v>
+      </c>
+      <c r="D166" s="153">
+        <v>30.897637600365364</v>
+      </c>
+      <c r="E166" s="20">
+        <v>-34.40387189041919</v>
+      </c>
+      <c r="F166" s="135"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="134" t="s">
+        <v>351</v>
+      </c>
+      <c r="B167" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="C167" s="82" t="s">
+        <v>353</v>
+      </c>
+      <c r="D167" s="82" t="s">
+        <v>353</v>
+      </c>
+      <c r="E167" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="F167" s="135"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="150" t="s">
+        <v>363</v>
+      </c>
+      <c r="B168" s="151">
+        <f>B139</f>
+        <v>31.099709848275001</v>
+      </c>
+      <c r="C168" s="87">
+        <f>B141</f>
+        <v>20</v>
+      </c>
+      <c r="D168" s="87">
+        <f>B143</f>
+        <v>0.5</v>
+      </c>
+      <c r="E168" s="22">
+        <v>0</v>
+      </c>
+      <c r="F168" s="83"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="133" t="s">
+        <v>354</v>
+      </c>
+      <c r="B169" s="140">
+        <f>IF(B167="N",0,$B$140*10^6/(B$163*10^4)*(_td-B$164)/B162)</f>
+        <v>0</v>
+      </c>
+      <c r="C169" s="125">
+        <f>IF(C167="N",0,$B$142*10^6/(C$163*10^4)*(_td-C$164)/C162)</f>
+        <v>1.0553637496642678</v>
+      </c>
+      <c r="D169" s="125">
+        <f>IF(D167="N",0,$B$144*10^6/(D$163*10^4)*(_td-D$164)/D162)</f>
+        <v>9.2213191083356905E-2</v>
+      </c>
+      <c r="E169" s="141">
+        <f>IF(E167="N",0,$B$153*10^6/(E$163*10^4)*(_td-E$164)/E162)</f>
+        <v>1.0533792862815441</v>
+      </c>
+      <c r="F169" s="128">
+        <f>1.35*(B169+C169)+1.5*D169+1.35*E169</f>
+        <v>2.9851228851518821</v>
+      </c>
+      <c r="G169">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="133" t="s">
+        <v>355</v>
+      </c>
+      <c r="B170" s="140">
+        <f>$B$140*10^6/(B$163*10^4)*(0-B$164)</f>
+        <v>233.73367475903353</v>
+      </c>
+      <c r="C170" s="125">
+        <f>$B$142*10^6/(C$163*10^4)*(0-C$164)</f>
+        <v>5.9341924626898717</v>
+      </c>
+      <c r="D170" s="124">
+        <f>$B$144*10^6/(D$163*10^4)*(0-D$164)</f>
+        <v>-0.30887784995541961</v>
+      </c>
+      <c r="E170" s="142">
+        <f>$B$153*10^6/(E$163*10^4)*(0-E$164)</f>
+        <v>5.0555608376464338</v>
+      </c>
+      <c r="F170" s="128">
+        <f t="shared" ref="F170:F171" si="22">1.35*(B170+C170)+1.5*D170+1.35*E170</f>
+        <v>329.91331110521622</v>
+      </c>
+      <c r="G170">
+        <v>329.4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="134" t="s">
+        <v>356</v>
+      </c>
+      <c r="B171" s="143">
+        <f>$B$140*10^6/(B$163*10^4)*(-_h-B$164)</f>
+        <v>-160.19948494720276</v>
+      </c>
+      <c r="C171" s="137">
+        <f>$B$142*10^6/(C$163*10^4)*(-_h-C$164)</f>
+        <v>-60.493335104734065</v>
+      </c>
+      <c r="D171" s="136">
+        <f>$B$144*10^6/(D$163*10^4)*(-_h-D$164)</f>
+        <v>-2.6971086485797984</v>
+      </c>
+      <c r="E171" s="144">
+        <f>$B$153*10^6/(E$163*10^4)*(-_h-E$164)</f>
+        <v>-58.938880145219827</v>
+      </c>
+      <c r="F171" s="138">
+        <f t="shared" si="22"/>
+        <v>-381.54845823903122</v>
+      </c>
+      <c r="G171">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="133" t="s">
+        <v>348</v>
+      </c>
+      <c r="B172" s="145">
+        <f>B169/(0.85*_fck_dalle/1.5)</f>
+        <v>0</v>
+      </c>
+      <c r="C172" s="8">
+        <f>C169/(0.85*_fck_dalle/1.5)</f>
+        <v>9.3120330852729513E-2</v>
+      </c>
+      <c r="D172" s="8">
+        <f>D169/(0.85*_fck_dalle/1.5)</f>
+        <v>8.136458036766785E-3</v>
+      </c>
+      <c r="E172" s="146">
+        <f>E169/(0.85*_fck_dalle/1.5)</f>
+        <v>9.2945231142489176E-2</v>
+      </c>
+      <c r="F172" s="129">
+        <f>F169/(0.85*_fck_dalle/1.5)</f>
+        <v>0.26339319574869546</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="133" t="s">
+        <v>349</v>
+      </c>
+      <c r="B173" s="147">
+        <f>B170/(_fy)</f>
+        <v>0.55650874942627027</v>
+      </c>
+      <c r="C173" s="125">
+        <f>C170/(_fy)</f>
+        <v>1.4129029673071123E-2</v>
+      </c>
+      <c r="D173" s="125">
+        <f>D170/(_fy)</f>
+        <v>-7.3542345227480856E-4</v>
+      </c>
+      <c r="E173" s="141">
+        <f>E170/(_fy)</f>
+        <v>1.203704961344389E-2</v>
+      </c>
+      <c r="F173" s="130">
+        <f>F170/(_fy)</f>
+        <v>0.78550788358384815</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="134" t="s">
+        <v>350</v>
+      </c>
+      <c r="B174" s="148">
+        <f>ABS(B171/(_fy))</f>
+        <v>0.38142734511238752</v>
+      </c>
+      <c r="C174" s="126">
+        <f>ABS(C171/(_fy))</f>
+        <v>0.14403175024936682</v>
+      </c>
+      <c r="D174" s="126">
+        <f>ABS(D171/(_fy))</f>
+        <v>6.4216872585233292E-3</v>
+      </c>
+      <c r="E174" s="149">
+        <f>ABS(E171/(_fy))</f>
+        <v>0.14033066701242816</v>
+      </c>
+      <c r="F174" s="131">
+        <f>ABS(F171/(_fy))</f>
+        <v>0.90844871009293149</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="B175" s="124">
+        <f>ABS(IF(B167="N",0,_beff_appuis*1000*(_td-_tj)/B162*(B166-((_td-_tj)/2+_tj))))</f>
+        <v>0</v>
+      </c>
+      <c r="C175" s="124">
+        <f>ABS(IF(C167="N",0,_beff_appuis*1000*(_td-_tj)/C162*(C166-((_td-_tj)/2+_tj))))</f>
+        <v>568499.95572826616</v>
+      </c>
+      <c r="D175" s="124">
+        <f>ABS(IF(D167="N",0,_beff_appuis*1000*(_td-_tj)/D162*(D166-((_td-_tj)/2+_tj))))</f>
+        <v>856207.67223048443</v>
+      </c>
+      <c r="E175" s="124">
+        <f>ABS(IF(E167="N",0,_beff_appuis*1000*(_td-_tj)/E162*(E166-((_td-_tj)/2+_tj))))</f>
+        <v>601205.54820322257</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B176" s="157">
+        <f>B168*1000*B175/B165/1000</f>
+        <v>0</v>
+      </c>
+      <c r="C176" s="157">
+        <f t="shared" ref="C176:E176" si="23">C168*1000*C175/C165/1000</f>
+        <v>528.09792272631466</v>
+      </c>
+      <c r="D176" s="157">
+        <f t="shared" si="23"/>
+        <v>14.15962974203657</v>
+      </c>
+      <c r="E176" s="157">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="F176">
+        <f>1.35*B176+1.35*C176+1.5*D176+1.35*E176</f>
+        <v>734.17164029357969</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="7"/>
+      <c r="B177" s="121"/>
+      <c r="C177" s="124"/>
+      <c r="D177" s="124"/>
+      <c r="E177" s="121"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="7"/>
+      <c r="B178" s="121"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
         <v>245</v>
       </c>
-      <c r="B135" s="23">
+      <c r="B179" s="23">
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>487.74585382155738</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B136" s="23"/>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="123" t="s">
+        <v>123</v>
+      </c>
+      <c r="B180" s="23">
+        <v>464.72471483007769</v>
+      </c>
+      <c r="C180">
+        <f>B180*B181</f>
+        <v>464.72471483007769</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="123" t="s">
+        <v>359</v>
+      </c>
+      <c r="B181" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="123" t="s">
+        <v>364</v>
+      </c>
+      <c r="B182" s="25">
+        <f>_PRd/(_sx/1000)</f>
+        <v>341.22561783575122</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B183" s="23"/>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
         <v>141</v>
       </c>
-      <c r="B137">
-        <f>B129/_Mpl_Rd</f>
-        <v>0.38470560684733546</v>
+      <c r="B184" s="26">
+        <f>MAX(F172:F174)</f>
+        <v>0.90844871009293149</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>142</v>
+      </c>
+      <c r="B185" s="26">
+        <f>B154/B179</f>
+        <v>0.14297324672017361</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>358</v>
+      </c>
+      <c r="B186" s="26">
+        <f>B155/(B181*B180)</f>
+        <v>0.52140015676004936</v>
+      </c>
+      <c r="C186" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="A110:B110"/>
-    <mergeCell ref="A133:B133"/>
+  <mergeCells count="17">
+    <mergeCell ref="A159:B159"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
@@ -8745,6 +9884,12 @@
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A136:B136"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -262,7 +262,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="371">
   <si>
     <t>h (mm)</t>
   </si>
@@ -1372,6 +1372,9 @@
   </si>
   <si>
     <t>Propriétés plastiques à mi travée (eta)</t>
+  </si>
+  <si>
+    <t>Critere connex</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1390,7 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="0.000000"/>
-    <numFmt numFmtId="174" formatCode="_-* #,##0.0\ _€_-;\-* #,##0.0\ _€_-;_-* &quot;-&quot;?\ _€_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_-* #,##0.0\ _€_-;\-* #,##0.0\ _€_-;_-* &quot;-&quot;?\ _€_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1925,30 +1928,6 @@
     <xf numFmtId="170" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2041,7 +2020,31 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2337,20 +2340,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="150" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="114"/>
+      <c r="B1" s="151"/>
       <c r="C1"/>
-      <c r="D1" s="113" t="s">
+      <c r="D1" s="150" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="114"/>
+      <c r="E1" s="151"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="113" t="s">
+      <c r="G1" s="150" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="114"/>
+      <c r="H1" s="151"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -2612,10 +2615,10 @@
         <v>0.81361651346682706</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="113" t="s">
+      <c r="D15" s="150" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="114"/>
+      <c r="E15" s="151"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
@@ -2754,10 +2757,10 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="113" t="s">
+      <c r="A30" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="114"/>
+      <c r="B30" s="151"/>
       <c r="C30" s="24" t="s">
         <v>53</v>
       </c>
@@ -3025,10 +3028,10 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="113" t="s">
+      <c r="A50" s="150" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="114"/>
+      <c r="B50" s="151"/>
       <c r="D50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3065,10 +3068,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E52" s="115" t="s">
+      <c r="E52" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="F52" s="116"/>
+      <c r="F52" s="153"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -3316,10 +3319,10 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="113" t="s">
+      <c r="A68" s="150" t="s">
         <v>79</v>
       </c>
-      <c r="B68" s="114"/>
+      <c r="B68" s="151"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -3603,10 +3606,10 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="113" t="s">
+      <c r="A96" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="B96" s="114"/>
+      <c r="B96" s="151"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -3710,10 +3713,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="113" t="s">
+      <c r="A109" s="150" t="s">
         <v>133</v>
       </c>
-      <c r="B109" s="114"/>
+      <c r="B109" s="151"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -3796,10 +3799,10 @@
     </row>
     <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="113" t="s">
+      <c r="A120" s="150" t="s">
         <v>134</v>
       </c>
-      <c r="B120" s="114"/>
+      <c r="B120" s="151"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
@@ -3924,20 +3927,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="150" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="114"/>
+      <c r="B1" s="151"/>
       <c r="C1"/>
-      <c r="D1" s="113" t="s">
+      <c r="D1" s="150" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="114"/>
+      <c r="E1" s="151"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="113" t="s">
+      <c r="G1" s="150" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="114"/>
+      <c r="H1" s="151"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -4172,16 +4175,16 @@
         <f>500/1.15</f>
         <v>434.78260869565219</v>
       </c>
-      <c r="G12" s="113" t="s">
+      <c r="G12" s="150" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="114"/>
+      <c r="H12" s="151"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="113" t="s">
+      <c r="A13" s="150" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="114"/>
+      <c r="B13" s="151"/>
       <c r="C13"/>
       <c r="D13" t="s">
         <v>125</v>
@@ -4220,10 +4223,10 @@
         <v>200</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="113" t="s">
+      <c r="D15" s="150" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="114"/>
+      <c r="E15" s="151"/>
       <c r="G15" t="s">
         <v>166</v>
       </c>
@@ -4527,10 +4530,10 @@
       <c r="C30"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="113" t="s">
+      <c r="A31" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="114"/>
+      <c r="B31" s="151"/>
       <c r="C31" s="24" t="s">
         <v>53</v>
       </c>
@@ -4798,10 +4801,10 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="113" t="s">
+      <c r="A51" s="150" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="114"/>
+      <c r="B51" s="151"/>
       <c r="D51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4838,10 +4841,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E53" s="115" t="s">
+      <c r="E53" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="116"/>
+      <c r="F53" s="153"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -5089,10 +5092,10 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="113" t="s">
+      <c r="A69" s="150" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="114"/>
+      <c r="B69" s="151"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -5273,10 +5276,10 @@
       <c r="C84" s="36"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="117" t="s">
+      <c r="A85" s="154" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="118"/>
+      <c r="B85" s="155"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -5419,10 +5422,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="113" t="s">
+      <c r="A101" s="150" t="s">
         <v>111</v>
       </c>
-      <c r="B101" s="114"/>
+      <c r="B101" s="151"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
@@ -5562,10 +5565,10 @@
     </row>
     <row r="117" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="118" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="113" t="s">
+      <c r="A118" s="150" t="s">
         <v>133</v>
       </c>
-      <c r="B118" s="114"/>
+      <c r="B118" s="151"/>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
@@ -5684,10 +5687,10 @@
     </row>
     <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="113" t="s">
+      <c r="A133" s="150" t="s">
         <v>134</v>
       </c>
-      <c r="B133" s="114"/>
+      <c r="B133" s="151"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
@@ -5803,10 +5806,10 @@
     </row>
     <row r="146" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="147" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="113" t="s">
+      <c r="A147" s="150" t="s">
         <v>207</v>
       </c>
-      <c r="B147" s="114"/>
+      <c r="B147" s="151"/>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
@@ -5872,6 +5875,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D15:E15"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="G12:H12"/>
@@ -5882,11 +5890,6 @@
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A118:B118"/>
     <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D15:E15"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16">
@@ -5925,18 +5928,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="150" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="D1" s="113" t="s">
+      <c r="B1" s="151"/>
+      <c r="D1" s="150" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="G1" s="113" t="s">
+      <c r="E1" s="151"/>
+      <c r="G1" s="150" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="114"/>
+      <c r="H1" s="151"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -6060,10 +6063,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="113" t="s">
+      <c r="A9" s="150" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="114"/>
+      <c r="B9" s="151"/>
       <c r="D9" t="s">
         <v>32</v>
       </c>
@@ -6262,10 +6265,10 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="113" t="s">
+      <c r="A29" s="150" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="114"/>
+      <c r="B29" s="151"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -6284,10 +6287,10 @@
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>1042.1194079466816</v>
       </c>
-      <c r="D31" s="115" t="s">
+      <c r="D31" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="116"/>
+      <c r="E31" s="153"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -6467,10 +6470,10 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="113" t="s">
+      <c r="A47" s="150" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="114"/>
+      <c r="B47" s="151"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="107" t="s">
@@ -6638,10 +6641,10 @@
     </row>
     <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="113" t="s">
+      <c r="A69" s="150" t="s">
         <v>134</v>
       </c>
-      <c r="B69" s="114"/>
+      <c r="B69" s="151"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -7020,18 +7023,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="150" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="D1" s="113" t="s">
+      <c r="B1" s="151"/>
+      <c r="D1" s="150" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="114"/>
-      <c r="G1" s="113" t="s">
+      <c r="E1" s="151"/>
+      <c r="G1" s="150" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="114"/>
+      <c r="H1" s="151"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -7253,10 +7256,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="113" t="s">
+      <c r="A13" s="150" t="s">
         <v>256</v>
       </c>
-      <c r="B13" s="114"/>
+      <c r="B13" s="151"/>
       <c r="D13" t="s">
         <v>38</v>
       </c>
@@ -7280,10 +7283,10 @@
         <f>(_bfi-2*_r-_tw)/2</f>
         <v>71.45</v>
       </c>
-      <c r="G14" s="113" t="s">
+      <c r="G14" s="150" t="s">
         <v>162</v>
       </c>
-      <c r="H14" s="114"/>
+      <c r="H14" s="151"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -7542,10 +7545,10 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="113" t="s">
+      <c r="A33" s="150" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="114"/>
+      <c r="B33" s="151"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -7564,10 +7567,10 @@
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>487.74585382155738</v>
       </c>
-      <c r="D35" s="115" t="s">
+      <c r="D35" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="116"/>
+      <c r="E35" s="153"/>
       <c r="G35" s="21" t="s">
         <v>44</v>
       </c>
@@ -7677,10 +7680,10 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J40" s="115" t="s">
+      <c r="J40" s="152" t="s">
         <v>276</v>
       </c>
-      <c r="K40" s="116"/>
+      <c r="K40" s="153"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -7739,10 +7742,10 @@
         <f>B45-300</f>
         <v>-178.04000000000002</v>
       </c>
-      <c r="J45" s="115" t="s">
+      <c r="J45" s="152" t="s">
         <v>277</v>
       </c>
-      <c r="K45" s="116"/>
+      <c r="K45" s="153"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -7790,10 +7793,10 @@
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J49" s="115" t="s">
+      <c r="J49" s="152" t="s">
         <v>278</v>
       </c>
-      <c r="K49" s="116"/>
+      <c r="K49" s="153"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -7828,10 +7831,10 @@
         <f>IF(B47&gt;0.5,IF(B42&lt;=K41,1,IF(B42&lt;=K42,2,IF(B48&gt;-1,IF(B42&lt;=K50,3,4),IF(B42&lt;=K54,3,4)))),IF(B42&lt;=K46,1,IF(B42&lt;=K47,2,IF(B48&gt;-1,IF(B42&lt;=K50,3,4),IF(B42&lt;=K54,3,4)))))</f>
         <v>2</v>
       </c>
-      <c r="J52" s="115" t="s">
+      <c r="J52" s="152" t="s">
         <v>280</v>
       </c>
-      <c r="K52" s="116"/>
+      <c r="K52" s="153"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -7895,10 +7898,10 @@
       <c r="B62" s="70"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="119" t="s">
+      <c r="A63" s="156" t="s">
         <v>188</v>
       </c>
-      <c r="B63" s="120"/>
+      <c r="B63" s="157"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -8044,10 +8047,10 @@
       <c r="B78" s="70"/>
     </row>
     <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="113" t="s">
+      <c r="A79" s="150" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="114"/>
+      <c r="B79" s="151"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
@@ -8284,16 +8287,16 @@
     </row>
     <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="113" t="s">
+      <c r="A96" s="150" t="s">
         <v>369</v>
       </c>
-      <c r="B96" s="114"/>
+      <c r="B96" s="151"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B97" s="121">
+      <c r="B97" s="113">
         <f>_L/4</f>
         <v>2.5</v>
       </c>
@@ -8302,7 +8305,7 @@
       <c r="A98" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="B98" s="122">
+      <c r="B98" s="114">
         <v>5</v>
       </c>
     </row>
@@ -8310,13 +8313,13 @@
       <c r="A99" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="B99" s="121">
+      <c r="B99" s="113">
         <f>IF(B98&lt;=B97,_beff_appuis+(_beff_mi_travee-_beff_appuis)/B97*B98,_beff_mi_travee)</f>
         <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100" s="123" t="s">
+      <c r="A100" s="115" t="s">
         <v>341</v>
       </c>
       <c r="B100" s="14">
@@ -8325,7 +8328,7 @@
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A101" s="123" t="s">
+      <c r="A101" s="115" t="s">
         <v>342</v>
       </c>
       <c r="B101" s="14">
@@ -8334,7 +8337,7 @@
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102" s="123" t="s">
+      <c r="A102" s="115" t="s">
         <v>343</v>
       </c>
       <c r="B102" s="14">
@@ -8343,8 +8346,8 @@
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A103" s="121"/>
-      <c r="B103" s="121"/>
+      <c r="A103" s="113"/>
+      <c r="B103" s="113"/>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
@@ -8748,16 +8751,16 @@
     </row>
     <row r="115" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="116" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="113" t="s">
+      <c r="A116" s="150" t="s">
         <v>338</v>
       </c>
-      <c r="B116" s="114"/>
+      <c r="B116" s="151"/>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="B117" s="121">
+      <c r="B117" s="113">
         <f>_L/4</f>
         <v>2.5</v>
       </c>
@@ -8766,7 +8769,7 @@
       <c r="A118" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="B118" s="122">
+      <c r="B118" s="114">
         <v>0.5</v>
       </c>
     </row>
@@ -8774,13 +8777,13 @@
       <c r="A119" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="B119" s="121">
+      <c r="B119" s="113">
         <f>IF(B118&lt;=B117,_beff_appuis+(_beff_mi_travee-_beff_appuis)/B117*B118,_beff_mi_travee)</f>
         <v>1.6800000000000002</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A120" s="123" t="s">
+      <c r="A120" s="115" t="s">
         <v>341</v>
       </c>
       <c r="B120" s="14">
@@ -8790,7 +8793,7 @@
       <c r="C120" s="24"/>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A121" s="123" t="s">
+      <c r="A121" s="115" t="s">
         <v>342</v>
       </c>
       <c r="B121" s="14">
@@ -8800,7 +8803,7 @@
       <c r="C121" s="24"/>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122" s="123" t="s">
+      <c r="A122" s="115" t="s">
         <v>343</v>
       </c>
       <c r="B122" s="14">
@@ -8810,7 +8813,7 @@
       <c r="C122" s="24"/>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A123" s="123"/>
+      <c r="A123" s="115"/>
       <c r="B123" s="14"/>
       <c r="C123" s="24"/>
     </row>
@@ -9216,10 +9219,10 @@
     </row>
     <row r="135" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="136" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="113" t="s">
+      <c r="A136" s="150" t="s">
         <v>133</v>
       </c>
-      <c r="B136" s="114"/>
+      <c r="B136" s="151"/>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
@@ -9430,17 +9433,17 @@
     </row>
     <row r="158" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="159" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="113" t="s">
+      <c r="A159" s="150" t="s">
         <v>134</v>
       </c>
-      <c r="B159" s="114"/>
+      <c r="B159" s="151"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" s="121"/>
-      <c r="B160" s="121"/>
+      <c r="A160" s="113"/>
+      <c r="B160" s="113"/>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A161" s="121"/>
+      <c r="A161" s="113"/>
       <c r="B161" s="77" t="s">
         <v>344</v>
       </c>
@@ -9458,10 +9461,10 @@
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A162" s="132" t="s">
+      <c r="A162" s="124" t="s">
         <v>328</v>
       </c>
-      <c r="B162" s="139"/>
+      <c r="B162" s="131"/>
       <c r="C162" s="66">
         <v>30.8</v>
       </c>
@@ -9471,31 +9474,31 @@
       <c r="E162" s="29">
         <v>29.1</v>
       </c>
-      <c r="F162" s="127"/>
+      <c r="F162" s="119"/>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="28" t="s">
         <v>365</v>
       </c>
-      <c r="B163" s="155">
+      <c r="B163" s="147">
         <v>5921</v>
       </c>
-      <c r="C163" s="154">
+      <c r="C163" s="146">
         <v>22581</v>
       </c>
-      <c r="D163" s="154">
+      <c r="D163" s="146">
         <v>31404</v>
       </c>
-      <c r="E163" s="156">
+      <c r="E163" s="148">
         <v>22952</v>
       </c>
-      <c r="F163" s="127"/>
+      <c r="F163" s="119"/>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A164" s="134" t="s">
+      <c r="A164" s="126" t="s">
         <v>366</v>
       </c>
-      <c r="B164" s="152">
+      <c r="B164" s="144">
         <v>-178</v>
       </c>
       <c r="C164" s="82">
@@ -9507,46 +9510,46 @@
       <c r="E164" s="30">
         <v>-23.7</v>
       </c>
-      <c r="F164" s="135"/>
+      <c r="F164" s="127"/>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="28" t="s">
         <v>367</v>
       </c>
-      <c r="B165" s="155">
+      <c r="B165" s="147">
         <v>5921</v>
       </c>
-      <c r="C165" s="154">
+      <c r="C165" s="146">
         <v>21530.096266744444</v>
       </c>
-      <c r="D165" s="154">
+      <c r="D165" s="146">
         <v>30234.112325995633</v>
       </c>
-      <c r="E165" s="156">
+      <c r="E165" s="148">
         <v>21539.889165989531</v>
       </c>
-      <c r="F165" s="127"/>
+      <c r="F165" s="119"/>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="134" t="s">
+      <c r="A166" s="126" t="s">
         <v>368</v>
       </c>
-      <c r="B166" s="152">
+      <c r="B166" s="144">
         <v>-178</v>
       </c>
       <c r="C166" s="96">
         <v>-34.487492252446586</v>
       </c>
-      <c r="D166" s="153">
+      <c r="D166" s="145">
         <v>30.897637600365364</v>
       </c>
       <c r="E166" s="20">
         <v>-34.40387189041919</v>
       </c>
-      <c r="F166" s="135"/>
+      <c r="F166" s="127"/>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A167" s="134" t="s">
+      <c r="A167" s="126" t="s">
         <v>351</v>
       </c>
       <c r="B167" s="16" t="s">
@@ -9561,13 +9564,13 @@
       <c r="E167" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="F167" s="135"/>
+      <c r="F167" s="127"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A168" s="150" t="s">
+      <c r="A168" s="142" t="s">
         <v>363</v>
       </c>
-      <c r="B168" s="151">
+      <c r="B168" s="143">
         <f>B139</f>
         <v>31.099709848275001</v>
       </c>
@@ -9585,26 +9588,26 @@
       <c r="F168" s="83"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A169" s="133" t="s">
+      <c r="A169" s="125" t="s">
         <v>354</v>
       </c>
-      <c r="B169" s="140">
+      <c r="B169" s="132">
         <f>IF(B167="N",0,$B$140*10^6/(B$163*10^4)*(_td-B$164)/B162)</f>
         <v>0</v>
       </c>
-      <c r="C169" s="125">
+      <c r="C169" s="117">
         <f>IF(C167="N",0,$B$142*10^6/(C$163*10^4)*(_td-C$164)/C162)</f>
         <v>1.0553637496642678</v>
       </c>
-      <c r="D169" s="125">
+      <c r="D169" s="117">
         <f>IF(D167="N",0,$B$144*10^6/(D$163*10^4)*(_td-D$164)/D162)</f>
         <v>9.2213191083356905E-2</v>
       </c>
-      <c r="E169" s="141">
+      <c r="E169" s="133">
         <f>IF(E167="N",0,$B$153*10^6/(E$163*10^4)*(_td-E$164)/E162)</f>
         <v>1.0533792862815441</v>
       </c>
-      <c r="F169" s="128">
+      <c r="F169" s="120">
         <f>1.35*(B169+C169)+1.5*D169+1.35*E169</f>
         <v>2.9851228851518821</v>
       </c>
@@ -9613,26 +9616,26 @@
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="133" t="s">
+      <c r="A170" s="125" t="s">
         <v>355</v>
       </c>
-      <c r="B170" s="140">
+      <c r="B170" s="132">
         <f>$B$140*10^6/(B$163*10^4)*(0-B$164)</f>
         <v>233.73367475903353</v>
       </c>
-      <c r="C170" s="125">
+      <c r="C170" s="117">
         <f>$B$142*10^6/(C$163*10^4)*(0-C$164)</f>
         <v>5.9341924626898717</v>
       </c>
-      <c r="D170" s="124">
+      <c r="D170" s="116">
         <f>$B$144*10^6/(D$163*10^4)*(0-D$164)</f>
         <v>-0.30887784995541961</v>
       </c>
-      <c r="E170" s="142">
+      <c r="E170" s="134">
         <f>$B$153*10^6/(E$163*10^4)*(0-E$164)</f>
         <v>5.0555608376464338</v>
       </c>
-      <c r="F170" s="128">
+      <c r="F170" s="120">
         <f t="shared" ref="F170:F171" si="22">1.35*(B170+C170)+1.5*D170+1.35*E170</f>
         <v>329.91331110521622</v>
       </c>
@@ -9641,26 +9644,26 @@
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A171" s="134" t="s">
+      <c r="A171" s="126" t="s">
         <v>356</v>
       </c>
-      <c r="B171" s="143">
+      <c r="B171" s="135">
         <f>$B$140*10^6/(B$163*10^4)*(-_h-B$164)</f>
         <v>-160.19948494720276</v>
       </c>
-      <c r="C171" s="137">
+      <c r="C171" s="129">
         <f>$B$142*10^6/(C$163*10^4)*(-_h-C$164)</f>
         <v>-60.493335104734065</v>
       </c>
-      <c r="D171" s="136">
+      <c r="D171" s="128">
         <f>$B$144*10^6/(D$163*10^4)*(-_h-D$164)</f>
         <v>-2.6971086485797984</v>
       </c>
-      <c r="E171" s="144">
+      <c r="E171" s="136">
         <f>$B$153*10^6/(E$163*10^4)*(-_h-E$164)</f>
         <v>-58.938880145219827</v>
       </c>
-      <c r="F171" s="138">
+      <c r="F171" s="130">
         <f t="shared" si="22"/>
         <v>-381.54845823903122</v>
       </c>
@@ -9669,10 +9672,10 @@
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A172" s="133" t="s">
+      <c r="A172" s="125" t="s">
         <v>348</v>
       </c>
-      <c r="B172" s="145">
+      <c r="B172" s="137">
         <f>B169/(0.85*_fck_dalle/1.5)</f>
         <v>0</v>
       </c>
@@ -9684,61 +9687,61 @@
         <f>D169/(0.85*_fck_dalle/1.5)</f>
         <v>8.136458036766785E-3</v>
       </c>
-      <c r="E172" s="146">
+      <c r="E172" s="138">
         <f>E169/(0.85*_fck_dalle/1.5)</f>
         <v>9.2945231142489176E-2</v>
       </c>
-      <c r="F172" s="129">
+      <c r="F172" s="121">
         <f>F169/(0.85*_fck_dalle/1.5)</f>
         <v>0.26339319574869546</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A173" s="133" t="s">
+      <c r="A173" s="125" t="s">
         <v>349</v>
       </c>
-      <c r="B173" s="147">
+      <c r="B173" s="139">
         <f>B170/(_fy)</f>
         <v>0.55650874942627027</v>
       </c>
-      <c r="C173" s="125">
+      <c r="C173" s="117">
         <f>C170/(_fy)</f>
         <v>1.4129029673071123E-2</v>
       </c>
-      <c r="D173" s="125">
+      <c r="D173" s="117">
         <f>D170/(_fy)</f>
         <v>-7.3542345227480856E-4</v>
       </c>
-      <c r="E173" s="141">
+      <c r="E173" s="133">
         <f>E170/(_fy)</f>
         <v>1.203704961344389E-2</v>
       </c>
-      <c r="F173" s="130">
+      <c r="F173" s="122">
         <f>F170/(_fy)</f>
         <v>0.78550788358384815</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A174" s="134" t="s">
+      <c r="A174" s="126" t="s">
         <v>350</v>
       </c>
-      <c r="B174" s="148">
+      <c r="B174" s="140">
         <f>ABS(B171/(_fy))</f>
         <v>0.38142734511238752</v>
       </c>
-      <c r="C174" s="126">
+      <c r="C174" s="118">
         <f>ABS(C171/(_fy))</f>
         <v>0.14403175024936682</v>
       </c>
-      <c r="D174" s="126">
+      <c r="D174" s="118">
         <f>ABS(D171/(_fy))</f>
         <v>6.4216872585233292E-3</v>
       </c>
-      <c r="E174" s="149">
+      <c r="E174" s="141">
         <f>ABS(E171/(_fy))</f>
         <v>0.14033066701242816</v>
       </c>
-      <c r="F174" s="131">
+      <c r="F174" s="123">
         <f>ABS(F171/(_fy))</f>
         <v>0.90844871009293149</v>
       </c>
@@ -9747,19 +9750,19 @@
       <c r="A175" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="B175" s="124">
+      <c r="B175" s="116">
         <f>ABS(IF(B167="N",0,_beff_appuis*1000*(_td-_tj)/B162*(B166-((_td-_tj)/2+_tj))))</f>
         <v>0</v>
       </c>
-      <c r="C175" s="124">
+      <c r="C175" s="116">
         <f>ABS(IF(C167="N",0,_beff_appuis*1000*(_td-_tj)/C162*(C166-((_td-_tj)/2+_tj))))</f>
         <v>568499.95572826616</v>
       </c>
-      <c r="D175" s="124">
+      <c r="D175" s="116">
         <f>ABS(IF(D167="N",0,_beff_appuis*1000*(_td-_tj)/D162*(D166-((_td-_tj)/2+_tj))))</f>
         <v>856207.67223048443</v>
       </c>
-      <c r="E175" s="124">
+      <c r="E175" s="116">
         <f>ABS(IF(E167="N",0,_beff_appuis*1000*(_td-_tj)/E162*(E166-((_td-_tj)/2+_tj))))</f>
         <v>601205.54820322257</v>
       </c>
@@ -9768,19 +9771,19 @@
       <c r="A176" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="B176" s="157">
+      <c r="B176" s="149">
         <f>B168*1000*B175/B165/1000</f>
         <v>0</v>
       </c>
-      <c r="C176" s="157">
+      <c r="C176" s="149">
         <f t="shared" ref="C176:E176" si="23">C168*1000*C175/C165/1000</f>
         <v>528.09792272631466</v>
       </c>
-      <c r="D176" s="157">
+      <c r="D176" s="149">
         <f t="shared" si="23"/>
         <v>14.15962974203657</v>
       </c>
-      <c r="E176" s="157">
+      <c r="E176" s="149">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
@@ -9789,90 +9792,97 @@
         <v>734.17164029357969</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="7"/>
-      <c r="B177" s="121"/>
-      <c r="C177" s="124"/>
-      <c r="D177" s="124"/>
-      <c r="E177" s="121"/>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" s="7"/>
-      <c r="B178" s="121"/>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
+      <c r="B177" s="113"/>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
         <v>245</v>
       </c>
-      <c r="B179" s="23">
+      <c r="B178" s="23">
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>487.74585382155738</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" s="123" t="s">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="115" t="s">
         <v>123</v>
       </c>
-      <c r="B180" s="23">
+      <c r="B179" s="23">
         <v>464.72471483007769</v>
       </c>
-      <c r="C180">
-        <f>B180*B181</f>
+      <c r="C179">
+        <f>B179*B180</f>
         <v>464.72471483007769</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181" s="123" t="s">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="115" t="s">
         <v>359</v>
       </c>
+      <c r="B180" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="115" t="s">
+        <v>364</v>
+      </c>
       <c r="B181" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A182" s="123" t="s">
-        <v>364</v>
-      </c>
-      <c r="B182" s="25">
         <f>_PRd/(_sx/1000)</f>
         <v>341.22561783575122</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B183" s="23"/>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B182" s="23"/>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
         <v>141</v>
       </c>
-      <c r="B184" s="26">
+      <c r="B183" s="26">
         <f>MAX(F172:F174)</f>
         <v>0.90844871009293149</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>142</v>
+      </c>
+      <c r="B184" s="26">
+        <f>B154/B178</f>
+        <v>0.14297324672017361</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>142</v>
+        <v>358</v>
       </c>
       <c r="B185" s="26">
-        <f>B154/B179</f>
-        <v>0.14297324672017361</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+        <f>B155/(B180*B179)</f>
+        <v>0.52140015676004936</v>
+      </c>
+      <c r="C185" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="B186" s="26">
-        <f>B155/(B181*B180)</f>
-        <v>0.52140015676004936</v>
-      </c>
-      <c r="C186" t="s">
-        <v>360</v>
+        <f>F176/B181</f>
+        <v>2.1515724550522255</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A136:B136"/>
     <mergeCell ref="A159:B159"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
@@ -9885,11 +9895,6 @@
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="A116:B116"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="A136:B136"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Manuel Validation/Cas tests références.xlsx
+++ b/Manuel Validation/Cas tests références.xlsx
@@ -262,7 +262,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="378">
   <si>
     <t>h (mm)</t>
   </si>
@@ -1350,9 +1350,6 @@
     <t>flux cisaillement connecteur (kN/m)</t>
   </si>
   <si>
-    <t>Sh,i (mm3)</t>
-  </si>
-  <si>
     <t>Ved (kN)</t>
   </si>
   <si>
@@ -1375,6 +1372,30 @@
   </si>
   <si>
     <t>Critere connex</t>
+  </si>
+  <si>
+    <t>Sh,0 (mm3)</t>
+  </si>
+  <si>
+    <t>flux cisaillement soudure sup (kN/m)</t>
+  </si>
+  <si>
+    <t>Sh,1 (mm3)</t>
+  </si>
+  <si>
+    <t>Beta w</t>
+  </si>
+  <si>
+    <t>fu (Mpa)</t>
+  </si>
+  <si>
+    <t>aw,sup (mm)</t>
+  </si>
+  <si>
+    <t>aw,inf (mm)</t>
+  </si>
+  <si>
+    <t>Sh,2 (mm3)</t>
   </si>
 </sst>
 </file>
@@ -1798,7 +1819,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2020,9 +2041,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2045,6 +2063,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2340,20 +2373,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="149" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="151"/>
+      <c r="B1" s="150"/>
       <c r="C1"/>
-      <c r="D1" s="150" t="s">
+      <c r="D1" s="149" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="151"/>
+      <c r="E1" s="150"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="150" t="s">
+      <c r="G1" s="149" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="151"/>
+      <c r="H1" s="150"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -2615,10 +2648,10 @@
         <v>0.81361651346682706</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="150" t="s">
+      <c r="D15" s="149" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="151"/>
+      <c r="E15" s="150"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6"/>
@@ -2757,10 +2790,10 @@
       <c r="C29"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="150" t="s">
+      <c r="A30" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="151"/>
+      <c r="B30" s="150"/>
       <c r="C30" s="24" t="s">
         <v>53</v>
       </c>
@@ -3028,10 +3061,10 @@
       </c>
     </row>
     <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="150" t="s">
+      <c r="A50" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="B50" s="151"/>
+      <c r="B50" s="150"/>
       <c r="D50" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3068,10 +3101,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E52" s="152" t="s">
+      <c r="E52" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="F52" s="153"/>
+      <c r="F52" s="152"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -3319,10 +3352,10 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="150" t="s">
+      <c r="A68" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="B68" s="151"/>
+      <c r="B68" s="150"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
@@ -3606,10 +3639,10 @@
     </row>
     <row r="95" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="150" t="s">
+      <c r="A96" s="149" t="s">
         <v>111</v>
       </c>
-      <c r="B96" s="151"/>
+      <c r="B96" s="150"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -3713,10 +3746,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="109" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="150" t="s">
+      <c r="A109" s="149" t="s">
         <v>133</v>
       </c>
-      <c r="B109" s="151"/>
+      <c r="B109" s="150"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
@@ -3799,10 +3832,10 @@
     </row>
     <row r="119" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="150" t="s">
+      <c r="A120" s="149" t="s">
         <v>134</v>
       </c>
-      <c r="B120" s="151"/>
+      <c r="B120" s="150"/>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
@@ -3927,20 +3960,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="149" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="151"/>
+      <c r="B1" s="150"/>
       <c r="C1"/>
-      <c r="D1" s="150" t="s">
+      <c r="D1" s="149" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="151"/>
+      <c r="E1" s="150"/>
       <c r="F1" s="24"/>
-      <c r="G1" s="150" t="s">
+      <c r="G1" s="149" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="151"/>
+      <c r="H1" s="150"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -4175,16 +4208,16 @@
         <f>500/1.15</f>
         <v>434.78260869565219</v>
       </c>
-      <c r="G12" s="150" t="s">
+      <c r="G12" s="149" t="s">
         <v>162</v>
       </c>
-      <c r="H12" s="151"/>
+      <c r="H12" s="150"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="150" t="s">
+      <c r="A13" s="149" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="151"/>
+      <c r="B13" s="150"/>
       <c r="C13"/>
       <c r="D13" t="s">
         <v>125</v>
@@ -4223,10 +4256,10 @@
         <v>200</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="150" t="s">
+      <c r="D15" s="149" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="151"/>
+      <c r="E15" s="150"/>
       <c r="G15" t="s">
         <v>166</v>
       </c>
@@ -4530,10 +4563,10 @@
       <c r="C30"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="150" t="s">
+      <c r="A31" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="151"/>
+      <c r="B31" s="150"/>
       <c r="C31" s="24" t="s">
         <v>53</v>
       </c>
@@ -4801,10 +4834,10 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="150" t="s">
+      <c r="A51" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="B51" s="151"/>
+      <c r="B51" s="150"/>
       <c r="D51" s="26" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4841,10 +4874,10 @@
         <f t="shared" si="0"/>
         <v>0.41222226735473377</v>
       </c>
-      <c r="E53" s="152" t="s">
+      <c r="E53" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="F53" s="153"/>
+      <c r="F53" s="152"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
@@ -5092,10 +5125,10 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="150" t="s">
+      <c r="A69" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="B69" s="151"/>
+      <c r="B69" s="150"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -5276,10 +5309,10 @@
       <c r="C84" s="36"/>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="154" t="s">
+      <c r="A85" s="153" t="s">
         <v>188</v>
       </c>
-      <c r="B85" s="155"/>
+      <c r="B85" s="154"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -5422,10 +5455,10 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="150" t="s">
+      <c r="A101" s="149" t="s">
         <v>111</v>
       </c>
-      <c r="B101" s="151"/>
+      <c r="B101" s="150"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
@@ -5565,10 +5598,10 @@
     </row>
     <row r="117" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="118" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="150" t="s">
+      <c r="A118" s="149" t="s">
         <v>133</v>
       </c>
-      <c r="B118" s="151"/>
+      <c r="B118" s="150"/>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
@@ -5687,10 +5720,10 @@
     </row>
     <row r="132" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="133" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="150" t="s">
+      <c r="A133" s="149" t="s">
         <v>134</v>
       </c>
-      <c r="B133" s="151"/>
+      <c r="B133" s="150"/>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
@@ -5806,10 +5839,10 @@
     </row>
     <row r="146" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="147" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="150" t="s">
+      <c r="A147" s="149" t="s">
         <v>207</v>
       </c>
-      <c r="B147" s="151"/>
+      <c r="B147" s="150"/>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
@@ -5875,11 +5908,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D15:E15"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="G12:H12"/>
@@ -5890,6 +5918,11 @@
     <mergeCell ref="A101:B101"/>
     <mergeCell ref="A118:B118"/>
     <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D15:E15"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E16">
@@ -5928,18 +5961,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="149" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="D1" s="150" t="s">
+      <c r="B1" s="150"/>
+      <c r="D1" s="149" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="151"/>
-      <c r="G1" s="150" t="s">
+      <c r="E1" s="150"/>
+      <c r="G1" s="149" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="151"/>
+      <c r="H1" s="150"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -6063,10 +6096,10 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="150" t="s">
+      <c r="A9" s="149" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="151"/>
+      <c r="B9" s="150"/>
       <c r="D9" t="s">
         <v>32</v>
       </c>
@@ -6265,10 +6298,10 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="150" t="s">
+      <c r="A29" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="151"/>
+      <c r="B29" s="150"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
@@ -6287,10 +6320,10 @@
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>1042.1194079466816</v>
       </c>
-      <c r="D31" s="152" t="s">
+      <c r="D31" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="153"/>
+      <c r="E31" s="152"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -6470,10 +6503,10 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="150" t="s">
+      <c r="A47" s="149" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="151"/>
+      <c r="B47" s="150"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="107" t="s">
@@ -6641,10 +6674,10 @@
     </row>
     <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="150" t="s">
+      <c r="A69" s="149" t="s">
         <v>134</v>
       </c>
-      <c r="B69" s="151"/>
+      <c r="B69" s="150"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -7006,7 +7039,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q186"/>
+  <dimension ref="A1:Q203"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.5703125" bestFit="1" customWidth="1"/>
@@ -7023,18 +7056,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="149" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="D1" s="150" t="s">
+      <c r="B1" s="150"/>
+      <c r="D1" s="149" t="s">
         <v>221</v>
       </c>
-      <c r="E1" s="151"/>
-      <c r="G1" s="150" t="s">
+      <c r="E1" s="150"/>
+      <c r="G1" s="149" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="151"/>
+      <c r="H1" s="150"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -7256,10 +7289,10 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="150" t="s">
+      <c r="A13" s="149" t="s">
         <v>256</v>
       </c>
-      <c r="B13" s="151"/>
+      <c r="B13" s="150"/>
       <c r="D13" t="s">
         <v>38</v>
       </c>
@@ -7283,10 +7316,10 @@
         <f>(_bfi-2*_r-_tw)/2</f>
         <v>71.45</v>
       </c>
-      <c r="G14" s="150" t="s">
+      <c r="G14" s="149" t="s">
         <v>162</v>
       </c>
-      <c r="H14" s="151"/>
+      <c r="H14" s="150"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -7545,10 +7578,10 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="150" t="s">
+      <c r="A33" s="149" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="151"/>
+      <c r="B33" s="150"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -7567,10 +7600,10 @@
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>487.74585382155738</v>
       </c>
-      <c r="D35" s="152" t="s">
+      <c r="D35" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="153"/>
+      <c r="E35" s="152"/>
       <c r="G35" s="21" t="s">
         <v>44</v>
       </c>
@@ -7680,10 +7713,10 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J40" s="152" t="s">
+      <c r="J40" s="151" t="s">
         <v>276</v>
       </c>
-      <c r="K40" s="153"/>
+      <c r="K40" s="152"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -7742,10 +7775,10 @@
         <f>B45-300</f>
         <v>-178.04000000000002</v>
       </c>
-      <c r="J45" s="152" t="s">
+      <c r="J45" s="151" t="s">
         <v>277</v>
       </c>
-      <c r="K45" s="153"/>
+      <c r="K45" s="152"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
@@ -7793,10 +7826,10 @@
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J49" s="152" t="s">
+      <c r="J49" s="151" t="s">
         <v>278</v>
       </c>
-      <c r="K49" s="153"/>
+      <c r="K49" s="152"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -7831,10 +7864,10 @@
         <f>IF(B47&gt;0.5,IF(B42&lt;=K41,1,IF(B42&lt;=K42,2,IF(B48&gt;-1,IF(B42&lt;=K50,3,4),IF(B42&lt;=K54,3,4)))),IF(B42&lt;=K46,1,IF(B42&lt;=K47,2,IF(B48&gt;-1,IF(B42&lt;=K50,3,4),IF(B42&lt;=K54,3,4)))))</f>
         <v>2</v>
       </c>
-      <c r="J52" s="152" t="s">
+      <c r="J52" s="151" t="s">
         <v>280</v>
       </c>
-      <c r="K52" s="153"/>
+      <c r="K52" s="152"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
@@ -7898,10 +7931,10 @@
       <c r="B62" s="70"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="156" t="s">
+      <c r="A63" s="155" t="s">
         <v>188</v>
       </c>
-      <c r="B63" s="157"/>
+      <c r="B63" s="156"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -8047,10 +8080,10 @@
       <c r="B78" s="70"/>
     </row>
     <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="150" t="s">
+      <c r="A79" s="149" t="s">
         <v>79</v>
       </c>
-      <c r="B79" s="151"/>
+      <c r="B79" s="150"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
@@ -8287,10 +8320,10 @@
     </row>
     <row r="95" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="96" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="150" t="s">
-        <v>369</v>
-      </c>
-      <c r="B96" s="151"/>
+      <c r="A96" s="149" t="s">
+        <v>368</v>
+      </c>
+      <c r="B96" s="150"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
@@ -8751,10 +8784,10 @@
     </row>
     <row r="115" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="116" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="150" t="s">
+      <c r="A116" s="149" t="s">
         <v>338</v>
       </c>
-      <c r="B116" s="151"/>
+      <c r="B116" s="150"/>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
@@ -9219,10 +9252,10 @@
     </row>
     <row r="135" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="136" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="150" t="s">
+      <c r="A136" s="149" t="s">
         <v>133</v>
       </c>
-      <c r="B136" s="151"/>
+      <c r="B136" s="150"/>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
@@ -9433,10 +9466,10 @@
     </row>
     <row r="158" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="159" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="150" t="s">
+      <c r="A159" s="149" t="s">
         <v>134</v>
       </c>
-      <c r="B159" s="151"/>
+      <c r="B159" s="150"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="113"/>
@@ -9478,7 +9511,7 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="28" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B163" s="147">
         <v>5921</v>
@@ -9496,7 +9529,7 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="126" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B164" s="144">
         <v>-178</v>
@@ -9514,7 +9547,7 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B165" s="147">
         <v>5921</v>
@@ -9532,7 +9565,7 @@
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="126" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B166" s="144">
         <v>-178</v>
@@ -9568,7 +9601,7 @@
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="142" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B168" s="143">
         <f>B139</f>
@@ -9747,142 +9780,336 @@
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="B175" s="116">
+      <c r="A175" s="159" t="s">
+        <v>370</v>
+      </c>
+      <c r="B175" s="157">
         <f>ABS(IF(B167="N",0,_beff_appuis*1000*(_td-_tj)/B162*(B166-((_td-_tj)/2+_tj))))</f>
         <v>0</v>
       </c>
-      <c r="C175" s="116">
+      <c r="C175" s="157">
         <f>ABS(IF(C167="N",0,_beff_appuis*1000*(_td-_tj)/C162*(C166-((_td-_tj)/2+_tj))))</f>
         <v>568499.95572826616</v>
       </c>
-      <c r="D175" s="116">
+      <c r="D175" s="157">
         <f>ABS(IF(D167="N",0,_beff_appuis*1000*(_td-_tj)/D162*(D166-((_td-_tj)/2+_tj))))</f>
         <v>856207.67223048443</v>
       </c>
-      <c r="E175" s="116">
+      <c r="E175" s="157">
         <f>ABS(IF(E167="N",0,_beff_appuis*1000*(_td-_tj)/E162*(E166-((_td-_tj)/2+_tj))))</f>
         <v>601205.54820322257</v>
       </c>
+      <c r="F175" s="29"/>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A176" s="7" t="s">
+      <c r="A176" s="160" t="s">
         <v>361</v>
       </c>
-      <c r="B176" s="149">
-        <f>B168*1000*B175/B165/1000</f>
+      <c r="B176" s="158">
+        <f>B168*B175/(B165*10^4)*1000</f>
         <v>0</v>
       </c>
-      <c r="C176" s="149">
-        <f t="shared" ref="C176:E176" si="23">C168*1000*C175/C165/1000</f>
-        <v>528.09792272631466</v>
-      </c>
-      <c r="D176" s="149">
-        <f t="shared" si="23"/>
-        <v>14.15962974203657</v>
-      </c>
-      <c r="E176" s="149">
-        <f t="shared" si="23"/>
+      <c r="C176" s="158">
+        <f>C168*C175/(C165*10^4)*1000</f>
+        <v>52.809792272631476</v>
+      </c>
+      <c r="D176" s="158">
+        <f>D168*D175/(D165*10^4)*1000</f>
+        <v>1.4159629742036572</v>
+      </c>
+      <c r="E176" s="158">
+        <f t="shared" ref="E176" si="23">E168*1000*E175/E165/1000</f>
         <v>0</v>
       </c>
-      <c r="F176">
+      <c r="F176" s="20">
         <f>1.35*B176+1.35*C176+1.5*D176+1.35*E176</f>
-        <v>734.17164029357969</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" s="7"/>
-      <c r="B177" s="113"/>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
+        <v>73.417164029357977</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="159" t="s">
+        <v>372</v>
+      </c>
+      <c r="B177" s="161">
+        <f>ABS(_hw*_tw*(-_tfs-_hw/2-B166)+_bfi*_tfi*(-_h+_tfi/2-B166))</f>
+        <v>126176.34949999998</v>
+      </c>
+      <c r="C177" s="161">
+        <f>ABS(_hw*_tw*(-_tfs-_hw/2-C166)+_bfi*_tfi*(-_h+_tfi/2-C166))</f>
+        <v>645179.28789348458</v>
+      </c>
+      <c r="D177" s="161">
+        <f>ABS(_hw*_tw*(-_tfs-_hw/2-D166)+_bfi*_tfi*(-_h+_tfi/2-D166))</f>
+        <v>881640.03304708935</v>
+      </c>
+      <c r="E177" s="161">
+        <f>ABS(_hw*_tw*(-_tfs-_hw/2-E166)+_bfi*_tfi*(-_h+_tfi/2-E166))</f>
+        <v>645481.69507933129</v>
+      </c>
+      <c r="F177" s="74"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="160" t="s">
+        <v>371</v>
+      </c>
+      <c r="B178" s="158">
+        <f>B168*B177/(B165*10^4)*1000</f>
+        <v>66.273397384977841</v>
+      </c>
+      <c r="C178" s="158">
+        <f t="shared" ref="C178:E178" si="24">C168*C177/(C165*10^4)*1000</f>
+        <v>59.932782454859115</v>
+      </c>
+      <c r="D178" s="158">
+        <f t="shared" si="24"/>
+        <v>1.4580220241641513</v>
+      </c>
+      <c r="E178" s="158">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F178" s="20">
+        <f>1.35*B178+1.35*C178+1.5*D178+1.35*E178</f>
+        <v>172.56537582002613</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="159" t="s">
+        <v>377</v>
+      </c>
+      <c r="B179" s="161">
+        <f>ABS(_bfi*_tfi*(-_h+_tfi/2-B166))</f>
+        <v>187223.24999999997</v>
+      </c>
+      <c r="C179" s="161">
+        <f>ABS(_bfi*_tfi*(-_h+_tfi/2-C166))</f>
+        <v>417560.82493482315</v>
+      </c>
+      <c r="D179" s="161">
+        <f>ABS(_bfi*_tfi*(-_h+_tfi/2-D166))</f>
+        <v>522503.9583485864</v>
+      </c>
+      <c r="E179" s="161">
+        <f>ABS(_bfi*_tfi*(-_h+_tfi/2-E166))</f>
+        <v>417695.03561587719</v>
+      </c>
+      <c r="F179" s="74"/>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="160" t="s">
+        <v>371</v>
+      </c>
+      <c r="B180" s="158">
+        <f>B168*B179/(B165*10^4)*1000</f>
+        <v>98.33792859062747</v>
+      </c>
+      <c r="C180" s="158">
+        <f t="shared" ref="C180:E180" si="25">C168*C179/(C165*10^4)*1000</f>
+        <v>38.788570172794898</v>
+      </c>
+      <c r="D180" s="158">
+        <f t="shared" si="25"/>
+        <v>0.86409674065299358</v>
+      </c>
+      <c r="E180" s="158">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="F180" s="20">
+        <f>1.35*B180+1.35*C180+1.5*D180+1.35*E180</f>
+        <v>186.41691844159968</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="7"/>
+      <c r="B181" s="113"/>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
         <v>245</v>
       </c>
-      <c r="B178" s="23">
+      <c r="B182" s="23">
         <f>_Av*100*_fy/(1000*SQRT(3))</f>
         <v>487.74585382155738</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" s="115" t="s">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="115" t="s">
         <v>123</v>
       </c>
-      <c r="B179" s="23">
+      <c r="B183" s="23">
         <v>464.72471483007769</v>
       </c>
-      <c r="C179">
-        <f>B179*B180</f>
+      <c r="C183">
+        <f>B183*B184</f>
         <v>464.72471483007769</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" s="115" t="s">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="115" t="s">
         <v>359</v>
       </c>
-      <c r="B180" s="25">
+      <c r="B184" s="25">
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" s="115" t="s">
-        <v>364</v>
-      </c>
-      <c r="B181" s="25">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="115" t="s">
+        <v>363</v>
+      </c>
+      <c r="B185" s="3">
         <f>_PRd/(_sx/1000)</f>
         <v>341.22561783575122</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B182" s="23"/>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="115" t="s">
+        <v>373</v>
+      </c>
+      <c r="B186" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="115" t="s">
+        <v>374</v>
+      </c>
+      <c r="B187" s="3">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B188" s="23"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="B183" s="26">
+      <c r="B189" s="69">
         <f>MAX(F172:F174)</f>
         <v>0.90844871009293149</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="B184" s="26">
-        <f>B154/B178</f>
+      <c r="B190" s="17">
+        <f>B154/B182</f>
         <v>0.14297324672017361</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="B185" s="26">
-        <f>B155/(B180*B179)</f>
+      <c r="B191" s="17">
+        <f>B155/(B184*B183)</f>
         <v>0.52140015676004936</v>
       </c>
-      <c r="C185" t="s">
+      <c r="C191" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>370</v>
-      </c>
-      <c r="B186" s="26">
-        <f>F176/B181</f>
-        <v>2.1515724550522255</v>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="B192" s="17">
+        <f>F176/B185</f>
+        <v>0.21515724550522256</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A193" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="B193" s="17">
+        <f>SQRT(3)/2*F178*B186*1.25/B187</f>
+        <v>0.35924519056190274</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A194" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="B194" s="18">
+        <f>SQRT(3)/2*F180*B186*1.25/B187</f>
+        <v>0.38808121890778152</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="196" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="149" t="s">
+        <v>207</v>
+      </c>
+      <c r="B196" s="150"/>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>209</v>
+      </c>
+      <c r="B197" s="3">
+        <f>_nr*_PRd/(_sx/1000)</f>
+        <v>341.22561783575122</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>208</v>
+      </c>
+      <c r="B198" s="3">
+        <f>B197/(_td-_tj)</f>
+        <v>3.1020510712341021</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>210</v>
+      </c>
+      <c r="B199" s="33">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>212</v>
+      </c>
+      <c r="B200" s="3">
+        <f>0.6*(1-_fck_dalle/250)</f>
+        <v>0.55200000000000005</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>211</v>
+      </c>
+      <c r="B201" s="3">
+        <f>B200*_fck_dalle/1.5*SIN(RADIANS(B199))*COS(RADIANS(B199))</f>
+        <v>2.9771825392998066</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>213</v>
+      </c>
+      <c r="B202" s="3">
+        <f>B198/B201</f>
+        <v>1.0419418461199437</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>214</v>
+      </c>
+      <c r="B203" s="3">
+        <f>B198*(_td-_tj)*TAN(RADIANS(B199))/(500/1.15)*10</f>
+        <v>3.9988521350558321</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="J52:K52"/>
-    <mergeCell ref="A136:B136"/>
+  <mergeCells count="18">
+    <mergeCell ref="A196:B196"/>
     <mergeCell ref="A159:B159"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
@@ -9895,6 +10122,11 @@
     <mergeCell ref="A79:B79"/>
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="A116:B116"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="A136:B136"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
